--- a/financial_models/templates/Valuation_v2.01.xlsx
+++ b/financial_models/templates/Valuation_v2.01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD774B77-EDDB-4505-A4AE-3C3779BF1BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21856DC-DC64-42E2-A556-BC80C87DE9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11517,7 +11517,7 @@
         <v>0.90909090909090906</v>
       </c>
       <c r="E34" s="157">
-        <f>C34*D34</f>
+        <f t="shared" ref="E34:E43" si="0">C34*D34</f>
         <v>1212914.3030418304</v>
       </c>
     </row>
@@ -11530,11 +11530,11 @@
         <v>1400916.0200133144</v>
       </c>
       <c r="D35" s="168">
-        <f t="shared" ref="D35:D53" si="0">IF($C$30&lt;B35,0,1/(1+$C$5)^B35)</f>
+        <f t="shared" ref="D35:D53" si="1">IF($C$30&lt;B35,0,1/(1+$C$5)^B35)</f>
         <v>0.82644628099173545</v>
       </c>
       <c r="E35" s="157">
-        <f>C35*D35</f>
+        <f t="shared" si="0"/>
         <v>1157781.8347217473</v>
       </c>
     </row>
@@ -11543,15 +11543,15 @@
         <v>3</v>
       </c>
       <c r="C36" s="166">
-        <f t="shared" ref="C36:C53" si="1">IF(ROW()-ROW($C$34)&lt;$C$30, $C$34*(1+$C$29)^(ROW()-ROW($C$34)), 0)</f>
+        <f t="shared" ref="C36:C53" si="2">IF(ROW()-ROW($C$34)&lt;$C$30, $C$34*(1+$C$29)^(ROW()-ROW($C$34)), 0)</f>
         <v>1470961.8210139801</v>
       </c>
       <c r="D36" s="168">
+        <f t="shared" si="1"/>
+        <v>0.75131480090157754</v>
+      </c>
+      <c r="E36" s="157">
         <f t="shared" si="0"/>
-        <v>0.75131480090157754</v>
-      </c>
-      <c r="E36" s="157">
-        <f>C36*D36</f>
         <v>1105155.3876889404</v>
       </c>
     </row>
@@ -11560,15 +11560,15 @@
         <v>4</v>
       </c>
       <c r="C37" s="166">
+        <f t="shared" si="2"/>
+        <v>1544509.9120646792</v>
+      </c>
+      <c r="D37" s="168">
         <f t="shared" si="1"/>
-        <v>1544509.9120646792</v>
-      </c>
-      <c r="D37" s="168">
+        <v>0.68301345536507052</v>
+      </c>
+      <c r="E37" s="157">
         <f t="shared" si="0"/>
-        <v>0.68301345536507052</v>
-      </c>
-      <c r="E37" s="157">
-        <f>C37*D37</f>
         <v>1054921.0518848978</v>
       </c>
     </row>
@@ -11577,15 +11577,15 @@
         <v>5</v>
       </c>
       <c r="C38" s="166">
+        <f t="shared" si="2"/>
+        <v>1621735.407667913</v>
+      </c>
+      <c r="D38" s="168">
         <f t="shared" si="1"/>
-        <v>1621735.407667913</v>
-      </c>
-      <c r="D38" s="168">
+        <v>0.62092132305915493</v>
+      </c>
+      <c r="E38" s="157">
         <f t="shared" si="0"/>
-        <v>0.62092132305915493</v>
-      </c>
-      <c r="E38" s="157">
-        <f>C38*D38</f>
         <v>1006970.0949810385</v>
       </c>
     </row>
@@ -11594,15 +11594,15 @@
         <v>6</v>
       </c>
       <c r="C39" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D39" s="168">
+      <c r="E39" s="157">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E39" s="157">
-        <f>C39*D39</f>
         <v>0</v>
       </c>
     </row>
@@ -11611,15 +11611,15 @@
         <v>7</v>
       </c>
       <c r="C40" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D40" s="168">
+      <c r="E40" s="157">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E40" s="157">
-        <f>C40*D40</f>
         <v>0</v>
       </c>
     </row>
@@ -11628,15 +11628,15 @@
         <v>8</v>
       </c>
       <c r="C41" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D41" s="168">
+      <c r="E41" s="157">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E41" s="157">
-        <f>C41*D41</f>
         <v>0</v>
       </c>
     </row>
@@ -11645,15 +11645,15 @@
         <v>9</v>
       </c>
       <c r="C42" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D42" s="168">
+      <c r="E42" s="157">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E42" s="157">
-        <f>C42*D42</f>
         <v>0</v>
       </c>
     </row>
@@ -11662,15 +11662,15 @@
         <v>10</v>
       </c>
       <c r="C43" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D43" s="168">
+      <c r="E43" s="157">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E43" s="157">
-        <f>C43*D43</f>
         <v>0</v>
       </c>
     </row>
@@ -11679,15 +11679,15 @@
         <v>11</v>
       </c>
       <c r="C44" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D44" s="168">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="E44" s="157">
-        <f t="shared" ref="E44:E53" si="2">C44*D44</f>
+        <f t="shared" ref="E44:E53" si="3">C44*D44</f>
         <v>0</v>
       </c>
     </row>
@@ -11696,15 +11696,15 @@
         <v>12</v>
       </c>
       <c r="C45" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D45" s="168">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="E45" s="157">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11713,15 +11713,15 @@
         <v>13</v>
       </c>
       <c r="C46" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D46" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D46" s="168">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="E46" s="157">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11730,15 +11730,15 @@
         <v>14</v>
       </c>
       <c r="C47" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D47" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D47" s="168">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="E47" s="157">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11747,15 +11747,15 @@
         <v>15</v>
       </c>
       <c r="C48" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D48" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D48" s="168">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="E48" s="157">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11764,15 +11764,15 @@
         <v>16</v>
       </c>
       <c r="C49" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D49" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D49" s="168">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="E49" s="157">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11781,15 +11781,15 @@
         <v>17</v>
       </c>
       <c r="C50" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D50" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D50" s="168">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="E50" s="157">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11798,15 +11798,15 @@
         <v>18</v>
       </c>
       <c r="C51" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D51" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D51" s="168">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="E51" s="157">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11815,15 +11815,15 @@
         <v>19</v>
       </c>
       <c r="C52" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D52" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D52" s="168">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="E52" s="157">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11832,15 +11832,15 @@
         <v>20</v>
       </c>
       <c r="C53" s="166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D53" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D53" s="168">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="E53" s="157">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11967,11 +11967,11 @@
         <v>-0.05</v>
       </c>
       <c r="D65" s="170">
-        <f t="shared" ref="D65:E65" si="3">D59</f>
+        <f t="shared" ref="D65:E65" si="4">D59</f>
         <v>-0.03</v>
       </c>
       <c r="E65" s="170">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.01</v>
       </c>
     </row>
@@ -11981,69 +11981,69 @@
         <v>5</v>
       </c>
       <c r="C66" s="168">
-        <f>(C60-$C$8)/Common_Shares*$C$3</f>
+        <f t="shared" ref="C66:E69" si="5">(C60-$C$8)/Common_Shares*$C$3</f>
         <v>13.53401931330214</v>
       </c>
       <c r="D66" s="168">
-        <f>(D60-$C$8)/Common_Shares*$C$3</f>
+        <f t="shared" si="5"/>
         <v>15.26614328033296</v>
       </c>
       <c r="E66" s="168">
-        <f>(E60-$C$8)/Common_Shares*$C$3</f>
+        <f t="shared" si="5"/>
         <v>19.237110334060205</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B67">
-        <f t="shared" ref="B67:B69" si="4">B61</f>
+        <f t="shared" ref="B67:B69" si="6">B61</f>
         <v>10</v>
       </c>
       <c r="C67" s="168">
-        <f>(C61-$C$8)/Common_Shares*$C$3</f>
+        <f t="shared" si="5"/>
         <v>11.823239978783297</v>
       </c>
       <c r="D67" s="168">
-        <f>(D61-$C$8)/Common_Shares*$C$3</f>
+        <f t="shared" si="5"/>
         <v>14.060314861979329</v>
       </c>
       <c r="E67" s="168">
-        <f>(E61-$C$8)/Common_Shares*$C$3</f>
+        <f t="shared" si="5"/>
         <v>19.787758947446527</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="C68" s="168">
-        <f>(C62-$C$8)/Common_Shares*$C$3</f>
+        <f t="shared" si="5"/>
         <v>11.00128392925885</v>
       </c>
       <c r="D68" s="168">
-        <f>(D62-$C$8)/Common_Shares*$C$3</f>
+        <f t="shared" si="5"/>
         <v>13.417359591911914</v>
       </c>
       <c r="E68" s="168">
-        <f>(E62-$C$8)/Common_Shares*$C$3</f>
+        <f t="shared" si="5"/>
         <v>20.147109231979158</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B69">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="C69" s="168">
-        <f>(C63-$C$8)/Common_Shares*$C$3</f>
+        <f t="shared" si="5"/>
         <v>10.60636932296344</v>
       </c>
       <c r="D69" s="168">
-        <f>(D63-$C$8)/Common_Shares*$C$3</f>
+        <f t="shared" si="5"/>
         <v>13.074531812258247</v>
       </c>
       <c r="E69" s="168">
-        <f>(E63-$C$8)/Common_Shares*$C$3</f>
+        <f t="shared" si="5"/>
         <v>20.381619269513912</v>
       </c>
     </row>

--- a/financial_models/templates/Valuation_v2.01.xlsx
+++ b/financial_models/templates/Valuation_v2.01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21856DC-DC64-42E2-A556-BC80C87DE9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FEA0D6-88D9-4647-932E-84B3364145B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1067,10 +1067,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Equity Cost(r) =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Holding Period</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1180,6 +1176,10 @@
   </si>
   <si>
     <t>Expected HGP and HGR =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equity Cost of Capital (r) =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1487,7 +1487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1911,6 +1911,7 @@
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2165,7 +2166,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
@@ -2432,272 +2433,287 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C37" s="124">
+        <v>296</v>
+      </c>
+      <c r="C37" s="183">
         <f>r_e!C20</f>
         <v>0.1</v>
       </c>
     </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C38" s="124"/>
+    </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="19" t="str">
+      <c r="C39" s="124"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C40" s="124"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C41" s="124"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C42" s="124"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="19" t="str">
         <f>"3."</f>
         <v>3.</v>
       </c>
-      <c r="B39" s="52" t="s">
+      <c r="B44" s="52" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B40" s="52" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B45" s="52" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B41" s="1" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B46" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B42" s="1" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B44" s="52" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B49" s="52" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B45" s="1" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B50" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="19" t="str">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="19" t="str">
         <f>"4."</f>
         <v>4.</v>
       </c>
-      <c r="B47" s="52" t="s">
+      <c r="B52" s="52" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B48" s="52" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B53" s="52" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B49" s="1" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B54" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B51" s="52" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B56" s="52" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B52" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B54" s="52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B55" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B56" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B57" s="1" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B59" s="52" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B60" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B61" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B62" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B64" s="52" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="19" t="str">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="19" t="str">
         <f>"5."</f>
         <v>5.</v>
       </c>
-      <c r="B61" s="52" t="s">
+      <c r="B66" s="52" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B62" s="52" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B67" s="52" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B63" s="1" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B68" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B64" s="1" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B69" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B65" s="1" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B70" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B67" s="1" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B72" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B69" s="52" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B74" s="52" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B70" s="1" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B75" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="19" t="str">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="19" t="str">
         <f>"6."</f>
         <v>6.</v>
       </c>
-      <c r="B72" s="52" t="s">
+      <c r="B77" s="52" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B73" s="52" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B78" s="52" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B74" s="1" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B79" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B76" s="52" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B77" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B78" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A80" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="B80" s="39"/>
-      <c r="C80" s="39"/>
-      <c r="D80" s="39"/>
-      <c r="E80" s="39"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B81" s="52" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B82" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B83" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A85" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="B85" s="39"/>
+      <c r="C85" s="39"/>
+      <c r="D85" s="39"/>
+      <c r="E85" s="39"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B86" s="52" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B83" s="52" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B84" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B85" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B86" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B88" s="52" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B89" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B90" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B91" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A93" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="B93" s="39"/>
-      <c r="C93" s="39"/>
-      <c r="D93" s="39"/>
-      <c r="E93" s="39"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B93" s="52" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B94" s="52" t="s">
-        <v>133</v>
+      <c r="B94" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B95" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B96" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A98" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="B98" s="39"/>
+      <c r="C98" s="39"/>
+      <c r="D98" s="39"/>
+      <c r="E98" s="39"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B99" s="52" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B100" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B97" s="52" t="s">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B102" s="52" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B98" s="1" t="s">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B103" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B100" s="52" t="s">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B105" s="52" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B101" s="1" t="s">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B106" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -10302,7 +10318,7 @@
     </row>
     <row r="13" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C13" s="164">
         <v>3</v>
@@ -11279,7 +11295,7 @@
   <sheetData>
     <row r="2" spans="2:5" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="39" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -11318,18 +11334,18 @@
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="139" t="s">
+        <v>289</v>
+      </c>
+      <c r="C6" s="156">
+        <v>0</v>
+      </c>
+      <c r="E6" s="139" t="s">
         <v>290</v>
-      </c>
-      <c r="C6" s="156">
-        <v>0</v>
-      </c>
-      <c r="E6" s="139" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B7" s="158" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C7" s="159">
         <f>C4/C5</f>
@@ -11338,7 +11354,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="139" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C8" s="161">
         <f>BS!G27</f>
@@ -11347,7 +11363,7 @@
     </row>
     <row r="9" spans="2:5" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B9" s="158" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C9" s="159">
         <f>C7-C8</f>
@@ -11356,7 +11372,7 @@
     </row>
     <row r="10" spans="2:5" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C10" s="160">
         <f>(C9*FCF!C3)/Common_Shares</f>
@@ -11365,17 +11381,17 @@
     </row>
     <row r="12" spans="2:5" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B12" s="169" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="139" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="139" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.35">
@@ -11400,19 +11416,19 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="139" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C19" s="165">
         <f>r_e!C13</f>
         <v>3</v>
       </c>
       <c r="D19" s="139" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="139" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C20" s="166">
         <f>FCF!C87</f>
@@ -11421,7 +11437,7 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="139" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C22" s="167">
         <f>PV(C18, 3, -C20)</f>
@@ -11430,7 +11446,7 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="139" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C23" s="167">
         <f>C9/(1+C18)^3</f>
@@ -11439,7 +11455,7 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="139" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C24" s="167">
         <f>C22+C23</f>
@@ -11465,12 +11481,12 @@
     </row>
     <row r="28" spans="2:5" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B28" s="174" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="171" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C29" s="172">
         <v>0.05</v>
@@ -11478,7 +11494,7 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="171" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C30" s="173">
         <v>5</v>
@@ -11486,22 +11502,22 @@
     </row>
     <row r="32" spans="2:5" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B32" s="175" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C32" s="166"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33" s="180" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C33" s="178" t="s">
         <v>170</v>
       </c>
       <c r="D33" s="179" t="s">
+        <v>286</v>
+      </c>
+      <c r="E33" s="179" t="s">
         <v>287</v>
-      </c>
-      <c r="E33" s="179" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.35">
@@ -11846,7 +11862,7 @@
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B54" s="176" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C54" s="166">
         <f>C$34*(1+$C$29)^$C$30/C5</f>
@@ -11864,7 +11880,7 @@
     <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="C55" s="166"/>
       <c r="D55" s="139" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E55" s="157">
         <f>SUM(E34:E54)</f>
@@ -12049,7 +12065,7 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B71" s="139" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73" spans="2:5" ht="13.9" x14ac:dyDescent="0.45">
@@ -12072,7 +12088,7 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B76" s="139" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/templates/Valuation_v2.01.xlsx
+++ b/financial_models/templates/Valuation_v2.01.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FEA0D6-88D9-4647-932E-84B3364145B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDE3B4C-0838-4DCA-B2B6-7550F7972CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="17040" windowHeight="10680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="FCF" sheetId="2" r:id="rId3"/>
     <sheet name="BS" sheetId="3" r:id="rId4"/>
-    <sheet name="r_e" sheetId="1" r:id="rId5"/>
-    <sheet name="Model" sheetId="8" r:id="rId6"/>
+    <sheet name="Model" sheetId="8" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Model!$B$69:$F$69</definedName>
     <definedName name="Common_Shares">Thesis!$C$11</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$10</definedName>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="292">
   <si>
     <t>HKD</t>
   </si>
@@ -207,15 +207,6 @@
     <t>Operating LT Financial Assets</t>
   </si>
   <si>
-    <t>CN Riskfree</t>
-  </si>
-  <si>
-    <t>US BBB Bond yield</t>
-  </si>
-  <si>
-    <t>CN Onshore BBB- Bond yield</t>
-  </si>
-  <si>
     <t>HK</t>
   </si>
   <si>
@@ -259,10 +250,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Return</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Most Recent Quarter</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -295,10 +282,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Market Yields</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Model last updated:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -348,10 +331,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>US Riskfree</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Review Interval:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -360,10 +339,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Risk-Free Rate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>R&amp;D</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -385,10 +360,6 @@
   </si>
   <si>
     <t>Other Data</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Adjusted FCFE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -473,26 +444,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Testing</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equity Cost of Capital: ±1.5% (e.g., 5.5%–8.5%).</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Growth Rate: ±1.5% (e.g., 1.5%–4.5%).</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Maintenance Capex: ±20%.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Variables Adjusted:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Output:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -553,10 +504,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>15–20%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Margin of Safety:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -927,267 +874,303 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Implied Growth Sensitivity Test</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Data (Dirty)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating after-tax Profit = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Operating after-tax Profit = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted FCFE = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted FCFE per share = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FCFE/Market Price = </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net borrowing is excluded</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Borrowing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Adjusted) FCFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dividend</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FCFE Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dividend Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dividend/FCFE before WCInv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qualitative Adjustments</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nonexistent moats</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weak balance sheets</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Poor management</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stable Business</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total PV</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buy Below</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equity Value per share</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No-Growth DCF Valuation Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equity Cost of Capital (r) =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>INDEX(C66:E69, ...) retrieves the value from the specified range.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATCH(5, B66:B69, 0) finds the row number for HGP = 5.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATCH(1%, C65:E65, 0) finds the column number for HGR = 1%.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value Per Share</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Year</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>FCFE</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Discount Factor</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>PV of FCFE</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Annual Dividend per share</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HGP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value per share</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No Growth</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Optimistic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pessimistic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scenarios</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Price</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Rates</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Probabilities</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expected Value =</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>PV(Dividends)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Buy at &lt; PV(dividends, 3yrs, r) + PV(Equity value, 3yrs, r)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Data (Dirty)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Operating after-tax Profit = </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Operating after-tax Profit = </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted FCFE = </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted FCFE per share = </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">FCFE/Market Price = </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Net borrowing is excluded</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Net Borrowing</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(Adjusted) FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>US Market</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>China Market</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Other Market</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Japan Market</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Japan Riskfree</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Japan BBB Bond yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Riskfree</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BBB Bond yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equity Cost of Capital</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FCFE Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend/FCFE before WCInv</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Investor Preference</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Qualitative Adjustments</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ERP</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assumptions</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nonexistent moats</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weak balance sheets</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Poor management</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stable Business</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Holding Period</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>yrs</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Holding Period (yrs)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">PV(dividends, 3yrs, r) = </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Year</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Total PV</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">PV(Equity Value, 3yrs, r) = </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Buy Below</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equity Value per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No-Growth DCF Valuation Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equity Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Interest Bearing Debt</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Firm Value (Debt + Equity)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>During this period, the company is expected to distribute annual dividends, which we assume will not impair future profitability or cash flow generation.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>We project that the intrinsic Equity Value will be conservatively realized over a three-year holding period.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>High-Growth Scenarios</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FCFE Projection (for current scenario)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Discount Factor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PV of FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Terminal Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Terminal Growth Rate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The mature company is expected to have stable cash flows with no significant growth, reflecting its declining industry and avoiding overvaluation.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Discount Rate</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Investment Horizon Analysis (Margin of Safety)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>High Growth Period (HGP):</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>High Growth Rate (HGR):</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Expected HGP and HGR =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equity Cost of Capital (r) =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>PV(Equity Value)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>= Enterprise Value</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Equity Cost of Capital</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Interest Bearing Debt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>= Equity Value</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Special Assumption</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Expects no significant growth at terminal years</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>over a holding period of</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inputs</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>the Equity Value will be conservatively realized</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Terminal Growth Rate:</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Avoids overvaluation.</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>at a MOS of</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Margin of Safety (MOS)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adjusted FCFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sensitivity Analysis (Enterprise Value)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sensitivity Analysis (Equity Value per share)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Terminal Year</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HGR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>High Growth Period (HGP)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>High Growth Rate (HGR)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FCFE Projection</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>52 week Low</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reference Price Points</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>52 week High</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target Return</t>
+    <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="15">
+  <numFmts count="17">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="178" formatCode="#,##0.00&quot;x&quot;"/>
@@ -1203,8 +1186,10 @@
     <numFmt numFmtId="188" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
     <numFmt numFmtId="189" formatCode="#,##0_);[Red]\(#,##0\)"/>
     <numFmt numFmtId="190" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="192" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="193" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1414,20 +1399,54 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="DengXian"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1458,8 +1477,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0047AB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1483,11 +1514,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1849,74 +1895,146 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="184" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="183" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="186" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="187" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="187" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="184" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="190" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="186" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="31" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="27" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="192" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="31" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="192" fontId="27" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="193" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="192" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="192" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2166,7 +2284,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
@@ -2178,30 +2296,30 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B1" s="52" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C1" s="55" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D1" s="56" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C2" s="48">
         <v>45643</v>
       </c>
       <c r="D2" s="59"/>
       <c r="E2" s="123" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A3" s="39" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -2214,22 +2332,22 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B4" s="50" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C4" s="51"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C6" s="49">
         <v>8</v>
@@ -2238,7 +2356,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C7" s="36">
         <f>EOMONTH(EDATE(BS!C1,Thesis!C6),0)</f>
@@ -2255,13 +2373,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="C10" s="57">
         <v>13.82</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -2309,7 +2427,7 @@
     </row>
     <row r="16" spans="1:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A16" s="39" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B16" s="39"/>
       <c r="C16" s="39"/>
@@ -2322,22 +2440,22 @@
         <v>1.</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B19" s="52" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B22" s="52" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C22" s="149">
         <f>Data!C3</f>
@@ -2346,7 +2464,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="C23" s="100">
         <f>FCF!C11</f>
@@ -2359,7 +2477,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="C24" s="100">
         <f>FCF!C12</f>
@@ -2368,7 +2486,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B25" s="146" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="C25" s="100">
         <f>C23+C24</f>
@@ -2377,7 +2495,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C27" s="100">
         <f>FCF!C19</f>
@@ -2386,7 +2504,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="C28" s="144">
         <f>C27/(Common_Shares/Data!C3)</f>
@@ -2395,7 +2513,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B29" s="1" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="C29" s="124">
         <f>C28/Market_Price</f>
@@ -2404,327 +2522,340 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B31" s="53" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B32" s="53" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B33" s="53" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B34" s="53" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="19" t="str">
         <f>"2."</f>
         <v>2.</v>
       </c>
       <c r="B36" s="52" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C37" s="183">
-        <f>r_e!C20</f>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+      <c r="C37" s="167">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C38" s="124"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C39" s="124"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C40" s="124"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C41" s="124"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C42" s="124"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="19" t="str">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="18" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="146" t="s">
+        <v>234</v>
+      </c>
+      <c r="C40" s="152">
+        <v>0</v>
+      </c>
+      <c r="D40" s="54" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="146" t="s">
+        <v>235</v>
+      </c>
+      <c r="C41" s="152">
+        <v>0</v>
+      </c>
+      <c r="D41" s="151" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="146" t="s">
+        <v>236</v>
+      </c>
+      <c r="C42" s="152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B43" s="91" t="s">
+        <v>233</v>
+      </c>
+      <c r="C43" s="92">
+        <f>SUM(C40:C42)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="19" t="str">
         <f>"3."</f>
         <v>3.</v>
       </c>
-      <c r="B44" s="52" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B45" s="52" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B46" s="52" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B50" s="52" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B46" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B47" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B49" s="52" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B50" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="19" t="str">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B51" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="19" t="str">
         <f>"4."</f>
         <v>4.</v>
       </c>
-      <c r="B52" s="52" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B53" s="52" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="52" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B55" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B57" s="52" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B58" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B60" s="52" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B56" s="52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B57" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B59" s="52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B60" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B61" s="1" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B64" s="52" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B63" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B65" s="52" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="19" t="str">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B67" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C67" s="211">
+        <f>Model!E86</f>
+        <v>0.2608169671725179</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B69" s="52" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B70" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="19" t="str">
         <f>"5."</f>
         <v>5.</v>
       </c>
-      <c r="B66" s="52" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B67" s="52" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B68" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B69" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B70" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B72" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B74" s="52" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B75" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="19" t="str">
-        <f>"6."</f>
-        <v>6.</v>
-      </c>
-      <c r="B77" s="52" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B78" s="52" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B79" s="1" t="s">
-        <v>129</v>
-      </c>
+      <c r="B72" s="52" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B73" s="52" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B74" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B76" s="52" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B77" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B78" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A80" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="B80" s="39"/>
+      <c r="C80" s="39"/>
+      <c r="D80" s="39"/>
+      <c r="E80" s="39"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B81" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="C81" s="199">
+        <f>Model!C86</f>
+        <v>13.195609147085756</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B83" s="52" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B84" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B82" s="1" t="s">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B85" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B86" s="1" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B83" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A85" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="B85" s="39"/>
-      <c r="C85" s="39"/>
-      <c r="D85" s="39"/>
-      <c r="E85" s="39"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B86" s="52" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B88" s="52" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B89" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B90" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B91" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B93" s="52" t="s">
-        <v>145</v>
-      </c>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A93" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="B93" s="39"/>
+      <c r="C93" s="39"/>
+      <c r="D93" s="39"/>
+      <c r="E93" s="39"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B94" s="1" t="s">
-        <v>146</v>
+      <c r="B94" s="52" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B95" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B96" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A98" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="B98" s="39"/>
-      <c r="C98" s="39"/>
-      <c r="D98" s="39"/>
-      <c r="E98" s="39"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B99" s="52" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B100" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B102" s="52" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B103" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B105" s="52" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B106" s="1" t="s">
-        <v>138</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B97" s="52" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B98" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B100" s="52" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B101" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="C12" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Status: Not Held, Status: Held"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D40" xr:uid="{7A4D0D78-B7B0-41D6-9553-BB65BF9D0DE8}">
+      <formula1>"US, CN, HK, Others"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D41" xr:uid="{E2751D42-64D4-404F-8920-D495B29DB1C3}">
+      <formula1>"Stable Business, Moderate Risk, High Risk"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2797,7 +2928,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="39" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -2849,7 +2980,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="44" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C5" s="76">
         <v>11151623</v>
@@ -2877,7 +3008,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="44" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C6" s="76">
         <v>2297566</v>
@@ -2905,7 +3036,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="89" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C7" s="90">
         <v>2043459</v>
@@ -2929,7 +3060,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="44" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C8" s="76"/>
       <c r="D8" s="76"/>
@@ -2945,7 +3076,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="44" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C9" s="76">
         <v>59596</v>
@@ -2973,7 +3104,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="44" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="C10" s="76">
         <v>28977</v>
@@ -2997,7 +3128,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="44" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C11" s="76">
         <v>327166</v>
@@ -3021,7 +3152,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="47" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C12" s="88">
         <v>1767305</v>
@@ -3047,7 +3178,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="31" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C13" s="76">
         <v>-9467</v>
@@ -3075,13 +3206,13 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="18" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C15" s="11"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="30" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C16" s="76">
         <v>463424</v>
@@ -3105,7 +3236,7 @@
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B17" s="30" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C17" s="76">
         <v>676387</v>
@@ -3129,7 +3260,7 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="30" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C18" s="76">
         <v>626583</v>
@@ -3153,7 +3284,7 @@
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C19" s="42">
         <v>1.3599999999999999</v>
@@ -3231,7 +3362,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="32" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C24" s="88">
         <v>3990166</v>
@@ -3279,13 +3410,13 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="18" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C27" s="11"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C28" s="76">
         <f>20356+1075000</f>
@@ -3313,7 +3444,7 @@
     </row>
     <row r="30" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B30" s="39" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
@@ -3383,7 +3514,7 @@
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B33" s="44" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C33" s="65">
         <f t="shared" ref="C33:M33" si="2">IF(C$4="","",-C5)</f>
@@ -3432,7 +3563,7 @@
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B34" s="34" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C34" s="80">
         <f>IF(C32="","",C32+C33)</f>
@@ -3481,7 +3612,7 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="44" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C35" s="65">
         <f t="shared" ref="C35:M35" si="13">IF(C$4="","",-C6)</f>
@@ -3530,7 +3661,7 @@
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B36" s="89" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="C36" s="94">
         <f t="shared" ref="C36:M36" si="14">IF(C$4="","",-C7)</f>
@@ -3579,7 +3710,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="89" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C37" s="94">
         <f>IF(C$4="","",C35-C36)</f>
@@ -3628,7 +3759,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="44" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C38" s="65">
         <f t="shared" ref="C38:M38" si="16">IF(C$4="","",-C8)</f>
@@ -3677,7 +3808,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="47" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C39" s="68">
         <f>IF(C$4="","",C34+C35+C38)</f>
@@ -3726,7 +3857,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="44" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C40" s="100">
         <f>IF(C$4="","",C41+C42)</f>
@@ -3775,7 +3906,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="89" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C41" s="94">
         <f t="shared" ref="C41:M41" si="19">IF(C$4="","",-C9)</f>
@@ -3824,7 +3955,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="89" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C42" s="94">
         <f t="shared" ref="C42:M42" si="20">IF(C$4="","",C10)</f>
@@ -3873,7 +4004,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="44" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="C43" s="100">
         <f>IF(C$4="","",C45-C44-C40-C39)</f>
@@ -3922,7 +4053,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="44" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C44" s="65">
         <f t="shared" ref="C44:M44" si="22">IF(C$4="","",-C11)</f>
@@ -3971,7 +4102,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C45" s="68">
         <f t="shared" ref="C45:M45" si="23">IF(C$4="","",C12)</f>
@@ -4020,7 +4151,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="31" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C46" s="65">
         <f t="shared" ref="C46:M46" si="24">IF(C$4="","",MIN(-C13,0))</f>
@@ -4069,13 +4200,13 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="18" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C48" s="11"/>
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B49" s="30" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C49" s="65">
         <f t="shared" ref="C49:M49" si="25">IF(C$4="","",-C16)</f>
@@ -4124,7 +4255,7 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="30" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C50" s="65">
         <f t="shared" ref="C50:M50" si="26">IF(C$4="","",-C17)</f>
@@ -4173,7 +4304,7 @@
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="30" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C51" s="65">
         <f t="shared" ref="C51:M51" si="27">IF(C$4="","",-C18)</f>
@@ -4222,7 +4353,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="27" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C52" s="95">
         <f t="shared" ref="C52:H52" si="28">IF(C$4="","",C19)</f>
@@ -4271,7 +4402,7 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="122" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
@@ -4526,7 +4657,7 @@
     </row>
     <row r="61" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B61" s="39" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C61" s="40"/>
       <c r="D61" s="40"/>
@@ -4597,7 +4728,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="127" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C64" s="94">
         <f t="shared" ref="C64:H65" si="36">IF(C$4="","",C22)</f>
@@ -4631,7 +4762,7 @@
     </row>
     <row r="65" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B65" s="127" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C65" s="94">
         <f t="shared" si="36"/>
@@ -4665,7 +4796,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="29" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C66" s="65">
         <f t="shared" ref="C66:M66" si="37">IF(C$4="","",C24)</f>
@@ -4763,21 +4894,21 @@
     </row>
     <row r="69" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B69" s="125" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="C69" s="126" t="s">
-        <v>59</v>
-      </c>
       <c r="D69" s="126" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E69" s="120" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B70" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C70" s="14">
         <f>FCF!L8</f>
@@ -4793,7 +4924,7 @@
     </row>
     <row r="71" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B71" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C71" s="8">
         <f>(D70/C70)^(1/E70)-1</f>
@@ -4805,12 +4936,12 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M13 C16:M19 C22:M25 C28:M28 C35:M39 C41:M42 C44:M46 C64:H65 C66:M67">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32:M33 C49:M52">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>ISBLANK(C32)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4848,7 +4979,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D1" s="60"/>
       <c r="E1" s="60"/>
@@ -4901,12 +5032,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="61" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="C2" s="61"/>
       <c r="D2" s="63"/>
       <c r="E2" s="81" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F2" s="63"/>
       <c r="G2" s="40"/>
@@ -4924,7 +5055,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="18" t="s">
-        <v>98</v>
+        <v>279</v>
       </c>
       <c r="C3" s="148">
         <f>Data!C3</f>
@@ -4945,7 +5076,7 @@
       </c>
       <c r="D4" s="64"/>
       <c r="E4" s="83" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="F4" s="64"/>
       <c r="G4" s="65">
@@ -4996,7 +5127,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C5" s="77">
         <f>C44</f>
@@ -5051,7 +5182,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12"/>
       <c r="B6" s="34" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C6" s="77">
         <f>C4+C5</f>
@@ -5106,7 +5237,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12"/>
       <c r="B7" s="10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C7" s="77">
         <f>C47</f>
@@ -5161,7 +5292,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="32" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C8" s="71">
         <f>C6+C7</f>
@@ -5218,7 +5349,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C9" s="77">
         <f>C60</f>
@@ -5273,7 +5404,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="2" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C10" s="77">
         <f>-(C8+C9)*C37</f>
@@ -5328,7 +5459,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="45" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C11" s="73">
         <f>SUM(C8:C10)</f>
@@ -5385,7 +5516,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="34" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="C12" s="145">
         <f>MIN(G12:J12)</f>
@@ -5393,7 +5524,7 @@
       </c>
       <c r="D12" s="66"/>
       <c r="E12" s="85" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="F12" s="66"/>
       <c r="G12" s="68">
@@ -5444,7 +5575,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="C13" s="77">
         <f>BS!$G$25*BS!C42</f>
@@ -5499,7 +5630,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="2" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="C14" s="77">
         <f>-C4*C31</f>
@@ -5554,7 +5685,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12"/>
       <c r="B15" s="44" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C15" s="77">
         <f>-C4*C33</f>
@@ -5611,7 +5742,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
       <c r="B16" s="34" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C16" s="80">
         <f>SUM(C11:C15)</f>
@@ -5668,7 +5799,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="30" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C17" s="77">
         <f>-C4*C32</f>
@@ -5725,14 +5856,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12"/>
       <c r="B18" s="30" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="C18" s="77">
         <v>0</v>
       </c>
       <c r="D18" s="66"/>
       <c r="E18" s="85" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="F18" s="66"/>
       <c r="G18" s="150"/>
@@ -5750,7 +5881,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12"/>
       <c r="B19" s="34" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="C19" s="80">
         <f>C16+C17</f>
@@ -5826,7 +5957,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="93" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C21" s="74"/>
       <c r="D21" s="30"/>
@@ -5847,7 +5978,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12"/>
       <c r="B22" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C22" s="101">
         <f t="shared" ref="C22:C30" si="9">ABS(C5/C$4)</f>
@@ -5904,7 +6035,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12"/>
       <c r="B23" s="34" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C23" s="102">
         <f t="shared" si="9"/>
@@ -5961,7 +6092,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12"/>
       <c r="B24" s="10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C24" s="101">
         <f t="shared" si="9"/>
@@ -6018,7 +6149,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12"/>
       <c r="B25" s="32" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C25" s="102">
         <f t="shared" si="9"/>
@@ -6075,7 +6206,7 @@
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="12"/>
       <c r="B26" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C26" s="101">
         <f t="shared" si="9"/>
@@ -6132,7 +6263,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12"/>
       <c r="B27" s="2" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C27" s="101">
         <f t="shared" si="9"/>
@@ -6189,7 +6320,7 @@
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12"/>
       <c r="B28" s="45" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C28" s="102">
         <f t="shared" si="9"/>
@@ -6246,7 +6377,7 @@
     <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12"/>
       <c r="B29" s="30" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="C29" s="101">
         <f t="shared" si="9"/>
@@ -6303,7 +6434,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12"/>
       <c r="B30" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="C30" s="101">
         <f t="shared" si="9"/>
@@ -6360,7 +6491,7 @@
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12"/>
       <c r="B31" s="2" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="C31" s="118">
         <f>MAX(AVERAGE(G31:J31),C30)</f>
@@ -6368,7 +6499,7 @@
       </c>
       <c r="D31" s="30"/>
       <c r="E31" s="83" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="F31" s="30"/>
       <c r="G31" s="8">
@@ -6419,7 +6550,7 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12"/>
       <c r="B32" s="30" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C32" s="118">
         <f>MIN(AVERAGE(G32:J32)/2,0)</f>
@@ -6427,7 +6558,7 @@
       </c>
       <c r="D32" s="30"/>
       <c r="E32" s="86" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="F32" s="30"/>
       <c r="G32" s="8">
@@ -6478,7 +6609,7 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12"/>
       <c r="B33" s="44" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C33" s="118">
         <f>IF(BS!G29&lt;=0,0,BS!G29/BS!G30)</f>
@@ -6535,7 +6666,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
       <c r="B34" s="34" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="C34" s="102">
         <f>ABS(C19/C$4)</f>
@@ -6592,7 +6723,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12"/>
       <c r="B35" s="93" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C35" s="74"/>
       <c r="D35" s="30"/>
@@ -6613,7 +6744,7 @@
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12"/>
       <c r="B36" s="134" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="C36" s="74"/>
       <c r="D36" s="30"/>
@@ -6634,7 +6765,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
       <c r="B37" s="30" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="C37" s="75">
         <f>MAX(G37:J37)</f>
@@ -6642,7 +6773,7 @@
       </c>
       <c r="D37" s="30"/>
       <c r="E37" s="86" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="F37" s="30"/>
       <c r="G37" s="8">
@@ -6693,7 +6824,7 @@
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12"/>
       <c r="B38" s="30" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="C38" s="101">
         <f>C19*$C$3/(Market_Price*Common_Shares)</f>
@@ -6769,12 +6900,12 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A40" s="12"/>
       <c r="B40" s="61" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="C40" s="61"/>
       <c r="D40" s="63"/>
       <c r="E40" s="81" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F40" s="63"/>
       <c r="G40" s="40"/>
@@ -6792,7 +6923,7 @@
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12"/>
       <c r="B41" s="78" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C41" s="74"/>
       <c r="D41" s="30"/>
@@ -6813,7 +6944,7 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12"/>
       <c r="B42" s="30" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C42" s="98">
         <f>-C4*C50</f>
@@ -6870,7 +7001,7 @@
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="12"/>
       <c r="B43" s="87" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="C43" s="77">
         <f>-C4*C51</f>
@@ -6927,7 +7058,7 @@
     <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="12"/>
       <c r="B44" s="91" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C44" s="80">
         <f>C42+C43</f>
@@ -6984,14 +7115,14 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="12"/>
       <c r="B45" s="10" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="C45" s="97">
         <f>AVERAGE(G45:J45)</f>
         <v>-302359.25</v>
       </c>
       <c r="E45" s="83" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="G45" s="77">
         <f>Data!C37</f>
@@ -7049,7 +7180,7 @@
       </c>
       <c r="D46" s="66"/>
       <c r="E46" s="83" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="F46" s="66"/>
       <c r="G46" s="65">
@@ -7100,7 +7231,7 @@
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="12"/>
       <c r="B47" s="91" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C47" s="80">
         <f>C45+C46</f>
@@ -7160,13 +7291,13 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="12"/>
       <c r="B49" s="93" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
       <c r="B50" s="29" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C50" s="75">
         <f>AVERAGE(G50:L50)</f>
@@ -7174,7 +7305,7 @@
       </c>
       <c r="D50" s="29"/>
       <c r="E50" s="83" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="F50" s="29"/>
       <c r="G50" s="15">
@@ -7234,7 +7365,7 @@
       </c>
       <c r="D51" s="29"/>
       <c r="E51" s="83" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="F51" s="29"/>
       <c r="G51" s="15">
@@ -7285,7 +7416,7 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="12"/>
       <c r="B52" s="91" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C52" s="92">
         <f>ABS(C44/$C$4)</f>
@@ -7455,7 +7586,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="12"/>
       <c r="B55" s="91" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C55" s="92">
         <f t="shared" si="31"/>
@@ -7512,13 +7643,13 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="12"/>
       <c r="B57" s="78" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="12"/>
       <c r="B58" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C58" s="77">
         <f>-BS!G27*BS!C40</f>
@@ -7572,7 +7703,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="12"/>
       <c r="B59" s="2" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="C59" s="77">
         <f>BS!$G$24*BS!C41</f>
@@ -7626,7 +7757,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="12"/>
       <c r="B60" s="91" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C60" s="80">
         <f>C58+C59</f>
@@ -7683,12 +7814,12 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A62" s="3"/>
       <c r="B62" s="61" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C62" s="61"/>
       <c r="D62" s="63"/>
       <c r="E62" s="81" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F62" s="63"/>
       <c r="G62" s="40"/>
@@ -7769,7 +7900,7 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="12"/>
       <c r="B65" s="127" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C65" s="130">
         <f>BS!C4</f>
@@ -7826,7 +7957,7 @@
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
       <c r="B66" s="127" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C66" s="130">
         <f>BS!C7+BS!C8</f>
@@ -7883,7 +8014,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12"/>
       <c r="B67" s="29" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C67" s="129">
         <f>BS!G26</f>
@@ -8016,7 +8147,7 @@
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="12"/>
       <c r="B70" s="122" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C70" s="29"/>
       <c r="D70" s="29"/>
@@ -8037,7 +8168,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="12"/>
       <c r="B71" s="29" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="C71" s="132">
         <f>C65/C$4</f>
@@ -8094,7 +8225,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="12"/>
       <c r="B72" s="29" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="C72" s="132">
         <f>C66/C$4</f>
@@ -8170,13 +8301,13 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="12"/>
       <c r="B74" s="122" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12"/>
       <c r="B75" s="29" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="C75" s="46">
         <f>-C4/C58</f>
@@ -8230,7 +8361,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="12"/>
       <c r="B76" s="29" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C76" s="26">
         <f>C68/C64</f>
@@ -8287,7 +8418,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="12"/>
       <c r="B78" s="122" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C78" s="62"/>
       <c r="D78" s="62"/>
@@ -8341,7 +8472,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="12"/>
       <c r="B79" s="9" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="C79" s="26">
         <f>C25</f>
@@ -8394,7 +8525,7 @@
     </row>
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="9" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="C80" s="46">
         <f>C4/C64</f>
@@ -8447,7 +8578,7 @@
     </row>
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C81" s="17">
         <f>C64/C68</f>
@@ -8504,7 +8635,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="12"/>
       <c r="B82" s="91" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C82" s="141">
         <f>C8/C68</f>
@@ -8564,12 +8695,12 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A84" s="12"/>
       <c r="B84" s="61" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="C84" s="61"/>
       <c r="D84" s="63"/>
       <c r="E84" s="81" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="F84" s="63"/>
       <c r="G84" s="40"/>
@@ -8587,59 +8718,59 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="12"/>
       <c r="B85" s="78" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="12"/>
       <c r="B86" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C86" s="163">
+        <v>61</v>
+      </c>
+      <c r="C86" s="159">
         <f>G86</f>
         <v>1.3599999999999999</v>
       </c>
-      <c r="G86" s="162">
+      <c r="G86" s="158">
         <f>Data!C52</f>
         <v>1.3599999999999999</v>
       </c>
-      <c r="H86" s="162">
+      <c r="H86" s="158">
         <f>Data!D52</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="I86" s="162">
+      <c r="I86" s="158">
         <f>Data!E52</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="J86" s="162">
+      <c r="J86" s="158">
         <f>Data!F52</f>
         <v>1</v>
       </c>
-      <c r="K86" s="162">
+      <c r="K86" s="158">
         <f>Data!G52</f>
         <v>1</v>
       </c>
-      <c r="L86" s="162">
+      <c r="L86" s="158">
         <f>Data!H52</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="M86" s="162" t="str">
+      <c r="M86" s="158" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N86" s="162" t="str">
+      <c r="N86" s="158" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O86" s="162" t="str">
+      <c r="O86" s="158" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P86" s="162" t="str">
+      <c r="P86" s="158" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q86" s="162" t="str">
+      <c r="Q86" s="158" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -8647,7 +8778,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="12"/>
       <c r="B87" s="2" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="C87" s="96">
         <f>C86*Common_Shares/$C$3</f>
@@ -8701,7 +8832,7 @@
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="12"/>
       <c r="B88" s="2" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="C88" s="26">
         <f>C86/(C16*$C$3/Common_Shares)</f>
@@ -9516,7 +9647,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q9 G11:Q12 G15:Q15 G42:Q43 G46:Q46">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9550,7 +9681,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="21" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C1" s="137">
         <v>45382</v>
@@ -9563,7 +9694,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="105" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -9580,16 +9711,16 @@
         <v>7</v>
       </c>
       <c r="D3" s="115" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="115" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9604,7 +9735,7 @@
       </c>
       <c r="E4" s="28"/>
       <c r="F4" s="5" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="G4" s="22">
         <v>1998219</v>
@@ -9678,7 +9809,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="C8" s="22">
         <v>0</v>
@@ -9688,7 +9819,7 @@
       </c>
       <c r="E8" s="28"/>
       <c r="F8" s="1" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="G8" s="22">
         <v>0</v>
@@ -9729,7 +9860,7 @@
         <v>0.05</v>
       </c>
       <c r="F10" s="107" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G10" s="108">
         <f>SUM(G4:G9)</f>
@@ -9739,7 +9870,7 @@
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="107" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C11" s="108">
         <f>SUM(C4:C10)</f>
@@ -9747,7 +9878,7 @@
       </c>
       <c r="D11" s="110"/>
       <c r="F11" s="5" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="G11" s="22">
         <v>0</v>
@@ -9758,7 +9889,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="5" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="C12" s="22">
         <v>103050</v>
@@ -9798,7 +9929,7 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="5" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="C14" s="22">
         <v>0</v>
@@ -9867,7 +9998,7 @@
         <v>0.05</v>
       </c>
       <c r="F17" s="107" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="G17" s="108">
         <f>SUM(G11:G16)</f>
@@ -9899,7 +10030,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="107" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C20" s="108">
         <f>SUM(C12:C19)</f>
@@ -9908,7 +10039,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="18" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9919,7 +10050,7 @@
         <v>1427805</v>
       </c>
       <c r="F23" s="59" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="G23" s="108">
         <f>C11+C20+G10+G17</f>
@@ -9934,7 +10065,7 @@
         <v>287697</v>
       </c>
       <c r="F24" s="106" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="G24" s="23">
         <f>G4+G5+G11</f>
@@ -9949,7 +10080,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="106" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="G25" s="23">
         <f>SUM(C14:C17)+SUM(G15:G16)</f>
@@ -9980,7 +10111,7 @@
         <v>1715502</v>
       </c>
       <c r="F27" s="106" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="G27" s="23">
         <f>C27+C34</f>
@@ -10010,7 +10141,7 @@
         <v>3516809</v>
       </c>
       <c r="F29" s="112" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="G29" s="14">
         <v>-26962</v>
@@ -10024,7 +10155,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="106" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="G30" s="16">
         <f>G28-G29</f>
@@ -10084,7 +10215,7 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="105" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C38" s="40"/>
       <c r="D38" s="40"/>
@@ -10095,22 +10226,22 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="134" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="C39" s="135" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D39" s="135" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="138" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="10" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C40" s="109">
         <f>D40</f>
@@ -10121,12 +10252,12 @@
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="F40" s="86" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="10" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C41" s="117">
         <v>1.4501413508729523E-2</v>
@@ -10136,12 +10267,12 @@
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="F41" s="86" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="2" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="C42" s="117">
         <f>D42</f>
@@ -10152,12 +10283,12 @@
         <v>0.11625172085779995</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C43" s="136"/>
       <c r="D43" s="124">
@@ -10167,7 +10298,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="10" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="C44" s="136"/>
       <c r="D44" s="133">
@@ -10183,1138 +10314,49 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1">
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G872"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:H91"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.796875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="14.796875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="1" max="1" width="5.59765625" customWidth="1"/>
+    <col min="2" max="6" width="20.59765625" customWidth="1"/>
+    <col min="7" max="7" width="5.59765625" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="39" t="s">
-        <v>74</v>
+        <v>241</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
       <c r="E2" s="40"/>
       <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-    </row>
-    <row r="3" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="C3" s="152" t="s">
-        <v>247</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="F3" s="152" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="151">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F4" s="151"/>
-    </row>
-    <row r="5" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="151">
-        <v>5.2299999999999999E-2</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F5" s="151"/>
-    </row>
-    <row r="6" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="C7" s="152" t="s">
-        <v>247</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="F7" s="152" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="151">
-        <v>1.8100000000000002E-2</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F8" s="151"/>
-    </row>
-    <row r="9" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="151">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F9" s="151"/>
-    </row>
-    <row r="10" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="C11" s="152" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="109">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C13" s="164">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="39" t="s">
-        <v>263</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-    </row>
-    <row r="16" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="18" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="154">
-        <f>IF(E17="CN",r_e!C8,r_e!C4)</f>
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C18" s="154">
-        <f>IF(LEFT(E18,1)="S",4%,IF(LEFT(E18,1)="M",6%,8%))</f>
-        <v>0.04</v>
-      </c>
-      <c r="E18" s="153" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C19" s="124">
-        <f>C26</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="107" t="s">
-        <v>263</v>
-      </c>
-      <c r="C20" s="124">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="18" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="146" t="s">
-        <v>264</v>
-      </c>
-      <c r="C23" s="154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="146" t="s">
-        <v>265</v>
-      </c>
-      <c r="C24" s="154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="146" t="s">
-        <v>266</v>
-      </c>
-      <c r="C25" s="154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="91" t="s">
-        <v>260</v>
-      </c>
-      <c r="C26" s="92">
-        <f>SUM(C23:C25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E18" xr:uid="{E2751D42-64D4-404F-8920-D495B29DB1C3}">
-      <formula1>"Stable Business, Moderate Risk, High Risk"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17" xr:uid="{7A4D0D78-B7B0-41D6-9553-BB65BF9D0DE8}">
-      <formula1>"US, CN, HK, Others"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup scale="99" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
-  <dimension ref="B2:E76"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="24.9296875" customWidth="1"/>
-    <col min="3" max="5" width="20.59765625" customWidth="1"/>
-    <col min="6" max="6" width="8.19921875" customWidth="1"/>
-    <col min="7" max="7" width="20.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:5" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B2" s="39" t="s">
-        <v>278</v>
-      </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-    </row>
-    <row r="3" spans="2:5" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B3" s="155" t="s">
-        <v>114</v>
+      <c r="H2" s="176" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B3" s="153" t="s">
+        <v>106</v>
       </c>
       <c r="C3" s="148">
         <f>FCF!C3</f>
         <v>1000</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E3" s="153" t="s">
+        <v>270</v>
+      </c>
+      <c r="H3" s="166"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="139" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="157">
+        <v>279</v>
+      </c>
+      <c r="C4" s="154">
         <f>FCF!C19</f>
         <v>1270672.1269962033</v>
       </c>
@@ -11322,777 +10364,1417 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B5" s="139" t="s">
-        <v>254</v>
-      </c>
-      <c r="C5" s="156">
-        <f>r_e!C20</f>
+      <c r="E4" s="139" t="s">
+        <v>275</v>
+      </c>
+      <c r="F4" s="180">
+        <v>0</v>
+      </c>
+      <c r="H4" s="166"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B5" s="200" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" s="204">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B6" s="139" t="s">
-        <v>289</v>
-      </c>
-      <c r="C6" s="156">
-        <v>0</v>
-      </c>
-      <c r="E6" s="139" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B7" s="158" t="s">
-        <v>281</v>
-      </c>
-      <c r="C7" s="159">
+      <c r="E5" s="200" t="s">
+        <v>271</v>
+      </c>
+      <c r="H5" s="166"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B6" s="202" t="s">
+        <v>266</v>
+      </c>
+      <c r="C6" s="181">
         <f>C4/C5</f>
         <v>12706721.269962033</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B8" s="139" t="s">
-        <v>280</v>
-      </c>
-      <c r="C8" s="161">
+      <c r="E6" s="200" t="s">
+        <v>276</v>
+      </c>
+      <c r="H6" s="166"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B7" s="200" t="s">
+        <v>268</v>
+      </c>
+      <c r="C7" s="157">
         <f>BS!G27</f>
         <v>2034922</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B9" s="158" t="s">
-        <v>279</v>
-      </c>
-      <c r="C9" s="159">
-        <f>C7-C8</f>
+      <c r="H7" s="166"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B8" s="202" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="181">
+        <f>C6-C7</f>
         <v>10671799.269962033</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B10" s="158" t="s">
+      <c r="H8" s="166"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B9" s="201" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="156">
+        <f>(C8*FCF!C3)/Common_Shares</f>
+        <v>18.176897600606146</v>
+      </c>
+      <c r="H9" s="166"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="H10" s="166"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B11" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="H11" s="166"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B12" s="165" t="s">
+        <v>286</v>
+      </c>
+      <c r="E12" s="153" t="s">
+        <v>288</v>
+      </c>
+      <c r="F12" s="210" t="str">
+        <f>"("&amp;D4&amp;")"</f>
+        <v>(HKD)</v>
+      </c>
+      <c r="H12" s="166"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="208" t="s">
+        <v>284</v>
+      </c>
+      <c r="C13" s="206">
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="E13" s="139" t="s">
+        <v>259</v>
+      </c>
+      <c r="F13">
+        <f>Market_Price</f>
+        <v>13.82</v>
+      </c>
+      <c r="H13" s="166"/>
+    </row>
+    <row r="14" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="164" t="s">
+        <v>285</v>
+      </c>
+      <c r="C14" s="207">
+        <v>10</v>
+      </c>
+      <c r="E14" s="139" t="s">
+        <v>290</v>
+      </c>
+      <c r="H14" s="166"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="209" t="s">
+        <v>246</v>
+      </c>
+      <c r="C15" s="187">
+        <f>(F49-C7)/Common_Shares*C3</f>
+        <v>13.822088197770135</v>
+      </c>
+      <c r="D15" t="str">
+        <f>IF(ROUND(C15,1)=ROUND(F13,1),"equals Market Price","a Current Projection")</f>
+        <v>equals Market Price</v>
+      </c>
+      <c r="E15" s="139" t="s">
+        <v>287</v>
+      </c>
+      <c r="H15" s="166"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="H16" s="166"/>
+    </row>
+    <row r="17" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B17" s="174" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="174" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" s="174" t="s">
+        <v>260</v>
+      </c>
+      <c r="E17" s="174" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" s="175" t="s">
+        <v>250</v>
+      </c>
+      <c r="H17" s="166"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B18" s="168">
+        <v>1</v>
+      </c>
+      <c r="C18" s="169">
+        <f>C4*(1+D18)</f>
+        <v>1179183.7338524768</v>
+      </c>
+      <c r="D18" s="185">
+        <f>IF($C$14&lt;B18,0,Model!$C$13)</f>
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="E18" s="170">
+        <f>IF($C$14&lt;B18,0,1/(1+$C$5)^B18)</f>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="F18" s="171">
+        <f t="shared" ref="F18:F48" si="0">C18*E18</f>
+        <v>1071985.2125931608</v>
+      </c>
+      <c r="H18" s="166"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B19" s="168">
+        <v>2</v>
+      </c>
+      <c r="C19" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D19)^(ROW()-ROW($C$18)), 0)</f>
+        <v>1094282.5050150985</v>
+      </c>
+      <c r="D19" s="185">
+        <f>IF($C$14&lt;B19,0,Model!$C$13)</f>
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="E19" s="170">
+        <f>IF($C$14&lt;B19,0,1/(1+$C$5)^B19)</f>
+        <v>0.82644628099173545</v>
+      </c>
+      <c r="F19" s="171">
+        <f t="shared" si="0"/>
+        <v>904365.7066240483</v>
+      </c>
+      <c r="H19" s="166"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B20" s="168">
+        <v>3</v>
+      </c>
+      <c r="C20" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D20)^(ROW()-ROW($C$18)), 0)</f>
+        <v>1015494.1646540115</v>
+      </c>
+      <c r="D20" s="185">
+        <f>IF($C$14&lt;B20,0,Model!$C$13)</f>
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="E20" s="170">
+        <f>IF($C$14&lt;B20,0,1/(1+$C$5)^B20)</f>
+        <v>0.75131480090157754</v>
+      </c>
+      <c r="F20" s="171">
+        <f t="shared" si="0"/>
+        <v>762955.79613374243</v>
+      </c>
+      <c r="H20" s="166"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B21" s="168">
+        <v>4</v>
+      </c>
+      <c r="C21" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D21)^(ROW()-ROW($C$18)), 0)</f>
+        <v>942378.58479892265</v>
+      </c>
+      <c r="D21" s="185">
+        <f>IF($C$14&lt;B21,0,Model!$C$13)</f>
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="E21" s="170">
+        <f>IF($C$14&lt;B21,0,1/(1+$C$5)^B21)</f>
+        <v>0.68301345536507052</v>
+      </c>
+      <c r="F21" s="171">
+        <f t="shared" si="0"/>
+        <v>643657.25346555724</v>
+      </c>
+      <c r="H21" s="166"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B22" s="168">
+        <v>5</v>
+      </c>
+      <c r="C22" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D22)^(ROW()-ROW($C$18)), 0)</f>
+        <v>874527.32669340027</v>
+      </c>
+      <c r="D22" s="185">
+        <f>IF($C$14&lt;B22,0,Model!$C$13)</f>
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="E22" s="170">
+        <f>IF($C$14&lt;B22,0,1/(1+$C$5)^B22)</f>
+        <v>0.62092132305915493</v>
+      </c>
+      <c r="F22" s="171">
+        <f t="shared" si="0"/>
+        <v>543012.66474185197</v>
+      </c>
+      <c r="H22" s="166"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="168">
+        <v>6</v>
+      </c>
+      <c r="C23" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D23)^(ROW()-ROW($C$18)), 0)</f>
+        <v>811561.35917147552</v>
+      </c>
+      <c r="D23" s="185">
+        <f>IF($C$14&lt;B23,0,Model!$C$13)</f>
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="E23" s="170">
+        <f>IF($C$14&lt;B23,0,1/(1+$C$5)^B23)</f>
+        <v>0.56447393005377722</v>
+      </c>
+      <c r="F23" s="171">
+        <f t="shared" si="0"/>
+        <v>458105.22989130783</v>
+      </c>
+      <c r="H23" s="166"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="168">
+        <v>7</v>
+      </c>
+      <c r="C24" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D24)^(ROW()-ROW($C$18)), 0)</f>
+        <v>753128.94131112937</v>
+      </c>
+      <c r="D24" s="185">
+        <f>IF($C$14&lt;B24,0,Model!$C$13)</f>
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="E24" s="170">
+        <f>IF($C$14&lt;B24,0,1/(1+$C$5)^B24)</f>
+        <v>0.51315811823070645</v>
+      </c>
+      <c r="F24" s="171">
+        <f t="shared" si="0"/>
+        <v>386474.23030830332</v>
+      </c>
+      <c r="H24" s="166"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B25" s="168">
+        <v>8</v>
+      </c>
+      <c r="C25" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D25)^(ROW()-ROW($C$18)), 0)</f>
+        <v>698903.65753672796</v>
+      </c>
+      <c r="D25" s="185">
+        <f>IF($C$14&lt;B25,0,Model!$C$13)</f>
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="E25" s="170">
+        <f>IF($C$14&lt;B25,0,1/(1+$C$5)^B25)</f>
+        <v>0.46650738020973315</v>
+      </c>
+      <c r="F25" s="171">
+        <f t="shared" si="0"/>
+        <v>326043.71429645945</v>
+      </c>
+      <c r="H25" s="166"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="168">
+        <v>9</v>
+      </c>
+      <c r="C26" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D26)^(ROW()-ROW($C$18)), 0)</f>
+        <v>648582.59419408359</v>
+      </c>
+      <c r="D26" s="185">
+        <f>IF($C$14&lt;B26,0,Model!$C$13)</f>
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="E26" s="170">
+        <f>IF($C$14&lt;B26,0,1/(1+$C$5)^B26)</f>
+        <v>0.42409761837248466</v>
+      </c>
+      <c r="F26" s="171">
+        <f t="shared" si="0"/>
+        <v>275062.33351555857</v>
+      </c>
+      <c r="H26" s="166"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B27" s="168">
+        <v>10</v>
+      </c>
+      <c r="C27" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D27)^(ROW()-ROW($C$18)), 0)</f>
+        <v>601884.64741210965</v>
+      </c>
+      <c r="D27" s="185">
+        <f>IF($C$14&lt;B27,0,Model!$C$13)</f>
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="E27" s="170">
+        <f>IF($C$14&lt;B27,0,1/(1+$C$5)^B27)</f>
+        <v>0.38554328942953148</v>
+      </c>
+      <c r="F27" s="171">
+        <f t="shared" si="0"/>
+        <v>232052.58682039849</v>
+      </c>
+      <c r="H27" s="166"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B28" s="168">
+        <v>11</v>
+      </c>
+      <c r="C28" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D28)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="185">
+        <f>IF($C$14&lt;B28,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="170">
+        <f>IF($C$14&lt;B28,0,1/(1+$C$5)^B28)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="166"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B29" s="168">
+        <v>12</v>
+      </c>
+      <c r="C29" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D29)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="185">
+        <f>IF($C$14&lt;B29,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="170">
+        <f>IF($C$14&lt;B29,0,1/(1+$C$5)^B29)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="166"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B30" s="168">
+        <v>13</v>
+      </c>
+      <c r="C30" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D30)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="185">
+        <f>IF($C$14&lt;B30,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="170">
+        <f>IF($C$14&lt;B30,0,1/(1+$C$5)^B30)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="166"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="168">
+        <v>14</v>
+      </c>
+      <c r="C31" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D31)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="185">
+        <f>IF($C$14&lt;B31,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="170">
+        <f>IF($C$14&lt;B31,0,1/(1+$C$5)^B31)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="166"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B32" s="168">
+        <v>15</v>
+      </c>
+      <c r="C32" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D32)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="185">
+        <f>IF($C$14&lt;B32,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="170">
+        <f>IF($C$14&lt;B32,0,1/(1+$C$5)^B32)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="166"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33" s="168">
+        <v>16</v>
+      </c>
+      <c r="C33" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D33)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="185">
+        <f>IF($C$14&lt;B33,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="170">
+        <f>IF($C$14&lt;B33,0,1/(1+$C$5)^B33)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="166"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34" s="168">
+        <v>17</v>
+      </c>
+      <c r="C34" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D34)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="185">
+        <f>IF($C$14&lt;B34,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="170">
+        <f>IF($C$14&lt;B34,0,1/(1+$C$5)^B34)</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="166"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B35" s="168">
+        <v>18</v>
+      </c>
+      <c r="C35" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D35)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="185">
+        <f>IF($C$14&lt;B35,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="170">
+        <f>IF($C$14&lt;B35,0,1/(1+$C$5)^B35)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="166"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B36" s="168">
+        <v>19</v>
+      </c>
+      <c r="C36" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D36)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="185">
+        <f>IF($C$14&lt;B36,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="170">
+        <f>IF($C$14&lt;B36,0,1/(1+$C$5)^B36)</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="166"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="168">
+        <v>20</v>
+      </c>
+      <c r="C37" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D37)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="185">
+        <f>IF($C$14&lt;B37,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="170">
+        <f>IF($C$14&lt;B37,0,1/(1+$C$5)^B37)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="166"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38" s="168">
+        <v>21</v>
+      </c>
+      <c r="C38" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D38)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D38" s="185">
+        <f>IF($C$14&lt;B38,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="170">
+        <f>IF($C$14&lt;B38,0,1/(1+$C$5)^B38)</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="166"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B39" s="168">
+        <v>22</v>
+      </c>
+      <c r="C39" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D39)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="185">
+        <f>IF($C$14&lt;B39,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="170">
+        <f>IF($C$14&lt;B39,0,1/(1+$C$5)^B39)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="166"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B40" s="168">
+        <v>23</v>
+      </c>
+      <c r="C40" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D40)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="185">
+        <f>IF($C$14&lt;B40,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="170">
+        <f>IF($C$14&lt;B40,0,1/(1+$C$5)^B40)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="166"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B41" s="168">
+        <v>24</v>
+      </c>
+      <c r="C41" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D41)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="185">
+        <f>IF($C$14&lt;B41,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="170">
+        <f>IF($C$14&lt;B41,0,1/(1+$C$5)^B41)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="166"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B42" s="168">
+        <v>25</v>
+      </c>
+      <c r="C42" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D42)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="185">
+        <f>IF($C$14&lt;B42,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="170">
+        <f>IF($C$14&lt;B42,0,1/(1+$C$5)^B42)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="166"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B43" s="168">
+        <v>26</v>
+      </c>
+      <c r="C43" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D43)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D43" s="185">
+        <f>IF($C$14&lt;B43,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="170">
+        <f>IF($C$14&lt;B43,0,1/(1+$C$5)^B43)</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="166"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B44" s="168">
+        <v>27</v>
+      </c>
+      <c r="C44" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D44)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="185">
+        <f>IF($C$14&lt;B44,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="170">
+        <f>IF($C$14&lt;B44,0,1/(1+$C$5)^B44)</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="166"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B45" s="168">
+        <v>28</v>
+      </c>
+      <c r="C45" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D45)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="185">
+        <f>IF($C$14&lt;B45,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="170">
+        <f>IF($C$14&lt;B45,0,1/(1+$C$5)^B45)</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="166"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B46" s="168">
+        <v>29</v>
+      </c>
+      <c r="C46" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D46)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="185">
+        <f>IF($C$14&lt;B46,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="170">
+        <f>IF($C$14&lt;B46,0,1/(1+$C$5)^B46)</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="166"/>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B47" s="168">
+        <v>30</v>
+      </c>
+      <c r="C47" s="169">
+        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D47)^(ROW()-ROW($C$18)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="185">
+        <f>IF($C$14&lt;B47,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="170">
+        <f>IF($C$14&lt;B47,0,1/(1+$C$5)^B47)</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="171">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="166"/>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B48" s="172" t="s">
+        <v>282</v>
+      </c>
+      <c r="C48" s="169">
+        <f>C$18*(1+D48)^$C$14/C5</f>
+        <v>11791837.338524768</v>
+      </c>
+      <c r="D48" s="186">
+        <f>F4</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="170">
+        <f>1/(1+C5)^C14</f>
+        <v>0.38554328942953148</v>
+      </c>
+      <c r="F48" s="171">
+        <f t="shared" si="0"/>
+        <v>4546263.7559128106</v>
+      </c>
+      <c r="H48" s="166"/>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C49" s="160"/>
+      <c r="E49" s="173" t="s">
+        <v>238</v>
+      </c>
+      <c r="F49" s="184">
+        <f>SUM(F18:F48)</f>
+        <v>10149978.484303199</v>
+      </c>
+      <c r="H49" s="166"/>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C50" s="160"/>
+      <c r="H50" s="166"/>
+    </row>
+    <row r="51" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="B51" s="165" t="s">
+        <v>280</v>
+      </c>
+      <c r="C51" s="183"/>
+      <c r="D51" s="183"/>
+      <c r="E51" s="163"/>
+      <c r="F51" s="163"/>
+      <c r="H51" s="166"/>
+    </row>
+    <row r="52" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B52" s="179">
+        <f>F49</f>
+        <v>10149978.484303199</v>
+      </c>
+      <c r="C52" s="177">
+        <f>C73</f>
+        <v>-0.15</v>
+      </c>
+      <c r="D52" s="177">
+        <f>C72</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="177">
+        <f>C71</f>
+        <v>0.01</v>
+      </c>
+      <c r="F52" s="177">
+        <f>C70</f>
+        <v>0.02</v>
+      </c>
+      <c r="H52" s="166"/>
+    </row>
+    <row r="53" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B53" s="192">
+        <v>5</v>
+      </c>
+      <c r="C53" s="169">
+        <f t="dataTable" ref="C53:F58" dt2D="1" dtr="1" r1="C13" r2="C14"/>
+        <v>9836413.3965352103</v>
+      </c>
+      <c r="D53" s="169">
+        <v>12706721.269962028</v>
+      </c>
+      <c r="E53" s="169">
+        <v>12922692.982327804</v>
+      </c>
+      <c r="F53" s="169">
+        <v>13142141.538962446</v>
+      </c>
+      <c r="H53" s="166"/>
+    </row>
+    <row r="54" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B54" s="192">
+        <v>10</v>
+      </c>
+      <c r="C54" s="169">
+        <v>8156502.4549473226</v>
+      </c>
+      <c r="D54" s="169">
+        <v>12706721.269962028</v>
+      </c>
+      <c r="E54" s="169">
+        <v>13134802.320367645</v>
+      </c>
+      <c r="F54" s="169">
+        <v>13583940.944009084</v>
+      </c>
+      <c r="H54" s="166"/>
+    </row>
+    <row r="55" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B55" s="192">
+        <v>15</v>
+      </c>
+      <c r="C55" s="169">
+        <v>6815544.6738921013</v>
+      </c>
+      <c r="D55" s="169">
+        <v>12706721.269962026</v>
+      </c>
+      <c r="E55" s="169">
+        <v>13368901.948442612</v>
+      </c>
+      <c r="F55" s="169">
+        <v>14083969.893871106</v>
+      </c>
+      <c r="H55" s="166"/>
+    </row>
+    <row r="56" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B56" s="193">
+        <v>20</v>
+      </c>
+      <c r="C56" s="169">
+        <v>5900851.7022183863</v>
+      </c>
+      <c r="D56" s="169">
+        <v>12706721.269962026</v>
+      </c>
+      <c r="E56" s="169">
+        <v>13581082.743169647</v>
+      </c>
+      <c r="F56" s="169">
+        <v>14549180.863933826</v>
+      </c>
+      <c r="H56" s="166"/>
+    </row>
+    <row r="57" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B57" s="193">
+        <v>25</v>
+      </c>
+      <c r="C57" s="169">
+        <v>5310290.2851397078</v>
+      </c>
+      <c r="D57" s="169">
+        <v>12706721.269962026</v>
+      </c>
+      <c r="E57" s="169">
+        <v>13756438.873081338</v>
+      </c>
+      <c r="F57" s="169">
+        <v>14944116.610065991</v>
+      </c>
+      <c r="H57" s="166"/>
+    </row>
+    <row r="58" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B58" s="193">
+        <v>30</v>
+      </c>
+      <c r="C58" s="169">
+        <v>4937369.1785926893</v>
+      </c>
+      <c r="D58" s="169">
+        <v>12706721.269962024</v>
+      </c>
+      <c r="E58" s="169">
+        <v>13893779.935453041</v>
+      </c>
+      <c r="F58" s="169">
+        <v>15262060.98258711</v>
+      </c>
+      <c r="H58" s="166"/>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C59" s="160"/>
+      <c r="D59" s="160"/>
+      <c r="E59" s="160"/>
+      <c r="F59" s="160"/>
+      <c r="H59" s="166"/>
+    </row>
+    <row r="60" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="B60" s="165" t="s">
+        <v>281</v>
+      </c>
+      <c r="C60" s="160"/>
+      <c r="D60" s="160"/>
+      <c r="E60" s="160"/>
+      <c r="F60" s="160"/>
+      <c r="H60" s="166"/>
+    </row>
+    <row r="61" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="C61" s="178">
+        <f>C52</f>
+        <v>-0.15</v>
+      </c>
+      <c r="D61" s="178">
+        <f>D52</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="178">
+        <f>E52</f>
+        <v>0.01</v>
+      </c>
+      <c r="F61" s="178">
+        <f>F52</f>
+        <v>0.02</v>
+      </c>
+      <c r="H61" s="166"/>
+    </row>
+    <row r="62" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B62" s="192">
+        <f>B53</f>
+        <v>5</v>
+      </c>
+      <c r="C62" s="205">
+        <f t="shared" ref="B62:F67" si="1">(C53-$C$7)/Common_Shares*$C$3</f>
+        <v>13.288003893211801</v>
+      </c>
+      <c r="D62" s="188">
+        <f t="shared" si="1"/>
+        <v>18.176897600606136</v>
+      </c>
+      <c r="E62" s="205">
+        <f t="shared" si="1"/>
+        <v>18.544754566520961</v>
+      </c>
+      <c r="F62" s="205">
+        <f t="shared" si="1"/>
+        <v>18.918533518096286</v>
+      </c>
+      <c r="H62" s="166"/>
+    </row>
+    <row r="63" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B63" s="192">
+        <f>B54</f>
+        <v>10</v>
+      </c>
+      <c r="C63" s="205">
+        <f t="shared" si="1"/>
+        <v>10.426671104716659</v>
+      </c>
+      <c r="D63" s="205">
+        <f t="shared" si="1"/>
+        <v>18.176897600606136</v>
+      </c>
+      <c r="E63" s="205">
+        <f t="shared" si="1"/>
+        <v>18.906032887088198</v>
+      </c>
+      <c r="F63" s="205">
+        <f t="shared" si="1"/>
+        <v>19.671034792004711</v>
+      </c>
+      <c r="H63" s="166"/>
+    </row>
+    <row r="64" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B64" s="192">
+        <f>B55</f>
+        <v>15</v>
+      </c>
+      <c r="C64" s="205">
+        <f t="shared" si="1"/>
+        <v>8.1426652256346106</v>
+      </c>
+      <c r="D64" s="205">
+        <f t="shared" si="1"/>
+        <v>18.176897600606136</v>
+      </c>
+      <c r="E64" s="205">
+        <f t="shared" si="1"/>
+        <v>19.304766489568504</v>
+      </c>
+      <c r="F64" s="205">
+        <f t="shared" si="1"/>
+        <v>20.522716386556755</v>
+      </c>
+      <c r="H64" s="166"/>
+    </row>
+    <row r="65" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B65" s="193">
+        <f>B56</f>
+        <v>20</v>
+      </c>
+      <c r="C65" s="205">
+        <f t="shared" si="1"/>
+        <v>6.5847010940466664</v>
+      </c>
+      <c r="D65" s="205">
+        <f t="shared" si="1"/>
+        <v>18.176897600606136</v>
+      </c>
+      <c r="E65" s="205">
+        <f t="shared" si="1"/>
+        <v>19.666166519779367</v>
+      </c>
+      <c r="F65" s="205">
+        <f t="shared" si="1"/>
+        <v>21.315093749698331</v>
+      </c>
+      <c r="H65" s="166"/>
+    </row>
+    <row r="66" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B66" s="193">
+        <f>B57</f>
+        <v>25</v>
+      </c>
+      <c r="C66" s="205">
+        <f t="shared" si="1"/>
+        <v>5.5788187555995172</v>
+      </c>
+      <c r="D66" s="205">
+        <f t="shared" si="1"/>
+        <v>18.176897600606136</v>
+      </c>
+      <c r="E66" s="205">
+        <f t="shared" si="1"/>
+        <v>19.964844403087675</v>
+      </c>
+      <c r="F66" s="205">
+        <f t="shared" si="1"/>
+        <v>21.987773813731142</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B67" s="193">
+        <f>B58</f>
+        <v>30</v>
+      </c>
+      <c r="C67" s="205">
+        <f t="shared" si="1"/>
+        <v>4.9436354472056356</v>
+      </c>
+      <c r="D67" s="205">
+        <f t="shared" si="1"/>
+        <v>18.176897600606132</v>
+      </c>
+      <c r="E67" s="205">
+        <f t="shared" si="1"/>
+        <v>20.198772568707845</v>
+      </c>
+      <c r="F67" s="205">
+        <f t="shared" si="1"/>
+        <v>22.529317198853857</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B69" s="174" t="s">
+        <v>258</v>
+      </c>
+      <c r="C69" s="174" t="s">
+        <v>283</v>
+      </c>
+      <c r="D69" s="174" t="s">
+        <v>252</v>
+      </c>
+      <c r="E69" s="175" t="s">
+        <v>253</v>
+      </c>
+      <c r="F69" s="175" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B70" s="173" t="s">
+        <v>255</v>
+      </c>
+      <c r="C70" s="189">
+        <v>0.02</v>
+      </c>
+      <c r="D70" s="194">
+        <v>10</v>
+      </c>
+      <c r="E70" s="182">
+        <f>INDEX(C$62:F$67, MATCH(D70, B$62:B$67, 0), MATCH(C70, C$61:F$61, 0))</f>
+        <v>19.671034792004711</v>
+      </c>
+      <c r="F70" s="189">
+        <v>0.15</v>
+      </c>
+      <c r="H70" s="166" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B71" s="173" t="s">
+        <v>256</v>
+      </c>
+      <c r="C71" s="189">
+        <v>0.01</v>
+      </c>
+      <c r="D71" s="194">
+        <v>5</v>
+      </c>
+      <c r="E71" s="182">
+        <f>INDEX(C$62:F$67, MATCH(D71, B$62:B$67, 0), MATCH(C71, C$61:F$61, 0))</f>
+        <v>18.544754566520961</v>
+      </c>
+      <c r="F71" s="189">
+        <v>0.5</v>
+      </c>
+      <c r="H71" s="166" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B72" s="173" t="s">
+        <v>254</v>
+      </c>
+      <c r="C72" s="190">
+        <v>0</v>
+      </c>
+      <c r="D72" s="195">
+        <v>0</v>
+      </c>
+      <c r="E72" s="182">
+        <f>$C$9</f>
+        <v>18.176897600606146</v>
+      </c>
+      <c r="F72" s="189">
+        <v>0.2</v>
+      </c>
+      <c r="H72" s="166" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B73" s="173" t="s">
+        <v>257</v>
+      </c>
+      <c r="C73" s="189">
+        <v>-0.15</v>
+      </c>
+      <c r="D73" s="194">
+        <v>5</v>
+      </c>
+      <c r="E73" s="182">
+        <f>INDEX(C$62:F$67, MATCH(D73, B$62:B$67, 0), MATCH(C73, C$61:F$61, 0))</f>
+        <v>13.288003893211801</v>
+      </c>
+      <c r="F73" s="189">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B74" t="str">
+        <f>IF(VLOOKUP("No Growth",B70:E73,4,FALSE)&gt;VLOOKUP("Base",B70:E73,4,FALSE),"Note: the No Growth value being higher than the Base or Optimistic values is unusual.","OK")</f>
+        <v>OK</v>
+      </c>
+      <c r="F74" s="191" t="str">
+        <f>IF(SUM(F70:F73)=1,"100% - OK",SUM(F70:F73)*100&amp;"% Error")</f>
+        <v>100% - OK</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B76" s="139" t="s">
+        <v>262</v>
+      </c>
+      <c r="C76" s="196">
+        <f>E70*F70+E71*F71+E72*F72+E73*F73</f>
+        <v>17.851612606164188</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B78" s="39" t="s">
+        <v>278</v>
+      </c>
+      <c r="C78" s="40"/>
+      <c r="D78" s="40"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
+    </row>
+    <row r="79" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B79" s="153" t="s">
+        <v>273</v>
+      </c>
+      <c r="E79" s="153" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B80" s="139" t="s">
+        <v>291</v>
+      </c>
+      <c r="C80" s="180">
+        <f>Thesis!C37</f>
+        <v>0.2</v>
+      </c>
+      <c r="E80" s="139" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B81" s="139" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81">
+        <f>FCF!C86</f>
+        <v>1.3599999999999999</v>
+      </c>
+      <c r="D81" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E81" s="139" t="s">
+        <v>272</v>
+      </c>
+      <c r="F81" s="203">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B83" s="153" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B84" s="139" t="s">
+        <v>263</v>
+      </c>
+      <c r="C84" s="162">
+        <f>PV(C80, F81, -C81, 0)</f>
+        <v>2.8648148148148143</v>
+      </c>
+      <c r="D84" s="139"/>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B85" s="139" t="s">
+        <v>265</v>
+      </c>
+      <c r="C85" s="162">
+        <f>C76/(1+C80)^F81</f>
+        <v>10.330794332270942</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B86" s="155" t="s">
+        <v>239</v>
+      </c>
+      <c r="C86" s="156">
+        <f>C84+C85</f>
+        <v>13.195609147085756</v>
+      </c>
+      <c r="D86" s="197" t="s">
         <v>277</v>
       </c>
-      <c r="C10" s="160">
-        <f>(C9*FCF!C3)/Common_Shares</f>
-        <v>18.176897600606146</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B12" s="169" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B13" s="139" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B14" s="139" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B15" s="139" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B17" s="155" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B18" t="str">
-        <f>r_e!B12</f>
-        <v>Target Return</v>
-      </c>
-      <c r="C18" s="156">
-        <f>r_e!C12</f>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="139" t="s">
-        <v>268</v>
-      </c>
-      <c r="C19" s="165">
-        <f>r_e!C13</f>
-        <v>3</v>
-      </c>
-      <c r="D19" s="139" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="139" t="s">
-        <v>272</v>
-      </c>
-      <c r="C20" s="166">
-        <f>FCF!C87</f>
-        <v>798466.67599999986</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="139" t="s">
-        <v>271</v>
-      </c>
-      <c r="C22" s="167">
-        <f>PV(C18, 3, -C20)</f>
-        <v>1823079.1698265788</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="139" t="s">
-        <v>275</v>
-      </c>
-      <c r="C23" s="167">
-        <f>C9/(1+C18)^3</f>
-        <v>7016881.2492558798</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="139" t="s">
-        <v>276</v>
-      </c>
-      <c r="C24" s="167">
-        <f>C22+C23</f>
-        <v>8839960.4190824591</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C25" s="168">
-        <f>C24/Common_Shares*1000</f>
-        <v>15.056791386935908</v>
-      </c>
-      <c r="D25" s="139" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B27" s="39" t="s">
-        <v>234</v>
-      </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-    </row>
-    <row r="28" spans="2:5" ht="13.15" x14ac:dyDescent="0.35">
-      <c r="B28" s="174" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B29" s="171" t="s">
-        <v>293</v>
-      </c>
-      <c r="C29" s="172">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B30" s="171" t="s">
-        <v>294</v>
-      </c>
-      <c r="C30" s="173">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" ht="13.15" x14ac:dyDescent="0.35">
-      <c r="B32" s="175" t="s">
-        <v>285</v>
-      </c>
-      <c r="C32" s="166"/>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B33" s="180" t="s">
-        <v>273</v>
-      </c>
-      <c r="C33" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="D33" s="179" t="s">
-        <v>286</v>
-      </c>
-      <c r="E33" s="179" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" s="166">
-        <f>C4*(1+Model!$C$29)</f>
-        <v>1334205.7333460136</v>
-      </c>
-      <c r="D34" s="168">
-        <f>IF($C$30&lt;B34,0,1/(1+$C$5)^B34)</f>
-        <v>0.90909090909090906</v>
-      </c>
-      <c r="E34" s="157">
-        <f t="shared" ref="E34:E43" si="0">C34*D34</f>
-        <v>1212914.3030418304</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B35">
-        <v>2</v>
-      </c>
-      <c r="C35" s="166">
-        <f>IF(ROW()-ROW($C$34)&lt;$C$30, $C$34*(1+$C$29)^(ROW()-ROW($C$34)), 0)</f>
-        <v>1400916.0200133144</v>
-      </c>
-      <c r="D35" s="168">
-        <f t="shared" ref="D35:D53" si="1">IF($C$30&lt;B35,0,1/(1+$C$5)^B35)</f>
-        <v>0.82644628099173545</v>
-      </c>
-      <c r="E35" s="157">
-        <f t="shared" si="0"/>
-        <v>1157781.8347217473</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B36">
-        <v>3</v>
-      </c>
-      <c r="C36" s="166">
-        <f t="shared" ref="C36:C53" si="2">IF(ROW()-ROW($C$34)&lt;$C$30, $C$34*(1+$C$29)^(ROW()-ROW($C$34)), 0)</f>
-        <v>1470961.8210139801</v>
-      </c>
-      <c r="D36" s="168">
-        <f t="shared" si="1"/>
-        <v>0.75131480090157754</v>
-      </c>
-      <c r="E36" s="157">
-        <f t="shared" si="0"/>
-        <v>1105155.3876889404</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B37">
-        <v>4</v>
-      </c>
-      <c r="C37" s="166">
-        <f t="shared" si="2"/>
-        <v>1544509.9120646792</v>
-      </c>
-      <c r="D37" s="168">
-        <f t="shared" si="1"/>
-        <v>0.68301345536507052</v>
-      </c>
-      <c r="E37" s="157">
-        <f t="shared" si="0"/>
-        <v>1054921.0518848978</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B38">
-        <v>5</v>
-      </c>
-      <c r="C38" s="166">
-        <f t="shared" si="2"/>
-        <v>1621735.407667913</v>
-      </c>
-      <c r="D38" s="168">
-        <f t="shared" si="1"/>
-        <v>0.62092132305915493</v>
-      </c>
-      <c r="E38" s="157">
-        <f t="shared" si="0"/>
-        <v>1006970.0949810385</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B39">
-        <v>6</v>
-      </c>
-      <c r="C39" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D39" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E39" s="157">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B40">
-        <v>7</v>
-      </c>
-      <c r="C40" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D40" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E40" s="157">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B41">
-        <v>8</v>
-      </c>
-      <c r="C41" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D41" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E41" s="157">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B42">
-        <v>9</v>
-      </c>
-      <c r="C42" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D42" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E42" s="157">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B43">
-        <v>10</v>
-      </c>
-      <c r="C43" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D43" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E43" s="157">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B44">
-        <v>11</v>
-      </c>
-      <c r="C44" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D44" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E44" s="157">
-        <f t="shared" ref="E44:E53" si="3">C44*D44</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B45">
-        <v>12</v>
-      </c>
-      <c r="C45" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D45" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E45" s="157">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B46">
-        <v>13</v>
-      </c>
-      <c r="C46" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D46" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E46" s="157">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B47">
-        <v>14</v>
-      </c>
-      <c r="C47" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D47" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E47" s="157">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B48">
-        <v>15</v>
-      </c>
-      <c r="C48" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D48" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E48" s="157">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B49">
-        <v>16</v>
-      </c>
-      <c r="C49" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D49" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E49" s="157">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B50">
-        <v>17</v>
-      </c>
-      <c r="C50" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D50" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E50" s="157">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B51">
-        <v>18</v>
-      </c>
-      <c r="C51" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D51" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E51" s="157">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B52">
-        <v>19</v>
-      </c>
-      <c r="C52" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D52" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E52" s="157">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B53">
-        <v>20</v>
-      </c>
-      <c r="C53" s="166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D53" s="168">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E53" s="157">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B54" s="176" t="s">
-        <v>288</v>
-      </c>
-      <c r="C54" s="166">
-        <f>C$34*(1+$C$29)^$C$30/C5</f>
-        <v>17028221.780513085</v>
-      </c>
-      <c r="D54" s="168">
-        <f>1/(1+C5)^C30</f>
-        <v>0.62092132305915493</v>
-      </c>
-      <c r="E54" s="157">
-        <f>C54*D54</f>
-        <v>10573185.997300904</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C55" s="166"/>
-      <c r="D55" s="139" t="s">
-        <v>274</v>
-      </c>
-      <c r="E55" s="157">
-        <f>SUM(E34:E54)</f>
-        <v>16110928.669619359</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C56" s="166"/>
-      <c r="E56" s="177">
-        <f>(E55-C8)/Common_Shares*C3</f>
-        <v>23.97516345526526</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C57" s="166"/>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C58" s="166"/>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B59" s="157">
-        <f>E55</f>
-        <v>16110928.669619359</v>
-      </c>
-      <c r="C59" s="181">
-        <v>-0.05</v>
-      </c>
-      <c r="D59" s="181">
-        <v>-0.03</v>
-      </c>
-      <c r="E59" s="181">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B60" s="182">
-        <v>5</v>
-      </c>
-      <c r="C60" s="166">
-        <f t="dataTable" ref="C60:E63" dt2D="1" dtr="1" r1="C29" r2="C30"/>
-        <v>9980850.9808912966</v>
-      </c>
-      <c r="D60" s="166">
-        <v>10997794.559108231</v>
-      </c>
-      <c r="E60" s="166">
-        <v>13329180.488442868</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B61" s="182">
-        <v>10</v>
-      </c>
-      <c r="C61" s="166">
-        <v>8976439.0039775074</v>
-      </c>
-      <c r="D61" s="166">
-        <v>10289843.228939731</v>
-      </c>
-      <c r="E61" s="166">
-        <v>13652470.611953594</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B62" s="182">
-        <v>15</v>
-      </c>
-      <c r="C62" s="166">
-        <v>8493862.1549467165</v>
-      </c>
-      <c r="D62" s="166">
-        <v>9912359.1426842809</v>
-      </c>
-      <c r="E62" s="166">
-        <v>13863447.984902434</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B63">
-        <v>20</v>
-      </c>
-      <c r="C63" s="166">
-        <v>8262004.6895110207</v>
-      </c>
-      <c r="D63" s="166">
-        <v>9711082.2620515432</v>
-      </c>
-      <c r="E63" s="166">
-        <v>14001130.668842884</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C64" s="166"/>
-      <c r="D64" s="166"/>
-      <c r="E64" s="166"/>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C65" s="170">
-        <f>C59</f>
-        <v>-0.05</v>
-      </c>
-      <c r="D65" s="170">
-        <f t="shared" ref="D65:E65" si="4">D59</f>
-        <v>-0.03</v>
-      </c>
-      <c r="E65" s="170">
-        <f t="shared" si="4"/>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B66">
-        <f>B60</f>
-        <v>5</v>
-      </c>
-      <c r="C66" s="168">
-        <f t="shared" ref="C66:E69" si="5">(C60-$C$8)/Common_Shares*$C$3</f>
-        <v>13.53401931330214</v>
-      </c>
-      <c r="D66" s="168">
-        <f t="shared" si="5"/>
-        <v>15.26614328033296</v>
-      </c>
-      <c r="E66" s="168">
-        <f t="shared" si="5"/>
-        <v>19.237110334060205</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B67">
-        <f t="shared" ref="B67:B69" si="6">B61</f>
-        <v>10</v>
-      </c>
-      <c r="C67" s="168">
-        <f t="shared" si="5"/>
-        <v>11.823239978783297</v>
-      </c>
-      <c r="D67" s="168">
-        <f t="shared" si="5"/>
-        <v>14.060314861979329</v>
-      </c>
-      <c r="E67" s="168">
-        <f t="shared" si="5"/>
-        <v>19.787758947446527</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B68">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="C68" s="168">
-        <f t="shared" si="5"/>
-        <v>11.00128392925885</v>
-      </c>
-      <c r="D68" s="168">
-        <f t="shared" si="5"/>
-        <v>13.417359591911914</v>
-      </c>
-      <c r="E68" s="168">
-        <f t="shared" si="5"/>
-        <v>20.147109231979158</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B69">
-        <f t="shared" si="6"/>
-        <v>20</v>
-      </c>
-      <c r="C69" s="168">
-        <f t="shared" si="5"/>
-        <v>10.60636932296344</v>
-      </c>
-      <c r="D69" s="168">
-        <f t="shared" si="5"/>
-        <v>13.074531812258247</v>
-      </c>
-      <c r="E69" s="168">
-        <f t="shared" si="5"/>
-        <v>20.381619269513912</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B71" s="139" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B73" s="39" t="s">
-        <v>233</v>
-      </c>
-      <c r="C73" s="40"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="40"/>
-    </row>
-    <row r="74" spans="2:5" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B74" s="155" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B75" s="139" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B76" s="139" t="s">
-        <v>291</v>
-      </c>
+      <c r="E86" s="198">
+        <f>-(C86/C76-1)</f>
+        <v>0.2608169671725179</v>
+      </c>
+      <c r="H86" s="166" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C89" s="161"/>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C90" s="161"/>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C91" s="161"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="B69:F69" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B70:F74">
+      <sortCondition descending="1" ref="E69"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="30" type="noConversion"/>
+  <conditionalFormatting sqref="C28:F47">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C62:F67">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>ISNUMBER(MATCH(C62, $E$70:$E$73, 0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E70:E73">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="lessThan">
+      <formula>$F$13</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D70:D73 C14" xr:uid="{A06882BF-7451-4B05-ADA9-B8AC5ACC7F23}">
+      <formula1>$B$53:$B$58</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/financial_models/templates/Valuation_v2.01.xlsx
+++ b/financial_models/templates/Valuation_v2.01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDE3B4C-0838-4DCA-B2B6-7550F7972CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB25BC2-9CFF-4955-B846-4DB0095C749C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="17040" windowHeight="10680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,9 +22,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Model!$B$69:$F$69</definedName>
     <definedName name="Common_Shares">Thesis!$C$11</definedName>
+    <definedName name="Equity_Cost">Model!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$10</definedName>
     <definedName name="Reporting_currency">Thesis!$C$12</definedName>
+    <definedName name="Terminal_Growth">Model!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="301">
   <si>
     <t>HKD</t>
   </si>
@@ -910,10 +912,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>(Adjusted) FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Dividend</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -987,19 +985,19 @@
   </si>
   <si>
     <t>Year</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>FCFE</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Discount Factor</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>PV of FCFE</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Annual Dividend per share</t>
@@ -1031,23 +1029,23 @@
   </si>
   <si>
     <t>Scenarios</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Market Price</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Growth Rates</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Probabilities</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Expected Value =</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>PV(Dividends)</t>
@@ -1055,7 +1053,7 @@
   </si>
   <si>
     <t>Buy at &lt; PV(dividends, 3yrs, r) + PV(Equity value, 3yrs, r)</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>PV(Equity Value)</t>
@@ -1063,7 +1061,7 @@
   </si>
   <si>
     <t>= Enterprise Value</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>/Equity Cost of Capital</t>
@@ -1075,39 +1073,39 @@
   </si>
   <si>
     <t>= Equity Value</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Special Assumption</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>- Expects no significant growth at terminal years</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>over a holding period of</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Inputs</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>the Equity Value will be conservatively realized</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Terminal Growth Rate:</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>- Avoids overvaluation.</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>at a MOS of</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Margin of Safety (MOS)</t>
@@ -1147,11 +1145,11 @@
   </si>
   <si>
     <t>52 week Low</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Reference Price Points</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Output</t>
@@ -1159,11 +1157,51 @@
   </si>
   <si>
     <t>52 week High</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
   </si>
   <si>
     <t>Target Return</t>
-    <phoneticPr fontId="30" type="noConversion"/>
+    <phoneticPr fontId="29" type="noConversion"/>
+  </si>
+  <si>
+    <t>Realizable Value Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Book</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Estimate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Non-operating Assets</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Operating Asset Yield</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Operating FCFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total FCFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Non-Operating Asset Yield</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Profibility %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leverage %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1186,8 +1224,8 @@
     <numFmt numFmtId="188" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
     <numFmt numFmtId="189" formatCode="#,##0_);[Red]\(#,##0\)"/>
     <numFmt numFmtId="190" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="192" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="193" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
+    <numFmt numFmtId="191" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="192" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
   <fonts count="35" x14ac:knownFonts="1">
     <font>
@@ -1368,14 +1406,6 @@
       <scheme val="major"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
       <i/>
       <u/>
       <sz val="9"/>
@@ -1444,6 +1474,15 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1533,7 +1572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="212">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1794,9 +1833,6 @@
     <xf numFmtId="10" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -1879,9 +1915,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="24" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1891,7 +1924,7 @@
     <xf numFmtId="188" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="188" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="184" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1899,12 +1932,12 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="186" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="186" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="187" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="187" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1915,10 +1948,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="184" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1928,17 +1961,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="183" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="183" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="186" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1948,29 +1981,23 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="190" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="190" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="186" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="31" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="30" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="27" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="191" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="30" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="192" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="31" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="192" fontId="27" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="193" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="191" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1981,31 +2008,44 @@
     </xf>
     <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="192" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="191" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="192" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="191" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="184" fontId="14" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="184" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2313,7 +2353,7 @@
         <v>45643</v>
       </c>
       <c r="D2" s="59"/>
-      <c r="E2" s="123" t="s">
+      <c r="E2" s="122" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2376,7 +2416,7 @@
         <v>213</v>
       </c>
       <c r="C10" s="57">
-        <v>13.82</v>
+        <v>15.68</v>
       </c>
       <c r="D10" s="55" t="s">
         <v>69</v>
@@ -2418,7 +2458,7 @@
       </c>
       <c r="C14" s="38">
         <f>Thesis!C10*Thesis!C11/1000000</f>
-        <v>8113.8304870000002</v>
+        <v>9205.8510879999994</v>
       </c>
       <c r="D14" s="55"/>
     </row>
@@ -2457,7 +2497,7 @@
       <c r="B22" s="52" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="149">
+      <c r="C22" s="147">
         <f>Data!C3</f>
         <v>1000</v>
       </c>
@@ -2480,12 +2520,12 @@
         <v>222</v>
       </c>
       <c r="C24" s="100">
-        <f>FCF!C12</f>
+        <f>FCF!C19</f>
         <v>190177</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B25" s="146" t="s">
+      <c r="B25" s="144" t="s">
         <v>142</v>
       </c>
       <c r="C25" s="100">
@@ -2498,7 +2538,7 @@
         <v>223</v>
       </c>
       <c r="C27" s="100">
-        <f>FCF!C19</f>
+        <f>FCF!C20</f>
         <v>1270672.1269962033</v>
       </c>
     </row>
@@ -2506,7 +2546,7 @@
       <c r="B28" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C28" s="144">
+      <c r="C28" s="143">
         <f>C27/(Common_Shares/Data!C3)</f>
         <v>2.1642908147050042</v>
       </c>
@@ -2515,9 +2555,9 @@
       <c r="B29" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C29" s="124">
+      <c r="C29" s="123">
         <f>C28/Market_Price</f>
-        <v>0.15660570294536932</v>
+        <v>0.13802875093781913</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -2551,25 +2591,25 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C37" s="167">
+        <v>241</v>
+      </c>
+      <c r="C37" s="165">
         <v>0.2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C38" s="124"/>
+      <c r="C38" s="123"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B39" s="18" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="144" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B40" s="146" t="s">
-        <v>234</v>
-      </c>
-      <c r="C40" s="152">
+      <c r="C40" s="150">
         <v>0</v>
       </c>
       <c r="D40" s="54" t="s">
@@ -2577,27 +2617,27 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B41" s="146" t="s">
+      <c r="B41" s="144" t="s">
+        <v>234</v>
+      </c>
+      <c r="C41" s="150">
+        <v>0</v>
+      </c>
+      <c r="D41" s="149" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="144" t="s">
         <v>235</v>
       </c>
-      <c r="C41" s="152">
-        <v>0</v>
-      </c>
-      <c r="D41" s="151" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B42" s="146" t="s">
-        <v>236</v>
-      </c>
-      <c r="C42" s="152">
+      <c r="C42" s="150">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B43" s="91" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C43" s="92">
         <f>SUM(C40:C42)</f>
@@ -2696,7 +2736,7 @@
       <c r="B67" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C67" s="211">
+      <c r="C67" s="206">
         <f>Model!E86</f>
         <v>0.2608169671725179</v>
       </c>
@@ -2758,9 +2798,13 @@
       <c r="B81" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="C81" s="199">
+      <c r="C81" s="195">
         <f>Model!C86</f>
         <v>13.195609147085756</v>
+      </c>
+      <c r="D81" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
@@ -2878,11 +2922,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B1" s="121" t="str">
+      <c r="B1" s="120" t="str">
         <f>Thesis!C12</f>
         <v>HKD</v>
       </c>
-      <c r="C1" s="143">
+      <c r="C1" s="142">
         <v>45382</v>
       </c>
       <c r="D1" s="41">
@@ -2946,7 +2990,7 @@
       <c r="B3" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="147">
+      <c r="C3" s="145">
         <v>1000</v>
       </c>
     </row>
@@ -4007,11 +4051,11 @@
         <v>184</v>
       </c>
       <c r="C43" s="100">
-        <f>IF(C$4="","",C45-C44-C40-C39)</f>
+        <f>IF(C$4="","",C45-(C39+C40+C44))</f>
         <v>248317</v>
       </c>
       <c r="D43" s="100">
-        <f t="shared" ref="D43:M43" si="21">IF(D$4="","",D45-D44-D40-D39)</f>
+        <f t="shared" ref="D43:M43" si="21">IF(D$4="","",D45-(D39+D40+D44))</f>
         <v>190177</v>
       </c>
       <c r="E43" s="100">
@@ -4401,7 +4445,7 @@
       </c>
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B54" s="122" t="s">
+      <c r="B54" s="121" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4410,47 +4454,47 @@
         <f>B32</f>
         <v>Sales</v>
       </c>
-      <c r="C55" s="124">
+      <c r="C55" s="123">
         <f t="shared" ref="C55:M55" si="30">IF(D$32="","",C32/D32-1)</f>
         <v>0.27952593137796744</v>
       </c>
-      <c r="D55" s="124">
+      <c r="D55" s="123">
         <f t="shared" si="30"/>
         <v>2.0450249505806095E-2</v>
       </c>
-      <c r="E55" s="124">
+      <c r="E55" s="123">
         <f t="shared" si="30"/>
         <v>0.32460887665346139</v>
       </c>
-      <c r="F55" s="124">
+      <c r="F55" s="123">
         <f t="shared" si="30"/>
         <v>-0.21118785490642455</v>
       </c>
-      <c r="G55" s="124">
+      <c r="G55" s="123">
         <f t="shared" si="30"/>
         <v>-0.29169116752280422</v>
       </c>
-      <c r="H55" s="124" t="str">
+      <c r="H55" s="123" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="I55" s="124" t="str">
+      <c r="I55" s="123" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="J55" s="124" t="str">
+      <c r="J55" s="123" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="K55" s="124" t="str">
+      <c r="K55" s="123" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="L55" s="124" t="str">
+      <c r="L55" s="123" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="M55" s="124" t="str">
+      <c r="M55" s="123" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -4460,47 +4504,47 @@
         <f>B39</f>
         <v>EBIT</v>
       </c>
-      <c r="C56" s="140">
+      <c r="C56" s="139">
         <f t="shared" ref="C56:M56" si="31">IF(D$32="","",C33/D33-1)</f>
         <v>0.27484316281081789</v>
       </c>
-      <c r="D56" s="140">
+      <c r="D56" s="139">
         <f t="shared" si="31"/>
         <v>2.8630254836090829E-2</v>
       </c>
-      <c r="E56" s="140">
+      <c r="E56" s="139">
         <f t="shared" si="31"/>
         <v>0.36521892689379709</v>
       </c>
-      <c r="F56" s="140">
+      <c r="F56" s="139">
         <f t="shared" si="31"/>
         <v>-0.21258803367720713</v>
       </c>
-      <c r="G56" s="140">
+      <c r="G56" s="139">
         <f t="shared" si="31"/>
         <v>-0.33107999439209057</v>
       </c>
-      <c r="H56" s="140" t="str">
+      <c r="H56" s="139" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="I56" s="140" t="str">
+      <c r="I56" s="139" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="J56" s="140" t="str">
+      <c r="J56" s="139" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="K56" s="140" t="str">
+      <c r="K56" s="139" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="L56" s="140" t="str">
+      <c r="L56" s="139" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="M56" s="140" t="str">
+      <c r="M56" s="139" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -4510,47 +4554,47 @@
         <f>B43</f>
         <v>Non-Operating Income (Est.)</v>
       </c>
-      <c r="C57" s="124">
+      <c r="C57" s="123">
         <f t="shared" ref="C57:M57" si="32">IF(D$32="","",C34/D34-1)</f>
         <v>0.29220619013700166</v>
       </c>
-      <c r="D57" s="124">
+      <c r="D57" s="123">
         <f t="shared" si="32"/>
         <v>-1.0606627998344109E-3</v>
       </c>
-      <c r="E57" s="124">
+      <c r="E57" s="123">
         <f t="shared" si="32"/>
         <v>0.22851064557243328</v>
       </c>
-      <c r="F57" s="124">
+      <c r="F57" s="123">
         <f t="shared" si="32"/>
         <v>-0.20785460213901807</v>
       </c>
-      <c r="G57" s="124">
+      <c r="G57" s="123">
         <f t="shared" si="32"/>
         <v>-0.1762134107583947</v>
       </c>
-      <c r="H57" s="124" t="str">
+      <c r="H57" s="123" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="I57" s="124" t="str">
+      <c r="I57" s="123" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="J57" s="124" t="str">
+      <c r="J57" s="123" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="K57" s="124" t="str">
+      <c r="K57" s="123" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="L57" s="124" t="str">
+      <c r="L57" s="123" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="M57" s="124" t="str">
+      <c r="M57" s="123" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -4560,47 +4604,47 @@
         <f>B45</f>
         <v>Reported Net Income</v>
       </c>
-      <c r="C58" s="140">
+      <c r="C58" s="139">
         <f t="shared" ref="C58:M58" si="33">IF(D$32="","",C35/D35-1)</f>
         <v>0.23027981033619538</v>
       </c>
-      <c r="D58" s="140">
+      <c r="D58" s="139">
         <f t="shared" si="33"/>
         <v>2.88709616106122E-2</v>
       </c>
-      <c r="E58" s="140">
+      <c r="E58" s="139">
         <f t="shared" si="33"/>
         <v>7.1190571738822594E-2</v>
       </c>
-      <c r="F58" s="140">
+      <c r="F58" s="139">
         <f t="shared" si="33"/>
         <v>-0.20005740582329201</v>
       </c>
-      <c r="G58" s="140">
+      <c r="G58" s="139">
         <f t="shared" si="33"/>
         <v>-0.12351904546938497</v>
       </c>
-      <c r="H58" s="140" t="str">
+      <c r="H58" s="139" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="I58" s="140" t="str">
+      <c r="I58" s="139" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="J58" s="140" t="str">
+      <c r="J58" s="139" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="K58" s="140" t="str">
+      <c r="K58" s="139" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="L58" s="140" t="str">
+      <c r="L58" s="139" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="M58" s="140" t="str">
+      <c r="M58" s="139" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
@@ -4610,47 +4654,47 @@
         <f>B46</f>
         <v>Non-controling Interests</v>
       </c>
-      <c r="C59" s="124">
+      <c r="C59" s="123">
         <f>IF(D$32="","",C52/D52-1)</f>
         <v>0.23636363636363611</v>
       </c>
-      <c r="D59" s="124">
+      <c r="D59" s="123">
         <f t="shared" ref="D59:M59" si="34">IF(E$32="","",D52/E52-1)</f>
         <v>0</v>
       </c>
-      <c r="E59" s="124">
+      <c r="E59" s="123">
         <f t="shared" si="34"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="F59" s="124">
+      <c r="F59" s="123">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="G59" s="124">
+      <c r="G59" s="123">
         <f t="shared" si="34"/>
         <v>-0.13043478260869557</v>
       </c>
-      <c r="H59" s="124" t="str">
+      <c r="H59" s="123" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="I59" s="124" t="str">
+      <c r="I59" s="123" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="J59" s="124" t="str">
+      <c r="J59" s="123" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="K59" s="124" t="str">
+      <c r="K59" s="123" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="L59" s="124" t="str">
+      <c r="L59" s="123" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="M59" s="124" t="str">
+      <c r="M59" s="123" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
@@ -4727,7 +4771,7 @@
       </c>
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B64" s="127" t="s">
+      <c r="B64" s="126" t="s">
         <v>199</v>
       </c>
       <c r="C64" s="94">
@@ -4754,14 +4798,14 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="I64" s="128"/>
-      <c r="J64" s="128"/>
-      <c r="K64" s="128"/>
-      <c r="L64" s="128"/>
-      <c r="M64" s="128"/>
+      <c r="I64" s="127"/>
+      <c r="J64" s="127"/>
+      <c r="K64" s="127"/>
+      <c r="L64" s="127"/>
+      <c r="M64" s="127"/>
     </row>
     <row r="65" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B65" s="127" t="s">
+      <c r="B65" s="126" t="s">
         <v>200</v>
       </c>
       <c r="C65" s="94">
@@ -4788,11 +4832,11 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="I65" s="128"/>
-      <c r="J65" s="128"/>
-      <c r="K65" s="128"/>
-      <c r="L65" s="128"/>
-      <c r="M65" s="128"/>
+      <c r="I65" s="127"/>
+      <c r="J65" s="127"/>
+      <c r="K65" s="127"/>
+      <c r="L65" s="127"/>
+      <c r="M65" s="127"/>
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="29" t="s">
@@ -4893,16 +4937,16 @@
       </c>
     </row>
     <row r="69" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B69" s="125" t="s">
+      <c r="B69" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="126" t="s">
+      <c r="C69" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="126" t="s">
+      <c r="D69" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="E69" s="120" t="s">
+      <c r="E69" s="119" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4959,7 +5003,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q797"/>
+  <dimension ref="A1:Q798"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
@@ -4974,7 +5018,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3"/>
-      <c r="B1" s="121" t="str">
+      <c r="B1" s="120" t="str">
         <f>Thesis!C12</f>
         <v>HKD</v>
       </c>
@@ -5032,7 +5076,7 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C2" s="61"/>
       <c r="D2" s="63"/>
@@ -5055,9 +5099,9 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="C3" s="148">
+        <v>278</v>
+      </c>
+      <c r="C3" s="146">
         <f>Data!C3</f>
         <v>1000</v>
       </c>
@@ -5130,16 +5174,16 @@
         <v>80</v>
       </c>
       <c r="C5" s="77">
-        <f>C44</f>
+        <f>C45</f>
         <v>-10739107.696087126</v>
       </c>
       <c r="E5" s="20"/>
       <c r="G5" s="65">
-        <f>G44</f>
+        <f>G45</f>
         <v>-13195082</v>
       </c>
       <c r="H5" s="65">
-        <f t="shared" ref="H5:Q5" si="1">H44</f>
+        <f t="shared" ref="H5:Q5" si="1">H45</f>
         <v>-10265436</v>
       </c>
       <c r="I5" s="65">
@@ -5240,16 +5284,16 @@
         <v>79</v>
       </c>
       <c r="C7" s="77">
-        <f>C47</f>
+        <f>C48</f>
         <v>-302359.25</v>
       </c>
       <c r="E7" s="20"/>
       <c r="G7" s="77">
-        <f>G47</f>
+        <f>G48</f>
         <v>-254107</v>
       </c>
       <c r="H7" s="77">
-        <f t="shared" ref="H7:Q7" si="3">H47</f>
+        <f t="shared" ref="H7:Q7" si="3">H48</f>
         <v>-349526</v>
       </c>
       <c r="I7" s="77">
@@ -5352,16 +5396,16 @@
         <v>159</v>
       </c>
       <c r="C9" s="77">
-        <f>C60</f>
+        <f>C61</f>
         <v>-30619</v>
       </c>
       <c r="E9" s="20"/>
       <c r="G9" s="77">
-        <f>G60</f>
+        <f>G61</f>
         <v>-30619</v>
       </c>
       <c r="H9" s="77">
-        <f t="shared" ref="H9:Q9" si="5">H60</f>
+        <f t="shared" ref="H9:Q9" si="5">H61</f>
         <v>12362</v>
       </c>
       <c r="I9" s="77">
@@ -5407,7 +5451,7 @@
         <v>151</v>
       </c>
       <c r="C10" s="77">
-        <f>-(C8+C9)*C37</f>
+        <f>-(C8+C9)*C38</f>
         <v>-346869.76025000488</v>
       </c>
       <c r="E10" s="20"/>
@@ -5515,450 +5559,486 @@
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
-      <c r="B12" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="C12" s="145">
-        <f>MIN(G12:J12)</f>
-        <v>190177</v>
-      </c>
-      <c r="D12" s="66"/>
-      <c r="E12" s="85" t="s">
-        <v>186</v>
-      </c>
-      <c r="F12" s="66"/>
-      <c r="G12" s="68">
-        <f>Data!C43</f>
-        <v>248317</v>
-      </c>
-      <c r="H12" s="68">
-        <f>Data!D43</f>
-        <v>190177</v>
-      </c>
-      <c r="I12" s="68">
-        <f>Data!E43</f>
-        <v>200697</v>
-      </c>
-      <c r="J12" s="68">
-        <f>Data!F43</f>
-        <v>281254</v>
-      </c>
-      <c r="K12" s="68">
-        <f>Data!G43</f>
-        <v>-275378</v>
-      </c>
-      <c r="L12" s="68">
-        <f>Data!H43</f>
-        <v>-1582814</v>
-      </c>
-      <c r="M12" s="68" t="str">
-        <f>Data!I43</f>
-        <v/>
-      </c>
-      <c r="N12" s="68" t="str">
-        <f>Data!J43</f>
-        <v/>
-      </c>
-      <c r="O12" s="68" t="str">
-        <f>Data!K43</f>
-        <v/>
-      </c>
-      <c r="P12" s="68" t="str">
-        <f>Data!L43</f>
-        <v/>
-      </c>
-      <c r="Q12" s="68" t="str">
-        <f>Data!M43</f>
+      <c r="B12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="77">
+        <f>BS!$G$25*BS!C42</f>
+        <v>463424</v>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="G12" s="96">
+        <f>IF(Data!C49="","",-Data!C49)</f>
+        <v>463424</v>
+      </c>
+      <c r="H12" s="96">
+        <f>IF(Data!D49="","",-Data!D49)</f>
+        <v>371724</v>
+      </c>
+      <c r="I12" s="96">
+        <f>IF(Data!E49="","",-Data!E49)</f>
+        <v>435672</v>
+      </c>
+      <c r="J12" s="96">
+        <f>IF(Data!F49="","",-Data!F49)</f>
+        <v>520888</v>
+      </c>
+      <c r="K12" s="96">
+        <f>IF(Data!G49="","",-Data!G49)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="96">
+        <f>IF(Data!H49="","",-Data!H49)</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="96" t="str">
+        <f>IF(Data!I49="","",-Data!I49)</f>
+        <v/>
+      </c>
+      <c r="N12" s="96" t="str">
+        <f>IF(Data!J49="","",-Data!J49)</f>
+        <v/>
+      </c>
+      <c r="O12" s="96" t="str">
+        <f>IF(Data!K49="","",-Data!K49)</f>
+        <v/>
+      </c>
+      <c r="P12" s="96" t="str">
+        <f>IF(Data!L49="","",-Data!L49)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="96" t="str">
+        <f>IF(Data!M49="","",-Data!M49)</f>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="2" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="C13" s="77">
-        <f>BS!$G$25*BS!C42</f>
-        <v>463424</v>
+        <f>-C4*C32</f>
+        <v>-463424.00000000006</v>
       </c>
       <c r="E13" s="20"/>
-      <c r="G13" s="96">
-        <f>IF(Data!C49="","",-Data!C49)</f>
-        <v>463424</v>
-      </c>
-      <c r="H13" s="96">
-        <f>IF(Data!D49="","",-Data!D49)</f>
-        <v>371724</v>
-      </c>
-      <c r="I13" s="96">
-        <f>IF(Data!E49="","",-Data!E49)</f>
-        <v>435672</v>
-      </c>
-      <c r="J13" s="96">
-        <f>IF(Data!F49="","",-Data!F49)</f>
-        <v>520888</v>
-      </c>
-      <c r="K13" s="96">
-        <f>IF(Data!G49="","",-Data!G49)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="96">
-        <f>IF(Data!H49="","",-Data!H49)</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="96" t="str">
-        <f>IF(Data!I49="","",-Data!I49)</f>
-        <v/>
-      </c>
-      <c r="N13" s="96" t="str">
-        <f>IF(Data!J49="","",-Data!J49)</f>
-        <v/>
-      </c>
-      <c r="O13" s="96" t="str">
-        <f>IF(Data!K49="","",-Data!K49)</f>
-        <v/>
-      </c>
-      <c r="P13" s="96" t="str">
-        <f>IF(Data!L49="","",-Data!L49)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="96" t="str">
-        <f>IF(Data!M49="","",-Data!M49)</f>
+      <c r="G13" s="77">
+        <f>Data!C50</f>
+        <v>-676387</v>
+      </c>
+      <c r="H13" s="77">
+        <f>Data!D50</f>
+        <v>-107280</v>
+      </c>
+      <c r="I13" s="77">
+        <f>Data!E50</f>
+        <v>-455483</v>
+      </c>
+      <c r="J13" s="77">
+        <f>Data!F50</f>
+        <v>-138937</v>
+      </c>
+      <c r="K13" s="77">
+        <f>Data!G50</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="77">
+        <f>Data!H50</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="77" t="str">
+        <f>Data!I50</f>
+        <v/>
+      </c>
+      <c r="N13" s="77" t="str">
+        <f>Data!J50</f>
+        <v/>
+      </c>
+      <c r="O13" s="77" t="str">
+        <f>Data!K50</f>
+        <v/>
+      </c>
+      <c r="P13" s="77" t="str">
+        <f>Data!L50</f>
+        <v/>
+      </c>
+      <c r="Q13" s="77" t="str">
+        <f>Data!M50</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
-      <c r="B14" s="2" t="s">
-        <v>193</v>
+      <c r="B14" s="44" t="s">
+        <v>78</v>
       </c>
       <c r="C14" s="77">
-        <f>-C4*C31</f>
-        <v>-463424.00000000006</v>
-      </c>
-      <c r="E14" s="20"/>
-      <c r="G14" s="77">
-        <f>Data!C50</f>
-        <v>-676387</v>
-      </c>
-      <c r="H14" s="77">
-        <f>Data!D50</f>
-        <v>-107280</v>
-      </c>
-      <c r="I14" s="77">
-        <f>Data!E50</f>
-        <v>-455483</v>
-      </c>
-      <c r="J14" s="77">
-        <f>Data!F50</f>
-        <v>-138937</v>
-      </c>
-      <c r="K14" s="77">
-        <f>Data!G50</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="77">
-        <f>Data!H50</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="77" t="str">
-        <f>Data!I50</f>
-        <v/>
-      </c>
-      <c r="N14" s="77" t="str">
-        <f>Data!J50</f>
-        <v/>
-      </c>
-      <c r="O14" s="77" t="str">
-        <f>Data!K50</f>
-        <v/>
-      </c>
-      <c r="P14" s="77" t="str">
-        <f>Data!L50</f>
-        <v/>
-      </c>
-      <c r="Q14" s="77" t="str">
-        <f>Data!M50</f>
+        <f>-C4*C34</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="69"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="65">
+        <f>Data!C46</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="65">
+        <f>Data!D46</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="65">
+        <f>Data!E46</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="65">
+        <f>Data!F46</f>
+        <v>-1799</v>
+      </c>
+      <c r="K14" s="65">
+        <f>Data!G46</f>
+        <v>-1337</v>
+      </c>
+      <c r="L14" s="65">
+        <f>Data!H46</f>
+        <v>-10908</v>
+      </c>
+      <c r="M14" s="65" t="str">
+        <f>Data!I46</f>
+        <v/>
+      </c>
+      <c r="N14" s="65" t="str">
+        <f>Data!J46</f>
+        <v/>
+      </c>
+      <c r="O14" s="65" t="str">
+        <f>Data!K46</f>
+        <v/>
+      </c>
+      <c r="P14" s="65" t="str">
+        <f>Data!L46</f>
+        <v/>
+      </c>
+      <c r="Q14" s="65" t="str">
+        <f>Data!M46</f>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12"/>
-      <c r="B15" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="77">
-        <f>-C4*C33</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="65">
-        <f>Data!C46</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="65">
-        <f>Data!D46</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="65">
-        <f>Data!E46</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="65">
-        <f>Data!F46</f>
-        <v>-1799</v>
-      </c>
-      <c r="K15" s="65">
-        <f>Data!G46</f>
-        <v>-1337</v>
-      </c>
-      <c r="L15" s="65">
-        <f>Data!H46</f>
-        <v>-10908</v>
-      </c>
-      <c r="M15" s="65" t="str">
-        <f>Data!I46</f>
-        <v/>
-      </c>
-      <c r="N15" s="65" t="str">
-        <f>Data!J46</f>
-        <v/>
-      </c>
-      <c r="O15" s="65" t="str">
-        <f>Data!K46</f>
-        <v/>
-      </c>
-      <c r="P15" s="65" t="str">
-        <f>Data!L46</f>
-        <v/>
-      </c>
-      <c r="Q15" s="65" t="str">
-        <f>Data!M46</f>
+      <c r="B15" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15" s="80">
+        <f>SUM(C11:C14)</f>
+        <v>1080495.1269962033</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="80">
+        <f>IF(G$4="","",SUM(G11:G14))</f>
+        <v>1306025</v>
+      </c>
+      <c r="H15" s="80">
+        <f>IF(H$4="","",SUM(H11:H14))</f>
+        <v>1359024</v>
+      </c>
+      <c r="I15" s="80">
+        <f>IF(I$4="","",SUM(I11:I14))</f>
+        <v>1171856</v>
+      </c>
+      <c r="J15" s="80">
+        <f>IF(J$4="","",SUM(J11:J14))</f>
+        <v>1116233</v>
+      </c>
+      <c r="K15" s="80">
+        <f>IF(K$4="","",SUM(K11:K14))</f>
+        <v>1140356</v>
+      </c>
+      <c r="L15" s="80">
+        <f>IF(L$4="","",SUM(L11:L14))</f>
+        <v>1571906</v>
+      </c>
+      <c r="M15" s="80" t="str">
+        <f>IF(M$4="","",SUM(M11:M14))</f>
+        <v/>
+      </c>
+      <c r="N15" s="80" t="str">
+        <f>IF(N$4="","",SUM(N11:N14))</f>
+        <v/>
+      </c>
+      <c r="O15" s="80" t="str">
+        <f>IF(O$4="","",SUM(O11:O14))</f>
+        <v/>
+      </c>
+      <c r="P15" s="80" t="str">
+        <f>IF(P$4="","",SUM(P11:P14))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="80" t="str">
+        <f>IF(Q$4="","",SUM(Q11:Q14))</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
-      <c r="B16" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="C16" s="80">
-        <f>SUM(C11:C15)</f>
-        <v>1270672.1269962033</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="80">
-        <f>IF(G$4="","",SUM(G11:G15))</f>
-        <v>1554342</v>
-      </c>
-      <c r="H16" s="80">
-        <f t="shared" ref="H16:Q16" si="7">IF(H$4="","",SUM(H11:H15))</f>
-        <v>1549201</v>
-      </c>
-      <c r="I16" s="80">
-        <f t="shared" si="7"/>
-        <v>1372553</v>
-      </c>
-      <c r="J16" s="80">
-        <f t="shared" si="7"/>
-        <v>1397487</v>
-      </c>
-      <c r="K16" s="80">
-        <f t="shared" si="7"/>
-        <v>864978</v>
-      </c>
-      <c r="L16" s="80">
-        <f t="shared" si="7"/>
-        <v>-10908</v>
-      </c>
-      <c r="M16" s="80" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="N16" s="80" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="O16" s="80" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P16" s="80" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="Q16" s="80" t="str">
-        <f t="shared" si="7"/>
+      <c r="B16" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="77">
+        <f>-C4*C33</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="66"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="77">
+        <f>Data!C51</f>
+        <v>-626583</v>
+      </c>
+      <c r="H16" s="77">
+        <f>Data!D51</f>
+        <v>-352099</v>
+      </c>
+      <c r="I16" s="77">
+        <f>Data!E51</f>
+        <v>-1045251</v>
+      </c>
+      <c r="J16" s="77">
+        <f>Data!F51</f>
+        <v>818677</v>
+      </c>
+      <c r="K16" s="77">
+        <f>Data!G51</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="77">
+        <f>Data!H51</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="77" t="str">
+        <f>Data!I51</f>
+        <v/>
+      </c>
+      <c r="N16" s="77" t="str">
+        <f>Data!J51</f>
+        <v/>
+      </c>
+      <c r="O16" s="77" t="str">
+        <f>Data!K51</f>
+        <v/>
+      </c>
+      <c r="P16" s="77" t="str">
+        <f>Data!L51</f>
+        <v/>
+      </c>
+      <c r="Q16" s="77" t="str">
+        <f>Data!M51</f>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="30" t="s">
-        <v>88</v>
+        <v>227</v>
       </c>
       <c r="C17" s="77">
-        <f>-C4*C32</f>
         <v>0</v>
       </c>
       <c r="D17" s="66"/>
-      <c r="E17" s="85"/>
+      <c r="E17" s="85" t="s">
+        <v>226</v>
+      </c>
       <c r="F17" s="66"/>
-      <c r="G17" s="77">
-        <f>Data!C51</f>
-        <v>-626583</v>
-      </c>
-      <c r="H17" s="77">
-        <f>Data!D51</f>
-        <v>-352099</v>
-      </c>
-      <c r="I17" s="77">
-        <f>Data!E51</f>
-        <v>-1045251</v>
-      </c>
-      <c r="J17" s="77">
-        <f>Data!F51</f>
-        <v>818677</v>
-      </c>
-      <c r="K17" s="77">
-        <f>Data!G51</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="77">
-        <f>Data!H51</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="77" t="str">
-        <f>Data!I51</f>
-        <v/>
-      </c>
-      <c r="N17" s="77" t="str">
-        <f>Data!J51</f>
-        <v/>
-      </c>
-      <c r="O17" s="77" t="str">
-        <f>Data!K51</f>
-        <v/>
-      </c>
-      <c r="P17" s="77" t="str">
-        <f>Data!L51</f>
-        <v/>
-      </c>
-      <c r="Q17" s="77" t="str">
-        <f>Data!M51</f>
-        <v/>
-      </c>
+      <c r="G17" s="148"/>
+      <c r="H17" s="148"/>
+      <c r="I17" s="148"/>
+      <c r="J17" s="148"/>
+      <c r="K17" s="148"/>
+      <c r="L17" s="148"/>
+      <c r="M17" s="148"/>
+      <c r="N17" s="148"/>
+      <c r="O17" s="148"/>
+      <c r="P17" s="148"/>
+      <c r="Q17" s="148"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12"/>
-      <c r="B18" s="30" t="s">
-        <v>227</v>
-      </c>
-      <c r="C18" s="77">
-        <v>0</v>
+      <c r="B18" s="34" t="s">
+        <v>296</v>
+      </c>
+      <c r="C18" s="80">
+        <f>SUM(C15:C17)</f>
+        <v>1080495.1269962033</v>
       </c>
       <c r="D18" s="66"/>
-      <c r="E18" s="85" t="s">
-        <v>226</v>
-      </c>
+      <c r="E18" s="85"/>
       <c r="F18" s="66"/>
-      <c r="G18" s="150"/>
-      <c r="H18" s="150"/>
-      <c r="I18" s="150"/>
-      <c r="J18" s="150"/>
-      <c r="K18" s="150"/>
-      <c r="L18" s="150"/>
-      <c r="M18" s="150"/>
-      <c r="N18" s="150"/>
-      <c r="O18" s="150"/>
-      <c r="P18" s="150"/>
-      <c r="Q18" s="150"/>
+      <c r="G18" s="212">
+        <f>IF(G$4="","",SUM(G15:G17))</f>
+        <v>679442</v>
+      </c>
+      <c r="H18" s="212">
+        <f t="shared" ref="H18:Q18" si="7">IF(H$4="","",SUM(H15:H17))</f>
+        <v>1006925</v>
+      </c>
+      <c r="I18" s="212">
+        <f t="shared" si="7"/>
+        <v>126605</v>
+      </c>
+      <c r="J18" s="212">
+        <f t="shared" si="7"/>
+        <v>1934910</v>
+      </c>
+      <c r="K18" s="212">
+        <f t="shared" si="7"/>
+        <v>1140356</v>
+      </c>
+      <c r="L18" s="212">
+        <f t="shared" si="7"/>
+        <v>1571906</v>
+      </c>
+      <c r="M18" s="212" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N18" s="212" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O18" s="212" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="P18" s="212" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="Q18" s="212" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12"/>
-      <c r="B19" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="C19" s="80">
-        <f>C16+C17</f>
-        <v>1270672.1269962033</v>
-      </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="68">
-        <f>IF(G$4="","",G16+G17)</f>
-        <v>927759</v>
-      </c>
-      <c r="H19" s="68">
-        <f t="shared" ref="H19:Q19" si="8">IF(H$4="","",H16+H17)</f>
-        <v>1197102</v>
-      </c>
-      <c r="I19" s="68">
-        <f t="shared" si="8"/>
-        <v>327302</v>
-      </c>
-      <c r="J19" s="68">
-        <f t="shared" si="8"/>
-        <v>2216164</v>
-      </c>
-      <c r="K19" s="68">
-        <f t="shared" si="8"/>
-        <v>864978</v>
-      </c>
-      <c r="L19" s="68">
-        <f t="shared" si="8"/>
-        <v>-10908</v>
-      </c>
-      <c r="M19" s="68" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N19" s="68" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O19" s="68" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="P19" s="68" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q19" s="68" t="str">
-        <f t="shared" si="8"/>
+      <c r="B19" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19" s="211">
+        <f>MIN(G19:J19)</f>
+        <v>190177</v>
+      </c>
+      <c r="D19" s="66"/>
+      <c r="E19" s="85" t="s">
+        <v>186</v>
+      </c>
+      <c r="F19" s="66"/>
+      <c r="G19" s="65">
+        <f>Data!C43</f>
+        <v>248317</v>
+      </c>
+      <c r="H19" s="65">
+        <f>Data!D43</f>
+        <v>190177</v>
+      </c>
+      <c r="I19" s="65">
+        <f>Data!E43</f>
+        <v>200697</v>
+      </c>
+      <c r="J19" s="65">
+        <f>Data!F43</f>
+        <v>281254</v>
+      </c>
+      <c r="K19" s="65">
+        <f>Data!G43</f>
+        <v>-275378</v>
+      </c>
+      <c r="L19" s="65">
+        <f>Data!H43</f>
+        <v>-1582814</v>
+      </c>
+      <c r="M19" s="65" t="str">
+        <f>Data!I43</f>
+        <v/>
+      </c>
+      <c r="N19" s="65" t="str">
+        <f>Data!J43</f>
+        <v/>
+      </c>
+      <c r="O19" s="65" t="str">
+        <f>Data!K43</f>
+        <v/>
+      </c>
+      <c r="P19" s="65" t="str">
+        <f>Data!L43</f>
+        <v/>
+      </c>
+      <c r="Q19" s="65" t="str">
+        <f>Data!M43</f>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="74"/>
+      <c r="B20" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="C20" s="80">
+        <f>C18+C19</f>
+        <v>1270672.1269962033</v>
+      </c>
       <c r="D20" s="30"/>
       <c r="E20" s="86"/>
       <c r="F20" s="30"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
+      <c r="G20" s="68">
+        <f>IF(G$4="","",G18+G19)</f>
+        <v>927759</v>
+      </c>
+      <c r="H20" s="68">
+        <f t="shared" ref="H20:Q20" si="8">IF(H$4="","",H18+H19)</f>
+        <v>1197102</v>
+      </c>
+      <c r="I20" s="68">
+        <f t="shared" si="8"/>
+        <v>327302</v>
+      </c>
+      <c r="J20" s="68">
+        <f t="shared" si="8"/>
+        <v>2216164</v>
+      </c>
+      <c r="K20" s="68">
+        <f t="shared" si="8"/>
+        <v>864978</v>
+      </c>
+      <c r="L20" s="68">
+        <f t="shared" si="8"/>
+        <v>-10908</v>
+      </c>
+      <c r="M20" s="68" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="N20" s="68" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="O20" s="68" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="P20" s="68" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="Q20" s="68" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
     </row>
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
-      <c r="B21" s="93" t="s">
-        <v>76</v>
-      </c>
+      <c r="B21" s="30"/>
       <c r="C21" s="74"/>
       <c r="D21" s="30"/>
       <c r="E21" s="86"/>
@@ -5977,774 +6057,774 @@
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12"/>
-      <c r="B22" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" s="101">
-        <f t="shared" ref="C22:C30" si="9">ABS(C5/C$4)</f>
-        <v>0.85916636172912864</v>
-      </c>
+      <c r="B22" s="93" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="74"/>
       <c r="D22" s="30"/>
       <c r="E22" s="86"/>
       <c r="F22" s="30"/>
-      <c r="G22" s="8">
-        <f t="shared" ref="G22:Q22" si="10">IF(G$4="","",ABS(G5/G$4))</f>
-        <v>0.86096272455849754</v>
-      </c>
-      <c r="H22" s="8">
-        <f t="shared" si="10"/>
-        <v>0.85703537297697319</v>
-      </c>
-      <c r="I22" s="8">
-        <f t="shared" si="10"/>
-        <v>0.85154513157189637</v>
-      </c>
-      <c r="J22" s="8">
-        <f t="shared" si="10"/>
-        <v>0.86234342793721264</v>
-      </c>
-      <c r="K22" s="8">
-        <f t="shared" si="10"/>
-        <v>0.70419372087965826</v>
-      </c>
-      <c r="L22" s="8">
-        <f t="shared" si="10"/>
-        <v>0.74565961264792724</v>
-      </c>
-      <c r="M22" s="8" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="N22" s="8" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O22" s="8" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="P22" s="8" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="Q22" s="8" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12"/>
-      <c r="B23" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="102">
-        <f t="shared" si="9"/>
-        <v>0.14083363827087136</v>
+      <c r="B23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="101">
+        <f>ABS(C5/C$4)</f>
+        <v>0.85916636172912864</v>
       </c>
       <c r="D23" s="30"/>
       <c r="E23" s="86"/>
       <c r="F23" s="30"/>
-      <c r="G23" s="79">
-        <f t="shared" ref="G23:Q23" si="11">IF(G$4="","",ABS(G6/G$4))</f>
-        <v>0.13903727544150246</v>
-      </c>
-      <c r="H23" s="79">
-        <f t="shared" si="11"/>
-        <v>0.14296462702302684</v>
-      </c>
-      <c r="I23" s="79">
-        <f t="shared" si="11"/>
-        <v>0.14845486842810363</v>
-      </c>
-      <c r="J23" s="79">
-        <f t="shared" si="11"/>
-        <v>0.13765657206278739</v>
-      </c>
-      <c r="K23" s="79">
-        <f t="shared" si="11"/>
-        <v>0.29580627912034169</v>
-      </c>
-      <c r="L23" s="79">
-        <f t="shared" si="11"/>
-        <v>0.25434038735207271</v>
-      </c>
-      <c r="M23" s="79" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="N23" s="79" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="O23" s="79" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P23" s="79" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q23" s="79" t="str">
-        <f t="shared" si="11"/>
+      <c r="G23" s="8">
+        <f>IF(G$4="","",ABS(G5/G$4))</f>
+        <v>0.86096272455849754</v>
+      </c>
+      <c r="H23" s="8">
+        <f>IF(H$4="","",ABS(H5/H$4))</f>
+        <v>0.85703537297697319</v>
+      </c>
+      <c r="I23" s="8">
+        <f>IF(I$4="","",ABS(I5/I$4))</f>
+        <v>0.85154513157189637</v>
+      </c>
+      <c r="J23" s="8">
+        <f>IF(J$4="","",ABS(J5/J$4))</f>
+        <v>0.86234342793721264</v>
+      </c>
+      <c r="K23" s="8">
+        <f>IF(K$4="","",ABS(K5/K$4))</f>
+        <v>0.70419372087965826</v>
+      </c>
+      <c r="L23" s="8">
+        <f>IF(L$4="","",ABS(L5/L$4))</f>
+        <v>0.74565961264792724</v>
+      </c>
+      <c r="M23" s="8" t="str">
+        <f>IF(M$4="","",ABS(M5/M$4))</f>
+        <v/>
+      </c>
+      <c r="N23" s="8" t="str">
+        <f>IF(N$4="","",ABS(N5/N$4))</f>
+        <v/>
+      </c>
+      <c r="O23" s="8" t="str">
+        <f>IF(O$4="","",ABS(O5/O$4))</f>
+        <v/>
+      </c>
+      <c r="P23" s="8" t="str">
+        <f>IF(P$4="","",ABS(P5/P$4))</f>
+        <v/>
+      </c>
+      <c r="Q23" s="8" t="str">
+        <f>IF(Q$4="","",ABS(Q5/Q$4))</f>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12"/>
-      <c r="B24" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="101">
-        <f t="shared" si="9"/>
-        <v>2.4189802738666985E-2</v>
+      <c r="B24" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="102">
+        <f>ABS(C6/C$4)</f>
+        <v>0.14083363827087136</v>
       </c>
       <c r="D24" s="30"/>
       <c r="E24" s="86"/>
       <c r="F24" s="30"/>
-      <c r="G24" s="8">
-        <f t="shared" ref="G24:Q24" si="12">IF(G$4="","",ABS(G7/G$4))</f>
-        <v>1.6580166386945237E-2</v>
-      </c>
-      <c r="H24" s="8">
-        <f t="shared" si="12"/>
-        <v>2.9181044602016856E-2</v>
-      </c>
-      <c r="I24" s="8">
-        <f t="shared" si="12"/>
-        <v>2.7587615842589962E-2</v>
-      </c>
-      <c r="J24" s="8">
-        <f t="shared" si="12"/>
-        <v>3.1822067442433898E-2</v>
-      </c>
-      <c r="K24" s="8">
-        <f t="shared" si="12"/>
-        <v>0.18856108069142588</v>
-      </c>
-      <c r="L24" s="8">
-        <f t="shared" si="12"/>
-        <v>0.15238149582692045</v>
-      </c>
-      <c r="M24" s="8" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="N24" s="8" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="O24" s="8" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P24" s="8" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="Q24" s="8" t="str">
-        <f t="shared" si="12"/>
+      <c r="G24" s="79">
+        <f>IF(G$4="","",ABS(G6/G$4))</f>
+        <v>0.13903727544150246</v>
+      </c>
+      <c r="H24" s="79">
+        <f>IF(H$4="","",ABS(H6/H$4))</f>
+        <v>0.14296462702302684</v>
+      </c>
+      <c r="I24" s="79">
+        <f>IF(I$4="","",ABS(I6/I$4))</f>
+        <v>0.14845486842810363</v>
+      </c>
+      <c r="J24" s="79">
+        <f>IF(J$4="","",ABS(J6/J$4))</f>
+        <v>0.13765657206278739</v>
+      </c>
+      <c r="K24" s="79">
+        <f>IF(K$4="","",ABS(K6/K$4))</f>
+        <v>0.29580627912034169</v>
+      </c>
+      <c r="L24" s="79">
+        <f>IF(L$4="","",ABS(L6/L$4))</f>
+        <v>0.25434038735207271</v>
+      </c>
+      <c r="M24" s="79" t="str">
+        <f>IF(M$4="","",ABS(M6/M$4))</f>
+        <v/>
+      </c>
+      <c r="N24" s="79" t="str">
+        <f>IF(N$4="","",ABS(N6/N$4))</f>
+        <v/>
+      </c>
+      <c r="O24" s="79" t="str">
+        <f>IF(O$4="","",ABS(O6/O$4))</f>
+        <v/>
+      </c>
+      <c r="P24" s="79" t="str">
+        <f>IF(P$4="","",ABS(P6/P$4))</f>
+        <v/>
+      </c>
+      <c r="Q24" s="79" t="str">
+        <f>IF(Q$4="","",ABS(Q6/Q$4))</f>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12"/>
-      <c r="B25" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="102">
-        <f t="shared" si="9"/>
-        <v>0.11664383553220437</v>
+      <c r="B25" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="101">
+        <f>ABS(C7/C$4)</f>
+        <v>2.4189802738666985E-2</v>
       </c>
       <c r="D25" s="30"/>
       <c r="E25" s="86"/>
       <c r="F25" s="30"/>
-      <c r="G25" s="79">
-        <f t="shared" ref="G25:Q25" si="13">IF(G$4="","",ABS(G8/G$4))</f>
-        <v>0.12245710905455723</v>
-      </c>
-      <c r="H25" s="79">
-        <f t="shared" si="13"/>
-        <v>0.11378358242100998</v>
-      </c>
-      <c r="I25" s="79">
-        <f t="shared" si="13"/>
-        <v>0.12086725258551366</v>
-      </c>
-      <c r="J25" s="79">
-        <f t="shared" si="13"/>
-        <v>0.10583450462035347</v>
-      </c>
-      <c r="K25" s="79">
-        <f t="shared" si="13"/>
-        <v>0.10724519842891581</v>
-      </c>
-      <c r="L25" s="79">
-        <f t="shared" si="13"/>
-        <v>0.10195889152515229</v>
-      </c>
-      <c r="M25" s="79" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="N25" s="79" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="O25" s="79" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="P25" s="79" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="Q25" s="79" t="str">
-        <f t="shared" si="13"/>
+      <c r="G25" s="8">
+        <f>IF(G$4="","",ABS(G7/G$4))</f>
+        <v>1.6580166386945237E-2</v>
+      </c>
+      <c r="H25" s="8">
+        <f>IF(H$4="","",ABS(H7/H$4))</f>
+        <v>2.9181044602016856E-2</v>
+      </c>
+      <c r="I25" s="8">
+        <f>IF(I$4="","",ABS(I7/I$4))</f>
+        <v>2.7587615842589962E-2</v>
+      </c>
+      <c r="J25" s="8">
+        <f>IF(J$4="","",ABS(J7/J$4))</f>
+        <v>3.1822067442433898E-2</v>
+      </c>
+      <c r="K25" s="8">
+        <f>IF(K$4="","",ABS(K7/K$4))</f>
+        <v>0.18856108069142588</v>
+      </c>
+      <c r="L25" s="8">
+        <f>IF(L$4="","",ABS(L7/L$4))</f>
+        <v>0.15238149582692045</v>
+      </c>
+      <c r="M25" s="8" t="str">
+        <f>IF(M$4="","",ABS(M7/M$4))</f>
+        <v/>
+      </c>
+      <c r="N25" s="8" t="str">
+        <f>IF(N$4="","",ABS(N7/N$4))</f>
+        <v/>
+      </c>
+      <c r="O25" s="8" t="str">
+        <f>IF(O$4="","",ABS(O7/O$4))</f>
+        <v/>
+      </c>
+      <c r="P25" s="8" t="str">
+        <f>IF(P$4="","",ABS(P7/P$4))</f>
+        <v/>
+      </c>
+      <c r="Q25" s="8" t="str">
+        <f>IF(Q$4="","",ABS(Q7/Q$4))</f>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="12"/>
-      <c r="B26" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C26" s="101">
-        <f t="shared" si="9"/>
-        <v>2.4496276203067853E-3</v>
+      <c r="B26" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="102">
+        <f>ABS(C8/C$4)</f>
+        <v>0.11664383553220437</v>
       </c>
       <c r="D26" s="30"/>
       <c r="E26" s="86"/>
       <c r="F26" s="30"/>
-      <c r="G26" s="8">
-        <f t="shared" ref="G26:Q26" si="14">IF(G$4="","",ABS(G9/G$4))</f>
-        <v>1.9978517498607917E-3</v>
-      </c>
-      <c r="H26" s="8">
-        <f t="shared" si="14"/>
-        <v>1.0320722160014773E-3</v>
-      </c>
-      <c r="I26" s="8">
-        <f t="shared" si="14"/>
-        <v>5.4735115251124938E-3</v>
-      </c>
-      <c r="J26" s="8">
-        <f t="shared" si="14"/>
-        <v>3.8988481983809435E-3</v>
-      </c>
-      <c r="K26" s="8">
-        <f t="shared" si="14"/>
-        <v>5.6147664039083583E-3</v>
-      </c>
-      <c r="L26" s="8">
-        <f t="shared" si="14"/>
-        <v>2.1597113239037349E-3</v>
-      </c>
-      <c r="M26" s="8" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="N26" s="8" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O26" s="8" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="P26" s="8" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Q26" s="8" t="str">
-        <f t="shared" si="14"/>
+      <c r="G26" s="79">
+        <f>IF(G$4="","",ABS(G8/G$4))</f>
+        <v>0.12245710905455723</v>
+      </c>
+      <c r="H26" s="79">
+        <f>IF(H$4="","",ABS(H8/H$4))</f>
+        <v>0.11378358242100998</v>
+      </c>
+      <c r="I26" s="79">
+        <f>IF(I$4="","",ABS(I8/I$4))</f>
+        <v>0.12086725258551366</v>
+      </c>
+      <c r="J26" s="79">
+        <f>IF(J$4="","",ABS(J8/J$4))</f>
+        <v>0.10583450462035347</v>
+      </c>
+      <c r="K26" s="79">
+        <f>IF(K$4="","",ABS(K8/K$4))</f>
+        <v>0.10724519842891581</v>
+      </c>
+      <c r="L26" s="79">
+        <f>IF(L$4="","",ABS(L8/L$4))</f>
+        <v>0.10195889152515229</v>
+      </c>
+      <c r="M26" s="79" t="str">
+        <f>IF(M$4="","",ABS(M8/M$4))</f>
+        <v/>
+      </c>
+      <c r="N26" s="79" t="str">
+        <f>IF(N$4="","",ABS(N8/N$4))</f>
+        <v/>
+      </c>
+      <c r="O26" s="79" t="str">
+        <f>IF(O$4="","",ABS(O8/O$4))</f>
+        <v/>
+      </c>
+      <c r="P26" s="79" t="str">
+        <f>IF(P$4="","",ABS(P8/P$4))</f>
+        <v/>
+      </c>
+      <c r="Q26" s="79" t="str">
+        <f>IF(Q$4="","",ABS(Q8/Q$4))</f>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12"/>
       <c r="B27" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C27" s="101">
-        <f t="shared" si="9"/>
-        <v>2.7750800005147281E-2</v>
+        <f>ABS(C9/C$4)</f>
+        <v>2.4496276203067853E-3</v>
       </c>
       <c r="D27" s="30"/>
       <c r="E27" s="86"/>
       <c r="F27" s="30"/>
       <c r="G27" s="8">
-        <f t="shared" ref="G27:Q27" si="15">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>2.134717546604905E-2</v>
+        <f>IF(G$4="","",ABS(G9/G$4))</f>
+        <v>1.9978517498607917E-3</v>
       </c>
       <c r="H27" s="8">
-        <f t="shared" si="15"/>
-        <v>2.3431929819757211E-2</v>
+        <f>IF(H$4="","",ABS(H9/H$4))</f>
+        <v>1.0320722160014773E-3</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" si="15"/>
-        <v>2.4816909944731565E-2</v>
+        <f>IF(I$4="","",ABS(I9/I$4))</f>
+        <v>5.4735115251124938E-3</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" si="15"/>
-        <v>2.6666749423196391E-2</v>
+        <f>IF(J$4="","",ABS(J9/J$4))</f>
+        <v>3.8988481983809435E-3</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>IF(K$4="","",ABS(K9/K$4))</f>
+        <v>5.6147664039083583E-3</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f>IF(L$4="","",ABS(L9/L$4))</f>
+        <v>2.1597113239037349E-3</v>
       </c>
       <c r="M27" s="8" t="str">
-        <f t="shared" si="15"/>
+        <f>IF(M$4="","",ABS(M9/M$4))</f>
         <v/>
       </c>
       <c r="N27" s="8" t="str">
-        <f t="shared" si="15"/>
+        <f>IF(N$4="","",ABS(N9/N$4))</f>
         <v/>
       </c>
       <c r="O27" s="8" t="str">
-        <f t="shared" si="15"/>
+        <f>IF(O$4="","",ABS(O9/O$4))</f>
         <v/>
       </c>
       <c r="P27" s="8" t="str">
-        <f t="shared" si="15"/>
+        <f>IF(P$4="","",ABS(P9/P$4))</f>
         <v/>
       </c>
       <c r="Q27" s="8" t="str">
-        <f t="shared" si="15"/>
+        <f>IF(Q$4="","",ABS(Q9/Q$4))</f>
         <v/>
       </c>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12"/>
-      <c r="B28" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="C28" s="102">
-        <f t="shared" si="9"/>
-        <v>8.64434079067503E-2</v>
+      <c r="B28" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" s="101">
+        <f>ABS(C10/C$4)</f>
+        <v>2.7750800005147281E-2</v>
       </c>
       <c r="D28" s="30"/>
       <c r="E28" s="86"/>
       <c r="F28" s="30"/>
-      <c r="G28" s="79">
-        <f t="shared" ref="G28:Q28" si="16">IF(G$4="","",ABS(G11/G$4))</f>
-        <v>9.9112081838647392E-2</v>
-      </c>
-      <c r="H28" s="79">
-        <f t="shared" si="16"/>
-        <v>9.1383724817254264E-2</v>
-      </c>
-      <c r="I28" s="79">
-        <f t="shared" si="16"/>
-        <v>0.10152385416589459</v>
-      </c>
-      <c r="J28" s="79">
-        <f t="shared" si="16"/>
-        <v>8.3066603395538036E-2</v>
-      </c>
-      <c r="K28" s="79">
-        <f t="shared" si="16"/>
-        <v>0.10163043202500745</v>
-      </c>
-      <c r="L28" s="79">
-        <f t="shared" si="16"/>
-        <v>9.9799180201248547E-2</v>
-      </c>
-      <c r="M28" s="79" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="N28" s="79" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O28" s="79" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="P28" s="79" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="Q28" s="79" t="str">
-        <f t="shared" si="16"/>
+      <c r="G28" s="8">
+        <f>IF(G$4="","",ABS(G10/G$4))</f>
+        <v>2.134717546604905E-2</v>
+      </c>
+      <c r="H28" s="8">
+        <f>IF(H$4="","",ABS(H10/H$4))</f>
+        <v>2.3431929819757211E-2</v>
+      </c>
+      <c r="I28" s="8">
+        <f>IF(I$4="","",ABS(I10/I$4))</f>
+        <v>2.4816909944731565E-2</v>
+      </c>
+      <c r="J28" s="8">
+        <f>IF(J$4="","",ABS(J10/J$4))</f>
+        <v>2.6666749423196391E-2</v>
+      </c>
+      <c r="K28" s="8">
+        <f>IF(K$4="","",ABS(K10/K$4))</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="8">
+        <f>IF(L$4="","",ABS(L10/L$4))</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="8" t="str">
+        <f>IF(M$4="","",ABS(M10/M$4))</f>
+        <v/>
+      </c>
+      <c r="N28" s="8" t="str">
+        <f>IF(N$4="","",ABS(N10/N$4))</f>
+        <v/>
+      </c>
+      <c r="O28" s="8" t="str">
+        <f>IF(O$4="","",ABS(O10/O$4))</f>
+        <v/>
+      </c>
+      <c r="P28" s="8" t="str">
+        <f>IF(P$4="","",ABS(P10/P$4))</f>
+        <v/>
+      </c>
+      <c r="Q28" s="8" t="str">
+        <f>IF(Q$4="","",ABS(Q10/Q$4))</f>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12"/>
-      <c r="B29" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="C29" s="101">
-        <f t="shared" si="9"/>
-        <v>1.5214828438129381E-2</v>
+      <c r="B29" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="102">
+        <f>ABS(C11/C$4)</f>
+        <v>8.64434079067503E-2</v>
       </c>
       <c r="D29" s="30"/>
       <c r="E29" s="86"/>
       <c r="F29" s="30"/>
-      <c r="G29" s="8">
-        <f t="shared" ref="G29:Q29" si="17">IF(G$4="","",G12/G$4)</f>
-        <v>1.6202376072705908E-2</v>
-      </c>
-      <c r="H29" s="8">
-        <f t="shared" si="17"/>
-        <v>1.5877398303066895E-2</v>
-      </c>
-      <c r="I29" s="8">
-        <f t="shared" si="17"/>
-        <v>1.7098344553916948E-2</v>
-      </c>
-      <c r="J29" s="8">
-        <f t="shared" si="17"/>
-        <v>3.1739461379126283E-2</v>
-      </c>
-      <c r="K29" s="8">
-        <f t="shared" si="17"/>
-        <v>-2.4513406940554511E-2</v>
-      </c>
-      <c r="L29" s="8">
-        <f t="shared" si="17"/>
-        <v>-9.9799180201248547E-2</v>
-      </c>
-      <c r="M29" s="8" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="N29" s="8" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="O29" s="8" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="P29" s="8" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="Q29" s="8" t="str">
-        <f t="shared" si="17"/>
+      <c r="G29" s="79">
+        <f>IF(G$4="","",ABS(G11/G$4))</f>
+        <v>9.9112081838647392E-2</v>
+      </c>
+      <c r="H29" s="79">
+        <f>IF(H$4="","",ABS(H11/H$4))</f>
+        <v>9.1383724817254264E-2</v>
+      </c>
+      <c r="I29" s="79">
+        <f>IF(I$4="","",ABS(I11/I$4))</f>
+        <v>0.10152385416589459</v>
+      </c>
+      <c r="J29" s="79">
+        <f>IF(J$4="","",ABS(J11/J$4))</f>
+        <v>8.3066603395538036E-2</v>
+      </c>
+      <c r="K29" s="79">
+        <f>IF(K$4="","",ABS(K11/K$4))</f>
+        <v>0.10163043202500745</v>
+      </c>
+      <c r="L29" s="79">
+        <f>IF(L$4="","",ABS(L11/L$4))</f>
+        <v>9.9799180201248547E-2</v>
+      </c>
+      <c r="M29" s="79" t="str">
+        <f>IF(M$4="","",ABS(M11/M$4))</f>
+        <v/>
+      </c>
+      <c r="N29" s="79" t="str">
+        <f>IF(N$4="","",ABS(N11/N$4))</f>
+        <v/>
+      </c>
+      <c r="O29" s="79" t="str">
+        <f>IF(O$4="","",ABS(O11/O$4))</f>
+        <v/>
+      </c>
+      <c r="P29" s="79" t="str">
+        <f>IF(P$4="","",ABS(P11/P$4))</f>
+        <v/>
+      </c>
+      <c r="Q29" s="79" t="str">
+        <f>IF(Q$4="","",ABS(Q11/Q$4))</f>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12"/>
-      <c r="B30" s="2" t="s">
-        <v>155</v>
+      <c r="B30" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="C30" s="101">
-        <f t="shared" si="9"/>
-        <v>3.7075548852446252E-2</v>
+        <f>ABS(C19/C$4)</f>
+        <v>1.5214828438129381E-2</v>
       </c>
       <c r="D30" s="30"/>
       <c r="E30" s="86"/>
       <c r="F30" s="30"/>
       <c r="G30" s="8">
-        <f t="shared" ref="G30:Q30" si="18">IF(G$4="","",G13/G$4)</f>
-        <v>3.0237840861147901E-2</v>
+        <f>IF(G$4="","",G19/G$4)</f>
+        <v>1.6202376072705908E-2</v>
       </c>
       <c r="H30" s="8">
-        <f t="shared" si="18"/>
-        <v>3.1034299661942499E-2</v>
+        <f>IF(H$4="","",H19/H$4)</f>
+        <v>1.5877398303066895E-2</v>
       </c>
       <c r="I30" s="8">
-        <f t="shared" si="18"/>
-        <v>3.7116997107550703E-2</v>
+        <f>IF(I$4="","",I19/I$4)</f>
+        <v>1.7098344553916948E-2</v>
       </c>
       <c r="J30" s="8">
-        <f t="shared" si="18"/>
-        <v>5.8782113530297636E-2</v>
+        <f>IF(J$4="","",J19/J$4)</f>
+        <v>3.1739461379126283E-2</v>
       </c>
       <c r="K30" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>IF(K$4="","",K19/K$4)</f>
+        <v>-2.4513406940554511E-2</v>
       </c>
       <c r="L30" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>IF(L$4="","",L19/L$4)</f>
+        <v>-9.9799180201248547E-2</v>
       </c>
       <c r="M30" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(M$4="","",M19/M$4)</f>
         <v/>
       </c>
       <c r="N30" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(N$4="","",N19/N$4)</f>
         <v/>
       </c>
       <c r="O30" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(O$4="","",O19/O$4)</f>
         <v/>
       </c>
       <c r="P30" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(P$4="","",P19/P$4)</f>
         <v/>
       </c>
       <c r="Q30" s="8" t="str">
-        <f t="shared" si="18"/>
+        <f>IF(Q$4="","",Q19/Q$4)</f>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12"/>
       <c r="B31" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C31" s="118">
-        <f>MAX(AVERAGE(G31:J31),C30)</f>
+        <v>155</v>
+      </c>
+      <c r="C31" s="101">
+        <f>ABS(C12/C$4)</f>
         <v>3.7075548852446252E-2</v>
       </c>
       <c r="D31" s="30"/>
-      <c r="E31" s="83" t="s">
-        <v>191</v>
-      </c>
+      <c r="E31" s="86"/>
       <c r="F31" s="30"/>
       <c r="G31" s="8">
-        <f t="shared" ref="G31:Q31" si="19">IF(G$4="","",-G14/G$4)</f>
-        <v>4.413341231043115E-2</v>
+        <f t="shared" ref="G31:Q31" si="9">IF(G$4="","",G12/G$4)</f>
+        <v>3.0237840861147901E-2</v>
       </c>
       <c r="H31" s="8">
-        <f t="shared" si="19"/>
-        <v>8.9565367523571013E-3</v>
+        <f t="shared" si="9"/>
+        <v>3.1034299661942499E-2</v>
       </c>
       <c r="I31" s="8">
-        <f t="shared" si="19"/>
-        <v>3.8804791663312119E-2</v>
+        <f t="shared" si="9"/>
+        <v>3.7116997107550703E-2</v>
       </c>
       <c r="J31" s="8">
-        <f t="shared" si="19"/>
-        <v>1.5679014505150749E-2</v>
+        <f t="shared" si="9"/>
+        <v>5.8782113530297636E-2</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L31" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M31" s="8" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N31" s="8" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="O31" s="8" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P31" s="8" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q31" s="8" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12"/>
-      <c r="B32" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" s="118">
-        <f>MIN(AVERAGE(G32:J32)/2,0)</f>
-        <v>0</v>
+      <c r="B32" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C32" s="117">
+        <f>MAX(AVERAGE(G32:J32),C31)</f>
+        <v>3.7075548852446252E-2</v>
       </c>
       <c r="D32" s="30"/>
-      <c r="E32" s="86" t="s">
-        <v>190</v>
+      <c r="E32" s="83" t="s">
+        <v>191</v>
       </c>
       <c r="F32" s="30"/>
       <c r="G32" s="8">
-        <f t="shared" ref="G32:Q32" si="20">IF(G$4="","",-G17/G$4)</f>
-        <v>4.0883763120383568E-2</v>
+        <f t="shared" ref="G32:Q32" si="10">IF(G$4="","",-G13/G$4)</f>
+        <v>4.413341231043115E-2</v>
       </c>
       <c r="H32" s="8">
-        <f t="shared" si="20"/>
-        <v>2.9395857885609465E-2</v>
+        <f t="shared" si="10"/>
+        <v>8.9565367523571013E-3</v>
       </c>
       <c r="I32" s="8">
-        <f t="shared" si="20"/>
-        <v>8.9049969572670459E-2</v>
+        <f t="shared" si="10"/>
+        <v>3.8804791663312119E-2</v>
       </c>
       <c r="J32" s="8">
-        <f t="shared" si="20"/>
-        <v>-9.2387546571707307E-2</v>
+        <f t="shared" si="10"/>
+        <v>1.5679014505150749E-2</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L32" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M32" s="8" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="N32" s="8" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="O32" s="8" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="P32" s="8" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="Q32" s="8" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12"/>
-      <c r="B33" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="118">
-        <f>IF(BS!G29&lt;=0,0,BS!G29/BS!G30)</f>
+      <c r="B33" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="117">
+        <f>MIN(AVERAGE(G33:J33)/2,0)</f>
         <v>0</v>
       </c>
       <c r="D33" s="30"/>
-      <c r="E33" s="86"/>
+      <c r="E33" s="86" t="s">
+        <v>190</v>
+      </c>
       <c r="F33" s="30"/>
       <c r="G33" s="8">
-        <f t="shared" ref="G33:Q33" si="21">IF(G$4="","",-G15/G$4)</f>
-        <v>0</v>
+        <f t="shared" ref="G33:Q33" si="11">IF(G$4="","",-G16/G$4)</f>
+        <v>4.0883763120383568E-2</v>
       </c>
       <c r="H33" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2.9395857885609465E-2</v>
       </c>
       <c r="I33" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>8.9049969572670459E-2</v>
       </c>
       <c r="J33" s="8">
-        <f t="shared" si="21"/>
-        <v>2.0301681405792693E-4</v>
+        <f t="shared" si="11"/>
+        <v>-9.2387546571707307E-2</v>
       </c>
       <c r="K33" s="8">
-        <f t="shared" si="21"/>
-        <v>1.1901613447523543E-4</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="L33" s="8">
-        <f t="shared" si="21"/>
-        <v>6.8776840338486973E-4</v>
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="M33" s="8" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N33" s="8" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O33" s="8" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="P33" s="8" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q33" s="8" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
-      <c r="B34" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="C34" s="102">
-        <f>ABS(C19/C$4)</f>
-        <v>0.10165823634487968</v>
-      </c>
-      <c r="D34" s="99"/>
+      <c r="B34" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="117">
+        <f>IF(BS!G29&lt;=0,0,BS!G29/BS!G30)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="30"/>
       <c r="E34" s="86"/>
-      <c r="F34" s="99"/>
-      <c r="G34" s="79">
-        <f t="shared" ref="G34:Q34" si="22">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>6.0535123341686481E-2</v>
-      </c>
-      <c r="H34" s="79">
-        <f t="shared" si="22"/>
-        <v>9.9943028144297091E-2</v>
-      </c>
-      <c r="I34" s="79">
-        <f t="shared" si="22"/>
-        <v>2.7884434591379664E-2</v>
-      </c>
-      <c r="J34" s="79">
-        <f t="shared" si="22"/>
-        <v>0.25009369355746058</v>
-      </c>
-      <c r="K34" s="79">
-        <f t="shared" si="22"/>
-        <v>7.69980089499777E-2</v>
-      </c>
-      <c r="L34" s="79">
-        <f t="shared" si="22"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="8">
+        <f t="shared" ref="G34:Q34" si="12">IF(G$4="","",-G14/G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="8">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="8">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="8">
+        <f t="shared" si="12"/>
+        <v>2.0301681405792693E-4</v>
+      </c>
+      <c r="K34" s="8">
+        <f t="shared" si="12"/>
+        <v>1.1901613447523543E-4</v>
+      </c>
+      <c r="L34" s="8">
+        <f t="shared" si="12"/>
         <v>6.8776840338486973E-4</v>
       </c>
-      <c r="M34" s="79" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="N34" s="79" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="O34" s="79" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="P34" s="79" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="Q34" s="79" t="str">
-        <f t="shared" si="22"/>
+      <c r="M34" s="8" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="N34" s="8" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="O34" s="8" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P34" s="8" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="Q34" s="8" t="str">
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12"/>
-      <c r="B35" s="93" t="s">
-        <v>176</v>
-      </c>
-      <c r="C35" s="74"/>
-      <c r="D35" s="30"/>
+      <c r="B35" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" s="102">
+        <f>ABS(C20/C$4)</f>
+        <v>0.10165823634487968</v>
+      </c>
+      <c r="D35" s="99"/>
       <c r="E35" s="86"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-      <c r="P35" s="14"/>
-      <c r="Q35" s="14"/>
+      <c r="F35" s="99"/>
+      <c r="G35" s="79">
+        <f t="shared" ref="G35:Q35" si="13">IF(G$4="","",ABS(G20/G$4))</f>
+        <v>6.0535123341686481E-2</v>
+      </c>
+      <c r="H35" s="79">
+        <f t="shared" si="13"/>
+        <v>9.9943028144297091E-2</v>
+      </c>
+      <c r="I35" s="79">
+        <f t="shared" si="13"/>
+        <v>2.7884434591379664E-2</v>
+      </c>
+      <c r="J35" s="79">
+        <f t="shared" si="13"/>
+        <v>0.25009369355746058</v>
+      </c>
+      <c r="K35" s="79">
+        <f t="shared" si="13"/>
+        <v>7.69980089499777E-2</v>
+      </c>
+      <c r="L35" s="79">
+        <f t="shared" si="13"/>
+        <v>6.8776840338486973E-4</v>
+      </c>
+      <c r="M35" s="79" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="N35" s="79" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="O35" s="79" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="P35" s="79" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Q35" s="79" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12"/>
-      <c r="B36" s="134" t="s">
-        <v>187</v>
+      <c r="B36" s="93" t="s">
+        <v>176</v>
       </c>
       <c r="C36" s="74"/>
       <c r="D36" s="30"/>
@@ -6764,604 +6844,565 @@
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
-      <c r="B37" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="C37" s="75">
-        <f>MAX(G37:J37)</f>
-        <v>0.24301407674334419</v>
-      </c>
+      <c r="B37" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="C37" s="74"/>
       <c r="D37" s="30"/>
-      <c r="E37" s="86" t="s">
-        <v>175</v>
-      </c>
+      <c r="E37" s="86"/>
       <c r="F37" s="30"/>
-      <c r="G37" s="8">
-        <f t="shared" ref="G37:Q37" si="23">IF(G$4="","",-G10/(G8+G9))</f>
-        <v>0.17721490189875819</v>
-      </c>
-      <c r="H37" s="8">
-        <f t="shared" si="23"/>
-        <v>0.20408305726111148</v>
-      </c>
-      <c r="I37" s="8">
-        <f t="shared" si="23"/>
-        <v>0.19642836672256828</v>
-      </c>
-      <c r="J37" s="8">
-        <f t="shared" si="23"/>
-        <v>0.24301407674334419</v>
-      </c>
-      <c r="K37" s="8">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="L37" s="8">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="M37" s="8" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="N37" s="8" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="O37" s="8" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="P37" s="8" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="Q37" s="8" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12"/>
       <c r="B38" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="C38" s="101">
-        <f>C19*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.15660570294536932</v>
+        <v>177</v>
+      </c>
+      <c r="C38" s="75">
+        <f>MAX(G38:J38)</f>
+        <v>0.24301407674334419</v>
       </c>
       <c r="D38" s="30"/>
-      <c r="E38" s="86"/>
+      <c r="E38" s="86" t="s">
+        <v>175</v>
+      </c>
       <c r="F38" s="30"/>
-      <c r="G38" s="101">
-        <f t="shared" ref="G38:Q38" si="24">IF(G$4="","",G19*$C$3/(Market_Price*Common_Shares))</f>
-        <v>0.11434291133965122</v>
-      </c>
-      <c r="H38" s="101">
-        <f t="shared" si="24"/>
-        <v>0.14753845325188886</v>
-      </c>
-      <c r="I38" s="101">
-        <f t="shared" si="24"/>
-        <v>4.0338777168737266E-2</v>
-      </c>
-      <c r="J38" s="101">
-        <f t="shared" si="24"/>
-        <v>0.27313412617514549</v>
-      </c>
-      <c r="K38" s="101">
-        <f t="shared" si="24"/>
-        <v>0.10660538217872187</v>
-      </c>
-      <c r="L38" s="101">
-        <f t="shared" si="24"/>
-        <v>-1.3443711964992151E-3</v>
-      </c>
-      <c r="M38" s="101" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="N38" s="101" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="O38" s="101" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="P38" s="101" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="Q38" s="101" t="str">
-        <f t="shared" si="24"/>
+      <c r="G38" s="8">
+        <f>IF(G$4="","",-G10/(G8+G9))</f>
+        <v>0.17721490189875819</v>
+      </c>
+      <c r="H38" s="8">
+        <f>IF(H$4="","",-H10/(H8+H9))</f>
+        <v>0.20408305726111148</v>
+      </c>
+      <c r="I38" s="8">
+        <f>IF(I$4="","",-I10/(I8+I9))</f>
+        <v>0.19642836672256828</v>
+      </c>
+      <c r="J38" s="8">
+        <f>IF(J$4="","",-J10/(J8+J9))</f>
+        <v>0.24301407674334419</v>
+      </c>
+      <c r="K38" s="8">
+        <f>IF(K$4="","",-K10/(K8+K9))</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="8">
+        <f>IF(L$4="","",-L10/(L8+L9))</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="8" t="str">
+        <f>IF(M$4="","",-M10/(M8+M9))</f>
+        <v/>
+      </c>
+      <c r="N38" s="8" t="str">
+        <f>IF(N$4="","",-N10/(N8+N9))</f>
+        <v/>
+      </c>
+      <c r="O38" s="8" t="str">
+        <f>IF(O$4="","",-O10/(O8+O9))</f>
+        <v/>
+      </c>
+      <c r="P38" s="8" t="str">
+        <f>IF(P$4="","",-P10/(P8+P9))</f>
+        <v/>
+      </c>
+      <c r="Q38" s="8" t="str">
+        <f>IF(Q$4="","",-Q10/(Q8+Q9))</f>
         <v/>
       </c>
     </row>
     <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="74"/>
+      <c r="B39" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="C39" s="101">
+        <f>C20*$C$3/(Market_Price*Common_Shares)</f>
+        <v>0.13802875093781916</v>
+      </c>
       <c r="D39" s="30"/>
       <c r="E39" s="86"/>
       <c r="F39" s="30"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="14"/>
-      <c r="O39" s="14"/>
-      <c r="P39" s="14"/>
-      <c r="Q39" s="14"/>
-    </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="G39" s="101">
+        <f t="shared" ref="G39:Q39" si="14">IF(G$4="","",G20*$C$3/(Market_Price*Common_Shares))</f>
+        <v>0.10077927517308544</v>
+      </c>
+      <c r="H39" s="101">
+        <f t="shared" si="14"/>
+        <v>0.13003708060848876</v>
+      </c>
+      <c r="I39" s="101">
+        <f t="shared" si="14"/>
+        <v>3.5553692632139609E-2</v>
+      </c>
+      <c r="J39" s="101">
+        <f t="shared" si="14"/>
+        <v>0.24073428722834889</v>
+      </c>
+      <c r="K39" s="101">
+        <f t="shared" si="14"/>
+        <v>9.3959590670276552E-2</v>
+      </c>
+      <c r="L39" s="101">
+        <f t="shared" si="14"/>
+        <v>-1.1848985928328542E-3</v>
+      </c>
+      <c r="M39" s="101" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="N39" s="101" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="O39" s="101" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="P39" s="101" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Q39" s="101" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12"/>
-      <c r="B40" s="61" t="s">
+      <c r="B40" s="30"/>
+      <c r="C40" s="74"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="86"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
+      <c r="P40" s="14"/>
+      <c r="Q40" s="14"/>
+    </row>
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A41" s="12"/>
+      <c r="B41" s="61" t="s">
         <v>157</v>
       </c>
-      <c r="C40" s="61"/>
-      <c r="D40" s="63"/>
-      <c r="E40" s="81" t="s">
+      <c r="C41" s="61"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="81" t="s">
         <v>146</v>
       </c>
-      <c r="F40" s="63"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="40"/>
-      <c r="L40" s="40"/>
-      <c r="M40" s="40"/>
-      <c r="N40" s="40"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-    </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="12"/>
-      <c r="B41" s="78" t="s">
-        <v>150</v>
-      </c>
-      <c r="C41" s="74"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="86"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="14"/>
-      <c r="Q41" s="14"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12"/>
-      <c r="B42" s="30" t="s">
+      <c r="B42" s="78" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" s="74"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="86"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14"/>
+      <c r="P42" s="14"/>
+      <c r="Q42" s="14"/>
+    </row>
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="12"/>
+      <c r="B43" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C42" s="98">
-        <f>-C4*C50</f>
+      <c r="C43" s="98">
+        <f>-C4*C51</f>
         <v>-9031319.1044627018</v>
       </c>
-      <c r="D42" s="66"/>
-      <c r="E42" s="85"/>
-      <c r="F42" s="66"/>
-      <c r="G42" s="65">
+      <c r="D43" s="66"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="65">
         <f>Data!C33</f>
         <v>-11151623</v>
       </c>
-      <c r="H42" s="65">
+      <c r="H43" s="65">
         <f>Data!D33</f>
         <v>-8747447</v>
       </c>
-      <c r="I42" s="65">
+      <c r="I43" s="65">
         <f>Data!E33</f>
         <v>-8503976</v>
       </c>
-      <c r="J42" s="65">
+      <c r="J43" s="65">
         <f>Data!F33</f>
         <v>-6229020</v>
       </c>
-      <c r="K42" s="65">
+      <c r="K43" s="65">
         <f>Data!G33</f>
         <v>-7910751</v>
       </c>
-      <c r="L42" s="65">
+      <c r="L43" s="65">
         <f>Data!H33</f>
         <v>-11826154</v>
       </c>
-      <c r="M42" s="65" t="str">
+      <c r="M43" s="65" t="str">
         <f>Data!I33</f>
         <v/>
       </c>
-      <c r="N42" s="65" t="str">
+      <c r="N43" s="65" t="str">
         <f>Data!J33</f>
         <v/>
       </c>
-      <c r="O42" s="65" t="str">
+      <c r="O43" s="65" t="str">
         <f>Data!K33</f>
         <v/>
       </c>
-      <c r="P42" s="65" t="str">
+      <c r="P43" s="65" t="str">
         <f>Data!L33</f>
         <v/>
       </c>
-      <c r="Q42" s="65" t="str">
+      <c r="Q43" s="65" t="str">
         <f>Data!M33</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="12"/>
-      <c r="B43" s="87" t="s">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="12"/>
+      <c r="B44" s="87" t="s">
         <v>149</v>
       </c>
-      <c r="C43" s="77">
-        <f>-C4*C51</f>
+      <c r="C44" s="77">
+        <f>-C4*C52</f>
         <v>-1707788.5916244236</v>
       </c>
-      <c r="D43" s="30"/>
-      <c r="E43" s="86"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="65">
+      <c r="D44" s="30"/>
+      <c r="E44" s="86"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="65">
         <f>Data!C36</f>
         <v>-2043459</v>
       </c>
-      <c r="H43" s="65">
+      <c r="H44" s="65">
         <f>Data!D36</f>
         <v>-1517989</v>
       </c>
-      <c r="I43" s="65">
+      <c r="I44" s="65">
         <f>Data!E36</f>
         <v>-1491293</v>
       </c>
-      <c r="J43" s="65">
+      <c r="J44" s="65">
         <f>Data!F36</f>
         <v>-1412494</v>
       </c>
-      <c r="K43" s="65">
+      <c r="K44" s="65">
         <f>Data!G36</f>
         <v>0</v>
       </c>
-      <c r="L43" s="65">
+      <c r="L44" s="65">
         <f>Data!H36</f>
         <v>0</v>
       </c>
-      <c r="M43" s="65" t="str">
+      <c r="M44" s="65" t="str">
         <f>Data!I36</f>
         <v/>
       </c>
-      <c r="N43" s="65" t="str">
+      <c r="N44" s="65" t="str">
         <f>Data!J36</f>
         <v/>
       </c>
-      <c r="O43" s="65" t="str">
+      <c r="O44" s="65" t="str">
         <f>Data!K36</f>
         <v/>
       </c>
-      <c r="P43" s="65" t="str">
+      <c r="P44" s="65" t="str">
         <f>Data!L36</f>
         <v/>
       </c>
-      <c r="Q43" s="65" t="str">
+      <c r="Q44" s="65" t="str">
         <f>Data!M36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="12"/>
-      <c r="B44" s="91" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" s="80">
-        <f>C42+C43</f>
-        <v>-10739107.696087126</v>
-      </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="82"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="80">
-        <f>IF(G$4="","",G42+G43)</f>
-        <v>-13195082</v>
-      </c>
-      <c r="H44" s="80">
-        <f t="shared" ref="H44:Q44" si="25">IF(H$4="","",H42+H43)</f>
-        <v>-10265436</v>
-      </c>
-      <c r="I44" s="80">
-        <f t="shared" si="25"/>
-        <v>-9995269</v>
-      </c>
-      <c r="J44" s="80">
-        <f t="shared" si="25"/>
-        <v>-7641514</v>
-      </c>
-      <c r="K44" s="80">
-        <f t="shared" si="25"/>
-        <v>-7910751</v>
-      </c>
-      <c r="L44" s="80">
-        <f t="shared" si="25"/>
-        <v>-11826154</v>
-      </c>
-      <c r="M44" s="80" t="str">
-        <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="N44" s="80" t="str">
-        <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="O44" s="80" t="str">
-        <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="P44" s="80" t="str">
-        <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="Q44" s="80" t="str">
-        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="12"/>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="91" t="s">
+        <v>80</v>
+      </c>
+      <c r="C45" s="80">
+        <f>C43+C44</f>
+        <v>-10739107.696087126</v>
+      </c>
+      <c r="D45" s="11"/>
+      <c r="E45" s="82"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="80">
+        <f>IF(G$4="","",G43+G44)</f>
+        <v>-13195082</v>
+      </c>
+      <c r="H45" s="80">
+        <f t="shared" ref="H45:Q45" si="15">IF(H$4="","",H43+H44)</f>
+        <v>-10265436</v>
+      </c>
+      <c r="I45" s="80">
+        <f t="shared" si="15"/>
+        <v>-9995269</v>
+      </c>
+      <c r="J45" s="80">
+        <f t="shared" si="15"/>
+        <v>-7641514</v>
+      </c>
+      <c r="K45" s="80">
+        <f t="shared" si="15"/>
+        <v>-7910751</v>
+      </c>
+      <c r="L45" s="80">
+        <f t="shared" si="15"/>
+        <v>-11826154</v>
+      </c>
+      <c r="M45" s="80" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="N45" s="80" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="O45" s="80" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="P45" s="80" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="Q45" s="80" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="12"/>
+      <c r="B46" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C45" s="97">
-        <f>AVERAGE(G45:J45)</f>
+      <c r="C46" s="97">
+        <f>AVERAGE(G46:J46)</f>
         <v>-302359.25</v>
       </c>
-      <c r="E45" s="83" t="s">
+      <c r="E46" s="83" t="s">
         <v>192</v>
       </c>
-      <c r="G45" s="77">
+      <c r="G46" s="77">
         <f>Data!C37</f>
         <v>-254107</v>
       </c>
-      <c r="H45" s="77">
+      <c r="H46" s="77">
         <f>Data!D37</f>
         <v>-349526</v>
       </c>
-      <c r="I45" s="77">
+      <c r="I46" s="77">
         <f>Data!E37</f>
         <v>-323818</v>
       </c>
-      <c r="J45" s="77">
+      <c r="J46" s="77">
         <f>Data!F37</f>
         <v>-281986</v>
       </c>
-      <c r="K45" s="77">
+      <c r="K46" s="77">
         <f>Data!G37</f>
         <v>-2118252</v>
       </c>
-      <c r="L45" s="77">
+      <c r="L46" s="77">
         <f>Data!H37</f>
         <v>-2416769</v>
       </c>
-      <c r="M45" s="77" t="str">
+      <c r="M46" s="77" t="str">
         <f>Data!I37</f>
         <v/>
       </c>
-      <c r="N45" s="77" t="str">
+      <c r="N46" s="77" t="str">
         <f>Data!J37</f>
         <v/>
       </c>
-      <c r="O45" s="77" t="str">
+      <c r="O46" s="77" t="str">
         <f>Data!K37</f>
         <v/>
       </c>
-      <c r="P45" s="77" t="str">
+      <c r="P46" s="77" t="str">
         <f>Data!L37</f>
         <v/>
       </c>
-      <c r="Q45" s="77" t="str">
+      <c r="Q46" s="77" t="str">
         <f>Data!M37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="12"/>
-      <c r="B46" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C46" s="97">
-        <f>AVERAGE(G46:J46)</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="66"/>
-      <c r="E46" s="83" t="s">
-        <v>192</v>
-      </c>
-      <c r="F46" s="66"/>
-      <c r="G46" s="65">
-        <f>Data!C38</f>
-        <v>0</v>
-      </c>
-      <c r="H46" s="65">
-        <f>Data!D38</f>
-        <v>0</v>
-      </c>
-      <c r="I46" s="65">
-        <f>Data!E38</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="65">
-        <f>Data!F38</f>
-        <v>0</v>
-      </c>
-      <c r="K46" s="65">
-        <f>Data!G38</f>
-        <v>0</v>
-      </c>
-      <c r="L46" s="65">
-        <f>Data!H38</f>
-        <v>0</v>
-      </c>
-      <c r="M46" s="65" t="str">
-        <f>Data!I38</f>
-        <v/>
-      </c>
-      <c r="N46" s="65" t="str">
-        <f>Data!J38</f>
-        <v/>
-      </c>
-      <c r="O46" s="65" t="str">
-        <f>Data!K38</f>
-        <v/>
-      </c>
-      <c r="P46" s="65" t="str">
-        <f>Data!L38</f>
-        <v/>
-      </c>
-      <c r="Q46" s="65" t="str">
-        <f>Data!M38</f>
         <v/>
       </c>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="12"/>
-      <c r="B47" s="91" t="s">
-        <v>79</v>
-      </c>
-      <c r="C47" s="80">
-        <f>C45+C46</f>
-        <v>-302359.25</v>
+      <c r="B47" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="97">
+        <f>AVERAGE(G47:J47)</f>
+        <v>0</v>
       </c>
       <c r="D47" s="66"/>
-      <c r="E47" s="85"/>
+      <c r="E47" s="83" t="s">
+        <v>192</v>
+      </c>
       <c r="F47" s="66"/>
-      <c r="G47" s="80">
-        <f t="shared" ref="G47:Q47" si="26">IF(G4="","",G45+G46)</f>
-        <v>-254107</v>
-      </c>
-      <c r="H47" s="80">
-        <f t="shared" si="26"/>
-        <v>-349526</v>
-      </c>
-      <c r="I47" s="80">
-        <f t="shared" si="26"/>
-        <v>-323818</v>
-      </c>
-      <c r="J47" s="80">
-        <f t="shared" si="26"/>
-        <v>-281986</v>
-      </c>
-      <c r="K47" s="80">
-        <f t="shared" si="26"/>
-        <v>-2118252</v>
-      </c>
-      <c r="L47" s="80">
-        <f t="shared" si="26"/>
-        <v>-2416769</v>
-      </c>
-      <c r="M47" s="80" t="str">
-        <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="N47" s="80" t="str">
-        <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="O47" s="80" t="str">
-        <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="P47" s="80" t="str">
-        <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="Q47" s="80" t="str">
-        <f t="shared" si="26"/>
+      <c r="G47" s="65">
+        <f>Data!C38</f>
+        <v>0</v>
+      </c>
+      <c r="H47" s="65">
+        <f>Data!D38</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="65">
+        <f>Data!E38</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="65">
+        <f>Data!F38</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="65">
+        <f>Data!G38</f>
+        <v>0</v>
+      </c>
+      <c r="L47" s="65">
+        <f>Data!H38</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="65" t="str">
+        <f>Data!I38</f>
+        <v/>
+      </c>
+      <c r="N47" s="65" t="str">
+        <f>Data!J38</f>
+        <v/>
+      </c>
+      <c r="O47" s="65" t="str">
+        <f>Data!K38</f>
+        <v/>
+      </c>
+      <c r="P47" s="65" t="str">
+        <f>Data!L38</f>
+        <v/>
+      </c>
+      <c r="Q47" s="65" t="str">
+        <f>Data!M38</f>
         <v/>
       </c>
     </row>
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="12"/>
+      <c r="B48" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" s="80">
+        <f>C46+C47</f>
+        <v>-302359.25</v>
+      </c>
+      <c r="D48" s="66"/>
+      <c r="E48" s="85"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="80">
+        <f>IF(G4="","",G46+G47)</f>
+        <v>-254107</v>
+      </c>
+      <c r="H48" s="80">
+        <f>IF(H4="","",H46+H47)</f>
+        <v>-349526</v>
+      </c>
+      <c r="I48" s="80">
+        <f>IF(I4="","",I46+I47)</f>
+        <v>-323818</v>
+      </c>
+      <c r="J48" s="80">
+        <f>IF(J4="","",J46+J47)</f>
+        <v>-281986</v>
+      </c>
+      <c r="K48" s="80">
+        <f>IF(K4="","",K46+K47)</f>
+        <v>-2118252</v>
+      </c>
+      <c r="L48" s="80">
+        <f>IF(L4="","",L46+L47)</f>
+        <v>-2416769</v>
+      </c>
+      <c r="M48" s="80" t="str">
+        <f>IF(M4="","",M46+M47)</f>
+        <v/>
+      </c>
+      <c r="N48" s="80" t="str">
+        <f>IF(N4="","",N46+N47)</f>
+        <v/>
+      </c>
+      <c r="O48" s="80" t="str">
+        <f>IF(O4="","",O46+O47)</f>
+        <v/>
+      </c>
+      <c r="P48" s="80" t="str">
+        <f>IF(P4="","",P46+P47)</f>
+        <v/>
+      </c>
+      <c r="Q48" s="80" t="str">
+        <f>IF(Q4="","",Q46+Q47)</f>
+        <v/>
+      </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="12"/>
-      <c r="B49" s="93" t="s">
-        <v>154</v>
-      </c>
     </row>
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
-      <c r="B50" s="29" t="s">
+      <c r="B50" s="93" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="12"/>
+      <c r="B51" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="C50" s="75">
-        <f>AVERAGE(G50:L50)</f>
+      <c r="C51" s="75">
+        <f>AVERAGE(G51:L51)</f>
         <v>0.72253727182782512</v>
-      </c>
-      <c r="D50" s="29"/>
-      <c r="E50" s="83" t="s">
-        <v>192</v>
-      </c>
-      <c r="F50" s="29"/>
-      <c r="G50" s="15">
-        <f>IF(G$4="","",ABS(G42/G$4))</f>
-        <v>0.72762956087193742</v>
-      </c>
-      <c r="H50" s="15">
-        <f t="shared" ref="H50:Q50" si="27">IF(H$4="","",ABS(H42/H$4))</f>
-        <v>0.7303022981431383</v>
-      </c>
-      <c r="I50" s="15">
-        <f t="shared" si="27"/>
-        <v>0.7244946946204498</v>
-      </c>
-      <c r="J50" s="15">
-        <f t="shared" si="27"/>
-        <v>0.70294374380383995</v>
-      </c>
-      <c r="K50" s="15">
-        <f t="shared" si="27"/>
-        <v>0.70419372087965826</v>
-      </c>
-      <c r="L50" s="15">
-        <f t="shared" si="27"/>
-        <v>0.74565961264792724</v>
-      </c>
-      <c r="M50" s="15" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="N50" s="15" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="O50" s="15" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="P50" s="15" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="Q50" s="15" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="12"/>
-      <c r="B51" s="87" t="str">
-        <f>B43</f>
-        <v>Selling Expenses</v>
-      </c>
-      <c r="C51" s="75">
-        <f>AVERAGE(G51:J51)</f>
-        <v>0.13662908990130354</v>
       </c>
       <c r="D51" s="29"/>
       <c r="E51" s="83" t="s">
@@ -7369,786 +7410,825 @@
       </c>
       <c r="F51" s="29"/>
       <c r="G51" s="15">
-        <f t="shared" ref="G51:G55" si="28">IF(G$4="","",ABS(G43/G$4))</f>
+        <f>IF(G$4="","",ABS(G43/G$4))</f>
+        <v>0.72762956087193742</v>
+      </c>
+      <c r="H51" s="15">
+        <f t="shared" ref="H51:Q51" si="16">IF(H$4="","",ABS(H43/H$4))</f>
+        <v>0.7303022981431383</v>
+      </c>
+      <c r="I51" s="15">
+        <f t="shared" si="16"/>
+        <v>0.7244946946204498</v>
+      </c>
+      <c r="J51" s="15">
+        <f t="shared" si="16"/>
+        <v>0.70294374380383995</v>
+      </c>
+      <c r="K51" s="15">
+        <f t="shared" si="16"/>
+        <v>0.70419372087965826</v>
+      </c>
+      <c r="L51" s="15">
+        <f t="shared" si="16"/>
+        <v>0.74565961264792724</v>
+      </c>
+      <c r="M51" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="N51" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="O51" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="P51" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Q51" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="12"/>
+      <c r="B52" s="87" t="str">
+        <f>B44</f>
+        <v>Selling Expenses</v>
+      </c>
+      <c r="C52" s="75">
+        <f>AVERAGE(G52:J52)</f>
+        <v>0.13662908990130354</v>
+      </c>
+      <c r="D52" s="29"/>
+      <c r="E52" s="83" t="s">
+        <v>192</v>
+      </c>
+      <c r="F52" s="29"/>
+      <c r="G52" s="15">
+        <f t="shared" ref="G52:G56" si="17">IF(G$4="","",ABS(G44/G$4))</f>
         <v>0.13333316368656009</v>
       </c>
-      <c r="H51" s="15">
-        <f t="shared" ref="H51:Q51" si="29">IF(H$4="","",ABS(H43/H$4))</f>
+      <c r="H52" s="15">
+        <f t="shared" ref="H52:Q52" si="18">IF(H$4="","",ABS(H44/H$4))</f>
         <v>0.12673307483383486</v>
       </c>
-      <c r="I51" s="15">
-        <f t="shared" si="29"/>
+      <c r="I52" s="15">
+        <f t="shared" si="18"/>
         <v>0.12705043695144655</v>
       </c>
-      <c r="J51" s="15">
-        <f t="shared" si="29"/>
+      <c r="J52" s="15">
+        <f t="shared" si="18"/>
         <v>0.15939968413337269</v>
       </c>
-      <c r="K51" s="15">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="L51" s="15">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="M51" s="15" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="N51" s="15" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="O51" s="15" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="P51" s="15" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="Q51" s="15" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="12"/>
-      <c r="B52" s="91" t="s">
-        <v>80</v>
-      </c>
-      <c r="C52" s="92">
-        <f>ABS(C44/$C$4)</f>
-        <v>0.85916636172912864</v>
-      </c>
-      <c r="G52" s="33">
-        <f t="shared" si="28"/>
-        <v>0.86096272455849754</v>
-      </c>
-      <c r="H52" s="33">
-        <f t="shared" ref="H52:Q52" si="30">IF(H$4="","",ABS(H44/H$4))</f>
-        <v>0.85703537297697319</v>
-      </c>
-      <c r="I52" s="33">
-        <f t="shared" si="30"/>
-        <v>0.85154513157189637</v>
-      </c>
-      <c r="J52" s="33">
-        <f t="shared" si="30"/>
-        <v>0.86234342793721264</v>
-      </c>
-      <c r="K52" s="33">
-        <f t="shared" si="30"/>
-        <v>0.70419372087965826</v>
-      </c>
-      <c r="L52" s="33">
-        <f t="shared" si="30"/>
-        <v>0.74565961264792724</v>
-      </c>
-      <c r="M52" s="33" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="N52" s="33" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="O52" s="33" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="P52" s="33" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="Q52" s="33" t="str">
-        <f t="shared" si="30"/>
+      <c r="K52" s="15">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="L52" s="15">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="M52" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="N52" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="O52" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="P52" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="Q52" s="15" t="str">
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="12"/>
-      <c r="B53" s="2" t="str">
-        <f>B45</f>
-        <v>Other Opex (Fixed Overhead)</v>
-      </c>
-      <c r="C53" s="26">
-        <f t="shared" ref="C53:C55" si="31">ABS(C45/$C$4)</f>
-        <v>2.4189802738666985E-2</v>
-      </c>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="15">
-        <f t="shared" si="28"/>
-        <v>1.6580166386945237E-2</v>
-      </c>
-      <c r="H53" s="15">
-        <f t="shared" ref="H53:Q53" si="32">IF(H$4="","",ABS(H45/H$4))</f>
-        <v>2.9181044602016856E-2</v>
-      </c>
-      <c r="I53" s="15">
-        <f t="shared" si="32"/>
-        <v>2.7587615842589962E-2</v>
-      </c>
-      <c r="J53" s="15">
-        <f t="shared" si="32"/>
-        <v>3.1822067442433898E-2</v>
-      </c>
-      <c r="K53" s="15">
-        <f t="shared" si="32"/>
-        <v>0.18856108069142588</v>
-      </c>
-      <c r="L53" s="15">
-        <f t="shared" si="32"/>
-        <v>0.15238149582692045</v>
-      </c>
-      <c r="M53" s="15" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="N53" s="15" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O53" s="15" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="P53" s="15" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="Q53" s="15" t="str">
-        <f t="shared" si="32"/>
+      <c r="B53" s="91" t="s">
+        <v>80</v>
+      </c>
+      <c r="C53" s="92">
+        <f>ABS(C45/$C$4)</f>
+        <v>0.85916636172912864</v>
+      </c>
+      <c r="G53" s="33">
+        <f t="shared" si="17"/>
+        <v>0.86096272455849754</v>
+      </c>
+      <c r="H53" s="33">
+        <f t="shared" ref="H53:Q53" si="19">IF(H$4="","",ABS(H45/H$4))</f>
+        <v>0.85703537297697319</v>
+      </c>
+      <c r="I53" s="33">
+        <f t="shared" si="19"/>
+        <v>0.85154513157189637</v>
+      </c>
+      <c r="J53" s="33">
+        <f t="shared" si="19"/>
+        <v>0.86234342793721264</v>
+      </c>
+      <c r="K53" s="33">
+        <f t="shared" si="19"/>
+        <v>0.70419372087965826</v>
+      </c>
+      <c r="L53" s="33">
+        <f t="shared" si="19"/>
+        <v>0.74565961264792724</v>
+      </c>
+      <c r="M53" s="33" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="N53" s="33" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="O53" s="33" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="P53" s="33" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="Q53" s="33" t="str">
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="12"/>
-      <c r="B54" s="30" t="str">
+      <c r="B54" s="2" t="str">
         <f>B46</f>
-        <v>- R&amp;D</v>
+        <v>Other Opex (Fixed Overhead)</v>
       </c>
       <c r="C54" s="26">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f t="shared" ref="C54:C56" si="20">ABS(C46/$C$4)</f>
+        <v>2.4189802738666985E-2</v>
       </c>
       <c r="D54" s="30"/>
       <c r="E54" s="30"/>
       <c r="F54" s="30"/>
       <c r="G54" s="15">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="17"/>
+        <v>1.6580166386945237E-2</v>
       </c>
       <c r="H54" s="15">
-        <f t="shared" ref="H54:Q54" si="33">IF(H$4="","",ABS(H46/H$4))</f>
-        <v>0</v>
+        <f t="shared" ref="H54:Q54" si="21">IF(H$4="","",ABS(H46/H$4))</f>
+        <v>2.9181044602016856E-2</v>
       </c>
       <c r="I54" s="15">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>2.7587615842589962E-2</v>
       </c>
       <c r="J54" s="15">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>3.1822067442433898E-2</v>
       </c>
       <c r="K54" s="15">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>0.18856108069142588</v>
       </c>
       <c r="L54" s="15">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>0.15238149582692045</v>
       </c>
       <c r="M54" s="15" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N54" s="15" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="O54" s="15" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P54" s="15" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Q54" s="15" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="12"/>
-      <c r="B55" s="91" t="s">
-        <v>79</v>
-      </c>
-      <c r="C55" s="92">
-        <f t="shared" si="31"/>
-        <v>2.4189802738666985E-2</v>
-      </c>
-      <c r="G55" s="33">
-        <f t="shared" si="28"/>
-        <v>1.6580166386945237E-2</v>
-      </c>
-      <c r="H55" s="33">
-        <f t="shared" ref="H55:Q55" si="34">IF(H$4="","",ABS(H47/H$4))</f>
-        <v>2.9181044602016856E-2</v>
-      </c>
-      <c r="I55" s="33">
-        <f t="shared" si="34"/>
-        <v>2.7587615842589962E-2</v>
-      </c>
-      <c r="J55" s="33">
-        <f t="shared" si="34"/>
-        <v>3.1822067442433898E-2</v>
-      </c>
-      <c r="K55" s="33">
-        <f t="shared" si="34"/>
-        <v>0.18856108069142588</v>
-      </c>
-      <c r="L55" s="33">
-        <f t="shared" si="34"/>
-        <v>0.15238149582692045</v>
-      </c>
-      <c r="M55" s="33" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="N55" s="33" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="O55" s="33" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="P55" s="33" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="Q55" s="33" t="str">
-        <f t="shared" si="34"/>
+      <c r="B55" s="30" t="str">
+        <f>B47</f>
+        <v>- R&amp;D</v>
+      </c>
+      <c r="C55" s="26">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="15">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="H55" s="15">
+        <f t="shared" ref="H55:Q55" si="22">IF(H$4="","",ABS(H47/H$4))</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="15">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="15">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="15">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="15">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="M55" s="15" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="N55" s="15" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="O55" s="15" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="P55" s="15" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="Q55" s="15" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="12"/>
+      <c r="B56" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" s="92">
+        <f t="shared" si="20"/>
+        <v>2.4189802738666985E-2</v>
+      </c>
+      <c r="G56" s="33">
+        <f t="shared" si="17"/>
+        <v>1.6580166386945237E-2</v>
+      </c>
+      <c r="H56" s="33">
+        <f t="shared" ref="H56:Q56" si="23">IF(H$4="","",ABS(H48/H$4))</f>
+        <v>2.9181044602016856E-2</v>
+      </c>
+      <c r="I56" s="33">
+        <f t="shared" si="23"/>
+        <v>2.7587615842589962E-2</v>
+      </c>
+      <c r="J56" s="33">
+        <f t="shared" si="23"/>
+        <v>3.1822067442433898E-2</v>
+      </c>
+      <c r="K56" s="33">
+        <f t="shared" si="23"/>
+        <v>0.18856108069142588</v>
+      </c>
+      <c r="L56" s="33">
+        <f t="shared" si="23"/>
+        <v>0.15238149582692045</v>
+      </c>
+      <c r="M56" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N56" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="O56" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="P56" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="Q56" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="12"/>
-      <c r="B57" s="78" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="12"/>
-      <c r="B58" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C58" s="77">
-        <f>-BS!G27*BS!C40</f>
-        <v>-59596</v>
-      </c>
-      <c r="G58" s="77">
-        <f>Data!C41</f>
-        <v>-59596</v>
-      </c>
-      <c r="H58" s="77">
-        <f>Data!D41</f>
-        <v>-20763</v>
-      </c>
-      <c r="I58" s="77">
-        <f>Data!E41</f>
-        <v>-23097</v>
-      </c>
-      <c r="J58" s="77">
-        <f>Data!F41</f>
-        <v>-28849</v>
-      </c>
-      <c r="K58" s="77">
-        <f>Data!G41</f>
-        <v>-63075</v>
-      </c>
-      <c r="L58" s="77">
-        <f>Data!H41</f>
-        <v>-34253</v>
-      </c>
-      <c r="M58" s="77" t="str">
-        <f>Data!I41</f>
-        <v/>
-      </c>
-      <c r="N58" s="77" t="str">
-        <f>Data!J41</f>
-        <v/>
-      </c>
-      <c r="O58" s="77" t="str">
-        <f>Data!K41</f>
-        <v/>
-      </c>
-      <c r="P58" s="77" t="str">
-        <f>Data!L41</f>
-        <v/>
-      </c>
-      <c r="Q58" s="77" t="str">
-        <f>Data!M41</f>
-        <v/>
+      <c r="B58" s="78" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="12"/>
       <c r="B59" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" s="77">
+        <f>-BS!G27*BS!C40</f>
+        <v>-59596</v>
+      </c>
+      <c r="G59" s="77">
+        <f>Data!C41</f>
+        <v>-59596</v>
+      </c>
+      <c r="H59" s="77">
+        <f>Data!D41</f>
+        <v>-20763</v>
+      </c>
+      <c r="I59" s="77">
+        <f>Data!E41</f>
+        <v>-23097</v>
+      </c>
+      <c r="J59" s="77">
+        <f>Data!F41</f>
+        <v>-28849</v>
+      </c>
+      <c r="K59" s="77">
+        <f>Data!G41</f>
+        <v>-63075</v>
+      </c>
+      <c r="L59" s="77">
+        <f>Data!H41</f>
+        <v>-34253</v>
+      </c>
+      <c r="M59" s="77" t="str">
+        <f>Data!I41</f>
+        <v/>
+      </c>
+      <c r="N59" s="77" t="str">
+        <f>Data!J41</f>
+        <v/>
+      </c>
+      <c r="O59" s="77" t="str">
+        <f>Data!K41</f>
+        <v/>
+      </c>
+      <c r="P59" s="77" t="str">
+        <f>Data!L41</f>
+        <v/>
+      </c>
+      <c r="Q59" s="77" t="str">
+        <f>Data!M41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="12"/>
+      <c r="B60" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C59" s="77">
+      <c r="C60" s="77">
         <f>BS!$G$24*BS!C41</f>
         <v>28977</v>
       </c>
-      <c r="G59" s="77">
+      <c r="G60" s="77">
         <f>Data!C42</f>
         <v>28977</v>
       </c>
-      <c r="H59" s="77">
+      <c r="H60" s="77">
         <f>Data!D42</f>
         <v>33125</v>
       </c>
-      <c r="I59" s="77">
+      <c r="I60" s="77">
         <f>Data!E42</f>
         <v>87344</v>
       </c>
-      <c r="J59" s="77">
+      <c r="J60" s="77">
         <f>Data!F42</f>
         <v>63398</v>
       </c>
-      <c r="K59" s="77">
+      <c r="K60" s="77">
         <f>Data!G42</f>
         <v>0</v>
       </c>
-      <c r="L59" s="77">
+      <c r="L60" s="77">
         <f>Data!H42</f>
         <v>0</v>
       </c>
-      <c r="M59" s="77" t="str">
+      <c r="M60" s="77" t="str">
         <f>Data!I42</f>
         <v/>
       </c>
-      <c r="N59" s="77" t="str">
+      <c r="N60" s="77" t="str">
         <f>Data!J42</f>
         <v/>
       </c>
-      <c r="O59" s="77" t="str">
+      <c r="O60" s="77" t="str">
         <f>Data!K42</f>
         <v/>
       </c>
-      <c r="P59" s="77" t="str">
+      <c r="P60" s="77" t="str">
         <f>Data!L42</f>
         <v/>
       </c>
-      <c r="Q59" s="77" t="str">
+      <c r="Q60" s="77" t="str">
         <f>Data!M42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="12"/>
-      <c r="B60" s="91" t="s">
-        <v>159</v>
-      </c>
-      <c r="C60" s="80">
-        <f>C58+C59</f>
-        <v>-30619</v>
-      </c>
-      <c r="G60" s="80">
-        <f t="shared" ref="G60:Q60" si="35">IF(G4="","",G58+G59)</f>
-        <v>-30619</v>
-      </c>
-      <c r="H60" s="80">
-        <f t="shared" si="35"/>
-        <v>12362</v>
-      </c>
-      <c r="I60" s="80">
-        <f t="shared" si="35"/>
-        <v>64247</v>
-      </c>
-      <c r="J60" s="80">
-        <f t="shared" si="35"/>
-        <v>34549</v>
-      </c>
-      <c r="K60" s="80">
-        <f t="shared" si="35"/>
-        <v>-63075</v>
-      </c>
-      <c r="L60" s="80">
-        <f t="shared" si="35"/>
-        <v>-34253</v>
-      </c>
-      <c r="M60" s="80" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N60" s="80" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="O60" s="80" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="P60" s="80" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="Q60" s="80" t="str">
-        <f t="shared" si="35"/>
         <v/>
       </c>
     </row>
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="12"/>
-    </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A62" s="3"/>
-      <c r="B62" s="61" t="s">
+      <c r="B61" s="91" t="s">
+        <v>159</v>
+      </c>
+      <c r="C61" s="80">
+        <f>C59+C60</f>
+        <v>-30619</v>
+      </c>
+      <c r="G61" s="80">
+        <f>IF(G4="","",G59+G60)</f>
+        <v>-30619</v>
+      </c>
+      <c r="H61" s="80">
+        <f>IF(H4="","",H59+H60)</f>
+        <v>12362</v>
+      </c>
+      <c r="I61" s="80">
+        <f>IF(I4="","",I59+I60)</f>
+        <v>64247</v>
+      </c>
+      <c r="J61" s="80">
+        <f>IF(J4="","",J59+J60)</f>
+        <v>34549</v>
+      </c>
+      <c r="K61" s="80">
+        <f>IF(K4="","",K59+K60)</f>
+        <v>-63075</v>
+      </c>
+      <c r="L61" s="80">
+        <f>IF(L4="","",L59+L60)</f>
+        <v>-34253</v>
+      </c>
+      <c r="M61" s="80" t="str">
+        <f>IF(M4="","",M59+M60)</f>
+        <v/>
+      </c>
+      <c r="N61" s="80" t="str">
+        <f>IF(N4="","",N59+N60)</f>
+        <v/>
+      </c>
+      <c r="O61" s="80" t="str">
+        <f>IF(O4="","",O59+O60)</f>
+        <v/>
+      </c>
+      <c r="P61" s="80" t="str">
+        <f>IF(P4="","",P59+P60)</f>
+        <v/>
+      </c>
+      <c r="Q61" s="80" t="str">
+        <f>IF(Q4="","",Q59+Q60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="12"/>
+    </row>
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A63" s="3"/>
+      <c r="B63" s="61" t="s">
         <v>216</v>
       </c>
-      <c r="C62" s="61"/>
-      <c r="D62" s="63"/>
-      <c r="E62" s="81" t="s">
+      <c r="C63" s="61"/>
+      <c r="D63" s="63"/>
+      <c r="E63" s="81" t="s">
         <v>146</v>
       </c>
-      <c r="F62" s="63"/>
-      <c r="G62" s="40"/>
-      <c r="H62" s="40"/>
-      <c r="I62" s="40"/>
-      <c r="J62" s="40"/>
-      <c r="K62" s="40"/>
-      <c r="L62" s="40"/>
-      <c r="M62" s="40"/>
-      <c r="N62" s="40"/>
-      <c r="O62" s="40"/>
-      <c r="P62" s="40"/>
-      <c r="Q62" s="40"/>
-    </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="12"/>
-      <c r="B63" s="78" t="s">
-        <v>44</v>
-      </c>
+      <c r="F63" s="63"/>
+      <c r="G63" s="40"/>
+      <c r="H63" s="40"/>
+      <c r="I63" s="40"/>
+      <c r="J63" s="40"/>
+      <c r="K63" s="40"/>
+      <c r="L63" s="40"/>
+      <c r="M63" s="40"/>
+      <c r="N63" s="40"/>
+      <c r="O63" s="40"/>
+      <c r="P63" s="40"/>
+      <c r="Q63" s="40"/>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="12"/>
-      <c r="B64" s="29" t="s">
+      <c r="B64" s="78" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="12"/>
+      <c r="B65" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="129">
+      <c r="C65" s="128">
         <f>BS!G23</f>
         <v>16854064</v>
       </c>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="16">
-        <f t="shared" ref="G64:Q64" si="36">IF(G$4="","",G68+G67)</f>
+      <c r="D65" s="29"/>
+      <c r="E65" s="29"/>
+      <c r="F65" s="29"/>
+      <c r="G65" s="16">
+        <f t="shared" ref="G65:Q65" si="24">IF(G$4="","",G69+G68)</f>
         <v>16854064</v>
       </c>
-      <c r="H64" s="16">
-        <f t="shared" si="36"/>
+      <c r="H65" s="16">
+        <f t="shared" si="24"/>
         <v>14687373</v>
       </c>
-      <c r="I64" s="16">
-        <f t="shared" si="36"/>
+      <c r="I65" s="16">
+        <f t="shared" si="24"/>
         <v>15987114</v>
       </c>
-      <c r="J64" s="16">
-        <f t="shared" si="36"/>
+      <c r="J65" s="16">
+        <f t="shared" si="24"/>
         <v>14270996</v>
       </c>
-      <c r="K64" s="16">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="L64" s="16">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="M64" s="16" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="N64" s="16" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="O64" s="16" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P64" s="16" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="Q64" s="16" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="12"/>
-      <c r="B65" s="127" t="s">
+      <c r="K65" s="16">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="L65" s="16">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="M65" s="16" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="N65" s="16" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="O65" s="16" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="P65" s="16" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="Q65" s="16" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="12"/>
+      <c r="B66" s="126" t="s">
         <v>199</v>
       </c>
-      <c r="C65" s="130">
+      <c r="C66" s="129">
         <f>BS!C4</f>
         <v>265773</v>
       </c>
-      <c r="D65" s="119"/>
-      <c r="E65" s="119"/>
-      <c r="F65" s="119"/>
-      <c r="G65" s="131">
+      <c r="D66" s="118"/>
+      <c r="E66" s="118"/>
+      <c r="F66" s="118"/>
+      <c r="G66" s="130">
         <f>IF(G$4="","",Data!D64)</f>
         <v>213823</v>
       </c>
-      <c r="H65" s="131">
+      <c r="H66" s="130">
         <f>IF(H$4="","",Data!E64)</f>
         <v>187711</v>
       </c>
-      <c r="I65" s="131">
+      <c r="I66" s="130">
         <f>IF(I$4="","",Data!F64)</f>
         <v>277338</v>
       </c>
-      <c r="J65" s="131">
+      <c r="J66" s="130">
         <f>IF(J$4="","",Data!G64)</f>
         <v>0</v>
       </c>
-      <c r="K65" s="131">
+      <c r="K66" s="130">
         <f>IF(K$4="","",Data!H64)</f>
         <v>0</v>
       </c>
-      <c r="L65" s="131">
+      <c r="L66" s="130">
         <f>IF(L$4="","",Data!I64)</f>
         <v>0</v>
       </c>
-      <c r="M65" s="131" t="str">
+      <c r="M66" s="130" t="str">
         <f>IF(M$4="","",Data!J64)</f>
         <v/>
       </c>
-      <c r="N65" s="131" t="str">
+      <c r="N66" s="130" t="str">
         <f>IF(N$4="","",Data!K64)</f>
         <v/>
       </c>
-      <c r="O65" s="131" t="str">
+      <c r="O66" s="130" t="str">
         <f>IF(O$4="","",Data!L64)</f>
         <v/>
       </c>
-      <c r="P65" s="131" t="str">
+      <c r="P66" s="130" t="str">
         <f>IF(P$4="","",Data!M64)</f>
         <v/>
       </c>
-      <c r="Q65" s="131" t="str">
+      <c r="Q66" s="130" t="str">
         <f>IF(Q$4="","",Data!N64)</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="12"/>
-      <c r="B66" s="127" t="s">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="12"/>
+      <c r="B67" s="126" t="s">
         <v>200</v>
       </c>
-      <c r="C66" s="130">
+      <c r="C67" s="129">
         <f>BS!C7+BS!C8</f>
         <v>9672256</v>
       </c>
-      <c r="D66" s="119"/>
-      <c r="E66" s="119"/>
-      <c r="F66" s="119"/>
-      <c r="G66" s="131">
+      <c r="D67" s="118"/>
+      <c r="E67" s="118"/>
+      <c r="F67" s="118"/>
+      <c r="G67" s="130">
         <f>IF(G$4="","",Data!D65)</f>
         <v>8852611</v>
       </c>
-      <c r="H66" s="131">
+      <c r="H67" s="130">
         <f>IF(H$4="","",Data!E65)</f>
         <v>8769304</v>
       </c>
-      <c r="I66" s="131">
+      <c r="I67" s="130">
         <f>IF(I$4="","",Data!F65)</f>
         <v>7321614</v>
       </c>
-      <c r="J66" s="131">
+      <c r="J67" s="130">
         <f>IF(J$4="","",Data!G65)</f>
         <v>0</v>
       </c>
-      <c r="K66" s="131">
+      <c r="K67" s="130">
         <f>IF(K$4="","",Data!H65)</f>
         <v>0</v>
       </c>
-      <c r="L66" s="131">
+      <c r="L67" s="130">
         <f>IF(L$4="","",Data!I65)</f>
         <v>0</v>
       </c>
-      <c r="M66" s="131" t="str">
+      <c r="M67" s="130" t="str">
         <f>IF(M$4="","",Data!J65)</f>
         <v/>
       </c>
-      <c r="N66" s="131" t="str">
+      <c r="N67" s="130" t="str">
         <f>IF(N$4="","",Data!K65)</f>
         <v/>
       </c>
-      <c r="O66" s="131" t="str">
+      <c r="O67" s="130" t="str">
         <f>IF(O$4="","",Data!L65)</f>
         <v/>
       </c>
-      <c r="P66" s="131" t="str">
+      <c r="P67" s="130" t="str">
         <f>IF(P$4="","",Data!M65)</f>
         <v/>
       </c>
-      <c r="Q66" s="131" t="str">
+      <c r="Q67" s="130" t="str">
         <f>IF(Q$4="","",Data!N65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="12"/>
-      <c r="B67" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="C67" s="129">
-        <f>BS!G26</f>
-        <v>3990166</v>
-      </c>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="16">
-        <f>Data!C66</f>
-        <v>3990166</v>
-      </c>
-      <c r="H67" s="16">
-        <f>Data!D66</f>
-        <v>2466431</v>
-      </c>
-      <c r="I67" s="16">
-        <f>Data!E66</f>
-        <v>3908586</v>
-      </c>
-      <c r="J67" s="16">
-        <f>Data!F66</f>
-        <v>2946772</v>
-      </c>
-      <c r="K67" s="16">
-        <f>Data!G66</f>
-        <v>0</v>
-      </c>
-      <c r="L67" s="16">
-        <f>Data!H66</f>
-        <v>0</v>
-      </c>
-      <c r="M67" s="16" t="str">
-        <f>Data!I66</f>
-        <v/>
-      </c>
-      <c r="N67" s="16" t="str">
-        <f>Data!J66</f>
-        <v/>
-      </c>
-      <c r="O67" s="16" t="str">
-        <f>Data!K66</f>
-        <v/>
-      </c>
-      <c r="P67" s="16" t="str">
-        <f>Data!L66</f>
-        <v/>
-      </c>
-      <c r="Q67" s="16" t="str">
-        <f>Data!M66</f>
         <v/>
       </c>
     </row>
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
       <c r="B68" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C68" s="129">
-        <f>BS!G28</f>
-        <v>12863898</v>
+        <v>67</v>
+      </c>
+      <c r="C68" s="128">
+        <f>BS!G26</f>
+        <v>3990166</v>
       </c>
       <c r="D68" s="29"/>
       <c r="E68" s="29"/>
       <c r="F68" s="29"/>
       <c r="G68" s="16">
-        <f>Data!C67</f>
-        <v>12863898</v>
+        <f>Data!C66</f>
+        <v>3990166</v>
       </c>
       <c r="H68" s="16">
-        <f>Data!D67</f>
-        <v>12220942</v>
+        <f>Data!D66</f>
+        <v>2466431</v>
       </c>
       <c r="I68" s="16">
-        <f>Data!E67</f>
-        <v>12078528</v>
+        <f>Data!E66</f>
+        <v>3908586</v>
       </c>
       <c r="J68" s="16">
-        <f>Data!F67</f>
-        <v>11324224</v>
+        <f>Data!F66</f>
+        <v>2946772</v>
       </c>
       <c r="K68" s="16">
-        <f>Data!G67</f>
+        <f>Data!G66</f>
         <v>0</v>
       </c>
       <c r="L68" s="16">
-        <f>Data!H67</f>
+        <f>Data!H66</f>
         <v>0</v>
       </c>
       <c r="M68" s="16" t="str">
-        <f>Data!I67</f>
+        <f>Data!I66</f>
         <v/>
       </c>
       <c r="N68" s="16" t="str">
-        <f>Data!J67</f>
+        <f>Data!J66</f>
         <v/>
       </c>
       <c r="O68" s="16" t="str">
-        <f>Data!K67</f>
+        <f>Data!K66</f>
         <v/>
       </c>
       <c r="P68" s="16" t="str">
-        <f>Data!L67</f>
+        <f>Data!L66</f>
         <v/>
       </c>
       <c r="Q68" s="16" t="str">
-        <f>Data!M67</f>
+        <f>Data!M66</f>
         <v/>
       </c>
     </row>
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="12"/>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
+      <c r="B69" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69" s="128">
+        <f>BS!G28</f>
+        <v>12863898</v>
+      </c>
       <c r="D69" s="29"/>
       <c r="E69" s="29"/>
       <c r="F69" s="29"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="14"/>
-      <c r="L69" s="14"/>
-      <c r="M69" s="14"/>
-      <c r="N69" s="14"/>
-      <c r="O69" s="14"/>
-      <c r="P69" s="14"/>
-      <c r="Q69" s="14"/>
+      <c r="G69" s="16">
+        <f>Data!C67</f>
+        <v>12863898</v>
+      </c>
+      <c r="H69" s="16">
+        <f>Data!D67</f>
+        <v>12220942</v>
+      </c>
+      <c r="I69" s="16">
+        <f>Data!E67</f>
+        <v>12078528</v>
+      </c>
+      <c r="J69" s="16">
+        <f>Data!F67</f>
+        <v>11324224</v>
+      </c>
+      <c r="K69" s="16">
+        <f>Data!G67</f>
+        <v>0</v>
+      </c>
+      <c r="L69" s="16">
+        <f>Data!H67</f>
+        <v>0</v>
+      </c>
+      <c r="M69" s="16" t="str">
+        <f>Data!I67</f>
+        <v/>
+      </c>
+      <c r="N69" s="16" t="str">
+        <f>Data!J67</f>
+        <v/>
+      </c>
+      <c r="O69" s="16" t="str">
+        <f>Data!K67</f>
+        <v/>
+      </c>
+      <c r="P69" s="16" t="str">
+        <f>Data!L67</f>
+        <v/>
+      </c>
+      <c r="Q69" s="16" t="str">
+        <f>Data!M67</f>
+        <v/>
+      </c>
     </row>
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="12"/>
-      <c r="B70" s="122" t="s">
-        <v>76</v>
-      </c>
+      <c r="B70" s="29"/>
       <c r="C70" s="29"/>
       <c r="D70" s="29"/>
       <c r="E70" s="29"/>
@@ -8167,724 +8247,742 @@
     </row>
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="12"/>
-      <c r="B71" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="C71" s="132">
-        <f>C65/C$4</f>
-        <v>2.1262774144544083E-2</v>
-      </c>
+      <c r="B71" s="121" t="s">
+        <v>76</v>
+      </c>
+      <c r="C71" s="29"/>
       <c r="D71" s="29"/>
       <c r="E71" s="29"/>
       <c r="F71" s="29"/>
-      <c r="G71" s="132">
-        <f>IF(G$4="","",G65/G$4)</f>
-        <v>1.3951685381968192E-2</v>
-      </c>
-      <c r="H71" s="132">
-        <f t="shared" ref="H71:Q71" si="37">IF(H$4="","",H65/H$4)</f>
-        <v>1.5671518179732512E-2</v>
-      </c>
-      <c r="I71" s="132">
-        <f t="shared" si="37"/>
-        <v>2.3627760663558588E-2</v>
-      </c>
-      <c r="J71" s="132">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K71" s="132">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="L71" s="132">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="M71" s="132" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="N71" s="132" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="O71" s="132" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="P71" s="132" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="Q71" s="132" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
+      <c r="G71" s="16"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
+      <c r="L71" s="14"/>
+      <c r="M71" s="14"/>
+      <c r="N71" s="14"/>
+      <c r="O71" s="14"/>
+      <c r="P71" s="14"/>
+      <c r="Q71" s="14"/>
     </row>
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="12"/>
       <c r="B72" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="C72" s="132">
+        <v>201</v>
+      </c>
+      <c r="C72" s="131">
         <f>C66/C$4</f>
-        <v>0.7738144762493232</v>
+        <v>2.1262774144544083E-2</v>
       </c>
       <c r="D72" s="29"/>
       <c r="E72" s="29"/>
       <c r="F72" s="29"/>
-      <c r="G72" s="132">
+      <c r="G72" s="131">
         <f>IF(G$4="","",G66/G$4)</f>
-        <v>0.57762188109301071</v>
-      </c>
-      <c r="H72" s="132">
-        <f t="shared" ref="H72:Q72" si="38">IF(H$4="","",H66/H$4)</f>
-        <v>0.73212708397270831</v>
-      </c>
-      <c r="I72" s="132">
-        <f t="shared" si="38"/>
-        <v>0.62376357824373097</v>
-      </c>
-      <c r="J72" s="132">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="K72" s="132">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="L72" s="132">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="M72" s="132" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="N72" s="132" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="O72" s="132" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P72" s="132" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="Q72" s="132" t="str">
-        <f t="shared" si="38"/>
+        <v>1.3951685381968192E-2</v>
+      </c>
+      <c r="H72" s="131">
+        <f t="shared" ref="H72:Q72" si="25">IF(H$4="","",H66/H$4)</f>
+        <v>1.5671518179732512E-2</v>
+      </c>
+      <c r="I72" s="131">
+        <f t="shared" si="25"/>
+        <v>2.3627760663558588E-2</v>
+      </c>
+      <c r="J72" s="131">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K72" s="131">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="L72" s="131">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="M72" s="131" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="N72" s="131" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="O72" s="131" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="P72" s="131" t="str">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="Q72" s="131" t="str">
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="12"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="29"/>
+      <c r="B73" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="C73" s="131">
+        <f>C67/C$4</f>
+        <v>0.7738144762493232</v>
+      </c>
       <c r="D73" s="29"/>
       <c r="E73" s="29"/>
       <c r="F73" s="29"/>
-      <c r="G73" s="16"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="14"/>
-      <c r="J73" s="14"/>
-      <c r="K73" s="14"/>
-      <c r="L73" s="14"/>
-      <c r="M73" s="14"/>
-      <c r="N73" s="14"/>
-      <c r="O73" s="14"/>
-      <c r="P73" s="14"/>
-      <c r="Q73" s="14"/>
+      <c r="G73" s="131">
+        <f>IF(G$4="","",G67/G$4)</f>
+        <v>0.57762188109301071</v>
+      </c>
+      <c r="H73" s="131">
+        <f t="shared" ref="H73:Q73" si="26">IF(H$4="","",H67/H$4)</f>
+        <v>0.73212708397270831</v>
+      </c>
+      <c r="I73" s="131">
+        <f t="shared" si="26"/>
+        <v>0.62376357824373097</v>
+      </c>
+      <c r="J73" s="131">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="K73" s="131">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="L73" s="131">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M73" s="131" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="N73" s="131" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="O73" s="131" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="P73" s="131" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="Q73" s="131" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
     </row>
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="12"/>
-      <c r="B74" s="122" t="s">
-        <v>208</v>
-      </c>
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
+      <c r="D74" s="29"/>
+      <c r="E74" s="29"/>
+      <c r="F74" s="29"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="14"/>
+      <c r="M74" s="14"/>
+      <c r="N74" s="14"/>
+      <c r="O74" s="14"/>
+      <c r="P74" s="14"/>
+      <c r="Q74" s="14"/>
     </row>
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12"/>
-      <c r="B75" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="C75" s="46">
-        <f>-C4/C58</f>
-        <v>209.73640568718258</v>
-      </c>
-      <c r="G75" s="46">
-        <f t="shared" ref="G75:Q75" si="39">IF(G4="","",-G4/G58)</f>
-        <v>257.16427276998456</v>
-      </c>
-      <c r="H75" s="46">
-        <f t="shared" si="39"/>
-        <v>576.88407262919611</v>
-      </c>
-      <c r="I75" s="46">
-        <f t="shared" si="39"/>
-        <v>508.19599948045203</v>
-      </c>
-      <c r="J75" s="46">
-        <f t="shared" si="39"/>
-        <v>307.162639952858</v>
-      </c>
-      <c r="K75" s="46">
-        <f t="shared" si="39"/>
-        <v>178.10179944510503</v>
-      </c>
-      <c r="L75" s="46">
-        <f t="shared" si="39"/>
-        <v>463.02484453916446</v>
-      </c>
-      <c r="M75" s="46" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="N75" s="46" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="O75" s="46" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="P75" s="46" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="Q75" s="46" t="str">
-        <f t="shared" si="39"/>
-        <v/>
+      <c r="B75" s="121" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="12"/>
       <c r="B76" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="C76" s="26">
-        <f>C68/C64</f>
-        <v>0.76325199666976462</v>
-      </c>
-      <c r="G76" s="15">
-        <f t="shared" ref="G76:Q76" si="40">IF(G68="","",G68/G64)</f>
-        <v>0.76325199666976462</v>
-      </c>
-      <c r="H76" s="15">
-        <f t="shared" si="40"/>
-        <v>0.83207133093167851</v>
-      </c>
-      <c r="I76" s="15">
-        <f t="shared" si="40"/>
-        <v>0.75551647408031242</v>
-      </c>
-      <c r="J76" s="15">
-        <f t="shared" si="40"/>
-        <v>0.79351322080112696</v>
-      </c>
-      <c r="K76" s="15" t="e">
-        <f t="shared" si="40"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L76" s="15" t="e">
-        <f t="shared" si="40"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M76" s="15" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="N76" s="15" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="O76" s="15" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="P76" s="15" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q76" s="15" t="str">
-        <f t="shared" si="40"/>
+        <v>207</v>
+      </c>
+      <c r="C76" s="46">
+        <f>-C4/C59</f>
+        <v>209.73640568718258</v>
+      </c>
+      <c r="G76" s="46">
+        <f>IF(G4="","",-G4/G59)</f>
+        <v>257.16427276998456</v>
+      </c>
+      <c r="H76" s="46">
+        <f>IF(H4="","",-H4/H59)</f>
+        <v>576.88407262919611</v>
+      </c>
+      <c r="I76" s="46">
+        <f>IF(I4="","",-I4/I59)</f>
+        <v>508.19599948045203</v>
+      </c>
+      <c r="J76" s="46">
+        <f>IF(J4="","",-J4/J59)</f>
+        <v>307.162639952858</v>
+      </c>
+      <c r="K76" s="46">
+        <f>IF(K4="","",-K4/K59)</f>
+        <v>178.10179944510503</v>
+      </c>
+      <c r="L76" s="46">
+        <f>IF(L4="","",-L4/L59)</f>
+        <v>463.02484453916446</v>
+      </c>
+      <c r="M76" s="46" t="str">
+        <f>IF(M4="","",-M4/M59)</f>
+        <v/>
+      </c>
+      <c r="N76" s="46" t="str">
+        <f>IF(N4="","",-N4/N59)</f>
+        <v/>
+      </c>
+      <c r="O76" s="46" t="str">
+        <f>IF(O4="","",-O4/O59)</f>
+        <v/>
+      </c>
+      <c r="P76" s="46" t="str">
+        <f>IF(P4="","",-P4/P59)</f>
+        <v/>
+      </c>
+      <c r="Q76" s="46" t="str">
+        <f>IF(Q4="","",-Q4/Q59)</f>
         <v/>
       </c>
     </row>
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="12"/>
+      <c r="B77" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="C77" s="26">
+        <f>C69/C65</f>
+        <v>0.76325199666976462</v>
+      </c>
+      <c r="G77" s="15">
+        <f t="shared" ref="G77:Q77" si="27">IF(G69="","",G69/G65)</f>
+        <v>0.76325199666976462</v>
+      </c>
+      <c r="H77" s="15">
+        <f t="shared" si="27"/>
+        <v>0.83207133093167851</v>
+      </c>
+      <c r="I77" s="15">
+        <f t="shared" si="27"/>
+        <v>0.75551647408031242</v>
+      </c>
+      <c r="J77" s="15">
+        <f t="shared" si="27"/>
+        <v>0.79351322080112696</v>
+      </c>
+      <c r="K77" s="15" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L77" s="15" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M77" s="15" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="N77" s="15" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="O77" s="15" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="P77" s="15" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="Q77" s="15" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
     </row>
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="12"/>
-      <c r="B78" s="122" t="s">
-        <v>64</v>
-      </c>
-      <c r="C78" s="62"/>
-      <c r="D78" s="62"/>
-      <c r="E78" s="62"/>
-      <c r="F78" s="62"/>
-      <c r="G78" s="26" t="str">
-        <f>IFERROR(IF(#REF!*G80*(1/G76)=G82,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H78" s="26" t="str">
-        <f>IFERROR(IF(#REF!*H80*(1/H76)=H82,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I78" s="26" t="str">
-        <f>IFERROR(IF(#REF!*I80*(1/I76)=I82,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J78" s="26" t="str">
-        <f>IFERROR(IF(#REF!*J80*(1/J76)=J82,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K78" s="26" t="str">
-        <f>IFERROR(IF(#REF!*K80*(1/K76)=K82,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L78" s="26" t="str">
-        <f>IFERROR(IF(#REF!*L80*(1/L76)=L82,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M78" s="26" t="str">
-        <f>IFERROR(IF(#REF!*M80*(1/M76)=M82,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N78" s="26" t="str">
-        <f>IFERROR(IF(#REF!*N80*(1/N76)=N82,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O78" s="26" t="str">
-        <f>IFERROR(IF(#REF!*O80*(1/O76)=O82,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P78" s="26" t="str">
-        <f>IFERROR(IF(#REF!*P80*(1/P76)=P82,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q78" s="26" t="str">
-        <f>IFERROR(IF(#REF!*Q80*(1/Q76)=Q82,"","Error"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="12"/>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="121" t="s">
+        <v>64</v>
+      </c>
+      <c r="C79" s="62"/>
+      <c r="D79" s="62"/>
+      <c r="E79" s="62"/>
+      <c r="F79" s="62"/>
+      <c r="G79" s="26" t="str">
+        <f>IFERROR(IF(#REF!*G81*(1/G77)=G83,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H79" s="26" t="str">
+        <f>IFERROR(IF(#REF!*H81*(1/H77)=H83,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I79" s="26" t="str">
+        <f>IFERROR(IF(#REF!*I81*(1/I77)=I83,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J79" s="26" t="str">
+        <f>IFERROR(IF(#REF!*J81*(1/J77)=J83,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K79" s="26" t="str">
+        <f>IFERROR(IF(#REF!*K81*(1/K77)=K83,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L79" s="26" t="str">
+        <f>IFERROR(IF(#REF!*L81*(1/L77)=L83,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M79" s="26" t="str">
+        <f>IFERROR(IF(#REF!*M81*(1/M77)=M83,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N79" s="26" t="str">
+        <f>IFERROR(IF(#REF!*N81*(1/N77)=N83,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O79" s="26" t="str">
+        <f>IFERROR(IF(#REF!*O81*(1/O77)=O83,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P79" s="26" t="str">
+        <f>IFERROR(IF(#REF!*P81*(1/P77)=P83,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q79" s="26" t="str">
+        <f>IFERROR(IF(#REF!*Q81*(1/Q77)=Q83,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="12"/>
+      <c r="B80" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="C79" s="26">
-        <f>C25</f>
+      <c r="C80" s="26">
+        <f>C26</f>
         <v>0.11664383553220437</v>
       </c>
-      <c r="G79" s="26">
-        <f>G25</f>
+      <c r="G80" s="26">
+        <f>G26</f>
         <v>0.12245710905455723</v>
       </c>
-      <c r="H79" s="26">
-        <f t="shared" ref="H79:Q79" si="41">H25</f>
+      <c r="H80" s="26">
+        <f t="shared" ref="H80:Q80" si="28">H26</f>
         <v>0.11378358242100998</v>
       </c>
-      <c r="I79" s="26">
-        <f t="shared" si="41"/>
+      <c r="I80" s="26">
+        <f t="shared" si="28"/>
         <v>0.12086725258551366</v>
       </c>
-      <c r="J79" s="26">
-        <f t="shared" si="41"/>
+      <c r="J80" s="26">
+        <f t="shared" si="28"/>
         <v>0.10583450462035347</v>
       </c>
-      <c r="K79" s="26">
-        <f t="shared" si="41"/>
+      <c r="K80" s="26">
+        <f t="shared" si="28"/>
         <v>0.10724519842891581</v>
       </c>
-      <c r="L79" s="26">
-        <f t="shared" si="41"/>
+      <c r="L80" s="26">
+        <f t="shared" si="28"/>
         <v>0.10195889152515229</v>
       </c>
-      <c r="M79" s="26" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="N79" s="26" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="O79" s="26" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="P79" s="26" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="Q79" s="26" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="C80" s="46">
-        <f>C4/C64</f>
-        <v>0.74162830005471281</v>
-      </c>
-      <c r="G80" s="46">
-        <f t="shared" ref="G80:Q80" si="42">IF(G4="","",G4/G64)</f>
-        <v>0.90933332162498015</v>
-      </c>
-      <c r="H80" s="46">
-        <f t="shared" si="42"/>
-        <v>0.81551983462257005</v>
-      </c>
-      <c r="I80" s="46">
-        <f t="shared" si="42"/>
-        <v>0.73420399704411943</v>
-      </c>
-      <c r="J80" s="46">
-        <f t="shared" si="42"/>
-        <v>0.62093318504188499</v>
-      </c>
-      <c r="K80" s="46" t="e">
-        <f t="shared" si="42"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L80" s="46" t="e">
-        <f t="shared" si="42"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M80" s="46" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="N80" s="46" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="O80" s="46" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="P80" s="46" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="Q80" s="46" t="str">
-        <f t="shared" si="42"/>
+      <c r="M80" s="26" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="N80" s="26" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="O80" s="26" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="P80" s="26" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Q80" s="26" t="str">
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C81" s="46">
+        <f>C4/C65</f>
+        <v>0.74162830005471281</v>
+      </c>
+      <c r="G81" s="46">
+        <f>IF(G4="","",G4/G65)</f>
+        <v>0.90933332162498015</v>
+      </c>
+      <c r="H81" s="46">
+        <f>IF(H4="","",H4/H65)</f>
+        <v>0.81551983462257005</v>
+      </c>
+      <c r="I81" s="46">
+        <f>IF(I4="","",I4/I65)</f>
+        <v>0.73420399704411943</v>
+      </c>
+      <c r="J81" s="46">
+        <f>IF(J4="","",J4/J65)</f>
+        <v>0.62093318504188499</v>
+      </c>
+      <c r="K81" s="46" t="e">
+        <f>IF(K4="","",K4/K65)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L81" s="46" t="e">
+        <f>IF(L4="","",L4/L65)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M81" s="46" t="str">
+        <f>IF(M4="","",M4/M65)</f>
+        <v/>
+      </c>
+      <c r="N81" s="46" t="str">
+        <f>IF(N4="","",N4/N65)</f>
+        <v/>
+      </c>
+      <c r="O81" s="46" t="str">
+        <f>IF(O4="","",O4/O65)</f>
+        <v/>
+      </c>
+      <c r="P81" s="46" t="str">
+        <f>IF(P4="","",P4/P65)</f>
+        <v/>
+      </c>
+      <c r="Q81" s="46" t="str">
+        <f>IF(Q4="","",Q4/Q65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B82" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C81" s="17">
-        <f>C64/C68</f>
+      <c r="C82" s="17">
+        <f>C65/C69</f>
         <v>1.3101832741522048</v>
       </c>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="17">
-        <f t="shared" ref="G81:Q81" si="43">IF(G$4="","",G64/G68)</f>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="17">
+        <f t="shared" ref="G82:Q82" si="29">IF(G$4="","",G65/G69)</f>
         <v>1.3101832741522048</v>
       </c>
-      <c r="H81" s="17">
-        <f t="shared" si="43"/>
+      <c r="H82" s="17">
+        <f t="shared" si="29"/>
         <v>1.2018200397317982</v>
       </c>
-      <c r="I81" s="17">
-        <f t="shared" si="43"/>
+      <c r="I82" s="17">
+        <f t="shared" si="29"/>
         <v>1.3235978755027102</v>
       </c>
-      <c r="J81" s="17">
-        <f t="shared" si="43"/>
+      <c r="J82" s="17">
+        <f t="shared" si="29"/>
         <v>1.2602184485223888</v>
       </c>
-      <c r="K81" s="17" t="e">
-        <f t="shared" si="43"/>
+      <c r="K82" s="17" t="e">
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L81" s="17" t="e">
-        <f t="shared" si="43"/>
+      <c r="L82" s="17" t="e">
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M81" s="17" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="N81" s="17" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="O81" s="17" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="P81" s="17" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="Q81" s="17" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="12"/>
-      <c r="B82" s="91" t="s">
-        <v>65</v>
-      </c>
-      <c r="C82" s="141">
-        <f>C8/C68</f>
-        <v>0.11333919837099207</v>
-      </c>
-      <c r="D82" s="142"/>
-      <c r="E82" s="142"/>
-      <c r="F82" s="142"/>
-      <c r="G82" s="141">
-        <f t="shared" ref="G82:Q82" si="44">IF(G$4="","",G8/G68)</f>
-        <v>0.14589458032083277</v>
-      </c>
-      <c r="H82" s="141">
-        <f t="shared" si="44"/>
-        <v>0.11152020850765841</v>
-      </c>
-      <c r="I82" s="141">
-        <f t="shared" si="44"/>
-        <v>0.1174576902086082</v>
-      </c>
-      <c r="J82" s="141">
-        <f t="shared" si="44"/>
-        <v>8.2816712209154458E-2</v>
-      </c>
-      <c r="K82" s="141" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L82" s="141" t="e">
-        <f t="shared" si="44"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M82" s="141" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="N82" s="141" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="O82" s="141" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="P82" s="141" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="Q82" s="141" t="str">
-        <f t="shared" si="44"/>
+      <c r="M82" s="17" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="N82" s="17" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="O82" s="17" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="P82" s="17" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Q82" s="17" t="str">
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
     <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="12"/>
-    </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B83" s="91" t="s">
+        <v>65</v>
+      </c>
+      <c r="C83" s="140">
+        <f>C8/C69</f>
+        <v>0.11333919837099207</v>
+      </c>
+      <c r="D83" s="141"/>
+      <c r="E83" s="141"/>
+      <c r="F83" s="141"/>
+      <c r="G83" s="140">
+        <f>IF(G$4="","",G8/G69)</f>
+        <v>0.14589458032083277</v>
+      </c>
+      <c r="H83" s="140">
+        <f>IF(H$4="","",H8/H69)</f>
+        <v>0.11152020850765841</v>
+      </c>
+      <c r="I83" s="140">
+        <f>IF(I$4="","",I8/I69)</f>
+        <v>0.1174576902086082</v>
+      </c>
+      <c r="J83" s="140">
+        <f>IF(J$4="","",J8/J69)</f>
+        <v>8.2816712209154458E-2</v>
+      </c>
+      <c r="K83" s="140" t="e">
+        <f>IF(K$4="","",K8/K69)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L83" s="140" t="e">
+        <f>IF(L$4="","",L8/L69)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M83" s="140" t="str">
+        <f>IF(M$4="","",M8/M69)</f>
+        <v/>
+      </c>
+      <c r="N83" s="140" t="str">
+        <f>IF(N$4="","",N8/N69)</f>
+        <v/>
+      </c>
+      <c r="O83" s="140" t="str">
+        <f>IF(O$4="","",O8/O69)</f>
+        <v/>
+      </c>
+      <c r="P83" s="140" t="str">
+        <f>IF(P$4="","",P8/P69)</f>
+        <v/>
+      </c>
+      <c r="Q83" s="140" t="str">
+        <f>IF(Q$4="","",Q8/Q69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="12"/>
-      <c r="B84" s="61" t="s">
-        <v>231</v>
-      </c>
-      <c r="C84" s="61"/>
-      <c r="D84" s="63"/>
-      <c r="E84" s="81" t="s">
+    </row>
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A85" s="12"/>
+      <c r="B85" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="C85" s="61"/>
+      <c r="D85" s="63"/>
+      <c r="E85" s="81" t="s">
         <v>146</v>
       </c>
-      <c r="F84" s="63"/>
-      <c r="G84" s="40"/>
-      <c r="H84" s="40"/>
-      <c r="I84" s="40"/>
-      <c r="J84" s="40"/>
-      <c r="K84" s="40"/>
-      <c r="L84" s="40"/>
-      <c r="M84" s="40"/>
-      <c r="N84" s="40"/>
-      <c r="O84" s="40"/>
-      <c r="P84" s="40"/>
-      <c r="Q84" s="40"/>
-    </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="12"/>
-      <c r="B85" s="78" t="s">
-        <v>229</v>
-      </c>
+      <c r="F85" s="63"/>
+      <c r="G85" s="40"/>
+      <c r="H85" s="40"/>
+      <c r="I85" s="40"/>
+      <c r="J85" s="40"/>
+      <c r="K85" s="40"/>
+      <c r="L85" s="40"/>
+      <c r="M85" s="40"/>
+      <c r="N85" s="40"/>
+      <c r="O85" s="40"/>
+      <c r="P85" s="40"/>
+      <c r="Q85" s="40"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="12"/>
-      <c r="B86" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C86" s="159">
-        <f>G86</f>
-        <v>1.3599999999999999</v>
-      </c>
-      <c r="G86" s="158">
-        <f>Data!C52</f>
-        <v>1.3599999999999999</v>
-      </c>
-      <c r="H86" s="158">
-        <f>Data!D52</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="I86" s="158">
-        <f>Data!E52</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="J86" s="158">
-        <f>Data!F52</f>
-        <v>1</v>
-      </c>
-      <c r="K86" s="158">
-        <f>Data!G52</f>
-        <v>1</v>
-      </c>
-      <c r="L86" s="158">
-        <f>Data!H52</f>
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="M86" s="158" t="str">
-        <f>Data!I52</f>
-        <v/>
-      </c>
-      <c r="N86" s="158" t="str">
-        <f>Data!J52</f>
-        <v/>
-      </c>
-      <c r="O86" s="158" t="str">
-        <f>Data!K52</f>
-        <v/>
-      </c>
-      <c r="P86" s="158" t="str">
-        <f>Data!L52</f>
-        <v/>
-      </c>
-      <c r="Q86" s="158" t="str">
-        <f>Data!M52</f>
-        <v/>
+      <c r="B86" s="78" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="12"/>
       <c r="B87" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C87" s="96">
-        <f>C86*Common_Shares/$C$3</f>
-        <v>798466.67599999986</v>
-      </c>
-      <c r="G87" s="96">
-        <f t="shared" ref="G87:Q87" si="45">IF(G$4="","",G86*Common_Shares/$C$3)</f>
-        <v>798466.67599999986</v>
-      </c>
-      <c r="H87" s="96">
-        <f t="shared" si="45"/>
-        <v>645818.63500000001</v>
-      </c>
-      <c r="I87" s="96">
-        <f t="shared" si="45"/>
-        <v>645818.63500000001</v>
-      </c>
-      <c r="J87" s="96">
-        <f t="shared" si="45"/>
-        <v>587107.85</v>
-      </c>
-      <c r="K87" s="96">
-        <f t="shared" si="45"/>
-        <v>587107.85</v>
-      </c>
-      <c r="L87" s="96">
-        <f t="shared" si="45"/>
-        <v>675174.02749999997</v>
-      </c>
-      <c r="M87" s="96" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="N87" s="96" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="O87" s="96" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="P87" s="96" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="Q87" s="96" t="str">
-        <f t="shared" si="45"/>
+        <v>61</v>
+      </c>
+      <c r="C87" s="157">
+        <f>G87</f>
+        <v>1.3599999999999999</v>
+      </c>
+      <c r="G87" s="156">
+        <f>Data!C52</f>
+        <v>1.3599999999999999</v>
+      </c>
+      <c r="H87" s="156">
+        <f>Data!D52</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I87" s="156">
+        <f>Data!E52</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="J87" s="156">
+        <f>Data!F52</f>
+        <v>1</v>
+      </c>
+      <c r="K87" s="156">
+        <f>Data!G52</f>
+        <v>1</v>
+      </c>
+      <c r="L87" s="156">
+        <f>Data!H52</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="M87" s="156" t="str">
+        <f>Data!I52</f>
+        <v/>
+      </c>
+      <c r="N87" s="156" t="str">
+        <f>Data!J52</f>
+        <v/>
+      </c>
+      <c r="O87" s="156" t="str">
+        <f>Data!K52</f>
+        <v/>
+      </c>
+      <c r="P87" s="156" t="str">
+        <f>Data!L52</f>
+        <v/>
+      </c>
+      <c r="Q87" s="156" t="str">
+        <f>Data!M52</f>
         <v/>
       </c>
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="12"/>
       <c r="B88" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C88" s="26">
-        <f>C86/(C16*$C$3/Common_Shares)</f>
-        <v>0.62838135742186285</v>
-      </c>
-      <c r="G88" s="26">
-        <f t="shared" ref="G88:Q88" si="46">IF(G$4="","",G86/(G16*$C$3/Common_Shares))</f>
-        <v>0.51370076598329062</v>
-      </c>
-      <c r="H88" s="26">
-        <f t="shared" si="46"/>
-        <v>0.41687207470173337</v>
-      </c>
-      <c r="I88" s="26">
-        <f t="shared" si="46"/>
-        <v>0.47052364098144123</v>
-      </c>
-      <c r="J88" s="26">
-        <f t="shared" si="46"/>
-        <v>0.42011685976327506</v>
-      </c>
-      <c r="K88" s="26">
-        <f t="shared" si="46"/>
-        <v>0.67875466196828127</v>
-      </c>
-      <c r="L88" s="26">
-        <f t="shared" si="46"/>
-        <v>-61.897142235056833</v>
-      </c>
-      <c r="M88" s="26" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="N88" s="26" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="O88" s="26" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="P88" s="26" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="Q88" s="26" t="str">
-        <f t="shared" si="46"/>
+        <v>228</v>
+      </c>
+      <c r="C88" s="96">
+        <f>C87*Common_Shares/$C$3</f>
+        <v>798466.67599999986</v>
+      </c>
+      <c r="G88" s="96">
+        <f t="shared" ref="G88:Q88" si="30">IF(G$4="","",G87*Common_Shares/$C$3)</f>
+        <v>798466.67599999986</v>
+      </c>
+      <c r="H88" s="96">
+        <f t="shared" si="30"/>
+        <v>645818.63500000001</v>
+      </c>
+      <c r="I88" s="96">
+        <f t="shared" si="30"/>
+        <v>645818.63500000001</v>
+      </c>
+      <c r="J88" s="96">
+        <f t="shared" si="30"/>
+        <v>587107.85</v>
+      </c>
+      <c r="K88" s="96">
+        <f t="shared" si="30"/>
+        <v>587107.85</v>
+      </c>
+      <c r="L88" s="96">
+        <f t="shared" si="30"/>
+        <v>675174.02749999997</v>
+      </c>
+      <c r="M88" s="96" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="N88" s="96" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="O88" s="96" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="P88" s="96" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="Q88" s="96" t="str">
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="12"/>
+      <c r="B89" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C89" s="26">
+        <f>C87/(C15*$C$3/Common_Shares)</f>
+        <v>0.73898220922083402</v>
+      </c>
+      <c r="G89" s="26">
+        <f t="shared" ref="G89:Q89" si="31">IF(G$4="","",G87/(G15*$C$3/Common_Shares))</f>
+        <v>0.61137166287015943</v>
+      </c>
+      <c r="H89" s="26">
+        <f t="shared" si="31"/>
+        <v>0.47520767477248388</v>
+      </c>
+      <c r="I89" s="26">
+        <f t="shared" si="31"/>
+        <v>0.55110750382299534</v>
+      </c>
+      <c r="J89" s="26">
+        <f t="shared" si="31"/>
+        <v>0.52597248961462351</v>
+      </c>
+      <c r="K89" s="26">
+        <f t="shared" si="31"/>
+        <v>0.51484610946055442</v>
+      </c>
+      <c r="L89" s="26">
+        <f t="shared" si="31"/>
+        <v>0.42952570160047737</v>
+      </c>
+      <c r="M89" s="26" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="N89" s="26" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="O89" s="26" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="P89" s="26" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="Q89" s="26" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="12"/>
@@ -8961,7 +9059,9 @@
     <row r="114" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="12"/>
     </row>
-    <row r="115" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="115" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="12"/>
+    </row>
     <row r="116" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="117" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="118" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -9644,9 +9744,10 @@
     <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="G4:Q9 G11:Q12 G15:Q15 G42:Q43 G46:Q46">
+  <conditionalFormatting sqref="G4:Q9 G14:Q14 G43:Q44 G47:Q47 G11:Q11 G19:Q19">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
@@ -9665,17 +9766,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:H44"/>
+  <dimension ref="B1:H50"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="33.9296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="5.59765625" style="1" customWidth="1"/>
     <col min="6" max="6" width="25.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
@@ -9683,10 +9782,10 @@
       <c r="B1" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="137">
+      <c r="C1" s="136">
         <v>45382</v>
       </c>
-      <c r="F1" s="116" t="str">
+      <c r="F1" s="115" t="str">
         <f>IF(MONTH(C1)=MONTH(FCF!G1),"FY","Quarter")&amp;" Report"</f>
         <v>FY Report</v>
       </c>
@@ -9710,7 +9809,7 @@
       <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="115" t="s">
+      <c r="D3" s="114" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="18" t="s">
@@ -9719,7 +9818,7 @@
       <c r="G3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="115" t="s">
+      <c r="H3" s="114" t="s">
         <v>52</v>
       </c>
     </row>
@@ -9866,7 +9965,10 @@
         <f>SUM(G4:G9)</f>
         <v>1998219</v>
       </c>
-      <c r="H10" s="110"/>
+      <c r="H10" s="23">
+        <f>G4*H4+G5*H5+G6*H6+G7*H7+G8*H8+G9*H9</f>
+        <v>1798397.1</v>
+      </c>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="107" t="s">
@@ -9876,7 +9978,10 @@
         <f>SUM(C4:C10)</f>
         <v>10334089</v>
       </c>
-      <c r="D11" s="110"/>
+      <c r="D11" s="23">
+        <f>C4*D4+C5*D5+C6*D6+C7*D7+C8*D8+C9*D9+C10*D10</f>
+        <v>5058769.8</v>
+      </c>
       <c r="F11" s="5" t="s">
         <v>180</v>
       </c>
@@ -10004,7 +10109,10 @@
         <f>SUM(G11:G16)</f>
         <v>925726</v>
       </c>
-      <c r="H17" s="110"/>
+      <c r="H17" s="23">
+        <f>G11*H11+G12*H12+G13*H13+G14*H14+G15*H15+G16*H16</f>
+        <v>185145.2</v>
+      </c>
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="5" t="s">
@@ -10027,6 +10135,17 @@
       <c r="D19" s="109">
         <v>0</v>
       </c>
+      <c r="F19" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="108">
+        <f>C11+C20</f>
+        <v>13930119</v>
+      </c>
+      <c r="H19" s="23">
+        <f>D11+D20</f>
+        <v>5518322.75</v>
+      </c>
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="107" t="s">
@@ -10036,11 +10155,32 @@
         <f>SUM(C12:C19)</f>
         <v>3596030</v>
       </c>
+      <c r="D20" s="23">
+        <f>C12*D12+C13*D13+C14*D14+C15*D15+C16*D16+C17*D17+C18*D18+C19*D19</f>
+        <v>459552.95</v>
+      </c>
+      <c r="F20" s="52" t="s">
+        <v>294</v>
+      </c>
+      <c r="G20" s="108">
+        <f>G10+G17</f>
+        <v>2923945</v>
+      </c>
+      <c r="H20" s="23">
+        <f>H10+H17</f>
+        <v>1983542.3</v>
+      </c>
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="18" t="s">
         <v>71</v>
       </c>
+      <c r="G22" s="210" t="s">
+        <v>292</v>
+      </c>
+      <c r="H22" s="210" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="5" t="s">
@@ -10053,8 +10193,12 @@
         <v>171</v>
       </c>
       <c r="G23" s="108">
-        <f>C11+C20+G10+G17</f>
+        <f>G19+G20</f>
         <v>16854064</v>
+      </c>
+      <c r="H23" s="23">
+        <f>H19+H20</f>
+        <v>7501865.0499999998</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10097,7 +10241,7 @@
       <c r="F26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G26" s="113">
+      <c r="G26" s="112">
         <f>Data!C24</f>
         <v>3990166</v>
       </c>
@@ -10129,18 +10273,18 @@
       <c r="F28" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G28" s="113">
+      <c r="G28" s="112">
         <v>12863898</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="111" t="s">
+      <c r="B29" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="113">
+      <c r="C29" s="112">
         <v>3516809</v>
       </c>
-      <c r="F29" s="112" t="s">
+      <c r="F29" s="111" t="s">
         <v>172</v>
       </c>
       <c r="G29" s="14">
@@ -10205,10 +10349,10 @@
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="111" t="s">
+      <c r="B36" s="110" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="114">
+      <c r="C36" s="113">
         <f>G26-C29</f>
         <v>473357</v>
       </c>
@@ -10225,17 +10369,17 @@
       <c r="H38" s="40"/>
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="134" t="s">
-        <v>187</v>
-      </c>
-      <c r="C39" s="135" t="s">
+      <c r="B39" s="133" t="s">
+        <v>300</v>
+      </c>
+      <c r="C39" s="134" t="s">
         <v>144</v>
       </c>
-      <c r="D39" s="135" t="s">
+      <c r="D39" s="134" t="s">
         <v>214</v>
       </c>
       <c r="E39" s="2"/>
-      <c r="F39" s="138" t="s">
+      <c r="F39" s="137" t="s">
         <v>146</v>
       </c>
     </row>
@@ -10248,7 +10392,7 @@
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="D40" s="26">
-        <f>IF(FCF!G4="","",ABS(FCF!G58/BS!$G$27))</f>
+        <f>IF(FCF!G4="","",ABS(FCF!G59/BS!$G$27))</f>
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="F40" s="86" t="s">
@@ -10259,11 +10403,11 @@
       <c r="B41" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="C41" s="117">
+      <c r="C41" s="116">
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="D41" s="8">
-        <f>IF(FCF!G4="","",FCF!G59/BS!$G$24)</f>
+        <f>IF(FCF!G4="","",FCF!G60/BS!$G$24)</f>
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="F41" s="86" t="s">
@@ -10274,12 +10418,12 @@
       <c r="B42" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C42" s="117">
+      <c r="C42" s="116">
         <f>D42</f>
         <v>0.11625172085779995</v>
       </c>
       <c r="D42" s="26">
-        <f>FCF!G13/BS!$G$25</f>
+        <f>FCF!G12/BS!$G$25</f>
         <v>0.11625172085779995</v>
       </c>
       <c r="F42" s="20" t="s">
@@ -10290,8 +10434,8 @@
       <c r="B43" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C43" s="136"/>
-      <c r="D43" s="124">
+      <c r="C43" s="135"/>
+      <c r="D43" s="123">
         <f>G25/G23</f>
         <v>0.23652360641326625</v>
       </c>
@@ -10300,11 +10444,59 @@
       <c r="B44" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="C44" s="136"/>
-      <c r="D44" s="133">
+      <c r="C44" s="135"/>
+      <c r="D44" s="132">
         <f>BS!G27/FCF!C8</f>
         <v>1.3957095258737691</v>
       </c>
+    </row>
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="133" t="s">
+        <v>299</v>
+      </c>
+      <c r="C46" s="134" t="s">
+        <v>144</v>
+      </c>
+      <c r="D46" s="134" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C47" s="123">
+        <f>FCF!C18/G19</f>
+        <v>7.756539100607851E-2</v>
+      </c>
+      <c r="D47" s="123">
+        <f>FCF!G18/G19</f>
+        <v>4.8775032000803437E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C48" s="123">
+        <f>FCF!C19/G20</f>
+        <v>6.5041237095773002E-2</v>
+      </c>
+      <c r="D48" s="123">
+        <f>FCF!G19/G20</f>
+        <v>8.4925332042839377E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="105" t="s">
+        <v>291</v>
+      </c>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -10329,106 +10521,106 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="39" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
       <c r="E2" s="40"/>
       <c r="F2" s="40"/>
-      <c r="H2" s="176" t="s">
+      <c r="H2" s="174" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B3" s="153" t="s">
+      <c r="B3" s="151" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="148">
+      <c r="C3" s="146">
         <f>FCF!C3</f>
         <v>1000</v>
       </c>
-      <c r="E3" s="153" t="s">
-        <v>270</v>
-      </c>
-      <c r="H3" s="166"/>
+      <c r="E3" s="151" t="s">
+        <v>269</v>
+      </c>
+      <c r="H3" s="164"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B4" s="139" t="s">
-        <v>279</v>
-      </c>
-      <c r="C4" s="154">
-        <f>FCF!C19</f>
+      <c r="B4" s="138" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" s="152">
+        <f>FCF!C20</f>
         <v>1270672.1269962033</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E4" s="139" t="s">
+      <c r="E4" s="138" t="s">
+        <v>274</v>
+      </c>
+      <c r="F4" s="178">
+        <v>0</v>
+      </c>
+      <c r="H4" s="164"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B5" s="196" t="s">
+        <v>266</v>
+      </c>
+      <c r="C5" s="200">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="196" t="s">
+        <v>270</v>
+      </c>
+      <c r="H5" s="164"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B6" s="198" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="179">
+        <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
+        <v>12706721.269962033</v>
+      </c>
+      <c r="E6" s="196" t="s">
         <v>275</v>
       </c>
-      <c r="F4" s="180">
-        <v>0</v>
-      </c>
-      <c r="H4" s="166"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B5" s="200" t="s">
+      <c r="H6" s="164"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B7" s="196" t="s">
         <v>267</v>
       </c>
-      <c r="C5" s="204">
-        <v>0.1</v>
-      </c>
-      <c r="E5" s="200" t="s">
-        <v>271</v>
-      </c>
-      <c r="H5" s="166"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B6" s="202" t="s">
-        <v>266</v>
-      </c>
-      <c r="C6" s="181">
-        <f>C4/C5</f>
-        <v>12706721.269962033</v>
-      </c>
-      <c r="E6" s="200" t="s">
-        <v>276</v>
-      </c>
-      <c r="H6" s="166"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B7" s="200" t="s">
-        <v>268</v>
-      </c>
-      <c r="C7" s="157">
+      <c r="C7" s="155">
         <f>BS!G27</f>
         <v>2034922</v>
       </c>
-      <c r="H7" s="166"/>
+      <c r="H7" s="164"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B8" s="202" t="s">
-        <v>269</v>
-      </c>
-      <c r="C8" s="181">
+      <c r="B8" s="198" t="s">
+        <v>268</v>
+      </c>
+      <c r="C8" s="179">
         <f>C6-C7</f>
         <v>10671799.269962033</v>
       </c>
-      <c r="H8" s="166"/>
+      <c r="H8" s="164"/>
     </row>
     <row r="9" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B9" s="201" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9" s="156">
+      <c r="B9" s="197" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="154">
         <f>(C8*FCF!C3)/Common_Shares</f>
         <v>18.176897600606146</v>
       </c>
-      <c r="H9" s="166"/>
+      <c r="H9" s="164"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="H10" s="166"/>
+      <c r="H10" s="164"/>
     </row>
     <row r="11" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B11" s="39" t="s">
@@ -10438,1218 +10630,1225 @@
       <c r="D11" s="40"/>
       <c r="E11" s="40"/>
       <c r="F11" s="40"/>
-      <c r="H11" s="166"/>
+      <c r="H11" s="164"/>
     </row>
     <row r="12" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B12" s="165" t="s">
-        <v>286</v>
-      </c>
-      <c r="E12" s="153" t="s">
-        <v>288</v>
-      </c>
-      <c r="F12" s="210" t="str">
+      <c r="B12" s="163" t="s">
+        <v>285</v>
+      </c>
+      <c r="E12" s="151" t="s">
+        <v>287</v>
+      </c>
+      <c r="F12" s="205" t="str">
         <f>"("&amp;D4&amp;")"</f>
         <v>(HKD)</v>
       </c>
-      <c r="H12" s="166"/>
+      <c r="H12" s="164"/>
     </row>
     <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="208" t="s">
-        <v>284</v>
-      </c>
-      <c r="C13" s="206">
-        <v>-7.1999999999999995E-2</v>
-      </c>
-      <c r="E13" s="139" t="s">
-        <v>259</v>
+      <c r="B13" s="203" t="s">
+        <v>283</v>
+      </c>
+      <c r="C13" s="201">
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="E13" s="138" t="s">
+        <v>258</v>
       </c>
       <c r="F13">
         <f>Market_Price</f>
-        <v>13.82</v>
-      </c>
-      <c r="H13" s="166"/>
+        <v>15.68</v>
+      </c>
+      <c r="H13" s="164"/>
     </row>
     <row r="14" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="164" t="s">
-        <v>285</v>
-      </c>
-      <c r="C14" s="207">
+      <c r="B14" s="162" t="s">
+        <v>284</v>
+      </c>
+      <c r="C14" s="202">
         <v>10</v>
       </c>
-      <c r="E14" s="139" t="s">
-        <v>290</v>
-      </c>
-      <c r="H14" s="166"/>
+      <c r="E14" s="138" t="s">
+        <v>289</v>
+      </c>
+      <c r="H14" s="164"/>
     </row>
     <row r="15" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="209" t="s">
-        <v>246</v>
-      </c>
-      <c r="C15" s="187">
+      <c r="B15" s="204" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="185">
         <f>(F49-C7)/Common_Shares*C3</f>
-        <v>13.822088197770135</v>
+        <v>15.699957264324397</v>
       </c>
       <c r="D15" t="str">
         <f>IF(ROUND(C15,1)=ROUND(F13,1),"equals Market Price","a Current Projection")</f>
         <v>equals Market Price</v>
       </c>
-      <c r="E15" s="139" t="s">
-        <v>287</v>
-      </c>
-      <c r="H15" s="166"/>
+      <c r="E15" s="138" t="s">
+        <v>286</v>
+      </c>
+      <c r="H15" s="164"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="H16" s="166"/>
+      <c r="H16" s="164"/>
     </row>
     <row r="17" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B17" s="174" t="s">
+      <c r="B17" s="172" t="s">
+        <v>246</v>
+      </c>
+      <c r="C17" s="172" t="s">
         <v>247</v>
       </c>
-      <c r="C17" s="174" t="s">
+      <c r="D17" s="172" t="s">
+        <v>259</v>
+      </c>
+      <c r="E17" s="172" t="s">
         <v>248</v>
       </c>
-      <c r="D17" s="174" t="s">
-        <v>260</v>
-      </c>
-      <c r="E17" s="174" t="s">
+      <c r="F17" s="173" t="s">
         <v>249</v>
       </c>
-      <c r="F17" s="175" t="s">
-        <v>250</v>
-      </c>
-      <c r="H17" s="166"/>
+      <c r="H17" s="164"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B18" s="168">
+      <c r="B18" s="166">
         <v>1</v>
       </c>
-      <c r="C18" s="169">
+      <c r="C18" s="167">
         <f>C4*(1+D18)</f>
-        <v>1179183.7338524768</v>
-      </c>
-      <c r="D18" s="185">
+        <v>1222386.5861703476</v>
+      </c>
+      <c r="D18" s="183">
         <f>IF($C$14&lt;B18,0,Model!$C$13)</f>
-        <v>-7.1999999999999995E-2</v>
-      </c>
-      <c r="E18" s="170">
-        <f>IF($C$14&lt;B18,0,1/(1+$C$5)^B18)</f>
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="E18" s="168">
+        <f t="shared" ref="E18:E47" si="0">IF($C$14&lt;B18,0,1/(1+Equity_Cost)^B18)</f>
         <v>0.90909090909090906</v>
       </c>
-      <c r="F18" s="171">
-        <f t="shared" ref="F18:F48" si="0">C18*E18</f>
-        <v>1071985.2125931608</v>
-      </c>
-      <c r="H18" s="166"/>
+      <c r="F18" s="169">
+        <f t="shared" ref="F18:F48" si="1">C18*E18</f>
+        <v>1111260.5328821342</v>
+      </c>
+      <c r="H18" s="164"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B19" s="168">
+      <c r="B19" s="166">
         <v>2</v>
       </c>
-      <c r="C19" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D19)^(ROW()-ROW($C$18)), 0)</f>
-        <v>1094282.5050150985</v>
-      </c>
-      <c r="D19" s="185">
+      <c r="C19" s="167">
+        <f t="shared" ref="C19:C47" si="2">IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D19)^(ROW()-ROW($C$18)), 0)</f>
+        <v>1175935.8958958744</v>
+      </c>
+      <c r="D19" s="183">
         <f>IF($C$14&lt;B19,0,Model!$C$13)</f>
-        <v>-7.1999999999999995E-2</v>
-      </c>
-      <c r="E19" s="170">
-        <f>IF($C$14&lt;B19,0,1/(1+$C$5)^B19)</f>
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="E19" s="168">
+        <f t="shared" si="0"/>
         <v>0.82644628099173545</v>
       </c>
-      <c r="F19" s="171">
+      <c r="F19" s="169">
+        <f t="shared" si="1"/>
+        <v>971847.84784782992</v>
+      </c>
+      <c r="H19" s="164"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B20" s="166">
+        <v>3</v>
+      </c>
+      <c r="C20" s="167">
+        <f t="shared" si="2"/>
+        <v>1131250.3318518312</v>
+      </c>
+      <c r="D20" s="183">
+        <f>IF($C$14&lt;B20,0,Model!$C$13)</f>
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="E20" s="168">
         <f t="shared" si="0"/>
-        <v>904365.7066240483</v>
-      </c>
-      <c r="H19" s="166"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B20" s="168">
-        <v>3</v>
-      </c>
-      <c r="C20" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D20)^(ROW()-ROW($C$18)), 0)</f>
-        <v>1015494.1646540115</v>
-      </c>
-      <c r="D20" s="185">
-        <f>IF($C$14&lt;B20,0,Model!$C$13)</f>
-        <v>-7.1999999999999995E-2</v>
-      </c>
-      <c r="E20" s="170">
-        <f>IF($C$14&lt;B20,0,1/(1+$C$5)^B20)</f>
         <v>0.75131480090157754</v>
       </c>
-      <c r="F20" s="171">
+      <c r="F20" s="169">
+        <f t="shared" si="1"/>
+        <v>849925.1178451021</v>
+      </c>
+      <c r="H20" s="164"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B21" s="166">
+        <v>4</v>
+      </c>
+      <c r="C21" s="167">
+        <f t="shared" si="2"/>
+        <v>1088262.8192414616</v>
+      </c>
+      <c r="D21" s="183">
+        <f>IF($C$14&lt;B21,0,Model!$C$13)</f>
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="E21" s="168">
         <f t="shared" si="0"/>
-        <v>762955.79613374243</v>
-      </c>
-      <c r="H20" s="166"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B21" s="168">
-        <v>4</v>
-      </c>
-      <c r="C21" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D21)^(ROW()-ROW($C$18)), 0)</f>
-        <v>942378.58479892265</v>
-      </c>
-      <c r="D21" s="185">
-        <f>IF($C$14&lt;B21,0,Model!$C$13)</f>
-        <v>-7.1999999999999995E-2</v>
-      </c>
-      <c r="E21" s="170">
-        <f>IF($C$14&lt;B21,0,1/(1+$C$5)^B21)</f>
         <v>0.68301345536507052</v>
       </c>
-      <c r="F21" s="171">
+      <c r="F21" s="169">
+        <f t="shared" si="1"/>
+        <v>743298.14851544378</v>
+      </c>
+      <c r="H21" s="164"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B22" s="166">
+        <v>5</v>
+      </c>
+      <c r="C22" s="167">
+        <f t="shared" si="2"/>
+        <v>1046908.832110286</v>
+      </c>
+      <c r="D22" s="183">
+        <f>IF($C$14&lt;B22,0,Model!$C$13)</f>
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="E22" s="168">
         <f t="shared" si="0"/>
-        <v>643657.25346555724</v>
-      </c>
-      <c r="H21" s="166"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B22" s="168">
-        <v>5</v>
-      </c>
-      <c r="C22" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D22)^(ROW()-ROW($C$18)), 0)</f>
-        <v>874527.32669340027</v>
-      </c>
-      <c r="D22" s="185">
-        <f>IF($C$14&lt;B22,0,Model!$C$13)</f>
-        <v>-7.1999999999999995E-2</v>
-      </c>
-      <c r="E22" s="170">
-        <f>IF($C$14&lt;B22,0,1/(1+$C$5)^B22)</f>
         <v>0.62092132305915493</v>
       </c>
-      <c r="F22" s="171">
+      <c r="F22" s="169">
+        <f t="shared" si="1"/>
+        <v>650048.01715623343</v>
+      </c>
+      <c r="H22" s="164"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="166">
+        <v>6</v>
+      </c>
+      <c r="C23" s="167">
+        <f t="shared" si="2"/>
+        <v>1007126.2964900951</v>
+      </c>
+      <c r="D23" s="183">
+        <f>IF($C$14&lt;B23,0,Model!$C$13)</f>
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="E23" s="168">
         <f t="shared" si="0"/>
-        <v>543012.66474185197</v>
-      </c>
-      <c r="H22" s="166"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B23" s="168">
-        <v>6</v>
-      </c>
-      <c r="C23" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D23)^(ROW()-ROW($C$18)), 0)</f>
-        <v>811561.35917147552</v>
-      </c>
-      <c r="D23" s="185">
-        <f>IF($C$14&lt;B23,0,Model!$C$13)</f>
-        <v>-7.1999999999999995E-2</v>
-      </c>
-      <c r="E23" s="170">
-        <f>IF($C$14&lt;B23,0,1/(1+$C$5)^B23)</f>
         <v>0.56447393005377722</v>
       </c>
-      <c r="F23" s="171">
+      <c r="F23" s="169">
+        <f t="shared" si="1"/>
+        <v>568496.53864026966</v>
+      </c>
+      <c r="H23" s="164"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="166">
+        <v>7</v>
+      </c>
+      <c r="C24" s="167">
+        <f t="shared" si="2"/>
+        <v>968855.49722347141</v>
+      </c>
+      <c r="D24" s="183">
+        <f>IF($C$14&lt;B24,0,Model!$C$13)</f>
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="E24" s="168">
         <f t="shared" si="0"/>
-        <v>458105.22989130783</v>
-      </c>
-      <c r="H23" s="166"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B24" s="168">
-        <v>7</v>
-      </c>
-      <c r="C24" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D24)^(ROW()-ROW($C$18)), 0)</f>
-        <v>753128.94131112937</v>
-      </c>
-      <c r="D24" s="185">
-        <f>IF($C$14&lt;B24,0,Model!$C$13)</f>
-        <v>-7.1999999999999995E-2</v>
-      </c>
-      <c r="E24" s="170">
-        <f>IF($C$14&lt;B24,0,1/(1+$C$5)^B24)</f>
         <v>0.51315811823070645</v>
       </c>
-      <c r="F24" s="171">
+      <c r="F24" s="169">
+        <f t="shared" si="1"/>
+        <v>497176.06379267201</v>
+      </c>
+      <c r="H24" s="164"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B25" s="166">
+        <v>8</v>
+      </c>
+      <c r="C25" s="167">
+        <f t="shared" si="2"/>
+        <v>932038.98832897947</v>
+      </c>
+      <c r="D25" s="183">
+        <f>IF($C$14&lt;B25,0,Model!$C$13)</f>
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="E25" s="168">
         <f t="shared" si="0"/>
-        <v>386474.23030830332</v>
-      </c>
-      <c r="H24" s="166"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B25" s="168">
-        <v>8</v>
-      </c>
-      <c r="C25" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D25)^(ROW()-ROW($C$18)), 0)</f>
-        <v>698903.65753672796</v>
-      </c>
-      <c r="D25" s="185">
-        <f>IF($C$14&lt;B25,0,Model!$C$13)</f>
-        <v>-7.1999999999999995E-2</v>
-      </c>
-      <c r="E25" s="170">
-        <f>IF($C$14&lt;B25,0,1/(1+$C$5)^B25)</f>
         <v>0.46650738020973315</v>
       </c>
-      <c r="F25" s="171">
+      <c r="F25" s="169">
+        <f t="shared" si="1"/>
+        <v>434803.06669868226</v>
+      </c>
+      <c r="H25" s="164"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="166">
+        <v>9</v>
+      </c>
+      <c r="C26" s="167">
+        <f t="shared" si="2"/>
+        <v>896621.50677247834</v>
+      </c>
+      <c r="D26" s="183">
+        <f>IF($C$14&lt;B26,0,Model!$C$13)</f>
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="E26" s="168">
         <f t="shared" si="0"/>
-        <v>326043.71429645945</v>
-      </c>
-      <c r="H25" s="166"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B26" s="168">
-        <v>9</v>
-      </c>
-      <c r="C26" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D26)^(ROW()-ROW($C$18)), 0)</f>
-        <v>648582.59419408359</v>
-      </c>
-      <c r="D26" s="185">
-        <f>IF($C$14&lt;B26,0,Model!$C$13)</f>
-        <v>-7.1999999999999995E-2</v>
-      </c>
-      <c r="E26" s="170">
-        <f>IF($C$14&lt;B26,0,1/(1+$C$5)^B26)</f>
         <v>0.42409761837248466</v>
       </c>
-      <c r="F26" s="171">
+      <c r="F26" s="169">
+        <f t="shared" si="1"/>
+        <v>380255.04560375668</v>
+      </c>
+      <c r="H26" s="164"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B27" s="166">
+        <v>10</v>
+      </c>
+      <c r="C27" s="167">
+        <f t="shared" si="2"/>
+        <v>862549.88951512414</v>
+      </c>
+      <c r="D27" s="183">
+        <f>IF($C$14&lt;B27,0,Model!$C$13)</f>
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="E27" s="168">
         <f t="shared" si="0"/>
-        <v>275062.33351555857</v>
-      </c>
-      <c r="H26" s="166"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B27" s="168">
-        <v>10</v>
-      </c>
-      <c r="C27" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D27)^(ROW()-ROW($C$18)), 0)</f>
-        <v>601884.64741210965</v>
-      </c>
-      <c r="D27" s="185">
-        <f>IF($C$14&lt;B27,0,Model!$C$13)</f>
-        <v>-7.1999999999999995E-2</v>
-      </c>
-      <c r="E27" s="170">
-        <f>IF($C$14&lt;B27,0,1/(1+$C$5)^B27)</f>
         <v>0.38554328942953148</v>
       </c>
-      <c r="F27" s="171">
+      <c r="F27" s="169">
+        <f t="shared" si="1"/>
+        <v>332550.32170073991</v>
+      </c>
+      <c r="H27" s="164"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B28" s="166">
+        <v>11</v>
+      </c>
+      <c r="C28" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="183">
+        <f>IF($C$14&lt;B28,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="168">
         <f t="shared" si="0"/>
-        <v>232052.58682039849</v>
-      </c>
-      <c r="H27" s="166"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B28" s="168">
-        <v>11</v>
-      </c>
-      <c r="C28" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D28)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="185">
-        <f>IF($C$14&lt;B28,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="170">
-        <f>IF($C$14&lt;B28,0,1/(1+$C$5)^B28)</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="171">
+        <v>0</v>
+      </c>
+      <c r="F28" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="164"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B29" s="166">
+        <v>12</v>
+      </c>
+      <c r="C29" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="183">
+        <f>IF($C$14&lt;B29,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H28" s="166"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B29" s="168">
-        <v>12</v>
-      </c>
-      <c r="C29" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D29)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="185">
-        <f>IF($C$14&lt;B29,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="170">
-        <f>IF($C$14&lt;B29,0,1/(1+$C$5)^B29)</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="171">
+      <c r="F29" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="164"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B30" s="166">
+        <v>13</v>
+      </c>
+      <c r="C30" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="183">
+        <f>IF($C$14&lt;B30,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H29" s="166"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B30" s="168">
-        <v>13</v>
-      </c>
-      <c r="C30" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D30)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="185">
-        <f>IF($C$14&lt;B30,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="170">
-        <f>IF($C$14&lt;B30,0,1/(1+$C$5)^B30)</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="171">
+      <c r="F30" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="164"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="166">
+        <v>14</v>
+      </c>
+      <c r="C31" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="183">
+        <f>IF($C$14&lt;B31,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H30" s="166"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B31" s="168">
-        <v>14</v>
-      </c>
-      <c r="C31" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D31)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D31" s="185">
-        <f>IF($C$14&lt;B31,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="170">
-        <f>IF($C$14&lt;B31,0,1/(1+$C$5)^B31)</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="171">
+      <c r="F31" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="164"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B32" s="166">
+        <v>15</v>
+      </c>
+      <c r="C32" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="183">
+        <f>IF($C$14&lt;B32,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H31" s="166"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B32" s="168">
-        <v>15</v>
-      </c>
-      <c r="C32" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D32)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="185">
-        <f>IF($C$14&lt;B32,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="170">
-        <f>IF($C$14&lt;B32,0,1/(1+$C$5)^B32)</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="171">
+      <c r="F32" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="164"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33" s="166">
+        <v>16</v>
+      </c>
+      <c r="C33" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="183">
+        <f>IF($C$14&lt;B33,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H32" s="166"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B33" s="168">
-        <v>16</v>
-      </c>
-      <c r="C33" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D33)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="185">
-        <f>IF($C$14&lt;B33,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="170">
-        <f>IF($C$14&lt;B33,0,1/(1+$C$5)^B33)</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="171">
+      <c r="F33" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="164"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34" s="166">
+        <v>17</v>
+      </c>
+      <c r="C34" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="183">
+        <f>IF($C$14&lt;B34,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H33" s="166"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B34" s="168">
-        <v>17</v>
-      </c>
-      <c r="C34" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D34)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="185">
-        <f>IF($C$14&lt;B34,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="170">
-        <f>IF($C$14&lt;B34,0,1/(1+$C$5)^B34)</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="171">
+      <c r="F34" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="164"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B35" s="166">
+        <v>18</v>
+      </c>
+      <c r="C35" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="183">
+        <f>IF($C$14&lt;B35,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H34" s="166"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B35" s="168">
-        <v>18</v>
-      </c>
-      <c r="C35" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D35)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D35" s="185">
-        <f>IF($C$14&lt;B35,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="170">
-        <f>IF($C$14&lt;B35,0,1/(1+$C$5)^B35)</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="171">
+      <c r="F35" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="164"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B36" s="166">
+        <v>19</v>
+      </c>
+      <c r="C36" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="183">
+        <f>IF($C$14&lt;B36,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H35" s="166"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B36" s="168">
-        <v>19</v>
-      </c>
-      <c r="C36" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D36)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="185">
-        <f>IF($C$14&lt;B36,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="170">
-        <f>IF($C$14&lt;B36,0,1/(1+$C$5)^B36)</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="171">
+      <c r="F36" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="164"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="166">
+        <v>20</v>
+      </c>
+      <c r="C37" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="183">
+        <f>IF($C$14&lt;B37,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H36" s="166"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B37" s="168">
-        <v>20</v>
-      </c>
-      <c r="C37" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D37)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="185">
-        <f>IF($C$14&lt;B37,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E37" s="170">
-        <f>IF($C$14&lt;B37,0,1/(1+$C$5)^B37)</f>
-        <v>0</v>
-      </c>
-      <c r="F37" s="171">
+      <c r="F37" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="164"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38" s="166">
+        <v>21</v>
+      </c>
+      <c r="C38" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="183">
+        <f>IF($C$14&lt;B38,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H37" s="166"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B38" s="168">
-        <v>21</v>
-      </c>
-      <c r="C38" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D38)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D38" s="185">
-        <f>IF($C$14&lt;B38,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="170">
-        <f>IF($C$14&lt;B38,0,1/(1+$C$5)^B38)</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="171">
+      <c r="F38" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="164"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B39" s="166">
+        <v>22</v>
+      </c>
+      <c r="C39" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="183">
+        <f>IF($C$14&lt;B39,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H38" s="166"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B39" s="168">
-        <v>22</v>
-      </c>
-      <c r="C39" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D39)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D39" s="185">
-        <f>IF($C$14&lt;B39,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="170">
-        <f>IF($C$14&lt;B39,0,1/(1+$C$5)^B39)</f>
-        <v>0</v>
-      </c>
-      <c r="F39" s="171">
+      <c r="F39" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="164"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B40" s="166">
+        <v>23</v>
+      </c>
+      <c r="C40" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="183">
+        <f>IF($C$14&lt;B40,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H39" s="166"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B40" s="168">
-        <v>23</v>
-      </c>
-      <c r="C40" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D40)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="185">
-        <f>IF($C$14&lt;B40,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="170">
-        <f>IF($C$14&lt;B40,0,1/(1+$C$5)^B40)</f>
-        <v>0</v>
-      </c>
-      <c r="F40" s="171">
+      <c r="F40" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="164"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B41" s="166">
+        <v>24</v>
+      </c>
+      <c r="C41" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="183">
+        <f>IF($C$14&lt;B41,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H40" s="166"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B41" s="168">
-        <v>24</v>
-      </c>
-      <c r="C41" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D41)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D41" s="185">
-        <f>IF($C$14&lt;B41,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E41" s="170">
-        <f>IF($C$14&lt;B41,0,1/(1+$C$5)^B41)</f>
-        <v>0</v>
-      </c>
-      <c r="F41" s="171">
+      <c r="F41" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="164"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B42" s="166">
+        <v>25</v>
+      </c>
+      <c r="C42" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="183">
+        <f>IF($C$14&lt;B42,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H41" s="166"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B42" s="168">
-        <v>25</v>
-      </c>
-      <c r="C42" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D42)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="185">
-        <f>IF($C$14&lt;B42,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="170">
-        <f>IF($C$14&lt;B42,0,1/(1+$C$5)^B42)</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="171">
+      <c r="F42" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="164"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B43" s="166">
+        <v>26</v>
+      </c>
+      <c r="C43" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="183">
+        <f>IF($C$14&lt;B43,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H42" s="166"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B43" s="168">
-        <v>26</v>
-      </c>
-      <c r="C43" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D43)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D43" s="185">
-        <f>IF($C$14&lt;B43,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="170">
-        <f>IF($C$14&lt;B43,0,1/(1+$C$5)^B43)</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="171">
+      <c r="F43" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="164"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B44" s="166">
+        <v>27</v>
+      </c>
+      <c r="C44" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="183">
+        <f>IF($C$14&lt;B44,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H43" s="166"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B44" s="168">
-        <v>27</v>
-      </c>
-      <c r="C44" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D44)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D44" s="185">
-        <f>IF($C$14&lt;B44,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="170">
-        <f>IF($C$14&lt;B44,0,1/(1+$C$5)^B44)</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="171">
+      <c r="F44" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="164"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B45" s="166">
+        <v>28</v>
+      </c>
+      <c r="C45" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="183">
+        <f>IF($C$14&lt;B45,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H44" s="166"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B45" s="168">
-        <v>28</v>
-      </c>
-      <c r="C45" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D45)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="185">
-        <f>IF($C$14&lt;B45,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E45" s="170">
-        <f>IF($C$14&lt;B45,0,1/(1+$C$5)^B45)</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="171">
+      <c r="F45" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="164"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B46" s="166">
+        <v>29</v>
+      </c>
+      <c r="C46" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D46" s="183">
+        <f>IF($C$14&lt;B46,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H45" s="166"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B46" s="168">
-        <v>29</v>
-      </c>
-      <c r="C46" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D46)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="185">
-        <f>IF($C$14&lt;B46,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E46" s="170">
-        <f>IF($C$14&lt;B46,0,1/(1+$C$5)^B46)</f>
-        <v>0</v>
-      </c>
-      <c r="F46" s="171">
+      <c r="F46" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="164"/>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B47" s="166">
+        <v>30</v>
+      </c>
+      <c r="C47" s="167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D47" s="183">
+        <f>IF($C$14&lt;B47,0,Model!$C$13)</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H46" s="166"/>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B47" s="168">
-        <v>30</v>
-      </c>
-      <c r="C47" s="169">
-        <f>IF(ROW()-ROW($C$18)&lt;$C$14, $C$18*(1+D47)^(ROW()-ROW($C$18)), 0)</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="185">
-        <f>IF($C$14&lt;B47,0,Model!$C$13)</f>
-        <v>0</v>
-      </c>
-      <c r="E47" s="170">
-        <f>IF($C$14&lt;B47,0,1/(1+$C$5)^B47)</f>
-        <v>0</v>
-      </c>
-      <c r="F47" s="171">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H47" s="166"/>
+      <c r="F47" s="169">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="164"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B48" s="172" t="s">
-        <v>282</v>
-      </c>
-      <c r="C48" s="169">
-        <f>C$18*(1+D48)^$C$14/C5</f>
-        <v>11791837.338524768</v>
-      </c>
-      <c r="D48" s="186">
-        <f>F4</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="170">
-        <f>1/(1+C5)^C14</f>
+      <c r="B48" s="170" t="s">
+        <v>281</v>
+      </c>
+      <c r="C48" s="167">
+        <f>C$18*(1+Terminal_Growth)^$C$14/Equity_Cost</f>
+        <v>12223865.861703476</v>
+      </c>
+      <c r="D48" s="184">
+        <f>Terminal_Growth</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="168">
+        <f>1/(1+Equity_Cost)^C14</f>
         <v>0.38554328942953148</v>
       </c>
-      <c r="F48" s="171">
-        <f t="shared" si="0"/>
-        <v>4546263.7559128106</v>
-      </c>
-      <c r="H48" s="166"/>
+      <c r="F48" s="169">
+        <f t="shared" si="1"/>
+        <v>4712829.4538665125</v>
+      </c>
+      <c r="H48" s="164"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C49" s="160"/>
-      <c r="E49" s="173" t="s">
-        <v>238</v>
-      </c>
-      <c r="F49" s="184">
+      <c r="C49" s="158"/>
+      <c r="E49" s="171" t="s">
+        <v>237</v>
+      </c>
+      <c r="F49" s="182">
         <f>SUM(F18:F48)</f>
-        <v>10149978.484303199</v>
-      </c>
-      <c r="H49" s="166"/>
+        <v>11252490.154549377</v>
+      </c>
+      <c r="H49" s="164"/>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C50" s="160"/>
-      <c r="H50" s="166"/>
+      <c r="C50" s="158"/>
+      <c r="H50" s="164"/>
     </row>
     <row r="51" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
-      <c r="B51" s="165" t="s">
-        <v>280</v>
-      </c>
-      <c r="C51" s="183"/>
-      <c r="D51" s="183"/>
-      <c r="E51" s="163"/>
-      <c r="F51" s="163"/>
-      <c r="H51" s="166"/>
+      <c r="B51" s="163" t="s">
+        <v>279</v>
+      </c>
+      <c r="C51" s="181"/>
+      <c r="D51" s="181"/>
+      <c r="E51" s="161"/>
+      <c r="F51" s="161"/>
+      <c r="H51" s="164"/>
     </row>
     <row r="52" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B52" s="179">
+      <c r="B52" s="177">
         <f>F49</f>
-        <v>10149978.484303199</v>
-      </c>
-      <c r="C52" s="177">
+        <v>11252490.154549377</v>
+      </c>
+      <c r="C52" s="175">
         <f>C73</f>
         <v>-0.15</v>
       </c>
-      <c r="D52" s="177">
+      <c r="D52" s="175">
         <f>C72</f>
         <v>0</v>
       </c>
-      <c r="E52" s="177">
+      <c r="E52" s="175">
         <f>C71</f>
         <v>0.01</v>
       </c>
-      <c r="F52" s="177">
+      <c r="F52" s="175">
         <f>C70</f>
         <v>0.02</v>
       </c>
-      <c r="H52" s="166"/>
+      <c r="H52" s="164"/>
     </row>
     <row r="53" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B53" s="192">
+      <c r="B53" s="189">
         <v>5</v>
       </c>
-      <c r="C53" s="169">
+      <c r="C53" s="167">
         <f t="dataTable" ref="C53:F58" dt2D="1" dtr="1" r1="C13" r2="C14"/>
         <v>9836413.3965352103</v>
       </c>
-      <c r="D53" s="169">
+      <c r="D53" s="167">
         <v>12706721.269962028</v>
       </c>
-      <c r="E53" s="169">
+      <c r="E53" s="167">
         <v>12922692.982327804</v>
       </c>
-      <c r="F53" s="169">
+      <c r="F53" s="167">
         <v>13142141.538962446</v>
       </c>
-      <c r="H53" s="166"/>
+      <c r="H53" s="164"/>
     </row>
     <row r="54" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B54" s="192">
+      <c r="B54" s="189">
         <v>10</v>
       </c>
-      <c r="C54" s="169">
+      <c r="C54" s="167">
         <v>8156502.4549473226</v>
       </c>
-      <c r="D54" s="169">
+      <c r="D54" s="167">
         <v>12706721.269962028</v>
       </c>
-      <c r="E54" s="169">
+      <c r="E54" s="167">
         <v>13134802.320367645</v>
       </c>
-      <c r="F54" s="169">
+      <c r="F54" s="167">
         <v>13583940.944009084</v>
       </c>
-      <c r="H54" s="166"/>
+      <c r="H54" s="164"/>
     </row>
     <row r="55" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B55" s="192">
+      <c r="B55" s="189">
         <v>15</v>
       </c>
-      <c r="C55" s="169">
+      <c r="C55" s="167">
         <v>6815544.6738921013</v>
       </c>
-      <c r="D55" s="169">
+      <c r="D55" s="167">
         <v>12706721.269962026</v>
       </c>
-      <c r="E55" s="169">
+      <c r="E55" s="167">
         <v>13368901.948442612</v>
       </c>
-      <c r="F55" s="169">
+      <c r="F55" s="167">
         <v>14083969.893871106</v>
       </c>
-      <c r="H55" s="166"/>
+      <c r="H55" s="164"/>
     </row>
     <row r="56" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B56" s="193">
+      <c r="B56" s="190">
         <v>20</v>
       </c>
-      <c r="C56" s="169">
+      <c r="C56" s="167">
         <v>5900851.7022183863</v>
       </c>
-      <c r="D56" s="169">
+      <c r="D56" s="167">
         <v>12706721.269962026</v>
       </c>
-      <c r="E56" s="169">
+      <c r="E56" s="167">
         <v>13581082.743169647</v>
       </c>
-      <c r="F56" s="169">
+      <c r="F56" s="167">
         <v>14549180.863933826</v>
       </c>
-      <c r="H56" s="166"/>
+      <c r="H56" s="164"/>
     </row>
     <row r="57" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B57" s="193">
+      <c r="B57" s="190">
         <v>25</v>
       </c>
-      <c r="C57" s="169">
+      <c r="C57" s="167">
         <v>5310290.2851397078</v>
       </c>
-      <c r="D57" s="169">
+      <c r="D57" s="167">
         <v>12706721.269962026</v>
       </c>
-      <c r="E57" s="169">
+      <c r="E57" s="167">
         <v>13756438.873081338</v>
       </c>
-      <c r="F57" s="169">
+      <c r="F57" s="167">
         <v>14944116.610065991</v>
       </c>
-      <c r="H57" s="166"/>
+      <c r="H57" s="164"/>
     </row>
     <row r="58" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B58" s="193">
+      <c r="B58" s="190">
         <v>30</v>
       </c>
-      <c r="C58" s="169">
+      <c r="C58" s="167">
         <v>4937369.1785926893</v>
       </c>
-      <c r="D58" s="169">
+      <c r="D58" s="167">
         <v>12706721.269962024</v>
       </c>
-      <c r="E58" s="169">
+      <c r="E58" s="167">
         <v>13893779.935453041</v>
       </c>
-      <c r="F58" s="169">
+      <c r="F58" s="167">
         <v>15262060.98258711</v>
       </c>
-      <c r="H58" s="166"/>
+      <c r="H58" s="164"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C59" s="160"/>
-      <c r="D59" s="160"/>
-      <c r="E59" s="160"/>
-      <c r="F59" s="160"/>
-      <c r="H59" s="166"/>
+      <c r="C59" s="158"/>
+      <c r="D59" s="158"/>
+      <c r="E59" s="158"/>
+      <c r="F59" s="158"/>
+      <c r="H59" s="164"/>
     </row>
     <row r="60" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
-      <c r="B60" s="165" t="s">
-        <v>281</v>
-      </c>
-      <c r="C60" s="160"/>
-      <c r="D60" s="160"/>
-      <c r="E60" s="160"/>
-      <c r="F60" s="160"/>
-      <c r="H60" s="166"/>
+      <c r="B60" s="163" t="s">
+        <v>280</v>
+      </c>
+      <c r="C60" s="158"/>
+      <c r="D60" s="158"/>
+      <c r="E60" s="158"/>
+      <c r="F60" s="158"/>
+      <c r="H60" s="164"/>
     </row>
     <row r="61" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="C61" s="178">
+      <c r="C61" s="176">
         <f>C52</f>
         <v>-0.15</v>
       </c>
-      <c r="D61" s="178">
+      <c r="D61" s="176">
         <f>D52</f>
         <v>0</v>
       </c>
-      <c r="E61" s="178">
+      <c r="E61" s="176">
         <f>E52</f>
         <v>0.01</v>
       </c>
-      <c r="F61" s="178">
+      <c r="F61" s="176">
         <f>F52</f>
         <v>0.02</v>
       </c>
-      <c r="H61" s="166"/>
+      <c r="H61" s="164"/>
     </row>
     <row r="62" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B62" s="192">
-        <f>B53</f>
+      <c r="B62" s="189">
+        <f t="shared" ref="B62:B67" si="3">B53</f>
         <v>5</v>
       </c>
-      <c r="C62" s="205">
-        <f t="shared" ref="B62:F67" si="1">(C53-$C$7)/Common_Shares*$C$3</f>
+      <c r="C62" s="168">
+        <f t="shared" ref="C62:F67" si="4">(C53-$C$7)/Common_Shares*$C$3</f>
         <v>13.288003893211801</v>
       </c>
-      <c r="D62" s="188">
-        <f t="shared" si="1"/>
+      <c r="D62" s="186">
+        <f t="shared" si="4"/>
         <v>18.176897600606136</v>
       </c>
-      <c r="E62" s="205">
-        <f t="shared" si="1"/>
+      <c r="E62" s="168">
+        <f t="shared" si="4"/>
         <v>18.544754566520961</v>
       </c>
-      <c r="F62" s="205">
-        <f t="shared" si="1"/>
+      <c r="F62" s="168">
+        <f t="shared" si="4"/>
         <v>18.918533518096286</v>
       </c>
-      <c r="H62" s="166"/>
+      <c r="H62" s="164"/>
     </row>
     <row r="63" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B63" s="192">
-        <f>B54</f>
+      <c r="B63" s="189">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="C63" s="205">
-        <f t="shared" si="1"/>
+      <c r="C63" s="168">
+        <f t="shared" si="4"/>
         <v>10.426671104716659</v>
       </c>
-      <c r="D63" s="205">
-        <f t="shared" si="1"/>
+      <c r="D63" s="168">
+        <f t="shared" si="4"/>
         <v>18.176897600606136</v>
       </c>
-      <c r="E63" s="205">
-        <f t="shared" si="1"/>
+      <c r="E63" s="168">
+        <f t="shared" si="4"/>
         <v>18.906032887088198</v>
       </c>
-      <c r="F63" s="205">
-        <f t="shared" si="1"/>
+      <c r="F63" s="168">
+        <f t="shared" si="4"/>
         <v>19.671034792004711</v>
       </c>
-      <c r="H63" s="166"/>
+      <c r="H63" s="164"/>
     </row>
     <row r="64" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B64" s="192">
-        <f>B55</f>
+      <c r="B64" s="189">
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="C64" s="205">
-        <f t="shared" si="1"/>
+      <c r="C64" s="168">
+        <f t="shared" si="4"/>
         <v>8.1426652256346106</v>
       </c>
-      <c r="D64" s="205">
-        <f t="shared" si="1"/>
+      <c r="D64" s="168">
+        <f t="shared" si="4"/>
         <v>18.176897600606136</v>
       </c>
-      <c r="E64" s="205">
-        <f t="shared" si="1"/>
+      <c r="E64" s="168">
+        <f t="shared" si="4"/>
         <v>19.304766489568504</v>
       </c>
-      <c r="F64" s="205">
-        <f t="shared" si="1"/>
+      <c r="F64" s="168">
+        <f t="shared" si="4"/>
         <v>20.522716386556755</v>
       </c>
-      <c r="H64" s="166"/>
+      <c r="H64" s="164"/>
     </row>
     <row r="65" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B65" s="193">
-        <f>B56</f>
+      <c r="B65" s="190">
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="C65" s="205">
-        <f t="shared" si="1"/>
+      <c r="C65" s="168">
+        <f t="shared" si="4"/>
         <v>6.5847010940466664</v>
       </c>
-      <c r="D65" s="205">
-        <f t="shared" si="1"/>
+      <c r="D65" s="168">
+        <f t="shared" si="4"/>
         <v>18.176897600606136</v>
       </c>
-      <c r="E65" s="205">
-        <f t="shared" si="1"/>
+      <c r="E65" s="168">
+        <f t="shared" si="4"/>
         <v>19.666166519779367</v>
       </c>
-      <c r="F65" s="205">
-        <f t="shared" si="1"/>
+      <c r="F65" s="168">
+        <f t="shared" si="4"/>
         <v>21.315093749698331</v>
       </c>
-      <c r="H65" s="166"/>
+      <c r="H65" s="164"/>
     </row>
     <row r="66" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B66" s="193">
-        <f>B57</f>
+      <c r="B66" s="190">
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="C66" s="205">
-        <f t="shared" si="1"/>
+      <c r="C66" s="168">
+        <f t="shared" si="4"/>
         <v>5.5788187555995172</v>
       </c>
-      <c r="D66" s="205">
-        <f t="shared" si="1"/>
+      <c r="D66" s="168">
+        <f t="shared" si="4"/>
         <v>18.176897600606136</v>
       </c>
-      <c r="E66" s="205">
-        <f t="shared" si="1"/>
+      <c r="E66" s="168">
+        <f t="shared" si="4"/>
         <v>19.964844403087675</v>
       </c>
-      <c r="F66" s="205">
-        <f t="shared" si="1"/>
+      <c r="F66" s="168">
+        <f t="shared" si="4"/>
         <v>21.987773813731142</v>
       </c>
     </row>
     <row r="67" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B67" s="193">
-        <f>B58</f>
+      <c r="B67" s="190">
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="C67" s="205">
-        <f t="shared" si="1"/>
+      <c r="C67" s="168">
+        <f t="shared" si="4"/>
         <v>4.9436354472056356</v>
       </c>
-      <c r="D67" s="205">
-        <f t="shared" si="1"/>
+      <c r="D67" s="168">
+        <f t="shared" si="4"/>
         <v>18.176897600606132</v>
       </c>
-      <c r="E67" s="205">
-        <f t="shared" si="1"/>
+      <c r="E67" s="168">
+        <f t="shared" si="4"/>
         <v>20.198772568707845</v>
       </c>
-      <c r="F67" s="205">
-        <f t="shared" si="1"/>
+      <c r="F67" s="168">
+        <f t="shared" si="4"/>
         <v>22.529317198853857</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B69" s="174" t="s">
-        <v>258</v>
-      </c>
-      <c r="C69" s="174" t="s">
-        <v>283</v>
-      </c>
-      <c r="D69" s="174" t="s">
+      <c r="B69" s="172" t="s">
+        <v>257</v>
+      </c>
+      <c r="C69" s="172" t="s">
+        <v>282</v>
+      </c>
+      <c r="D69" s="172" t="s">
+        <v>251</v>
+      </c>
+      <c r="E69" s="173" t="s">
         <v>252</v>
       </c>
-      <c r="E69" s="175" t="s">
-        <v>253</v>
-      </c>
-      <c r="F69" s="175" t="s">
-        <v>261</v>
+      <c r="F69" s="173" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B70" s="173" t="s">
-        <v>255</v>
-      </c>
-      <c r="C70" s="189">
+      <c r="B70" s="171" t="s">
+        <v>254</v>
+      </c>
+      <c r="C70" s="187">
         <v>0.02</v>
       </c>
-      <c r="D70" s="194">
+      <c r="D70" s="191">
         <v>10</v>
       </c>
-      <c r="E70" s="182">
+      <c r="E70" s="180">
         <f>INDEX(C$62:F$67, MATCH(D70, B$62:B$67, 0), MATCH(C70, C$61:F$61, 0))</f>
         <v>19.671034792004711</v>
       </c>
-      <c r="F70" s="189">
+      <c r="F70" s="187">
         <v>0.15</v>
       </c>
-      <c r="H70" s="166" t="s">
-        <v>245</v>
+      <c r="H70" s="164" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B71" s="173" t="s">
-        <v>256</v>
-      </c>
-      <c r="C71" s="189">
+      <c r="B71" s="171" t="s">
+        <v>255</v>
+      </c>
+      <c r="C71" s="187">
         <v>0.01</v>
       </c>
-      <c r="D71" s="194">
+      <c r="D71" s="191">
         <v>5</v>
       </c>
-      <c r="E71" s="182">
+      <c r="E71" s="180">
         <f>INDEX(C$62:F$67, MATCH(D71, B$62:B$67, 0), MATCH(C71, C$61:F$61, 0))</f>
         <v>18.544754566520961</v>
       </c>
-      <c r="F71" s="189">
+      <c r="F71" s="187">
         <v>0.5</v>
       </c>
-      <c r="H71" s="166" t="s">
-        <v>244</v>
+      <c r="H71" s="164" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B72" s="173" t="s">
-        <v>254</v>
-      </c>
-      <c r="C72" s="190">
-        <v>0</v>
-      </c>
-      <c r="D72" s="195">
-        <v>0</v>
-      </c>
-      <c r="E72" s="182">
+      <c r="B72" s="171" t="s">
+        <v>253</v>
+      </c>
+      <c r="C72" s="188">
+        <v>0</v>
+      </c>
+      <c r="D72" s="192">
+        <v>0</v>
+      </c>
+      <c r="E72" s="180">
         <f>$C$9</f>
         <v>18.176897600606146</v>
       </c>
-      <c r="F72" s="189">
+      <c r="F72" s="187">
         <v>0.2</v>
       </c>
-      <c r="H72" s="166" t="s">
-        <v>243</v>
+      <c r="H72" s="164" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B73" s="173" t="s">
-        <v>257</v>
-      </c>
-      <c r="C73" s="189">
+      <c r="B73" s="171" t="s">
+        <v>256</v>
+      </c>
+      <c r="C73" s="187">
         <v>-0.15</v>
       </c>
-      <c r="D73" s="194">
+      <c r="D73" s="191">
         <v>5</v>
       </c>
-      <c r="E73" s="182">
+      <c r="E73" s="180">
         <f>INDEX(C$62:F$67, MATCH(D73, B$62:B$67, 0), MATCH(C73, C$61:F$61, 0))</f>
         <v>13.288003893211801</v>
       </c>
-      <c r="F73" s="189">
+      <c r="F73" s="187">
         <v>0.15</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B74" t="str">
+      <c r="B74" s="208" t="str">
         <f>IF(VLOOKUP("No Growth",B70:E73,4,FALSE)&gt;VLOOKUP("Base",B70:E73,4,FALSE),"Note: the No Growth value being higher than the Base or Optimistic values is unusual.","OK")</f>
         <v>OK</v>
       </c>
-      <c r="F74" s="191" t="str">
+      <c r="C74" s="208"/>
+      <c r="D74" s="208"/>
+      <c r="E74" s="208"/>
+      <c r="F74" s="209" t="str">
         <f>IF(SUM(F70:F73)=1,"100% - OK",SUM(F70:F73)*100&amp;"% Error")</f>
         <v>100% - OK</v>
       </c>
     </row>
     <row r="76" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B76" s="139" t="s">
-        <v>262</v>
-      </c>
-      <c r="C76" s="196">
+      <c r="B76" s="138" t="s">
+        <v>261</v>
+      </c>
+      <c r="C76" s="207">
         <f>E70*F70+E71*F71+E72*F72+E73*F73</f>
         <v>17.851612606164188</v>
       </c>
+      <c r="D76" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
     </row>
     <row r="78" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B78" s="39" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C78" s="40"/>
       <c r="D78" s="40"/>
@@ -11657,95 +11856,95 @@
       <c r="F78" s="40"/>
     </row>
     <row r="79" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B79" s="153" t="s">
-        <v>273</v>
-      </c>
-      <c r="E79" s="153" t="s">
-        <v>270</v>
+      <c r="B79" s="151" t="s">
+        <v>272</v>
+      </c>
+      <c r="E79" s="151" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B80" s="139" t="s">
-        <v>291</v>
-      </c>
-      <c r="C80" s="180">
+      <c r="B80" s="138" t="s">
+        <v>290</v>
+      </c>
+      <c r="C80" s="178">
         <f>Thesis!C37</f>
         <v>0.2</v>
       </c>
-      <c r="E80" s="139" t="s">
-        <v>274</v>
+      <c r="E80" s="138" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B81" s="139" t="s">
-        <v>251</v>
+      <c r="B81" s="138" t="s">
+        <v>250</v>
       </c>
       <c r="C81">
-        <f>FCF!C86</f>
+        <f>FCF!C87</f>
         <v>1.3599999999999999</v>
       </c>
       <c r="D81" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E81" s="139" t="s">
-        <v>272</v>
-      </c>
-      <c r="F81" s="203">
+      <c r="E81" s="138" t="s">
+        <v>271</v>
+      </c>
+      <c r="F81" s="199">
         <v>3</v>
       </c>
     </row>
     <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B83" s="153" t="s">
-        <v>289</v>
+      <c r="B83" s="151" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B84" s="139" t="s">
-        <v>263</v>
-      </c>
-      <c r="C84" s="162">
+      <c r="B84" s="138" t="s">
+        <v>262</v>
+      </c>
+      <c r="C84" s="160">
         <f>PV(C80, F81, -C81, 0)</f>
         <v>2.8648148148148143</v>
       </c>
-      <c r="D84" s="139"/>
+      <c r="D84" s="138"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B85" s="139" t="s">
-        <v>265</v>
-      </c>
-      <c r="C85" s="162">
+      <c r="B85" s="138" t="s">
+        <v>264</v>
+      </c>
+      <c r="C85" s="160">
         <f>C76/(1+C80)^F81</f>
         <v>10.330794332270942</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B86" s="155" t="s">
-        <v>239</v>
-      </c>
-      <c r="C86" s="156">
+      <c r="B86" s="153" t="s">
+        <v>238</v>
+      </c>
+      <c r="C86" s="154">
         <f>C84+C85</f>
         <v>13.195609147085756</v>
       </c>
-      <c r="D86" s="197" t="s">
-        <v>277</v>
-      </c>
-      <c r="E86" s="198">
+      <c r="D86" s="193" t="s">
+        <v>276</v>
+      </c>
+      <c r="E86" s="194">
         <f>-(C86/C76-1)</f>
         <v>0.2608169671725179</v>
       </c>
-      <c r="H86" s="166" t="s">
-        <v>264</v>
+      <c r="H86" s="164" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C89" s="161"/>
+      <c r="C89" s="159"/>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C90" s="161"/>
+      <c r="C90" s="159"/>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C91" s="161"/>
+      <c r="C91" s="159"/>
     </row>
   </sheetData>
   <autoFilter ref="B69:F69" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
@@ -11753,19 +11952,19 @@
       <sortCondition descending="1" ref="E69"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="30" type="noConversion"/>
-  <conditionalFormatting sqref="C28:F47">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+  <phoneticPr fontId="29" type="noConversion"/>
+  <conditionalFormatting sqref="C18:F47">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C62:F67">
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="1" priority="6">
       <formula>ISNUMBER(MATCH(C62, $E$70:$E$73, 0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E70:E73">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
       <formula>$F$13</formula>
     </cfRule>
   </conditionalFormatting>

--- a/financial_models/templates/Valuation_v2.01.xlsx
+++ b/financial_models/templates/Valuation_v2.01.xlsx
@@ -1,32 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB25BC2-9CFF-4955-B846-4DB0095C749C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEB05DB-B186-4FDE-AC7A-28F585CD5C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
-    <sheet name="FCF" sheetId="2" r:id="rId3"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId3"/>
     <sheet name="BS" sheetId="3" r:id="rId4"/>
-    <sheet name="Model" sheetId="8" r:id="rId5"/>
+    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Model!$B$69:$F$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$69:$F$69</definedName>
     <definedName name="Common_Shares">Thesis!$C$11</definedName>
-    <definedName name="Equity_Cost">Model!$C$5</definedName>
+    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$10</definedName>
     <definedName name="Reporting_currency">Thesis!$C$12</definedName>
-    <definedName name="Terminal_Growth">Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="319">
   <si>
     <t>HKD</t>
   </si>
@@ -868,10 +869,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>FCFE Before WCInv</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FCFE/Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1184,10 +1181,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Operating FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Total FCFE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1201,6 +1194,86 @@
   </si>
   <si>
     <t>Leverage %</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>YoY Growth Rates</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sales</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Current Situation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Op. FCFE Before WCInv</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sales Growth Rates</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Past Years Selected</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Rate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Margin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Op. FCFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Optimistic Case</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Scenario</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No Growth Scenario</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Objective Scenarios</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Subjective Scenarios</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Probabilities</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target Return</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Business Story</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tie the business story into the three levers of value: FCFE, growth and risk.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unbiased Scenario where the company FCFE has no growth and no risk.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1227,7 +1300,7 @@
     <numFmt numFmtId="191" formatCode="0&quot; yrs&quot;"/>
     <numFmt numFmtId="192" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1484,6 +1557,24 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1529,7 +1620,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1568,11 +1659,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1986,24 +2114,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="186" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="30" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="191" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="191" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="30" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="191" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2016,12 +2135,6 @@
     </xf>
     <xf numFmtId="191" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="191" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2045,7 +2158,45 @@
     <xf numFmtId="184" fontId="14" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="184" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="191" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="191" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2100,8 +2251,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -2324,7 +2475,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
@@ -2504,10 +2655,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C23" s="100">
-        <f>FCF!C11</f>
+        <f>Normalized_FCF!C11</f>
         <v>1080495.1269962033</v>
       </c>
       <c r="D23" s="1" t="str">
@@ -2517,10 +2668,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C24" s="100">
-        <f>FCF!C19</f>
+        <f>Normalized_FCF!C19</f>
         <v>190177</v>
       </c>
     </row>
@@ -2535,16 +2686,16 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C27" s="100">
-        <f>FCF!C20</f>
+        <f>Normalized_FCF!C20</f>
         <v>1270672.1269962033</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C28" s="143">
         <f>C27/(Common_Shares/Data!C3)</f>
@@ -2553,7 +2704,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B29" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C29" s="123">
         <f>C28/Market_Price</f>
@@ -2591,10 +2742,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C37" s="165">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -2602,12 +2753,12 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B39" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B40" s="144" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C40" s="150">
         <v>0</v>
@@ -2618,18 +2769,18 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B41" s="144" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C41" s="150">
         <v>0</v>
       </c>
       <c r="D41" s="149" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B42" s="144" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C42" s="150">
         <v>0</v>
@@ -2637,7 +2788,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B43" s="91" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C43" s="92">
         <f>SUM(C40:C42)</f>
@@ -2727,162 +2878,184 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B65" s="52" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B67" s="1" t="s">
+    <row r="66" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="B66" s="138" t="s">
+        <v>272</v>
+      </c>
+      <c r="C66"/>
+    </row>
+    <row r="67" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="B67" s="138" t="s">
+        <v>270</v>
+      </c>
+      <c r="C67" s="196">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="B68" s="138" t="s">
+        <v>314</v>
+      </c>
+      <c r="C68" s="217">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B69" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C67" s="206">
-        <f>Model!E86</f>
-        <v>0.2608169671725179</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B69" s="52" t="s">
+      <c r="C69" s="201">
+        <f>Scenarios!F54</f>
+        <v>-0.2608169671725179</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B71" s="52" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B70" s="1" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B72" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="19" t="str">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="19" t="str">
         <f>"5."</f>
         <v>5.</v>
       </c>
-      <c r="B72" s="52" t="s">
+      <c r="B74" s="52" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B73" s="52" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B75" s="52" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B74" s="1" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B76" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B76" s="52" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B78" s="52" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B77" s="1" t="s">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B79" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B78" s="1" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B80" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A80" s="39" t="s">
+    <row r="82" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A82" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="B80" s="39"/>
-      <c r="C80" s="39"/>
-      <c r="D80" s="39"/>
-      <c r="E80" s="39"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B81" s="52" t="s">
+      <c r="B82" s="39"/>
+      <c r="C82" s="39"/>
+      <c r="D82" s="39"/>
+      <c r="E82" s="39"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B83" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="C81" s="195">
-        <f>Model!C86</f>
+      <c r="C83" s="192">
+        <f>Scenarios!C54</f>
         <v>13.195609147085756</v>
       </c>
-      <c r="D81" s="1" t="str">
+      <c r="D83" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B83" s="52" t="s">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B85" s="52" t="s">
         <v>127</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B84" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B85" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B86" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B87" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B88" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B88" s="52" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B90" s="52" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B89" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B90" s="1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B91" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B93" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A93" s="39" t="s">
+    <row r="95" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A95" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="B93" s="39"/>
-      <c r="C93" s="39"/>
-      <c r="D93" s="39"/>
-      <c r="E93" s="39"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B94" s="52" t="s">
+      <c r="B95" s="39"/>
+      <c r="C95" s="39"/>
+      <c r="D95" s="39"/>
+      <c r="E95" s="39"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B96" s="52" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B95" s="1" t="s">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B97" s="52" t="s">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B99" s="52" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B98" s="1" t="s">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B100" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B100" s="52" t="s">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B102" s="52" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B101" s="1" t="s">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B103" s="1" t="s">
         <v>125</v>
       </c>
     </row>
@@ -2912,7 +3085,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M71"/>
+  <dimension ref="B1:M67"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
@@ -2972,7 +3145,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="39" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -4935,47 +5108,6 @@
         <f t="shared" si="38"/>
         <v/>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B69" s="124" t="s">
-        <v>53</v>
-      </c>
-      <c r="C69" s="125" t="s">
-        <v>56</v>
-      </c>
-      <c r="D69" s="125" t="s">
-        <v>57</v>
-      </c>
-      <c r="E69" s="119" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B70" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C70" s="14">
-        <f>FCF!L8</f>
-        <v>1617067</v>
-      </c>
-      <c r="D70" s="14">
-        <f>FCF!G8</f>
-        <v>1876773</v>
-      </c>
-      <c r="E70" s="14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B71" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C71" s="8">
-        <f>(D70/C70)^(1/E70)-1</f>
-        <v>2.5133963029188244E-2</v>
-      </c>
-      <c r="D71" s="43"/>
-      <c r="E71" s="43"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -5003,7 +5135,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q798"/>
+  <dimension ref="A1:Q802"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
@@ -5076,7 +5208,7 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="61" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C2" s="61"/>
       <c r="D2" s="63"/>
@@ -5099,7 +5231,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C3" s="146">
         <f>Data!C3</f>
@@ -5174,16 +5306,16 @@
         <v>80</v>
       </c>
       <c r="C5" s="77">
-        <f>C45</f>
+        <f>C49</f>
         <v>-10739107.696087126</v>
       </c>
       <c r="E5" s="20"/>
       <c r="G5" s="65">
-        <f>G45</f>
+        <f>G49</f>
         <v>-13195082</v>
       </c>
       <c r="H5" s="65">
-        <f t="shared" ref="H5:Q5" si="1">H45</f>
+        <f t="shared" ref="H5:Q5" si="1">H49</f>
         <v>-10265436</v>
       </c>
       <c r="I5" s="65">
@@ -5284,16 +5416,16 @@
         <v>79</v>
       </c>
       <c r="C7" s="77">
-        <f>C48</f>
+        <f>C52</f>
         <v>-302359.25</v>
       </c>
       <c r="E7" s="20"/>
       <c r="G7" s="77">
-        <f>G48</f>
+        <f>G52</f>
         <v>-254107</v>
       </c>
       <c r="H7" s="77">
-        <f t="shared" ref="H7:Q7" si="3">H48</f>
+        <f t="shared" ref="H7:Q7" si="3">H52</f>
         <v>-349526</v>
       </c>
       <c r="I7" s="77">
@@ -5396,16 +5528,16 @@
         <v>159</v>
       </c>
       <c r="C9" s="77">
-        <f>C61</f>
+        <f>C65</f>
         <v>-30619</v>
       </c>
       <c r="E9" s="20"/>
       <c r="G9" s="77">
-        <f>G61</f>
+        <f>G65</f>
         <v>-30619</v>
       </c>
       <c r="H9" s="77">
-        <f t="shared" ref="H9:Q9" si="5">H61</f>
+        <f t="shared" ref="H9:Q9" si="5">H65</f>
         <v>12362</v>
       </c>
       <c r="I9" s="77">
@@ -5727,7 +5859,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12"/>
       <c r="B15" s="34" t="s">
-        <v>217</v>
+        <v>302</v>
       </c>
       <c r="C15" s="80">
         <f>SUM(C11:C14)</f>
@@ -5737,47 +5869,47 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="80">
-        <f>IF(G$4="","",SUM(G11:G14))</f>
+        <f t="shared" ref="G15:Q15" si="7">IF(G$4="","",SUM(G11:G14))</f>
         <v>1306025</v>
       </c>
       <c r="H15" s="80">
-        <f>IF(H$4="","",SUM(H11:H14))</f>
+        <f t="shared" si="7"/>
         <v>1359024</v>
       </c>
       <c r="I15" s="80">
-        <f>IF(I$4="","",SUM(I11:I14))</f>
+        <f t="shared" si="7"/>
         <v>1171856</v>
       </c>
       <c r="J15" s="80">
-        <f>IF(J$4="","",SUM(J11:J14))</f>
+        <f t="shared" si="7"/>
         <v>1116233</v>
       </c>
       <c r="K15" s="80">
-        <f>IF(K$4="","",SUM(K11:K14))</f>
+        <f t="shared" si="7"/>
         <v>1140356</v>
       </c>
       <c r="L15" s="80">
-        <f>IF(L$4="","",SUM(L11:L14))</f>
+        <f t="shared" si="7"/>
         <v>1571906</v>
       </c>
       <c r="M15" s="80" t="str">
-        <f>IF(M$4="","",SUM(M11:M14))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N15" s="80" t="str">
-        <f>IF(N$4="","",SUM(N11:N14))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="O15" s="80" t="str">
-        <f>IF(O$4="","",SUM(O11:O14))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="P15" s="80" t="str">
-        <f>IF(P$4="","",SUM(P11:P14))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="Q15" s="80" t="str">
-        <f>IF(Q$4="","",SUM(Q11:Q14))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -5841,14 +5973,14 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C17" s="77">
         <v>0</v>
       </c>
       <c r="D17" s="66"/>
       <c r="E17" s="85" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F17" s="66"/>
       <c r="G17" s="148"/>
@@ -5866,7 +5998,7 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12"/>
       <c r="B18" s="34" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="C18" s="80">
         <f>SUM(C15:C17)</f>
@@ -5875,48 +6007,48 @@
       <c r="D18" s="66"/>
       <c r="E18" s="85"/>
       <c r="F18" s="66"/>
-      <c r="G18" s="212">
+      <c r="G18" s="80">
         <f>IF(G$4="","",SUM(G15:G17))</f>
         <v>679442</v>
       </c>
-      <c r="H18" s="212">
-        <f t="shared" ref="H18:Q18" si="7">IF(H$4="","",SUM(H15:H17))</f>
+      <c r="H18" s="80">
+        <f t="shared" ref="H18:Q18" si="8">IF(H$4="","",SUM(H15:H17))</f>
         <v>1006925</v>
       </c>
-      <c r="I18" s="212">
-        <f t="shared" si="7"/>
+      <c r="I18" s="80">
+        <f t="shared" si="8"/>
         <v>126605</v>
       </c>
-      <c r="J18" s="212">
-        <f t="shared" si="7"/>
+      <c r="J18" s="80">
+        <f t="shared" si="8"/>
         <v>1934910</v>
       </c>
-      <c r="K18" s="212">
-        <f t="shared" si="7"/>
+      <c r="K18" s="80">
+        <f t="shared" si="8"/>
         <v>1140356</v>
       </c>
-      <c r="L18" s="212">
-        <f t="shared" si="7"/>
+      <c r="L18" s="80">
+        <f t="shared" si="8"/>
         <v>1571906</v>
       </c>
-      <c r="M18" s="212" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="N18" s="212" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="O18" s="212" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P18" s="212" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="Q18" s="212" t="str">
-        <f t="shared" si="7"/>
+      <c r="M18" s="80" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="N18" s="80" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="O18" s="80" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="P18" s="80" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="Q18" s="80" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
@@ -5925,7 +6057,7 @@
       <c r="B19" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="211">
+      <c r="C19" s="206">
         <f>MIN(G19:J19)</f>
         <v>190177</v>
       </c>
@@ -5982,7 +6114,7 @@
     <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12"/>
       <c r="B20" s="34" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C20" s="80">
         <f>C18+C19</f>
@@ -5996,43 +6128,43 @@
         <v>927759</v>
       </c>
       <c r="H20" s="68">
-        <f t="shared" ref="H20:Q20" si="8">IF(H$4="","",H18+H19)</f>
+        <f t="shared" ref="H20:Q20" si="9">IF(H$4="","",H18+H19)</f>
         <v>1197102</v>
       </c>
       <c r="I20" s="68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>327302</v>
       </c>
       <c r="J20" s="68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2216164</v>
       </c>
       <c r="K20" s="68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>864978</v>
       </c>
       <c r="L20" s="68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-10908</v>
       </c>
       <c r="M20" s="68" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="N20" s="68" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="O20" s="68" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="P20" s="68" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q20" s="68" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -6082,54 +6214,54 @@
         <v>80</v>
       </c>
       <c r="C23" s="101">
-        <f>ABS(C5/C$4)</f>
+        <f t="shared" ref="C23:C29" si="10">ABS(C5/C$4)</f>
         <v>0.85916636172912864</v>
       </c>
       <c r="D23" s="30"/>
       <c r="E23" s="86"/>
       <c r="F23" s="30"/>
       <c r="G23" s="8">
-        <f>IF(G$4="","",ABS(G5/G$4))</f>
+        <f t="shared" ref="G23:Q23" si="11">IF(G$4="","",ABS(G5/G$4))</f>
         <v>0.86096272455849754</v>
       </c>
       <c r="H23" s="8">
-        <f>IF(H$4="","",ABS(H5/H$4))</f>
+        <f t="shared" si="11"/>
         <v>0.85703537297697319</v>
       </c>
       <c r="I23" s="8">
-        <f>IF(I$4="","",ABS(I5/I$4))</f>
+        <f t="shared" si="11"/>
         <v>0.85154513157189637</v>
       </c>
       <c r="J23" s="8">
-        <f>IF(J$4="","",ABS(J5/J$4))</f>
+        <f t="shared" si="11"/>
         <v>0.86234342793721264</v>
       </c>
       <c r="K23" s="8">
-        <f>IF(K$4="","",ABS(K5/K$4))</f>
+        <f t="shared" si="11"/>
         <v>0.70419372087965826</v>
       </c>
       <c r="L23" s="8">
-        <f>IF(L$4="","",ABS(L5/L$4))</f>
+        <f t="shared" si="11"/>
         <v>0.74565961264792724</v>
       </c>
       <c r="M23" s="8" t="str">
-        <f>IF(M$4="","",ABS(M5/M$4))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="N23" s="8" t="str">
-        <f>IF(N$4="","",ABS(N5/N$4))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="O23" s="8" t="str">
-        <f>IF(O$4="","",ABS(O5/O$4))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="P23" s="8" t="str">
-        <f>IF(P$4="","",ABS(P5/P$4))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="Q23" s="8" t="str">
-        <f>IF(Q$4="","",ABS(Q5/Q$4))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -6139,54 +6271,54 @@
         <v>82</v>
       </c>
       <c r="C24" s="102">
-        <f>ABS(C6/C$4)</f>
+        <f t="shared" si="10"/>
         <v>0.14083363827087136</v>
       </c>
       <c r="D24" s="30"/>
       <c r="E24" s="86"/>
       <c r="F24" s="30"/>
       <c r="G24" s="79">
-        <f>IF(G$4="","",ABS(G6/G$4))</f>
+        <f t="shared" ref="G24:Q24" si="12">IF(G$4="","",ABS(G6/G$4))</f>
         <v>0.13903727544150246</v>
       </c>
       <c r="H24" s="79">
-        <f>IF(H$4="","",ABS(H6/H$4))</f>
+        <f t="shared" si="12"/>
         <v>0.14296462702302684</v>
       </c>
       <c r="I24" s="79">
-        <f>IF(I$4="","",ABS(I6/I$4))</f>
+        <f t="shared" si="12"/>
         <v>0.14845486842810363</v>
       </c>
       <c r="J24" s="79">
-        <f>IF(J$4="","",ABS(J6/J$4))</f>
+        <f t="shared" si="12"/>
         <v>0.13765657206278739</v>
       </c>
       <c r="K24" s="79">
-        <f>IF(K$4="","",ABS(K6/K$4))</f>
+        <f t="shared" si="12"/>
         <v>0.29580627912034169</v>
       </c>
       <c r="L24" s="79">
-        <f>IF(L$4="","",ABS(L6/L$4))</f>
+        <f t="shared" si="12"/>
         <v>0.25434038735207271</v>
       </c>
       <c r="M24" s="79" t="str">
-        <f>IF(M$4="","",ABS(M6/M$4))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="N24" s="79" t="str">
-        <f>IF(N$4="","",ABS(N6/N$4))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="O24" s="79" t="str">
-        <f>IF(O$4="","",ABS(O6/O$4))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="P24" s="79" t="str">
-        <f>IF(P$4="","",ABS(P6/P$4))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Q24" s="79" t="str">
-        <f>IF(Q$4="","",ABS(Q6/Q$4))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -6196,54 +6328,54 @@
         <v>79</v>
       </c>
       <c r="C25" s="101">
-        <f>ABS(C7/C$4)</f>
+        <f t="shared" si="10"/>
         <v>2.4189802738666985E-2</v>
       </c>
       <c r="D25" s="30"/>
       <c r="E25" s="86"/>
       <c r="F25" s="30"/>
       <c r="G25" s="8">
-        <f>IF(G$4="","",ABS(G7/G$4))</f>
+        <f t="shared" ref="G25:Q25" si="13">IF(G$4="","",ABS(G7/G$4))</f>
         <v>1.6580166386945237E-2</v>
       </c>
       <c r="H25" s="8">
-        <f>IF(H$4="","",ABS(H7/H$4))</f>
+        <f t="shared" si="13"/>
         <v>2.9181044602016856E-2</v>
       </c>
       <c r="I25" s="8">
-        <f>IF(I$4="","",ABS(I7/I$4))</f>
+        <f t="shared" si="13"/>
         <v>2.7587615842589962E-2</v>
       </c>
       <c r="J25" s="8">
-        <f>IF(J$4="","",ABS(J7/J$4))</f>
+        <f t="shared" si="13"/>
         <v>3.1822067442433898E-2</v>
       </c>
       <c r="K25" s="8">
-        <f>IF(K$4="","",ABS(K7/K$4))</f>
+        <f t="shared" si="13"/>
         <v>0.18856108069142588</v>
       </c>
       <c r="L25" s="8">
-        <f>IF(L$4="","",ABS(L7/L$4))</f>
+        <f t="shared" si="13"/>
         <v>0.15238149582692045</v>
       </c>
       <c r="M25" s="8" t="str">
-        <f>IF(M$4="","",ABS(M7/M$4))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="N25" s="8" t="str">
-        <f>IF(N$4="","",ABS(N7/N$4))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="O25" s="8" t="str">
-        <f>IF(O$4="","",ABS(O7/O$4))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="P25" s="8" t="str">
-        <f>IF(P$4="","",ABS(P7/P$4))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="Q25" s="8" t="str">
-        <f>IF(Q$4="","",ABS(Q7/Q$4))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -6253,54 +6385,54 @@
         <v>63</v>
       </c>
       <c r="C26" s="102">
-        <f>ABS(C8/C$4)</f>
+        <f t="shared" si="10"/>
         <v>0.11664383553220437</v>
       </c>
       <c r="D26" s="30"/>
       <c r="E26" s="86"/>
       <c r="F26" s="30"/>
       <c r="G26" s="79">
-        <f>IF(G$4="","",ABS(G8/G$4))</f>
+        <f t="shared" ref="G26:Q26" si="14">IF(G$4="","",ABS(G8/G$4))</f>
         <v>0.12245710905455723</v>
       </c>
       <c r="H26" s="79">
-        <f>IF(H$4="","",ABS(H8/H$4))</f>
+        <f t="shared" si="14"/>
         <v>0.11378358242100998</v>
       </c>
       <c r="I26" s="79">
-        <f>IF(I$4="","",ABS(I8/I$4))</f>
+        <f t="shared" si="14"/>
         <v>0.12086725258551366</v>
       </c>
       <c r="J26" s="79">
-        <f>IF(J$4="","",ABS(J8/J$4))</f>
+        <f t="shared" si="14"/>
         <v>0.10583450462035347</v>
       </c>
       <c r="K26" s="79">
-        <f>IF(K$4="","",ABS(K8/K$4))</f>
+        <f t="shared" si="14"/>
         <v>0.10724519842891581</v>
       </c>
       <c r="L26" s="79">
-        <f>IF(L$4="","",ABS(L8/L$4))</f>
+        <f t="shared" si="14"/>
         <v>0.10195889152515229</v>
       </c>
       <c r="M26" s="79" t="str">
-        <f>IF(M$4="","",ABS(M8/M$4))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N26" s="79" t="str">
-        <f>IF(N$4="","",ABS(N8/N$4))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="O26" s="79" t="str">
-        <f>IF(O$4="","",ABS(O8/O$4))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="P26" s="79" t="str">
-        <f>IF(P$4="","",ABS(P8/P$4))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q26" s="79" t="str">
-        <f>IF(Q$4="","",ABS(Q8/Q$4))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
@@ -6310,54 +6442,54 @@
         <v>159</v>
       </c>
       <c r="C27" s="101">
-        <f>ABS(C9/C$4)</f>
+        <f t="shared" si="10"/>
         <v>2.4496276203067853E-3</v>
       </c>
       <c r="D27" s="30"/>
       <c r="E27" s="86"/>
       <c r="F27" s="30"/>
       <c r="G27" s="8">
-        <f>IF(G$4="","",ABS(G9/G$4))</f>
+        <f t="shared" ref="G27:Q27" si="15">IF(G$4="","",ABS(G9/G$4))</f>
         <v>1.9978517498607917E-3</v>
       </c>
       <c r="H27" s="8">
-        <f>IF(H$4="","",ABS(H9/H$4))</f>
+        <f t="shared" si="15"/>
         <v>1.0320722160014773E-3</v>
       </c>
       <c r="I27" s="8">
-        <f>IF(I$4="","",ABS(I9/I$4))</f>
+        <f t="shared" si="15"/>
         <v>5.4735115251124938E-3</v>
       </c>
       <c r="J27" s="8">
-        <f>IF(J$4="","",ABS(J9/J$4))</f>
+        <f t="shared" si="15"/>
         <v>3.8988481983809435E-3</v>
       </c>
       <c r="K27" s="8">
-        <f>IF(K$4="","",ABS(K9/K$4))</f>
+        <f t="shared" si="15"/>
         <v>5.6147664039083583E-3</v>
       </c>
       <c r="L27" s="8">
-        <f>IF(L$4="","",ABS(L9/L$4))</f>
+        <f t="shared" si="15"/>
         <v>2.1597113239037349E-3</v>
       </c>
       <c r="M27" s="8" t="str">
-        <f>IF(M$4="","",ABS(M9/M$4))</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N27" s="8" t="str">
-        <f>IF(N$4="","",ABS(N9/N$4))</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="O27" s="8" t="str">
-        <f>IF(O$4="","",ABS(O9/O$4))</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="P27" s="8" t="str">
-        <f>IF(P$4="","",ABS(P9/P$4))</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="Q27" s="8" t="str">
-        <f>IF(Q$4="","",ABS(Q9/Q$4))</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -6367,54 +6499,54 @@
         <v>151</v>
       </c>
       <c r="C28" s="101">
-        <f>ABS(C10/C$4)</f>
+        <f t="shared" si="10"/>
         <v>2.7750800005147281E-2</v>
       </c>
       <c r="D28" s="30"/>
       <c r="E28" s="86"/>
       <c r="F28" s="30"/>
       <c r="G28" s="8">
-        <f>IF(G$4="","",ABS(G10/G$4))</f>
+        <f t="shared" ref="G28:Q28" si="16">IF(G$4="","",ABS(G10/G$4))</f>
         <v>2.134717546604905E-2</v>
       </c>
       <c r="H28" s="8">
-        <f>IF(H$4="","",ABS(H10/H$4))</f>
+        <f t="shared" si="16"/>
         <v>2.3431929819757211E-2</v>
       </c>
       <c r="I28" s="8">
-        <f>IF(I$4="","",ABS(I10/I$4))</f>
+        <f t="shared" si="16"/>
         <v>2.4816909944731565E-2</v>
       </c>
       <c r="J28" s="8">
-        <f>IF(J$4="","",ABS(J10/J$4))</f>
+        <f t="shared" si="16"/>
         <v>2.6666749423196391E-2</v>
       </c>
       <c r="K28" s="8">
-        <f>IF(K$4="","",ABS(K10/K$4))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="L28" s="8">
-        <f>IF(L$4="","",ABS(L10/L$4))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M28" s="8" t="str">
-        <f>IF(M$4="","",ABS(M10/M$4))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="N28" s="8" t="str">
-        <f>IF(N$4="","",ABS(N10/N$4))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O28" s="8" t="str">
-        <f>IF(O$4="","",ABS(O10/O$4))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="P28" s="8" t="str">
-        <f>IF(P$4="","",ABS(P10/P$4))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Q28" s="8" t="str">
-        <f>IF(Q$4="","",ABS(Q10/Q$4))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -6424,54 +6556,54 @@
         <v>185</v>
       </c>
       <c r="C29" s="102">
-        <f>ABS(C11/C$4)</f>
+        <f t="shared" si="10"/>
         <v>8.64434079067503E-2</v>
       </c>
       <c r="D29" s="30"/>
       <c r="E29" s="86"/>
       <c r="F29" s="30"/>
       <c r="G29" s="79">
-        <f>IF(G$4="","",ABS(G11/G$4))</f>
+        <f t="shared" ref="G29:Q29" si="17">IF(G$4="","",ABS(G11/G$4))</f>
         <v>9.9112081838647392E-2</v>
       </c>
       <c r="H29" s="79">
-        <f>IF(H$4="","",ABS(H11/H$4))</f>
+        <f t="shared" si="17"/>
         <v>9.1383724817254264E-2</v>
       </c>
       <c r="I29" s="79">
-        <f>IF(I$4="","",ABS(I11/I$4))</f>
+        <f t="shared" si="17"/>
         <v>0.10152385416589459</v>
       </c>
       <c r="J29" s="79">
-        <f>IF(J$4="","",ABS(J11/J$4))</f>
+        <f t="shared" si="17"/>
         <v>8.3066603395538036E-2</v>
       </c>
       <c r="K29" s="79">
-        <f>IF(K$4="","",ABS(K11/K$4))</f>
+        <f t="shared" si="17"/>
         <v>0.10163043202500745</v>
       </c>
       <c r="L29" s="79">
-        <f>IF(L$4="","",ABS(L11/L$4))</f>
+        <f t="shared" si="17"/>
         <v>9.9799180201248547E-2</v>
       </c>
       <c r="M29" s="79" t="str">
-        <f>IF(M$4="","",ABS(M11/M$4))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N29" s="79" t="str">
-        <f>IF(N$4="","",ABS(N11/N$4))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="O29" s="79" t="str">
-        <f>IF(O$4="","",ABS(O11/O$4))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P29" s="79" t="str">
-        <f>IF(P$4="","",ABS(P11/P$4))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="Q29" s="79" t="str">
-        <f>IF(Q$4="","",ABS(Q11/Q$4))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -6488,47 +6620,47 @@
       <c r="E30" s="86"/>
       <c r="F30" s="30"/>
       <c r="G30" s="8">
-        <f>IF(G$4="","",G19/G$4)</f>
+        <f t="shared" ref="G30:Q30" si="18">IF(G$4="","",G19/G$4)</f>
         <v>1.6202376072705908E-2</v>
       </c>
       <c r="H30" s="8">
-        <f>IF(H$4="","",H19/H$4)</f>
+        <f t="shared" si="18"/>
         <v>1.5877398303066895E-2</v>
       </c>
       <c r="I30" s="8">
-        <f>IF(I$4="","",I19/I$4)</f>
+        <f t="shared" si="18"/>
         <v>1.7098344553916948E-2</v>
       </c>
       <c r="J30" s="8">
-        <f>IF(J$4="","",J19/J$4)</f>
+        <f t="shared" si="18"/>
         <v>3.1739461379126283E-2</v>
       </c>
       <c r="K30" s="8">
-        <f>IF(K$4="","",K19/K$4)</f>
+        <f t="shared" si="18"/>
         <v>-2.4513406940554511E-2</v>
       </c>
       <c r="L30" s="8">
-        <f>IF(L$4="","",L19/L$4)</f>
+        <f t="shared" si="18"/>
         <v>-9.9799180201248547E-2</v>
       </c>
       <c r="M30" s="8" t="str">
-        <f>IF(M$4="","",M19/M$4)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N30" s="8" t="str">
-        <f>IF(N$4="","",N19/N$4)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="O30" s="8" t="str">
-        <f>IF(O$4="","",O19/O$4)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="P30" s="8" t="str">
-        <f>IF(P$4="","",P19/P$4)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="Q30" s="8" t="str">
-        <f>IF(Q$4="","",Q19/Q$4)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -6545,47 +6677,47 @@
       <c r="E31" s="86"/>
       <c r="F31" s="30"/>
       <c r="G31" s="8">
-        <f t="shared" ref="G31:Q31" si="9">IF(G$4="","",G12/G$4)</f>
+        <f t="shared" ref="G31:Q31" si="19">IF(G$4="","",G12/G$4)</f>
         <v>3.0237840861147901E-2</v>
       </c>
       <c r="H31" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>3.1034299661942499E-2</v>
       </c>
       <c r="I31" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>3.7116997107550703E-2</v>
       </c>
       <c r="J31" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>5.8782113530297636E-2</v>
       </c>
       <c r="K31" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="L31" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M31" s="8" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="N31" s="8" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="O31" s="8" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P31" s="8" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q31" s="8" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -6604,47 +6736,47 @@
       </c>
       <c r="F32" s="30"/>
       <c r="G32" s="8">
-        <f t="shared" ref="G32:Q32" si="10">IF(G$4="","",-G13/G$4)</f>
+        <f t="shared" ref="G32:Q32" si="20">IF(G$4="","",-G13/G$4)</f>
         <v>4.413341231043115E-2</v>
       </c>
       <c r="H32" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>8.9565367523571013E-3</v>
       </c>
       <c r="I32" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>3.8804791663312119E-2</v>
       </c>
       <c r="J32" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>1.5679014505150749E-2</v>
       </c>
       <c r="K32" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L32" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M32" s="8" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="N32" s="8" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O32" s="8" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="P32" s="8" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Q32" s="8" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -6663,47 +6795,47 @@
       </c>
       <c r="F33" s="30"/>
       <c r="G33" s="8">
-        <f t="shared" ref="G33:Q33" si="11">IF(G$4="","",-G16/G$4)</f>
+        <f t="shared" ref="G33:Q33" si="21">IF(G$4="","",-G16/G$4)</f>
         <v>4.0883763120383568E-2</v>
       </c>
       <c r="H33" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>2.9395857885609465E-2</v>
       </c>
       <c r="I33" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>8.9049969572670459E-2</v>
       </c>
       <c r="J33" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>-9.2387546571707307E-2</v>
       </c>
       <c r="K33" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L33" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M33" s="8" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N33" s="8" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="O33" s="8" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P33" s="8" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Q33" s="8" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -6720,47 +6852,47 @@
       <c r="E34" s="86"/>
       <c r="F34" s="30"/>
       <c r="G34" s="8">
-        <f t="shared" ref="G34:Q34" si="12">IF(G$4="","",-G14/G$4)</f>
+        <f t="shared" ref="G34:Q34" si="22">IF(G$4="","",-G14/G$4)</f>
         <v>0</v>
       </c>
       <c r="H34" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I34" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J34" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>2.0301681405792693E-4</v>
       </c>
       <c r="K34" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>1.1901613447523543E-4</v>
       </c>
       <c r="L34" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v>6.8776840338486973E-4</v>
       </c>
       <c r="M34" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="N34" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="O34" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="P34" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q34" s="8" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -6777,47 +6909,47 @@
       <c r="E35" s="86"/>
       <c r="F35" s="99"/>
       <c r="G35" s="79">
-        <f t="shared" ref="G35:Q35" si="13">IF(G$4="","",ABS(G20/G$4))</f>
+        <f t="shared" ref="G35:Q35" si="23">IF(G$4="","",ABS(G20/G$4))</f>
         <v>6.0535123341686481E-2</v>
       </c>
       <c r="H35" s="79">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>9.9943028144297091E-2</v>
       </c>
       <c r="I35" s="79">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>2.7884434591379664E-2</v>
       </c>
       <c r="J35" s="79">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>0.25009369355746058</v>
       </c>
       <c r="K35" s="79">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>7.69980089499777E-2</v>
       </c>
       <c r="L35" s="79">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v>6.8776840338486973E-4</v>
       </c>
       <c r="M35" s="79" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="N35" s="79" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="O35" s="79" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="P35" s="79" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Q35" s="79" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -6844,7 +6976,7 @@
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
-      <c r="B37" s="133" t="s">
+      <c r="B37" s="207" t="s">
         <v>187</v>
       </c>
       <c r="C37" s="74"/>
@@ -6878,54 +7010,54 @@
       </c>
       <c r="F38" s="30"/>
       <c r="G38" s="8">
-        <f>IF(G$4="","",-G10/(G8+G9))</f>
+        <f t="shared" ref="G38:Q38" si="24">IF(G$4="","",-G10/(G8+G9))</f>
         <v>0.17721490189875819</v>
       </c>
       <c r="H38" s="8">
-        <f>IF(H$4="","",-H10/(H8+H9))</f>
+        <f t="shared" si="24"/>
         <v>0.20408305726111148</v>
       </c>
       <c r="I38" s="8">
-        <f>IF(I$4="","",-I10/(I8+I9))</f>
+        <f t="shared" si="24"/>
         <v>0.19642836672256828</v>
       </c>
       <c r="J38" s="8">
-        <f>IF(J$4="","",-J10/(J8+J9))</f>
+        <f t="shared" si="24"/>
         <v>0.24301407674334419</v>
       </c>
       <c r="K38" s="8">
-        <f>IF(K$4="","",-K10/(K8+K9))</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L38" s="8">
-        <f>IF(L$4="","",-L10/(L8+L9))</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M38" s="8" t="str">
-        <f>IF(M$4="","",-M10/(M8+M9))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N38" s="8" t="str">
-        <f>IF(N$4="","",-N10/(N8+N9))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O38" s="8" t="str">
-        <f>IF(O$4="","",-O10/(O8+O9))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="P38" s="8" t="str">
-        <f>IF(P$4="","",-P10/(P8+P9))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="Q38" s="8" t="str">
-        <f>IF(Q$4="","",-Q10/(Q8+Q9))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12"/>
       <c r="B39" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C39" s="101">
         <f>C20*$C$3/(Market_Price*Common_Shares)</f>
@@ -6935,47 +7067,47 @@
       <c r="E39" s="86"/>
       <c r="F39" s="30"/>
       <c r="G39" s="101">
-        <f t="shared" ref="G39:Q39" si="14">IF(G$4="","",G20*$C$3/(Market_Price*Common_Shares))</f>
+        <f t="shared" ref="G39:Q39" si="25">IF(G$4="","",G20*$C$3/(Market_Price*Common_Shares))</f>
         <v>0.10077927517308544</v>
       </c>
       <c r="H39" s="101">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>0.13003708060848876</v>
       </c>
       <c r="I39" s="101">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>3.5553692632139609E-2</v>
       </c>
       <c r="J39" s="101">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>0.24073428722834889</v>
       </c>
       <c r="K39" s="101">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>9.3959590670276552E-2</v>
       </c>
       <c r="L39" s="101">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v>-1.1848985928328542E-3</v>
       </c>
       <c r="M39" s="101" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="N39" s="101" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O39" s="101" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="P39" s="101" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q39" s="101" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -6998,1385 +7130,1347 @@
       <c r="P40" s="14"/>
       <c r="Q40" s="14"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12"/>
-      <c r="B41" s="61" t="s">
-        <v>157</v>
-      </c>
-      <c r="C41" s="61"/>
-      <c r="D41" s="63"/>
-      <c r="E41" s="81" t="s">
-        <v>146</v>
-      </c>
-      <c r="F41" s="63"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="40"/>
-      <c r="M41" s="40"/>
-      <c r="N41" s="40"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
+      <c r="B41" s="207" t="s">
+        <v>299</v>
+      </c>
+      <c r="C41" s="74"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="86"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="14"/>
+      <c r="O41" s="14"/>
+      <c r="P41" s="14"/>
+      <c r="Q41" s="14"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12"/>
-      <c r="B42" s="78" t="s">
-        <v>150</v>
-      </c>
-      <c r="C42" s="74"/>
+      <c r="B42" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="C42" s="101">
+        <f>C4/G4-1</f>
+        <v>-0.18442634574369077</v>
+      </c>
       <c r="D42" s="30"/>
       <c r="E42" s="86"/>
       <c r="F42" s="30"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="14"/>
-      <c r="P42" s="14"/>
-      <c r="Q42" s="14"/>
+      <c r="G42" s="8">
+        <f>IF(H4="","",G4/H4-1)</f>
+        <v>0.27952593137796744</v>
+      </c>
+      <c r="H42" s="8">
+        <f t="shared" ref="H42:Q42" si="26">IF(I4="","",H4/I4-1)</f>
+        <v>2.0450249505806095E-2</v>
+      </c>
+      <c r="I42" s="8">
+        <f t="shared" si="26"/>
+        <v>0.32460887665346139</v>
+      </c>
+      <c r="J42" s="8">
+        <f t="shared" si="26"/>
+        <v>-0.21118785490642455</v>
+      </c>
+      <c r="K42" s="8">
+        <f t="shared" si="26"/>
+        <v>-0.29169116752280422</v>
+      </c>
+      <c r="L42" s="8" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="M42" s="8" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="N42" s="8" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="O42" s="8" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="P42" s="8" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="Q42" s="8" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="12"/>
-      <c r="B43" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C43" s="98">
-        <f>-C4*C51</f>
-        <v>-9031319.1044627018</v>
-      </c>
-      <c r="D43" s="66"/>
-      <c r="E43" s="85"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="65">
-        <f>Data!C33</f>
-        <v>-11151623</v>
-      </c>
-      <c r="H43" s="65">
-        <f>Data!D33</f>
-        <v>-8747447</v>
-      </c>
-      <c r="I43" s="65">
-        <f>Data!E33</f>
-        <v>-8503976</v>
-      </c>
-      <c r="J43" s="65">
-        <f>Data!F33</f>
-        <v>-6229020</v>
-      </c>
-      <c r="K43" s="65">
-        <f>Data!G33</f>
-        <v>-7910751</v>
-      </c>
-      <c r="L43" s="65">
-        <f>Data!H33</f>
-        <v>-11826154</v>
-      </c>
-      <c r="M43" s="65" t="str">
-        <f>Data!I33</f>
-        <v/>
-      </c>
-      <c r="N43" s="65" t="str">
-        <f>Data!J33</f>
-        <v/>
-      </c>
-      <c r="O43" s="65" t="str">
-        <f>Data!K33</f>
-        <v/>
-      </c>
-      <c r="P43" s="65" t="str">
-        <f>Data!L33</f>
-        <v/>
-      </c>
-      <c r="Q43" s="65" t="str">
-        <f>Data!M33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="30"/>
+      <c r="C43" s="74"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="86"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="14"/>
+      <c r="O43" s="14"/>
+      <c r="P43" s="14"/>
+      <c r="Q43" s="14"/>
+    </row>
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="12"/>
-      <c r="B44" s="87" t="s">
-        <v>149</v>
-      </c>
-      <c r="C44" s="77">
-        <f>-C4*C52</f>
-        <v>-1707788.5916244236</v>
-      </c>
+      <c r="B44" s="30"/>
+      <c r="C44" s="74"/>
       <c r="D44" s="30"/>
       <c r="E44" s="86"/>
       <c r="F44" s="30"/>
-      <c r="G44" s="65">
-        <f>Data!C36</f>
-        <v>-2043459</v>
-      </c>
-      <c r="H44" s="65">
-        <f>Data!D36</f>
-        <v>-1517989</v>
-      </c>
-      <c r="I44" s="65">
-        <f>Data!E36</f>
-        <v>-1491293</v>
-      </c>
-      <c r="J44" s="65">
-        <f>Data!F36</f>
-        <v>-1412494</v>
-      </c>
-      <c r="K44" s="65">
-        <f>Data!G36</f>
-        <v>0</v>
-      </c>
-      <c r="L44" s="65">
-        <f>Data!H36</f>
-        <v>0</v>
-      </c>
-      <c r="M44" s="65" t="str">
-        <f>Data!I36</f>
-        <v/>
-      </c>
-      <c r="N44" s="65" t="str">
-        <f>Data!J36</f>
-        <v/>
-      </c>
-      <c r="O44" s="65" t="str">
-        <f>Data!K36</f>
-        <v/>
-      </c>
-      <c r="P44" s="65" t="str">
-        <f>Data!L36</f>
-        <v/>
-      </c>
-      <c r="Q44" s="65" t="str">
-        <f>Data!M36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="14"/>
+      <c r="O44" s="14"/>
+      <c r="P44" s="14"/>
+      <c r="Q44" s="14"/>
+    </row>
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="12"/>
-      <c r="B45" s="91" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" s="80">
-        <f>C43+C44</f>
-        <v>-10739107.696087126</v>
-      </c>
-      <c r="D45" s="11"/>
-      <c r="E45" s="82"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="80">
-        <f>IF(G$4="","",G43+G44)</f>
-        <v>-13195082</v>
-      </c>
-      <c r="H45" s="80">
-        <f t="shared" ref="H45:Q45" si="15">IF(H$4="","",H43+H44)</f>
-        <v>-10265436</v>
-      </c>
-      <c r="I45" s="80">
-        <f t="shared" si="15"/>
-        <v>-9995269</v>
-      </c>
-      <c r="J45" s="80">
-        <f t="shared" si="15"/>
-        <v>-7641514</v>
-      </c>
-      <c r="K45" s="80">
-        <f t="shared" si="15"/>
-        <v>-7910751</v>
-      </c>
-      <c r="L45" s="80">
-        <f t="shared" si="15"/>
-        <v>-11826154</v>
-      </c>
-      <c r="M45" s="80" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="N45" s="80" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="O45" s="80" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="P45" s="80" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Q45" s="80" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+      <c r="B45" s="61" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="61"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="81" t="s">
+        <v>146</v>
+      </c>
+      <c r="F45" s="63"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="40"/>
+      <c r="K45" s="40"/>
+      <c r="L45" s="40"/>
+      <c r="M45" s="40"/>
+      <c r="N45" s="40"/>
+      <c r="O45" s="40"/>
+      <c r="P45" s="40"/>
+      <c r="Q45" s="40"/>
     </row>
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="12"/>
-      <c r="B46" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C46" s="97">
-        <f>AVERAGE(G46:J46)</f>
-        <v>-302359.25</v>
-      </c>
-      <c r="E46" s="83" t="s">
-        <v>192</v>
-      </c>
-      <c r="G46" s="77">
-        <f>Data!C37</f>
-        <v>-254107</v>
-      </c>
-      <c r="H46" s="77">
-        <f>Data!D37</f>
-        <v>-349526</v>
-      </c>
-      <c r="I46" s="77">
-        <f>Data!E37</f>
-        <v>-323818</v>
-      </c>
-      <c r="J46" s="77">
-        <f>Data!F37</f>
-        <v>-281986</v>
-      </c>
-      <c r="K46" s="77">
-        <f>Data!G37</f>
-        <v>-2118252</v>
-      </c>
-      <c r="L46" s="77">
-        <f>Data!H37</f>
-        <v>-2416769</v>
-      </c>
-      <c r="M46" s="77" t="str">
-        <f>Data!I37</f>
-        <v/>
-      </c>
-      <c r="N46" s="77" t="str">
-        <f>Data!J37</f>
-        <v/>
-      </c>
-      <c r="O46" s="77" t="str">
-        <f>Data!K37</f>
-        <v/>
-      </c>
-      <c r="P46" s="77" t="str">
-        <f>Data!L37</f>
-        <v/>
-      </c>
-      <c r="Q46" s="77" t="str">
-        <f>Data!M37</f>
-        <v/>
-      </c>
+      <c r="B46" s="78" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" s="74"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="86"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
+      <c r="M46" s="14"/>
+      <c r="N46" s="14"/>
+      <c r="O46" s="14"/>
+      <c r="P46" s="14"/>
+      <c r="Q46" s="14"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="12"/>
       <c r="B47" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C47" s="97">
-        <f>AVERAGE(G47:J47)</f>
-        <v>0</v>
+        <v>77</v>
+      </c>
+      <c r="C47" s="98">
+        <f>-C4*C55</f>
+        <v>-9031319.1044627018</v>
       </c>
       <c r="D47" s="66"/>
-      <c r="E47" s="83" t="s">
-        <v>192</v>
-      </c>
+      <c r="E47" s="85"/>
       <c r="F47" s="66"/>
       <c r="G47" s="65">
-        <f>Data!C38</f>
-        <v>0</v>
+        <f>Data!C33</f>
+        <v>-11151623</v>
       </c>
       <c r="H47" s="65">
-        <f>Data!D38</f>
-        <v>0</v>
+        <f>Data!D33</f>
+        <v>-8747447</v>
       </c>
       <c r="I47" s="65">
-        <f>Data!E38</f>
-        <v>0</v>
+        <f>Data!E33</f>
+        <v>-8503976</v>
       </c>
       <c r="J47" s="65">
-        <f>Data!F38</f>
-        <v>0</v>
+        <f>Data!F33</f>
+        <v>-6229020</v>
       </c>
       <c r="K47" s="65">
-        <f>Data!G38</f>
-        <v>0</v>
+        <f>Data!G33</f>
+        <v>-7910751</v>
       </c>
       <c r="L47" s="65">
-        <f>Data!H38</f>
-        <v>0</v>
+        <f>Data!H33</f>
+        <v>-11826154</v>
       </c>
       <c r="M47" s="65" t="str">
-        <f>Data!I38</f>
+        <f>Data!I33</f>
         <v/>
       </c>
       <c r="N47" s="65" t="str">
-        <f>Data!J38</f>
+        <f>Data!J33</f>
         <v/>
       </c>
       <c r="O47" s="65" t="str">
-        <f>Data!K38</f>
+        <f>Data!K33</f>
         <v/>
       </c>
       <c r="P47" s="65" t="str">
-        <f>Data!L38</f>
+        <f>Data!L33</f>
         <v/>
       </c>
       <c r="Q47" s="65" t="str">
-        <f>Data!M38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f>Data!M33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="12"/>
-      <c r="B48" s="91" t="s">
-        <v>79</v>
-      </c>
-      <c r="C48" s="80">
-        <f>C46+C47</f>
-        <v>-302359.25</v>
-      </c>
-      <c r="D48" s="66"/>
-      <c r="E48" s="85"/>
-      <c r="F48" s="66"/>
-      <c r="G48" s="80">
-        <f>IF(G4="","",G46+G47)</f>
-        <v>-254107</v>
-      </c>
-      <c r="H48" s="80">
-        <f>IF(H4="","",H46+H47)</f>
-        <v>-349526</v>
-      </c>
-      <c r="I48" s="80">
-        <f>IF(I4="","",I46+I47)</f>
-        <v>-323818</v>
-      </c>
-      <c r="J48" s="80">
-        <f>IF(J4="","",J46+J47)</f>
-        <v>-281986</v>
-      </c>
-      <c r="K48" s="80">
-        <f>IF(K4="","",K46+K47)</f>
-        <v>-2118252</v>
-      </c>
-      <c r="L48" s="80">
-        <f>IF(L4="","",L46+L47)</f>
-        <v>-2416769</v>
-      </c>
-      <c r="M48" s="80" t="str">
-        <f>IF(M4="","",M46+M47)</f>
-        <v/>
-      </c>
-      <c r="N48" s="80" t="str">
-        <f>IF(N4="","",N46+N47)</f>
-        <v/>
-      </c>
-      <c r="O48" s="80" t="str">
-        <f>IF(O4="","",O46+O47)</f>
-        <v/>
-      </c>
-      <c r="P48" s="80" t="str">
-        <f>IF(P4="","",P46+P47)</f>
-        <v/>
-      </c>
-      <c r="Q48" s="80" t="str">
-        <f>IF(Q4="","",Q46+Q47)</f>
+      <c r="B48" s="87" t="s">
+        <v>149</v>
+      </c>
+      <c r="C48" s="77">
+        <f>-C4*C56</f>
+        <v>-1707788.5916244236</v>
+      </c>
+      <c r="D48" s="30"/>
+      <c r="E48" s="86"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="65">
+        <f>Data!C36</f>
+        <v>-2043459</v>
+      </c>
+      <c r="H48" s="65">
+        <f>Data!D36</f>
+        <v>-1517989</v>
+      </c>
+      <c r="I48" s="65">
+        <f>Data!E36</f>
+        <v>-1491293</v>
+      </c>
+      <c r="J48" s="65">
+        <f>Data!F36</f>
+        <v>-1412494</v>
+      </c>
+      <c r="K48" s="65">
+        <f>Data!G36</f>
+        <v>0</v>
+      </c>
+      <c r="L48" s="65">
+        <f>Data!H36</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="65" t="str">
+        <f>Data!I36</f>
+        <v/>
+      </c>
+      <c r="N48" s="65" t="str">
+        <f>Data!J36</f>
+        <v/>
+      </c>
+      <c r="O48" s="65" t="str">
+        <f>Data!K36</f>
+        <v/>
+      </c>
+      <c r="P48" s="65" t="str">
+        <f>Data!L36</f>
+        <v/>
+      </c>
+      <c r="Q48" s="65" t="str">
+        <f>Data!M36</f>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="12"/>
+      <c r="B49" s="91" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" s="80">
+        <f>C47+C48</f>
+        <v>-10739107.696087126</v>
+      </c>
+      <c r="D49" s="11"/>
+      <c r="E49" s="82"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="80">
+        <f>IF(G$4="","",G47+G48)</f>
+        <v>-13195082</v>
+      </c>
+      <c r="H49" s="80">
+        <f t="shared" ref="H49:Q49" si="27">IF(H$4="","",H47+H48)</f>
+        <v>-10265436</v>
+      </c>
+      <c r="I49" s="80">
+        <f t="shared" si="27"/>
+        <v>-9995269</v>
+      </c>
+      <c r="J49" s="80">
+        <f t="shared" si="27"/>
+        <v>-7641514</v>
+      </c>
+      <c r="K49" s="80">
+        <f t="shared" si="27"/>
+        <v>-7910751</v>
+      </c>
+      <c r="L49" s="80">
+        <f t="shared" si="27"/>
+        <v>-11826154</v>
+      </c>
+      <c r="M49" s="80" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="N49" s="80" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="O49" s="80" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="P49" s="80" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="Q49" s="80" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
     </row>
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
-      <c r="B50" s="93" t="s">
-        <v>154</v>
+      <c r="B50" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" s="97">
+        <f>AVERAGE(G50:J50)</f>
+        <v>-302359.25</v>
+      </c>
+      <c r="E50" s="83" t="s">
+        <v>192</v>
+      </c>
+      <c r="G50" s="77">
+        <f>Data!C37</f>
+        <v>-254107</v>
+      </c>
+      <c r="H50" s="77">
+        <f>Data!D37</f>
+        <v>-349526</v>
+      </c>
+      <c r="I50" s="77">
+        <f>Data!E37</f>
+        <v>-323818</v>
+      </c>
+      <c r="J50" s="77">
+        <f>Data!F37</f>
+        <v>-281986</v>
+      </c>
+      <c r="K50" s="77">
+        <f>Data!G37</f>
+        <v>-2118252</v>
+      </c>
+      <c r="L50" s="77">
+        <f>Data!H37</f>
+        <v>-2416769</v>
+      </c>
+      <c r="M50" s="77" t="str">
+        <f>Data!I37</f>
+        <v/>
+      </c>
+      <c r="N50" s="77" t="str">
+        <f>Data!J37</f>
+        <v/>
+      </c>
+      <c r="O50" s="77" t="str">
+        <f>Data!K37</f>
+        <v/>
+      </c>
+      <c r="P50" s="77" t="str">
+        <f>Data!L37</f>
+        <v/>
+      </c>
+      <c r="Q50" s="77" t="str">
+        <f>Data!M37</f>
+        <v/>
       </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="12"/>
-      <c r="B51" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C51" s="75">
-        <f>AVERAGE(G51:L51)</f>
-        <v>0.72253727182782512</v>
-      </c>
-      <c r="D51" s="29"/>
+      <c r="B51" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" s="97">
+        <f>AVERAGE(G51:J51)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="66"/>
       <c r="E51" s="83" t="s">
         <v>192</v>
       </c>
-      <c r="F51" s="29"/>
-      <c r="G51" s="15">
-        <f>IF(G$4="","",ABS(G43/G$4))</f>
-        <v>0.72762956087193742</v>
-      </c>
-      <c r="H51" s="15">
-        <f t="shared" ref="H51:Q51" si="16">IF(H$4="","",ABS(H43/H$4))</f>
-        <v>0.7303022981431383</v>
-      </c>
-      <c r="I51" s="15">
-        <f t="shared" si="16"/>
-        <v>0.7244946946204498</v>
-      </c>
-      <c r="J51" s="15">
-        <f t="shared" si="16"/>
-        <v>0.70294374380383995</v>
-      </c>
-      <c r="K51" s="15">
-        <f t="shared" si="16"/>
-        <v>0.70419372087965826</v>
-      </c>
-      <c r="L51" s="15">
-        <f t="shared" si="16"/>
-        <v>0.74565961264792724</v>
-      </c>
-      <c r="M51" s="15" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="N51" s="15" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="O51" s="15" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="P51" s="15" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="Q51" s="15" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F51" s="66"/>
+      <c r="G51" s="65">
+        <f>Data!C38</f>
+        <v>0</v>
+      </c>
+      <c r="H51" s="65">
+        <f>Data!D38</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="65">
+        <f>Data!E38</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="65">
+        <f>Data!F38</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="65">
+        <f>Data!G38</f>
+        <v>0</v>
+      </c>
+      <c r="L51" s="65">
+        <f>Data!H38</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="65" t="str">
+        <f>Data!I38</f>
+        <v/>
+      </c>
+      <c r="N51" s="65" t="str">
+        <f>Data!J38</f>
+        <v/>
+      </c>
+      <c r="O51" s="65" t="str">
+        <f>Data!K38</f>
+        <v/>
+      </c>
+      <c r="P51" s="65" t="str">
+        <f>Data!L38</f>
+        <v/>
+      </c>
+      <c r="Q51" s="65" t="str">
+        <f>Data!M38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="12"/>
-      <c r="B52" s="87" t="str">
-        <f>B44</f>
-        <v>Selling Expenses</v>
-      </c>
-      <c r="C52" s="75">
-        <f>AVERAGE(G52:J52)</f>
-        <v>0.13662908990130354</v>
-      </c>
-      <c r="D52" s="29"/>
-      <c r="E52" s="83" t="s">
-        <v>192</v>
-      </c>
-      <c r="F52" s="29"/>
-      <c r="G52" s="15">
-        <f t="shared" ref="G52:G56" si="17">IF(G$4="","",ABS(G44/G$4))</f>
-        <v>0.13333316368656009</v>
-      </c>
-      <c r="H52" s="15">
-        <f t="shared" ref="H52:Q52" si="18">IF(H$4="","",ABS(H44/H$4))</f>
-        <v>0.12673307483383486</v>
-      </c>
-      <c r="I52" s="15">
-        <f t="shared" si="18"/>
-        <v>0.12705043695144655</v>
-      </c>
-      <c r="J52" s="15">
-        <f t="shared" si="18"/>
-        <v>0.15939968413337269</v>
-      </c>
-      <c r="K52" s="15">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="L52" s="15">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="M52" s="15" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="N52" s="15" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="O52" s="15" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="P52" s="15" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="Q52" s="15" t="str">
-        <f t="shared" si="18"/>
+      <c r="B52" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" s="80">
+        <f>C50+C51</f>
+        <v>-302359.25</v>
+      </c>
+      <c r="D52" s="66"/>
+      <c r="E52" s="85"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="80">
+        <f t="shared" ref="G52:Q52" si="28">IF(G4="","",G50+G51)</f>
+        <v>-254107</v>
+      </c>
+      <c r="H52" s="80">
+        <f t="shared" si="28"/>
+        <v>-349526</v>
+      </c>
+      <c r="I52" s="80">
+        <f t="shared" si="28"/>
+        <v>-323818</v>
+      </c>
+      <c r="J52" s="80">
+        <f t="shared" si="28"/>
+        <v>-281986</v>
+      </c>
+      <c r="K52" s="80">
+        <f t="shared" si="28"/>
+        <v>-2118252</v>
+      </c>
+      <c r="L52" s="80">
+        <f t="shared" si="28"/>
+        <v>-2416769</v>
+      </c>
+      <c r="M52" s="80" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="N52" s="80" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="O52" s="80" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="P52" s="80" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+      <c r="Q52" s="80" t="str">
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="12"/>
-      <c r="B53" s="91" t="s">
-        <v>80</v>
-      </c>
-      <c r="C53" s="92">
-        <f>ABS(C45/$C$4)</f>
-        <v>0.85916636172912864</v>
-      </c>
-      <c r="G53" s="33">
-        <f t="shared" si="17"/>
-        <v>0.86096272455849754</v>
-      </c>
-      <c r="H53" s="33">
-        <f t="shared" ref="H53:Q53" si="19">IF(H$4="","",ABS(H45/H$4))</f>
-        <v>0.85703537297697319</v>
-      </c>
-      <c r="I53" s="33">
-        <f t="shared" si="19"/>
-        <v>0.85154513157189637</v>
-      </c>
-      <c r="J53" s="33">
-        <f t="shared" si="19"/>
-        <v>0.86234342793721264</v>
-      </c>
-      <c r="K53" s="33">
-        <f t="shared" si="19"/>
-        <v>0.70419372087965826</v>
-      </c>
-      <c r="L53" s="33">
-        <f t="shared" si="19"/>
-        <v>0.74565961264792724</v>
-      </c>
-      <c r="M53" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="N53" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="O53" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="P53" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="Q53" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
     </row>
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="12"/>
-      <c r="B54" s="2" t="str">
-        <f>B46</f>
-        <v>Other Opex (Fixed Overhead)</v>
-      </c>
-      <c r="C54" s="26">
-        <f t="shared" ref="C54:C56" si="20">ABS(C46/$C$4)</f>
-        <v>2.4189802738666985E-2</v>
-      </c>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="15">
-        <f t="shared" si="17"/>
-        <v>1.6580166386945237E-2</v>
-      </c>
-      <c r="H54" s="15">
-        <f t="shared" ref="H54:Q54" si="21">IF(H$4="","",ABS(H46/H$4))</f>
-        <v>2.9181044602016856E-2</v>
-      </c>
-      <c r="I54" s="15">
-        <f t="shared" si="21"/>
-        <v>2.7587615842589962E-2</v>
-      </c>
-      <c r="J54" s="15">
-        <f t="shared" si="21"/>
-        <v>3.1822067442433898E-2</v>
-      </c>
-      <c r="K54" s="15">
-        <f t="shared" si="21"/>
-        <v>0.18856108069142588</v>
-      </c>
-      <c r="L54" s="15">
-        <f t="shared" si="21"/>
-        <v>0.15238149582692045</v>
-      </c>
-      <c r="M54" s="15" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="N54" s="15" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="O54" s="15" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="P54" s="15" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="Q54" s="15" t="str">
-        <f t="shared" si="21"/>
-        <v/>
+      <c r="B54" s="93" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="12"/>
-      <c r="B55" s="30" t="str">
-        <f>B47</f>
-        <v>- R&amp;D</v>
-      </c>
-      <c r="C55" s="26">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
+      <c r="B55" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C55" s="75">
+        <f>AVERAGE(G55:L55)</f>
+        <v>0.72253727182782512</v>
+      </c>
+      <c r="D55" s="29"/>
+      <c r="E55" s="83" t="s">
+        <v>192</v>
+      </c>
+      <c r="F55" s="29"/>
       <c r="G55" s="15">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>IF(G$4="","",ABS(G47/G$4))</f>
+        <v>0.72762956087193742</v>
       </c>
       <c r="H55" s="15">
-        <f t="shared" ref="H55:Q55" si="22">IF(H$4="","",ABS(H47/H$4))</f>
-        <v>0</v>
+        <f t="shared" ref="H55:Q55" si="29">IF(H$4="","",ABS(H47/H$4))</f>
+        <v>0.7303022981431383</v>
       </c>
       <c r="I55" s="15">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>0.7244946946204498</v>
       </c>
       <c r="J55" s="15">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>0.70294374380383995</v>
       </c>
       <c r="K55" s="15">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>0.70419372087965826</v>
       </c>
       <c r="L55" s="15">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>0.74565961264792724</v>
       </c>
       <c r="M55" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N55" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="O55" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="P55" s="15" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q55" s="15" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="12"/>
-      <c r="B56" s="91" t="s">
-        <v>79</v>
-      </c>
-      <c r="C56" s="92">
-        <f t="shared" si="20"/>
-        <v>2.4189802738666985E-2</v>
-      </c>
-      <c r="G56" s="33">
-        <f t="shared" si="17"/>
-        <v>1.6580166386945237E-2</v>
-      </c>
-      <c r="H56" s="33">
-        <f t="shared" ref="H56:Q56" si="23">IF(H$4="","",ABS(H48/H$4))</f>
-        <v>2.9181044602016856E-2</v>
-      </c>
-      <c r="I56" s="33">
-        <f t="shared" si="23"/>
-        <v>2.7587615842589962E-2</v>
-      </c>
-      <c r="J56" s="33">
-        <f t="shared" si="23"/>
-        <v>3.1822067442433898E-2</v>
-      </c>
-      <c r="K56" s="33">
-        <f t="shared" si="23"/>
-        <v>0.18856108069142588</v>
-      </c>
-      <c r="L56" s="33">
-        <f t="shared" si="23"/>
-        <v>0.15238149582692045</v>
-      </c>
-      <c r="M56" s="33" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="N56" s="33" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="O56" s="33" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="P56" s="33" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="Q56" s="33" t="str">
-        <f t="shared" si="23"/>
+      <c r="B56" s="87" t="str">
+        <f>B48</f>
+        <v>Selling Expenses</v>
+      </c>
+      <c r="C56" s="75">
+        <f>AVERAGE(G56:J56)</f>
+        <v>0.13662908990130354</v>
+      </c>
+      <c r="D56" s="29"/>
+      <c r="E56" s="83" t="s">
+        <v>192</v>
+      </c>
+      <c r="F56" s="29"/>
+      <c r="G56" s="15">
+        <f t="shared" ref="G56:G60" si="30">IF(G$4="","",ABS(G48/G$4))</f>
+        <v>0.13333316368656009</v>
+      </c>
+      <c r="H56" s="15">
+        <f t="shared" ref="H56:Q56" si="31">IF(H$4="","",ABS(H48/H$4))</f>
+        <v>0.12673307483383486</v>
+      </c>
+      <c r="I56" s="15">
+        <f t="shared" si="31"/>
+        <v>0.12705043695144655</v>
+      </c>
+      <c r="J56" s="15">
+        <f t="shared" si="31"/>
+        <v>0.15939968413337269</v>
+      </c>
+      <c r="K56" s="15">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="L56" s="15">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="M56" s="15" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="N56" s="15" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="O56" s="15" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="P56" s="15" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="Q56" s="15" t="str">
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="12"/>
+      <c r="B57" s="91" t="s">
+        <v>80</v>
+      </c>
+      <c r="C57" s="92">
+        <f>ABS(C49/$C$4)</f>
+        <v>0.85916636172912864</v>
+      </c>
+      <c r="G57" s="33">
+        <f t="shared" si="30"/>
+        <v>0.86096272455849754</v>
+      </c>
+      <c r="H57" s="33">
+        <f t="shared" ref="H57:Q57" si="32">IF(H$4="","",ABS(H49/H$4))</f>
+        <v>0.85703537297697319</v>
+      </c>
+      <c r="I57" s="33">
+        <f t="shared" si="32"/>
+        <v>0.85154513157189637</v>
+      </c>
+      <c r="J57" s="33">
+        <f t="shared" si="32"/>
+        <v>0.86234342793721264</v>
+      </c>
+      <c r="K57" s="33">
+        <f t="shared" si="32"/>
+        <v>0.70419372087965826</v>
+      </c>
+      <c r="L57" s="33">
+        <f t="shared" si="32"/>
+        <v>0.74565961264792724</v>
+      </c>
+      <c r="M57" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="N57" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="O57" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="P57" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="Q57" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="12"/>
-      <c r="B58" s="78" t="s">
-        <v>147</v>
+      <c r="B58" s="2" t="str">
+        <f>B50</f>
+        <v>Other Opex (Fixed Overhead)</v>
+      </c>
+      <c r="C58" s="26">
+        <f t="shared" ref="C58:C60" si="33">ABS(C50/$C$4)</f>
+        <v>2.4189802738666985E-2</v>
+      </c>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="15">
+        <f t="shared" si="30"/>
+        <v>1.6580166386945237E-2</v>
+      </c>
+      <c r="H58" s="15">
+        <f t="shared" ref="H58:Q58" si="34">IF(H$4="","",ABS(H50/H$4))</f>
+        <v>2.9181044602016856E-2</v>
+      </c>
+      <c r="I58" s="15">
+        <f t="shared" si="34"/>
+        <v>2.7587615842589962E-2</v>
+      </c>
+      <c r="J58" s="15">
+        <f t="shared" si="34"/>
+        <v>3.1822067442433898E-2</v>
+      </c>
+      <c r="K58" s="15">
+        <f t="shared" si="34"/>
+        <v>0.18856108069142588</v>
+      </c>
+      <c r="L58" s="15">
+        <f t="shared" si="34"/>
+        <v>0.15238149582692045</v>
+      </c>
+      <c r="M58" s="15" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="N58" s="15" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="O58" s="15" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="P58" s="15" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q58" s="15" t="str">
+        <f t="shared" si="34"/>
+        <v/>
       </c>
     </row>
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="12"/>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="30" t="str">
+        <f>B51</f>
+        <v>- R&amp;D</v>
+      </c>
+      <c r="C59" s="26">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="15">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="H59" s="15">
+        <f t="shared" ref="H59:Q59" si="35">IF(H$4="","",ABS(H51/H$4))</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="15">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="15">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="15">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="L59" s="15">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="M59" s="15" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="N59" s="15" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="O59" s="15" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="P59" s="15" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="Q59" s="15" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="12"/>
+      <c r="B60" s="91" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60" s="92">
+        <f t="shared" si="33"/>
+        <v>2.4189802738666985E-2</v>
+      </c>
+      <c r="G60" s="33">
+        <f t="shared" si="30"/>
+        <v>1.6580166386945237E-2</v>
+      </c>
+      <c r="H60" s="33">
+        <f t="shared" ref="H60:Q60" si="36">IF(H$4="","",ABS(H52/H$4))</f>
+        <v>2.9181044602016856E-2</v>
+      </c>
+      <c r="I60" s="33">
+        <f t="shared" si="36"/>
+        <v>2.7587615842589962E-2</v>
+      </c>
+      <c r="J60" s="33">
+        <f t="shared" si="36"/>
+        <v>3.1822067442433898E-2</v>
+      </c>
+      <c r="K60" s="33">
+        <f t="shared" si="36"/>
+        <v>0.18856108069142588</v>
+      </c>
+      <c r="L60" s="33">
+        <f t="shared" si="36"/>
+        <v>0.15238149582692045</v>
+      </c>
+      <c r="M60" s="33" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N60" s="33" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="O60" s="33" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="P60" s="33" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="Q60" s="33" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="12"/>
+    </row>
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="12"/>
+      <c r="B62" s="78" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="12"/>
+      <c r="B63" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C59" s="77">
+      <c r="C63" s="77">
         <f>-BS!G27*BS!C40</f>
         <v>-59596</v>
       </c>
-      <c r="G59" s="77">
+      <c r="G63" s="77">
         <f>Data!C41</f>
         <v>-59596</v>
       </c>
-      <c r="H59" s="77">
+      <c r="H63" s="77">
         <f>Data!D41</f>
         <v>-20763</v>
       </c>
-      <c r="I59" s="77">
+      <c r="I63" s="77">
         <f>Data!E41</f>
         <v>-23097</v>
       </c>
-      <c r="J59" s="77">
+      <c r="J63" s="77">
         <f>Data!F41</f>
         <v>-28849</v>
       </c>
-      <c r="K59" s="77">
+      <c r="K63" s="77">
         <f>Data!G41</f>
         <v>-63075</v>
       </c>
-      <c r="L59" s="77">
+      <c r="L63" s="77">
         <f>Data!H41</f>
         <v>-34253</v>
       </c>
-      <c r="M59" s="77" t="str">
+      <c r="M63" s="77" t="str">
         <f>Data!I41</f>
         <v/>
       </c>
-      <c r="N59" s="77" t="str">
+      <c r="N63" s="77" t="str">
         <f>Data!J41</f>
         <v/>
       </c>
-      <c r="O59" s="77" t="str">
+      <c r="O63" s="77" t="str">
         <f>Data!K41</f>
         <v/>
       </c>
-      <c r="P59" s="77" t="str">
+      <c r="P63" s="77" t="str">
         <f>Data!L41</f>
         <v/>
       </c>
-      <c r="Q59" s="77" t="str">
+      <c r="Q63" s="77" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="12"/>
-      <c r="B60" s="2" t="s">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="12"/>
+      <c r="B64" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C60" s="77">
+      <c r="C64" s="77">
         <f>BS!$G$24*BS!C41</f>
         <v>28977</v>
       </c>
-      <c r="G60" s="77">
+      <c r="G64" s="77">
         <f>Data!C42</f>
         <v>28977</v>
       </c>
-      <c r="H60" s="77">
+      <c r="H64" s="77">
         <f>Data!D42</f>
         <v>33125</v>
       </c>
-      <c r="I60" s="77">
+      <c r="I64" s="77">
         <f>Data!E42</f>
         <v>87344</v>
       </c>
-      <c r="J60" s="77">
+      <c r="J64" s="77">
         <f>Data!F42</f>
         <v>63398</v>
       </c>
-      <c r="K60" s="77">
+      <c r="K64" s="77">
         <f>Data!G42</f>
         <v>0</v>
       </c>
-      <c r="L60" s="77">
+      <c r="L64" s="77">
         <f>Data!H42</f>
         <v>0</v>
       </c>
-      <c r="M60" s="77" t="str">
+      <c r="M64" s="77" t="str">
         <f>Data!I42</f>
         <v/>
       </c>
-      <c r="N60" s="77" t="str">
+      <c r="N64" s="77" t="str">
         <f>Data!J42</f>
         <v/>
       </c>
-      <c r="O60" s="77" t="str">
+      <c r="O64" s="77" t="str">
         <f>Data!K42</f>
         <v/>
       </c>
-      <c r="P60" s="77" t="str">
+      <c r="P64" s="77" t="str">
         <f>Data!L42</f>
         <v/>
       </c>
-      <c r="Q60" s="77" t="str">
+      <c r="Q64" s="77" t="str">
         <f>Data!M42</f>
         <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="12"/>
-      <c r="B61" s="91" t="s">
-        <v>159</v>
-      </c>
-      <c r="C61" s="80">
-        <f>C59+C60</f>
-        <v>-30619</v>
-      </c>
-      <c r="G61" s="80">
-        <f>IF(G4="","",G59+G60)</f>
-        <v>-30619</v>
-      </c>
-      <c r="H61" s="80">
-        <f>IF(H4="","",H59+H60)</f>
-        <v>12362</v>
-      </c>
-      <c r="I61" s="80">
-        <f>IF(I4="","",I59+I60)</f>
-        <v>64247</v>
-      </c>
-      <c r="J61" s="80">
-        <f>IF(J4="","",J59+J60)</f>
-        <v>34549</v>
-      </c>
-      <c r="K61" s="80">
-        <f>IF(K4="","",K59+K60)</f>
-        <v>-63075</v>
-      </c>
-      <c r="L61" s="80">
-        <f>IF(L4="","",L59+L60)</f>
-        <v>-34253</v>
-      </c>
-      <c r="M61" s="80" t="str">
-        <f>IF(M4="","",M59+M60)</f>
-        <v/>
-      </c>
-      <c r="N61" s="80" t="str">
-        <f>IF(N4="","",N59+N60)</f>
-        <v/>
-      </c>
-      <c r="O61" s="80" t="str">
-        <f>IF(O4="","",O59+O60)</f>
-        <v/>
-      </c>
-      <c r="P61" s="80" t="str">
-        <f>IF(P4="","",P59+P60)</f>
-        <v/>
-      </c>
-      <c r="Q61" s="80" t="str">
-        <f>IF(Q4="","",Q59+Q60)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="12"/>
-    </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A63" s="3"/>
-      <c r="B63" s="61" t="s">
-        <v>216</v>
-      </c>
-      <c r="C63" s="61"/>
-      <c r="D63" s="63"/>
-      <c r="E63" s="81" t="s">
-        <v>146</v>
-      </c>
-      <c r="F63" s="63"/>
-      <c r="G63" s="40"/>
-      <c r="H63" s="40"/>
-      <c r="I63" s="40"/>
-      <c r="J63" s="40"/>
-      <c r="K63" s="40"/>
-      <c r="L63" s="40"/>
-      <c r="M63" s="40"/>
-      <c r="N63" s="40"/>
-      <c r="O63" s="40"/>
-      <c r="P63" s="40"/>
-      <c r="Q63" s="40"/>
-    </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="12"/>
-      <c r="B64" s="78" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="12"/>
-      <c r="B65" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="C65" s="128">
-        <f>BS!G23</f>
-        <v>16854064</v>
-      </c>
-      <c r="D65" s="29"/>
-      <c r="E65" s="29"/>
-      <c r="F65" s="29"/>
-      <c r="G65" s="16">
-        <f t="shared" ref="G65:Q65" si="24">IF(G$4="","",G69+G68)</f>
-        <v>16854064</v>
-      </c>
-      <c r="H65" s="16">
-        <f t="shared" si="24"/>
-        <v>14687373</v>
-      </c>
-      <c r="I65" s="16">
-        <f t="shared" si="24"/>
-        <v>15987114</v>
-      </c>
-      <c r="J65" s="16">
-        <f t="shared" si="24"/>
-        <v>14270996</v>
-      </c>
-      <c r="K65" s="16">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="L65" s="16">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="M65" s="16" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="N65" s="16" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="O65" s="16" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="P65" s="16" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="Q65" s="16" t="str">
-        <f t="shared" si="24"/>
+      <c r="B65" s="91" t="s">
+        <v>159</v>
+      </c>
+      <c r="C65" s="80">
+        <f>C63+C64</f>
+        <v>-30619</v>
+      </c>
+      <c r="G65" s="80">
+        <f t="shared" ref="G65:Q65" si="37">IF(G4="","",G63+G64)</f>
+        <v>-30619</v>
+      </c>
+      <c r="H65" s="80">
+        <f t="shared" si="37"/>
+        <v>12362</v>
+      </c>
+      <c r="I65" s="80">
+        <f t="shared" si="37"/>
+        <v>64247</v>
+      </c>
+      <c r="J65" s="80">
+        <f t="shared" si="37"/>
+        <v>34549</v>
+      </c>
+      <c r="K65" s="80">
+        <f t="shared" si="37"/>
+        <v>-63075</v>
+      </c>
+      <c r="L65" s="80">
+        <f t="shared" si="37"/>
+        <v>-34253</v>
+      </c>
+      <c r="M65" s="80" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N65" s="80" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="O65" s="80" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P65" s="80" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="Q65" s="80" t="str">
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
-      <c r="B66" s="126" t="s">
-        <v>199</v>
-      </c>
-      <c r="C66" s="129">
-        <f>BS!C4</f>
-        <v>265773</v>
-      </c>
-      <c r="D66" s="118"/>
-      <c r="E66" s="118"/>
-      <c r="F66" s="118"/>
-      <c r="G66" s="130">
-        <f>IF(G$4="","",Data!D64)</f>
-        <v>213823</v>
-      </c>
-      <c r="H66" s="130">
-        <f>IF(H$4="","",Data!E64)</f>
-        <v>187711</v>
-      </c>
-      <c r="I66" s="130">
-        <f>IF(I$4="","",Data!F64)</f>
-        <v>277338</v>
-      </c>
-      <c r="J66" s="130">
-        <f>IF(J$4="","",Data!G64)</f>
-        <v>0</v>
-      </c>
-      <c r="K66" s="130">
-        <f>IF(K$4="","",Data!H64)</f>
-        <v>0</v>
-      </c>
-      <c r="L66" s="130">
-        <f>IF(L$4="","",Data!I64)</f>
-        <v>0</v>
-      </c>
-      <c r="M66" s="130" t="str">
-        <f>IF(M$4="","",Data!J64)</f>
-        <v/>
-      </c>
-      <c r="N66" s="130" t="str">
-        <f>IF(N$4="","",Data!K64)</f>
-        <v/>
-      </c>
-      <c r="O66" s="130" t="str">
-        <f>IF(O$4="","",Data!L64)</f>
-        <v/>
-      </c>
-      <c r="P66" s="130" t="str">
-        <f>IF(P$4="","",Data!M64)</f>
-        <v/>
-      </c>
-      <c r="Q66" s="130" t="str">
-        <f>IF(Q$4="","",Data!N64)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="12"/>
-      <c r="B67" s="126" t="s">
-        <v>200</v>
-      </c>
-      <c r="C67" s="129">
-        <f>BS!C7+BS!C8</f>
-        <v>9672256</v>
-      </c>
-      <c r="D67" s="118"/>
-      <c r="E67" s="118"/>
-      <c r="F67" s="118"/>
-      <c r="G67" s="130">
-        <f>IF(G$4="","",Data!D65)</f>
-        <v>8852611</v>
-      </c>
-      <c r="H67" s="130">
-        <f>IF(H$4="","",Data!E65)</f>
-        <v>8769304</v>
-      </c>
-      <c r="I67" s="130">
-        <f>IF(I$4="","",Data!F65)</f>
-        <v>7321614</v>
-      </c>
-      <c r="J67" s="130">
-        <f>IF(J$4="","",Data!G65)</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="130">
-        <f>IF(K$4="","",Data!H65)</f>
-        <v>0</v>
-      </c>
-      <c r="L67" s="130">
-        <f>IF(L$4="","",Data!I65)</f>
-        <v>0</v>
-      </c>
-      <c r="M67" s="130" t="str">
-        <f>IF(M$4="","",Data!J65)</f>
-        <v/>
-      </c>
-      <c r="N67" s="130" t="str">
-        <f>IF(N$4="","",Data!K65)</f>
-        <v/>
-      </c>
-      <c r="O67" s="130" t="str">
-        <f>IF(O$4="","",Data!L65)</f>
-        <v/>
-      </c>
-      <c r="P67" s="130" t="str">
-        <f>IF(P$4="","",Data!M65)</f>
-        <v/>
-      </c>
-      <c r="Q67" s="130" t="str">
-        <f>IF(Q$4="","",Data!N65)</f>
-        <v/>
-      </c>
+    </row>
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A67" s="3"/>
+      <c r="B67" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="C67" s="61"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="81" t="s">
+        <v>146</v>
+      </c>
+      <c r="F67" s="63"/>
+      <c r="G67" s="40"/>
+      <c r="H67" s="40"/>
+      <c r="I67" s="40"/>
+      <c r="J67" s="40"/>
+      <c r="K67" s="40"/>
+      <c r="L67" s="40"/>
+      <c r="M67" s="40"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="40"/>
+      <c r="P67" s="40"/>
+      <c r="Q67" s="40"/>
     </row>
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
-      <c r="B68" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="C68" s="128">
-        <f>BS!G26</f>
-        <v>3990166</v>
-      </c>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
-      <c r="G68" s="16">
-        <f>Data!C66</f>
-        <v>3990166</v>
-      </c>
-      <c r="H68" s="16">
-        <f>Data!D66</f>
-        <v>2466431</v>
-      </c>
-      <c r="I68" s="16">
-        <f>Data!E66</f>
-        <v>3908586</v>
-      </c>
-      <c r="J68" s="16">
-        <f>Data!F66</f>
-        <v>2946772</v>
-      </c>
-      <c r="K68" s="16">
-        <f>Data!G66</f>
-        <v>0</v>
-      </c>
-      <c r="L68" s="16">
-        <f>Data!H66</f>
-        <v>0</v>
-      </c>
-      <c r="M68" s="16" t="str">
-        <f>Data!I66</f>
-        <v/>
-      </c>
-      <c r="N68" s="16" t="str">
-        <f>Data!J66</f>
-        <v/>
-      </c>
-      <c r="O68" s="16" t="str">
-        <f>Data!K66</f>
-        <v/>
-      </c>
-      <c r="P68" s="16" t="str">
-        <f>Data!L66</f>
-        <v/>
-      </c>
-      <c r="Q68" s="16" t="str">
-        <f>Data!M66</f>
-        <v/>
+      <c r="B68" s="78" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="12"/>
       <c r="B69" s="29" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="C69" s="128">
-        <f>BS!G28</f>
-        <v>12863898</v>
+        <f>BS!G23</f>
+        <v>16854064</v>
       </c>
       <c r="D69" s="29"/>
       <c r="E69" s="29"/>
       <c r="F69" s="29"/>
       <c r="G69" s="16">
-        <f>Data!C67</f>
-        <v>12863898</v>
+        <f t="shared" ref="G69:Q69" si="38">IF(G$4="","",G73+G72)</f>
+        <v>16854064</v>
       </c>
       <c r="H69" s="16">
-        <f>Data!D67</f>
-        <v>12220942</v>
+        <f t="shared" si="38"/>
+        <v>14687373</v>
       </c>
       <c r="I69" s="16">
-        <f>Data!E67</f>
-        <v>12078528</v>
+        <f t="shared" si="38"/>
+        <v>15987114</v>
       </c>
       <c r="J69" s="16">
-        <f>Data!F67</f>
-        <v>11324224</v>
+        <f t="shared" si="38"/>
+        <v>14270996</v>
       </c>
       <c r="K69" s="16">
-        <f>Data!G67</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="L69" s="16">
-        <f>Data!H67</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M69" s="16" t="str">
-        <f>Data!I67</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="N69" s="16" t="str">
-        <f>Data!J67</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O69" s="16" t="str">
-        <f>Data!K67</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="P69" s="16" t="str">
-        <f>Data!L67</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="Q69" s="16" t="str">
-        <f>Data!M67</f>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="12"/>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="16"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
-      <c r="M70" s="14"/>
-      <c r="N70" s="14"/>
-      <c r="O70" s="14"/>
-      <c r="P70" s="14"/>
-      <c r="Q70" s="14"/>
+      <c r="B70" s="126" t="s">
+        <v>199</v>
+      </c>
+      <c r="C70" s="129">
+        <f>BS!C4</f>
+        <v>265773</v>
+      </c>
+      <c r="D70" s="118"/>
+      <c r="E70" s="118"/>
+      <c r="F70" s="118"/>
+      <c r="G70" s="130">
+        <f>IF(G$4="","",Data!D64)</f>
+        <v>213823</v>
+      </c>
+      <c r="H70" s="130">
+        <f>IF(H$4="","",Data!E64)</f>
+        <v>187711</v>
+      </c>
+      <c r="I70" s="130">
+        <f>IF(I$4="","",Data!F64)</f>
+        <v>277338</v>
+      </c>
+      <c r="J70" s="130">
+        <f>IF(J$4="","",Data!G64)</f>
+        <v>0</v>
+      </c>
+      <c r="K70" s="130">
+        <f>IF(K$4="","",Data!H64)</f>
+        <v>0</v>
+      </c>
+      <c r="L70" s="130">
+        <f>IF(L$4="","",Data!I64)</f>
+        <v>0</v>
+      </c>
+      <c r="M70" s="130" t="str">
+        <f>IF(M$4="","",Data!J64)</f>
+        <v/>
+      </c>
+      <c r="N70" s="130" t="str">
+        <f>IF(N$4="","",Data!K64)</f>
+        <v/>
+      </c>
+      <c r="O70" s="130" t="str">
+        <f>IF(O$4="","",Data!L64)</f>
+        <v/>
+      </c>
+      <c r="P70" s="130" t="str">
+        <f>IF(P$4="","",Data!M64)</f>
+        <v/>
+      </c>
+      <c r="Q70" s="130" t="str">
+        <f>IF(Q$4="","",Data!N64)</f>
+        <v/>
+      </c>
     </row>
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="12"/>
-      <c r="B71" s="121" t="s">
-        <v>76</v>
-      </c>
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="16"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="14"/>
-      <c r="J71" s="14"/>
-      <c r="K71" s="14"/>
-      <c r="L71" s="14"/>
-      <c r="M71" s="14"/>
-      <c r="N71" s="14"/>
-      <c r="O71" s="14"/>
-      <c r="P71" s="14"/>
-      <c r="Q71" s="14"/>
+      <c r="B71" s="126" t="s">
+        <v>200</v>
+      </c>
+      <c r="C71" s="129">
+        <f>BS!C7+BS!C8</f>
+        <v>9672256</v>
+      </c>
+      <c r="D71" s="118"/>
+      <c r="E71" s="118"/>
+      <c r="F71" s="118"/>
+      <c r="G71" s="130">
+        <f>IF(G$4="","",Data!D65)</f>
+        <v>8852611</v>
+      </c>
+      <c r="H71" s="130">
+        <f>IF(H$4="","",Data!E65)</f>
+        <v>8769304</v>
+      </c>
+      <c r="I71" s="130">
+        <f>IF(I$4="","",Data!F65)</f>
+        <v>7321614</v>
+      </c>
+      <c r="J71" s="130">
+        <f>IF(J$4="","",Data!G65)</f>
+        <v>0</v>
+      </c>
+      <c r="K71" s="130">
+        <f>IF(K$4="","",Data!H65)</f>
+        <v>0</v>
+      </c>
+      <c r="L71" s="130">
+        <f>IF(L$4="","",Data!I65)</f>
+        <v>0</v>
+      </c>
+      <c r="M71" s="130" t="str">
+        <f>IF(M$4="","",Data!J65)</f>
+        <v/>
+      </c>
+      <c r="N71" s="130" t="str">
+        <f>IF(N$4="","",Data!K65)</f>
+        <v/>
+      </c>
+      <c r="O71" s="130" t="str">
+        <f>IF(O$4="","",Data!L65)</f>
+        <v/>
+      </c>
+      <c r="P71" s="130" t="str">
+        <f>IF(P$4="","",Data!M65)</f>
+        <v/>
+      </c>
+      <c r="Q71" s="130" t="str">
+        <f>IF(Q$4="","",Data!N65)</f>
+        <v/>
+      </c>
     </row>
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="12"/>
       <c r="B72" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="C72" s="131">
-        <f>C66/C$4</f>
-        <v>2.1262774144544083E-2</v>
+        <v>67</v>
+      </c>
+      <c r="C72" s="128">
+        <f>BS!G26</f>
+        <v>3990166</v>
       </c>
       <c r="D72" s="29"/>
       <c r="E72" s="29"/>
       <c r="F72" s="29"/>
-      <c r="G72" s="131">
-        <f>IF(G$4="","",G66/G$4)</f>
-        <v>1.3951685381968192E-2</v>
-      </c>
-      <c r="H72" s="131">
-        <f t="shared" ref="H72:Q72" si="25">IF(H$4="","",H66/H$4)</f>
-        <v>1.5671518179732512E-2</v>
-      </c>
-      <c r="I72" s="131">
-        <f t="shared" si="25"/>
-        <v>2.3627760663558588E-2</v>
-      </c>
-      <c r="J72" s="131">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="K72" s="131">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="L72" s="131">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="M72" s="131" t="str">
-        <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="N72" s="131" t="str">
-        <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="O72" s="131" t="str">
-        <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="P72" s="131" t="str">
-        <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="Q72" s="131" t="str">
-        <f t="shared" si="25"/>
+      <c r="G72" s="16">
+        <f>Data!C66</f>
+        <v>3990166</v>
+      </c>
+      <c r="H72" s="16">
+        <f>Data!D66</f>
+        <v>2466431</v>
+      </c>
+      <c r="I72" s="16">
+        <f>Data!E66</f>
+        <v>3908586</v>
+      </c>
+      <c r="J72" s="16">
+        <f>Data!F66</f>
+        <v>2946772</v>
+      </c>
+      <c r="K72" s="16">
+        <f>Data!G66</f>
+        <v>0</v>
+      </c>
+      <c r="L72" s="16">
+        <f>Data!H66</f>
+        <v>0</v>
+      </c>
+      <c r="M72" s="16" t="str">
+        <f>Data!I66</f>
+        <v/>
+      </c>
+      <c r="N72" s="16" t="str">
+        <f>Data!J66</f>
+        <v/>
+      </c>
+      <c r="O72" s="16" t="str">
+        <f>Data!K66</f>
+        <v/>
+      </c>
+      <c r="P72" s="16" t="str">
+        <f>Data!L66</f>
+        <v/>
+      </c>
+      <c r="Q72" s="16" t="str">
+        <f>Data!M66</f>
         <v/>
       </c>
     </row>
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="12"/>
       <c r="B73" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="C73" s="131">
-        <f>C67/C$4</f>
-        <v>0.7738144762493232</v>
+        <v>46</v>
+      </c>
+      <c r="C73" s="128">
+        <f>BS!G28</f>
+        <v>12863898</v>
       </c>
       <c r="D73" s="29"/>
       <c r="E73" s="29"/>
       <c r="F73" s="29"/>
-      <c r="G73" s="131">
-        <f>IF(G$4="","",G67/G$4)</f>
-        <v>0.57762188109301071</v>
-      </c>
-      <c r="H73" s="131">
-        <f t="shared" ref="H73:Q73" si="26">IF(H$4="","",H67/H$4)</f>
-        <v>0.73212708397270831</v>
-      </c>
-      <c r="I73" s="131">
-        <f t="shared" si="26"/>
-        <v>0.62376357824373097</v>
-      </c>
-      <c r="J73" s="131">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="K73" s="131">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="L73" s="131">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="M73" s="131" t="str">
-        <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="N73" s="131" t="str">
-        <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="O73" s="131" t="str">
-        <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="P73" s="131" t="str">
-        <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="Q73" s="131" t="str">
-        <f t="shared" si="26"/>
+      <c r="G73" s="16">
+        <f>Data!C67</f>
+        <v>12863898</v>
+      </c>
+      <c r="H73" s="16">
+        <f>Data!D67</f>
+        <v>12220942</v>
+      </c>
+      <c r="I73" s="16">
+        <f>Data!E67</f>
+        <v>12078528</v>
+      </c>
+      <c r="J73" s="16">
+        <f>Data!F67</f>
+        <v>11324224</v>
+      </c>
+      <c r="K73" s="16">
+        <f>Data!G67</f>
+        <v>0</v>
+      </c>
+      <c r="L73" s="16">
+        <f>Data!H67</f>
+        <v>0</v>
+      </c>
+      <c r="M73" s="16" t="str">
+        <f>Data!I67</f>
+        <v/>
+      </c>
+      <c r="N73" s="16" t="str">
+        <f>Data!J67</f>
+        <v/>
+      </c>
+      <c r="O73" s="16" t="str">
+        <f>Data!K67</f>
+        <v/>
+      </c>
+      <c r="P73" s="16" t="str">
+        <f>Data!L67</f>
+        <v/>
+      </c>
+      <c r="Q73" s="16" t="str">
+        <f>Data!M67</f>
         <v/>
       </c>
     </row>
@@ -8402,599 +8496,741 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12"/>
       <c r="B75" s="121" t="s">
-        <v>208</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="C75" s="29"/>
+      <c r="D75" s="29"/>
+      <c r="E75" s="29"/>
+      <c r="F75" s="29"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+      <c r="K75" s="14"/>
+      <c r="L75" s="14"/>
+      <c r="M75" s="14"/>
+      <c r="N75" s="14"/>
+      <c r="O75" s="14"/>
+      <c r="P75" s="14"/>
+      <c r="Q75" s="14"/>
     </row>
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="12"/>
       <c r="B76" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="C76" s="46">
-        <f>-C4/C59</f>
-        <v>209.73640568718258</v>
-      </c>
-      <c r="G76" s="46">
-        <f>IF(G4="","",-G4/G59)</f>
-        <v>257.16427276998456</v>
-      </c>
-      <c r="H76" s="46">
-        <f>IF(H4="","",-H4/H59)</f>
-        <v>576.88407262919611</v>
-      </c>
-      <c r="I76" s="46">
-        <f>IF(I4="","",-I4/I59)</f>
-        <v>508.19599948045203</v>
-      </c>
-      <c r="J76" s="46">
-        <f>IF(J4="","",-J4/J59)</f>
-        <v>307.162639952858</v>
-      </c>
-      <c r="K76" s="46">
-        <f>IF(K4="","",-K4/K59)</f>
-        <v>178.10179944510503</v>
-      </c>
-      <c r="L76" s="46">
-        <f>IF(L4="","",-L4/L59)</f>
-        <v>463.02484453916446</v>
-      </c>
-      <c r="M76" s="46" t="str">
-        <f>IF(M4="","",-M4/M59)</f>
-        <v/>
-      </c>
-      <c r="N76" s="46" t="str">
-        <f>IF(N4="","",-N4/N59)</f>
-        <v/>
-      </c>
-      <c r="O76" s="46" t="str">
-        <f>IF(O4="","",-O4/O59)</f>
-        <v/>
-      </c>
-      <c r="P76" s="46" t="str">
-        <f>IF(P4="","",-P4/P59)</f>
-        <v/>
-      </c>
-      <c r="Q76" s="46" t="str">
-        <f>IF(Q4="","",-Q4/Q59)</f>
+        <v>201</v>
+      </c>
+      <c r="C76" s="131">
+        <f>C70/C$4</f>
+        <v>2.1262774144544083E-2</v>
+      </c>
+      <c r="D76" s="29"/>
+      <c r="E76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="131">
+        <f>IF(G$4="","",G70/G$4)</f>
+        <v>1.3951685381968192E-2</v>
+      </c>
+      <c r="H76" s="131">
+        <f t="shared" ref="H76:Q76" si="39">IF(H$4="","",H70/H$4)</f>
+        <v>1.5671518179732512E-2</v>
+      </c>
+      <c r="I76" s="131">
+        <f t="shared" si="39"/>
+        <v>2.3627760663558588E-2</v>
+      </c>
+      <c r="J76" s="131">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="K76" s="131">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="L76" s="131">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="M76" s="131" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="N76" s="131" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="O76" s="131" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P76" s="131" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="Q76" s="131" t="str">
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="12"/>
       <c r="B77" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="C77" s="26">
-        <f>C69/C65</f>
-        <v>0.76325199666976462</v>
-      </c>
-      <c r="G77" s="15">
-        <f t="shared" ref="G77:Q77" si="27">IF(G69="","",G69/G65)</f>
-        <v>0.76325199666976462</v>
-      </c>
-      <c r="H77" s="15">
-        <f t="shared" si="27"/>
-        <v>0.83207133093167851</v>
-      </c>
-      <c r="I77" s="15">
-        <f t="shared" si="27"/>
-        <v>0.75551647408031242</v>
-      </c>
-      <c r="J77" s="15">
-        <f t="shared" si="27"/>
-        <v>0.79351322080112696</v>
-      </c>
-      <c r="K77" s="15" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L77" s="15" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M77" s="15" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="N77" s="15" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="O77" s="15" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="P77" s="15" t="str">
-        <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="Q77" s="15" t="str">
-        <f t="shared" si="27"/>
+        <v>202</v>
+      </c>
+      <c r="C77" s="131">
+        <f>C71/C$4</f>
+        <v>0.7738144762493232</v>
+      </c>
+      <c r="D77" s="29"/>
+      <c r="E77" s="29"/>
+      <c r="F77" s="29"/>
+      <c r="G77" s="131">
+        <f>IF(G$4="","",G71/G$4)</f>
+        <v>0.57762188109301071</v>
+      </c>
+      <c r="H77" s="131">
+        <f t="shared" ref="H77:Q77" si="40">IF(H$4="","",H71/H$4)</f>
+        <v>0.73212708397270831</v>
+      </c>
+      <c r="I77" s="131">
+        <f t="shared" si="40"/>
+        <v>0.62376357824373097</v>
+      </c>
+      <c r="J77" s="131">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="K77" s="131">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="L77" s="131">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="M77" s="131" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="N77" s="131" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="O77" s="131" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="P77" s="131" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q77" s="131" t="str">
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="12"/>
+      <c r="B78" s="29"/>
+      <c r="C78" s="29"/>
+      <c r="D78" s="29"/>
+      <c r="E78" s="29"/>
+      <c r="F78" s="29"/>
+      <c r="G78" s="16"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+      <c r="K78" s="14"/>
+      <c r="L78" s="14"/>
+      <c r="M78" s="14"/>
+      <c r="N78" s="14"/>
+      <c r="O78" s="14"/>
+      <c r="P78" s="14"/>
+      <c r="Q78" s="14"/>
     </row>
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="12"/>
       <c r="B79" s="121" t="s">
-        <v>64</v>
-      </c>
-      <c r="C79" s="62"/>
-      <c r="D79" s="62"/>
-      <c r="E79" s="62"/>
-      <c r="F79" s="62"/>
-      <c r="G79" s="26" t="str">
-        <f>IFERROR(IF(#REF!*G81*(1/G77)=G83,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H79" s="26" t="str">
-        <f>IFERROR(IF(#REF!*H81*(1/H77)=H83,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I79" s="26" t="str">
-        <f>IFERROR(IF(#REF!*I81*(1/I77)=I83,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J79" s="26" t="str">
-        <f>IFERROR(IF(#REF!*J81*(1/J77)=J83,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K79" s="26" t="str">
-        <f>IFERROR(IF(#REF!*K81*(1/K77)=K83,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L79" s="26" t="str">
-        <f>IFERROR(IF(#REF!*L81*(1/L77)=L83,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M79" s="26" t="str">
-        <f>IFERROR(IF(#REF!*M81*(1/M77)=M83,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N79" s="26" t="str">
-        <f>IFERROR(IF(#REF!*N81*(1/N77)=N83,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O79" s="26" t="str">
-        <f>IFERROR(IF(#REF!*O81*(1/O77)=O83,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P79" s="26" t="str">
-        <f>IFERROR(IF(#REF!*P81*(1/P77)=P83,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q79" s="26" t="str">
-        <f>IFERROR(IF(#REF!*Q81*(1/Q77)=Q83,"","Error"),"")</f>
-        <v/>
+        <v>208</v>
       </c>
     </row>
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="12"/>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="C80" s="46">
+        <f>-C4/C63</f>
+        <v>209.73640568718258</v>
+      </c>
+      <c r="G80" s="46">
+        <f t="shared" ref="G80:Q80" si="41">IF(G4="","",-G4/G63)</f>
+        <v>257.16427276998456</v>
+      </c>
+      <c r="H80" s="46">
+        <f t="shared" si="41"/>
+        <v>576.88407262919611</v>
+      </c>
+      <c r="I80" s="46">
+        <f t="shared" si="41"/>
+        <v>508.19599948045203</v>
+      </c>
+      <c r="J80" s="46">
+        <f t="shared" si="41"/>
+        <v>307.162639952858</v>
+      </c>
+      <c r="K80" s="46">
+        <f t="shared" si="41"/>
+        <v>178.10179944510503</v>
+      </c>
+      <c r="L80" s="46">
+        <f t="shared" si="41"/>
+        <v>463.02484453916446</v>
+      </c>
+      <c r="M80" s="46" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="N80" s="46" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="O80" s="46" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="P80" s="46" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="Q80" s="46" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="12"/>
+      <c r="B81" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="C81" s="26">
+        <f>C73/C69</f>
+        <v>0.76325199666976462</v>
+      </c>
+      <c r="G81" s="15">
+        <f t="shared" ref="G81:Q81" si="42">IF(G73="","",G73/G69)</f>
+        <v>0.76325199666976462</v>
+      </c>
+      <c r="H81" s="15">
+        <f t="shared" si="42"/>
+        <v>0.83207133093167851</v>
+      </c>
+      <c r="I81" s="15">
+        <f t="shared" si="42"/>
+        <v>0.75551647408031242</v>
+      </c>
+      <c r="J81" s="15">
+        <f t="shared" si="42"/>
+        <v>0.79351322080112696</v>
+      </c>
+      <c r="K81" s="15" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L81" s="15" t="e">
+        <f t="shared" si="42"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M81" s="15" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="N81" s="15" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="O81" s="15" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="P81" s="15" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="Q81" s="15" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="12"/>
+    </row>
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="12"/>
+      <c r="B83" s="121" t="s">
+        <v>64</v>
+      </c>
+      <c r="C83" s="62"/>
+      <c r="D83" s="62"/>
+      <c r="E83" s="62"/>
+      <c r="F83" s="62"/>
+      <c r="G83" s="26" t="str">
+        <f>IFERROR(IF(#REF!*G85*(1/G81)=G87,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H83" s="26" t="str">
+        <f>IFERROR(IF(#REF!*H85*(1/H81)=H87,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I83" s="26" t="str">
+        <f>IFERROR(IF(#REF!*I85*(1/I81)=I87,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J83" s="26" t="str">
+        <f>IFERROR(IF(#REF!*J85*(1/J81)=J87,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K83" s="26" t="str">
+        <f>IFERROR(IF(#REF!*K85*(1/K81)=K87,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L83" s="26" t="str">
+        <f>IFERROR(IF(#REF!*L85*(1/L81)=L87,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M83" s="26" t="str">
+        <f>IFERROR(IF(#REF!*M85*(1/M81)=M87,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N83" s="26" t="str">
+        <f>IFERROR(IF(#REF!*N85*(1/N81)=N87,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O83" s="26" t="str">
+        <f>IFERROR(IF(#REF!*O85*(1/O81)=O87,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P83" s="26" t="str">
+        <f>IFERROR(IF(#REF!*P85*(1/P81)=P87,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q83" s="26" t="str">
+        <f>IFERROR(IF(#REF!*Q85*(1/Q81)=Q87,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="12"/>
+      <c r="B84" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="C80" s="26">
+      <c r="C84" s="26">
         <f>C26</f>
         <v>0.11664383553220437</v>
       </c>
-      <c r="G80" s="26">
+      <c r="G84" s="26">
         <f>G26</f>
         <v>0.12245710905455723</v>
       </c>
-      <c r="H80" s="26">
-        <f t="shared" ref="H80:Q80" si="28">H26</f>
+      <c r="H84" s="26">
+        <f t="shared" ref="H84:Q84" si="43">H26</f>
         <v>0.11378358242100998</v>
       </c>
-      <c r="I80" s="26">
-        <f t="shared" si="28"/>
+      <c r="I84" s="26">
+        <f t="shared" si="43"/>
         <v>0.12086725258551366</v>
       </c>
-      <c r="J80" s="26">
-        <f t="shared" si="28"/>
+      <c r="J84" s="26">
+        <f t="shared" si="43"/>
         <v>0.10583450462035347</v>
       </c>
-      <c r="K80" s="26">
-        <f t="shared" si="28"/>
+      <c r="K84" s="26">
+        <f t="shared" si="43"/>
         <v>0.10724519842891581</v>
       </c>
-      <c r="L80" s="26">
-        <f t="shared" si="28"/>
+      <c r="L84" s="26">
+        <f t="shared" si="43"/>
         <v>0.10195889152515229</v>
       </c>
-      <c r="M80" s="26" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="N80" s="26" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="O80" s="26" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="P80" s="26" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="Q80" s="26" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="9" t="s">
+      <c r="M84" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="N84" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="O84" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="P84" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="Q84" s="26" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="C81" s="46">
-        <f>C4/C65</f>
+      <c r="C85" s="46">
+        <f>C4/C69</f>
         <v>0.74162830005471281</v>
       </c>
-      <c r="G81" s="46">
-        <f>IF(G4="","",G4/G65)</f>
+      <c r="G85" s="46">
+        <f t="shared" ref="G85:Q85" si="44">IF(G4="","",G4/G69)</f>
         <v>0.90933332162498015</v>
       </c>
-      <c r="H81" s="46">
-        <f>IF(H4="","",H4/H65)</f>
+      <c r="H85" s="46">
+        <f t="shared" si="44"/>
         <v>0.81551983462257005</v>
       </c>
-      <c r="I81" s="46">
-        <f>IF(I4="","",I4/I65)</f>
+      <c r="I85" s="46">
+        <f t="shared" si="44"/>
         <v>0.73420399704411943</v>
       </c>
-      <c r="J81" s="46">
-        <f>IF(J4="","",J4/J65)</f>
+      <c r="J85" s="46">
+        <f t="shared" si="44"/>
         <v>0.62093318504188499</v>
       </c>
-      <c r="K81" s="46" t="e">
-        <f>IF(K4="","",K4/K65)</f>
+      <c r="K85" s="46" t="e">
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L81" s="46" t="e">
-        <f>IF(L4="","",L4/L65)</f>
+      <c r="L85" s="46" t="e">
+        <f t="shared" si="44"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M81" s="46" t="str">
-        <f>IF(M4="","",M4/M65)</f>
-        <v/>
-      </c>
-      <c r="N81" s="46" t="str">
-        <f>IF(N4="","",N4/N65)</f>
-        <v/>
-      </c>
-      <c r="O81" s="46" t="str">
-        <f>IF(O4="","",O4/O65)</f>
-        <v/>
-      </c>
-      <c r="P81" s="46" t="str">
-        <f>IF(P4="","",P4/P65)</f>
-        <v/>
-      </c>
-      <c r="Q81" s="46" t="str">
-        <f>IF(Q4="","",Q4/Q65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B82" s="9" t="s">
+      <c r="M85" s="46" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="N85" s="46" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="O85" s="46" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="P85" s="46" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="Q85" s="46" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B86" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C82" s="17">
-        <f>C65/C69</f>
+      <c r="C86" s="17">
+        <f>C69/C73</f>
         <v>1.3101832741522048</v>
       </c>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="17">
-        <f t="shared" ref="G82:Q82" si="29">IF(G$4="","",G65/G69)</f>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="17">
+        <f t="shared" ref="G86:Q86" si="45">IF(G$4="","",G69/G73)</f>
         <v>1.3101832741522048</v>
       </c>
-      <c r="H82" s="17">
-        <f t="shared" si="29"/>
+      <c r="H86" s="17">
+        <f t="shared" si="45"/>
         <v>1.2018200397317982</v>
       </c>
-      <c r="I82" s="17">
-        <f t="shared" si="29"/>
+      <c r="I86" s="17">
+        <f t="shared" si="45"/>
         <v>1.3235978755027102</v>
       </c>
-      <c r="J82" s="17">
-        <f t="shared" si="29"/>
+      <c r="J86" s="17">
+        <f t="shared" si="45"/>
         <v>1.2602184485223888</v>
       </c>
-      <c r="K82" s="17" t="e">
-        <f t="shared" si="29"/>
+      <c r="K86" s="17" t="e">
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L82" s="17" t="e">
-        <f t="shared" si="29"/>
+      <c r="L86" s="17" t="e">
+        <f t="shared" si="45"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M82" s="17" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="N82" s="17" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="O82" s="17" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="P82" s="17" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="Q82" s="17" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="12"/>
-      <c r="B83" s="91" t="s">
-        <v>65</v>
-      </c>
-      <c r="C83" s="140">
-        <f>C8/C69</f>
-        <v>0.11333919837099207</v>
-      </c>
-      <c r="D83" s="141"/>
-      <c r="E83" s="141"/>
-      <c r="F83" s="141"/>
-      <c r="G83" s="140">
-        <f>IF(G$4="","",G8/G69)</f>
-        <v>0.14589458032083277</v>
-      </c>
-      <c r="H83" s="140">
-        <f>IF(H$4="","",H8/H69)</f>
-        <v>0.11152020850765841</v>
-      </c>
-      <c r="I83" s="140">
-        <f>IF(I$4="","",I8/I69)</f>
-        <v>0.1174576902086082</v>
-      </c>
-      <c r="J83" s="140">
-        <f>IF(J$4="","",J8/J69)</f>
-        <v>8.2816712209154458E-2</v>
-      </c>
-      <c r="K83" s="140" t="e">
-        <f>IF(K$4="","",K8/K69)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L83" s="140" t="e">
-        <f>IF(L$4="","",L8/L69)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M83" s="140" t="str">
-        <f>IF(M$4="","",M8/M69)</f>
-        <v/>
-      </c>
-      <c r="N83" s="140" t="str">
-        <f>IF(N$4="","",N8/N69)</f>
-        <v/>
-      </c>
-      <c r="O83" s="140" t="str">
-        <f>IF(O$4="","",O8/O69)</f>
-        <v/>
-      </c>
-      <c r="P83" s="140" t="str">
-        <f>IF(P$4="","",P8/P69)</f>
-        <v/>
-      </c>
-      <c r="Q83" s="140" t="str">
-        <f>IF(Q$4="","",Q8/Q69)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="12"/>
-    </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A85" s="12"/>
-      <c r="B85" s="61" t="s">
-        <v>230</v>
-      </c>
-      <c r="C85" s="61"/>
-      <c r="D85" s="63"/>
-      <c r="E85" s="81" t="s">
-        <v>146</v>
-      </c>
-      <c r="F85" s="63"/>
-      <c r="G85" s="40"/>
-      <c r="H85" s="40"/>
-      <c r="I85" s="40"/>
-      <c r="J85" s="40"/>
-      <c r="K85" s="40"/>
-      <c r="L85" s="40"/>
-      <c r="M85" s="40"/>
-      <c r="N85" s="40"/>
-      <c r="O85" s="40"/>
-      <c r="P85" s="40"/>
-      <c r="Q85" s="40"/>
-    </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="12"/>
-      <c r="B86" s="78" t="s">
-        <v>228</v>
+      <c r="M86" s="17" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="N86" s="17" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="O86" s="17" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="P86" s="17" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="Q86" s="17" t="str">
+        <f t="shared" si="45"/>
+        <v/>
       </c>
     </row>
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="12"/>
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="91" t="s">
+        <v>65</v>
+      </c>
+      <c r="C87" s="140">
+        <f>C8/C73</f>
+        <v>0.11333919837099207</v>
+      </c>
+      <c r="D87" s="141"/>
+      <c r="E87" s="141"/>
+      <c r="F87" s="141"/>
+      <c r="G87" s="140">
+        <f t="shared" ref="G87:Q87" si="46">IF(G$4="","",G8/G73)</f>
+        <v>0.14589458032083277</v>
+      </c>
+      <c r="H87" s="140">
+        <f t="shared" si="46"/>
+        <v>0.11152020850765841</v>
+      </c>
+      <c r="I87" s="140">
+        <f t="shared" si="46"/>
+        <v>0.1174576902086082</v>
+      </c>
+      <c r="J87" s="140">
+        <f t="shared" si="46"/>
+        <v>8.2816712209154458E-2</v>
+      </c>
+      <c r="K87" s="140" t="e">
+        <f t="shared" si="46"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L87" s="140" t="e">
+        <f t="shared" si="46"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M87" s="140" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="N87" s="140" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="O87" s="140" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="P87" s="140" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="Q87" s="140" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="12"/>
+    </row>
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A89" s="12"/>
+      <c r="B89" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="C89" s="61"/>
+      <c r="D89" s="63"/>
+      <c r="E89" s="81" t="s">
+        <v>146</v>
+      </c>
+      <c r="F89" s="63"/>
+      <c r="G89" s="40"/>
+      <c r="H89" s="40"/>
+      <c r="I89" s="40"/>
+      <c r="J89" s="40"/>
+      <c r="K89" s="40"/>
+      <c r="L89" s="40"/>
+      <c r="M89" s="40"/>
+      <c r="N89" s="40"/>
+      <c r="O89" s="40"/>
+      <c r="P89" s="40"/>
+      <c r="Q89" s="40"/>
+    </row>
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="12"/>
+      <c r="B90" s="78" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="12"/>
+      <c r="B91" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C87" s="157">
-        <f>G87</f>
+      <c r="C91" s="157">
+        <f>G91</f>
         <v>1.3599999999999999</v>
       </c>
-      <c r="G87" s="156">
+      <c r="G91" s="156">
         <f>Data!C52</f>
         <v>1.3599999999999999</v>
       </c>
-      <c r="H87" s="156">
+      <c r="H91" s="156">
         <f>Data!D52</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="I87" s="156">
+      <c r="I91" s="156">
         <f>Data!E52</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="J87" s="156">
+      <c r="J91" s="156">
         <f>Data!F52</f>
         <v>1</v>
       </c>
-      <c r="K87" s="156">
+      <c r="K91" s="156">
         <f>Data!G52</f>
         <v>1</v>
       </c>
-      <c r="L87" s="156">
+      <c r="L91" s="156">
         <f>Data!H52</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="M87" s="156" t="str">
+      <c r="M91" s="156" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N87" s="156" t="str">
+      <c r="N91" s="156" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O87" s="156" t="str">
+      <c r="O91" s="156" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P87" s="156" t="str">
+      <c r="P91" s="156" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q87" s="156" t="str">
+      <c r="Q91" s="156" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
-    </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="12"/>
-      <c r="B88" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C88" s="96">
-        <f>C87*Common_Shares/$C$3</f>
-        <v>798466.67599999986</v>
-      </c>
-      <c r="G88" s="96">
-        <f t="shared" ref="G88:Q88" si="30">IF(G$4="","",G87*Common_Shares/$C$3)</f>
-        <v>798466.67599999986</v>
-      </c>
-      <c r="H88" s="96">
-        <f t="shared" si="30"/>
-        <v>645818.63500000001</v>
-      </c>
-      <c r="I88" s="96">
-        <f t="shared" si="30"/>
-        <v>645818.63500000001</v>
-      </c>
-      <c r="J88" s="96">
-        <f t="shared" si="30"/>
-        <v>587107.85</v>
-      </c>
-      <c r="K88" s="96">
-        <f t="shared" si="30"/>
-        <v>587107.85</v>
-      </c>
-      <c r="L88" s="96">
-        <f t="shared" si="30"/>
-        <v>675174.02749999997</v>
-      </c>
-      <c r="M88" s="96" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="N88" s="96" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="O88" s="96" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="P88" s="96" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="Q88" s="96" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="12"/>
-      <c r="B89" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C89" s="26">
-        <f>C87/(C15*$C$3/Common_Shares)</f>
-        <v>0.73898220922083402</v>
-      </c>
-      <c r="G89" s="26">
-        <f t="shared" ref="G89:Q89" si="31">IF(G$4="","",G87/(G15*$C$3/Common_Shares))</f>
-        <v>0.61137166287015943</v>
-      </c>
-      <c r="H89" s="26">
-        <f t="shared" si="31"/>
-        <v>0.47520767477248388</v>
-      </c>
-      <c r="I89" s="26">
-        <f t="shared" si="31"/>
-        <v>0.55110750382299534</v>
-      </c>
-      <c r="J89" s="26">
-        <f t="shared" si="31"/>
-        <v>0.52597248961462351</v>
-      </c>
-      <c r="K89" s="26">
-        <f t="shared" si="31"/>
-        <v>0.51484610946055442</v>
-      </c>
-      <c r="L89" s="26">
-        <f t="shared" si="31"/>
-        <v>0.42952570160047737</v>
-      </c>
-      <c r="M89" s="26" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="N89" s="26" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="O89" s="26" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="P89" s="26" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="Q89" s="26" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="12"/>
-    </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="12"/>
     </row>
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="12"/>
+      <c r="B92" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C92" s="96">
+        <f>C91*Common_Shares/$C$3</f>
+        <v>798466.67599999986</v>
+      </c>
+      <c r="G92" s="96">
+        <f t="shared" ref="G92:Q92" si="47">IF(G$4="","",G91*Common_Shares/$C$3)</f>
+        <v>798466.67599999986</v>
+      </c>
+      <c r="H92" s="96">
+        <f t="shared" si="47"/>
+        <v>645818.63500000001</v>
+      </c>
+      <c r="I92" s="96">
+        <f t="shared" si="47"/>
+        <v>645818.63500000001</v>
+      </c>
+      <c r="J92" s="96">
+        <f t="shared" si="47"/>
+        <v>587107.85</v>
+      </c>
+      <c r="K92" s="96">
+        <f t="shared" si="47"/>
+        <v>587107.85</v>
+      </c>
+      <c r="L92" s="96">
+        <f t="shared" si="47"/>
+        <v>675174.02749999997</v>
+      </c>
+      <c r="M92" s="96" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="N92" s="96" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="O92" s="96" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="P92" s="96" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="Q92" s="96" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
     </row>
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="12"/>
+      <c r="B93" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C93" s="26">
+        <f>C91/(C15*$C$3/Common_Shares)</f>
+        <v>0.73898220922083402</v>
+      </c>
+      <c r="G93" s="26">
+        <f t="shared" ref="G93:Q93" si="48">IF(G$4="","",G91/(G15*$C$3/Common_Shares))</f>
+        <v>0.61137166287015943</v>
+      </c>
+      <c r="H93" s="26">
+        <f t="shared" si="48"/>
+        <v>0.47520767477248388</v>
+      </c>
+      <c r="I93" s="26">
+        <f t="shared" si="48"/>
+        <v>0.55110750382299534</v>
+      </c>
+      <c r="J93" s="26">
+        <f t="shared" si="48"/>
+        <v>0.52597248961462351</v>
+      </c>
+      <c r="K93" s="26">
+        <f t="shared" si="48"/>
+        <v>0.51484610946055442</v>
+      </c>
+      <c r="L93" s="26">
+        <f t="shared" si="48"/>
+        <v>0.42952570160047737</v>
+      </c>
+      <c r="M93" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="N93" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="O93" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="P93" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="Q93" s="26" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="12"/>
@@ -9062,10 +9298,18 @@
     <row r="115" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="12"/>
     </row>
-    <row r="116" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="117" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="118" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="119" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="116" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="12"/>
+    </row>
+    <row r="117" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="12"/>
+    </row>
+    <row r="118" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="12"/>
+    </row>
+    <row r="119" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="12"/>
+    </row>
     <row r="120" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="121" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="122" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -9745,9 +9989,13 @@
     <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="G4:Q9 G14:Q14 G43:Q44 G47:Q47 G11:Q11 G19:Q19">
+  <conditionalFormatting sqref="G4:Q9 G11:Q11 G14:Q14 G19:Q19 G47:Q48 G51:Q51">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
@@ -9786,7 +10034,7 @@
         <v>45382</v>
       </c>
       <c r="F1" s="115" t="str">
-        <f>IF(MONTH(C1)=MONTH(FCF!G1),"FY","Quarter")&amp;" Report"</f>
+        <f>IF(MONTH(C1)=MONTH(Normalized_FCF!G1),"FY","Quarter")&amp;" Report"</f>
         <v>FY Report</v>
       </c>
       <c r="H1" s="4"/>
@@ -10160,7 +10408,7 @@
         <v>459552.95</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G20" s="108">
         <f>G10+G17</f>
@@ -10175,11 +10423,11 @@
       <c r="B22" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="210" t="s">
+      <c r="G22" s="205" t="s">
+        <v>291</v>
+      </c>
+      <c r="H22" s="205" t="s">
         <v>292</v>
-      </c>
-      <c r="H22" s="210" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10370,7 +10618,7 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="133" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C39" s="134" t="s">
         <v>144</v>
@@ -10392,7 +10640,7 @@
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="D40" s="26">
-        <f>IF(FCF!G4="","",ABS(FCF!G59/BS!$G$27))</f>
+        <f>IF(Normalized_FCF!G4="","",ABS(Normalized_FCF!G63/BS!$G$27))</f>
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="F40" s="86" t="s">
@@ -10407,7 +10655,7 @@
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="D41" s="8">
-        <f>IF(FCF!G4="","",FCF!G60/BS!$G$24)</f>
+        <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G64/BS!$G$24)</f>
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="F41" s="86" t="s">
@@ -10423,7 +10671,7 @@
         <v>0.11625172085779995</v>
       </c>
       <c r="D42" s="26">
-        <f>FCF!G12/BS!$G$25</f>
+        <f>Normalized_FCF!G12/BS!$G$25</f>
         <v>0.11625172085779995</v>
       </c>
       <c r="F42" s="20" t="s">
@@ -10446,13 +10694,13 @@
       </c>
       <c r="C44" s="135"/>
       <c r="D44" s="132">
-        <f>BS!G27/FCF!C8</f>
+        <f>BS!G27/Normalized_FCF!C8</f>
         <v>1.3957095258737691</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="133" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C46" s="134" t="s">
         <v>144</v>
@@ -10463,33 +10711,33 @@
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C47" s="123">
-        <f>FCF!C18/G19</f>
+        <f>Normalized_FCF!C18/G19</f>
         <v>7.756539100607851E-2</v>
       </c>
       <c r="D47" s="123">
-        <f>FCF!G18/G19</f>
+        <f>Normalized_FCF!G18/G19</f>
         <v>4.8775032000803437E-2</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C48" s="123">
-        <f>FCF!C19/G20</f>
+        <f>Normalized_FCF!C19/G20</f>
         <v>6.5041237095773002E-2</v>
       </c>
       <c r="D48" s="123">
-        <f>FCF!G19/G20</f>
+        <f>Normalized_FCF!G19/G20</f>
         <v>8.4925332042839377E-2</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="105" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C50" s="40"/>
       <c r="D50" s="40"/>
@@ -10510,18 +10758,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H91"/>
+  <dimension ref="B2:H89"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.59765625" customWidth="1"/>
-    <col min="2" max="6" width="20.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.59765625" customWidth="1"/>
+    <col min="3" max="6" width="20.59765625" customWidth="1"/>
     <col min="7" max="7" width="5.59765625" customWidth="1"/>
     <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="39" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -10536,20 +10785,20 @@
         <v>106</v>
       </c>
       <c r="C3" s="146">
-        <f>FCF!C3</f>
+        <f>Normalized_FCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E3" s="151" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H3" s="164"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="138" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C4" s="152">
-        <f>FCF!C20</f>
+        <f>Normalized_FCF!C20</f>
         <v>1270672.1269962033</v>
       </c>
       <c r="D4" t="str">
@@ -10557,7 +10806,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="138" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F4" s="178">
         <v>0</v>
@@ -10565,33 +10814,34 @@
       <c r="H4" s="164"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B5" s="196" t="s">
-        <v>266</v>
-      </c>
-      <c r="C5" s="200">
+      <c r="B5" s="193" t="s">
+        <v>265</v>
+      </c>
+      <c r="C5" s="178">
+        <f>Thesis!C37</f>
         <v>0.1</v>
       </c>
-      <c r="E5" s="196" t="s">
-        <v>270</v>
+      <c r="E5" s="193" t="s">
+        <v>269</v>
       </c>
       <c r="H5" s="164"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B6" s="198" t="s">
-        <v>265</v>
+      <c r="B6" s="195" t="s">
+        <v>264</v>
       </c>
       <c r="C6" s="179">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>12706721.269962033</v>
       </c>
-      <c r="E6" s="196" t="s">
-        <v>275</v>
+      <c r="E6" s="193" t="s">
+        <v>274</v>
       </c>
       <c r="H6" s="164"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B7" s="196" t="s">
-        <v>267</v>
+      <c r="B7" s="193" t="s">
+        <v>266</v>
       </c>
       <c r="C7" s="155">
         <f>BS!G27</f>
@@ -10600,8 +10850,8 @@
       <c r="H7" s="164"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B8" s="198" t="s">
-        <v>268</v>
+      <c r="B8" s="195" t="s">
+        <v>267</v>
       </c>
       <c r="C8" s="179">
         <f>C6-C7</f>
@@ -10610,11 +10860,11 @@
       <c r="H8" s="164"/>
     </row>
     <row r="9" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B9" s="197" t="s">
-        <v>239</v>
+      <c r="B9" s="194" t="s">
+        <v>238</v>
       </c>
       <c r="C9" s="154">
-        <f>(C8*FCF!C3)/Common_Shares</f>
+        <f>(C8*Normalized_FCF!C3)/Common_Shares</f>
         <v>18.176897600606146</v>
       </c>
       <c r="H9" s="164"/>
@@ -10624,7 +10874,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B11" s="39" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C11" s="40"/>
       <c r="D11" s="40"/>
@@ -10634,26 +10884,27 @@
     </row>
     <row r="12" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B12" s="163" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E12" s="151" t="s">
-        <v>287</v>
-      </c>
-      <c r="F12" s="205" t="str">
+        <v>286</v>
+      </c>
+      <c r="F12" s="200" t="str">
         <f>"("&amp;D4&amp;")"</f>
         <v>(HKD)</v>
       </c>
       <c r="H12" s="164"/>
     </row>
     <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="203" t="s">
-        <v>283</v>
-      </c>
-      <c r="C13" s="201">
+      <c r="B13" s="198" t="s">
+        <v>282</v>
+      </c>
+      <c r="C13" s="211">
+        <f>Scenarios!C22</f>
         <v>-3.7999999999999999E-2</v>
       </c>
       <c r="E13" s="138" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F13">
         <f>Market_Price</f>
@@ -10663,19 +10914,20 @@
     </row>
     <row r="14" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="162" t="s">
-        <v>284</v>
-      </c>
-      <c r="C14" s="202">
+        <v>283</v>
+      </c>
+      <c r="C14" s="212">
+        <f>Scenarios!C21</f>
         <v>10</v>
       </c>
       <c r="E14" s="138" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H14" s="164"/>
     </row>
     <row r="15" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="204" t="s">
-        <v>245</v>
+      <c r="B15" s="199" t="s">
+        <v>244</v>
       </c>
       <c r="C15" s="185">
         <f>(F49-C7)/Common_Shares*C3</f>
@@ -10686,7 +10938,7 @@
         <v>equals Market Price</v>
       </c>
       <c r="E15" s="138" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H15" s="164"/>
     </row>
@@ -10695,19 +10947,19 @@
     </row>
     <row r="17" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="172" t="s">
+        <v>245</v>
+      </c>
+      <c r="C17" s="172" t="s">
         <v>246</v>
       </c>
-      <c r="C17" s="172" t="s">
+      <c r="D17" s="172" t="s">
+        <v>258</v>
+      </c>
+      <c r="E17" s="172" t="s">
         <v>247</v>
       </c>
-      <c r="D17" s="172" t="s">
-        <v>259</v>
-      </c>
-      <c r="E17" s="172" t="s">
+      <c r="F17" s="173" t="s">
         <v>248</v>
-      </c>
-      <c r="F17" s="173" t="s">
-        <v>249</v>
       </c>
       <c r="H17" s="164"/>
     </row>
@@ -10720,7 +10972,7 @@
         <v>1222386.5861703476</v>
       </c>
       <c r="D18" s="183">
-        <f>IF($C$14&lt;B18,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B18,0,Valuation_Model!$C$13)</f>
         <v>-3.7999999999999999E-2</v>
       </c>
       <c r="E18" s="168">
@@ -10742,7 +10994,7 @@
         <v>1175935.8958958744</v>
       </c>
       <c r="D19" s="183">
-        <f>IF($C$14&lt;B19,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B19,0,Valuation_Model!$C$13)</f>
         <v>-3.7999999999999999E-2</v>
       </c>
       <c r="E19" s="168">
@@ -10764,7 +11016,7 @@
         <v>1131250.3318518312</v>
       </c>
       <c r="D20" s="183">
-        <f>IF($C$14&lt;B20,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B20,0,Valuation_Model!$C$13)</f>
         <v>-3.7999999999999999E-2</v>
       </c>
       <c r="E20" s="168">
@@ -10786,7 +11038,7 @@
         <v>1088262.8192414616</v>
       </c>
       <c r="D21" s="183">
-        <f>IF($C$14&lt;B21,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B21,0,Valuation_Model!$C$13)</f>
         <v>-3.7999999999999999E-2</v>
       </c>
       <c r="E21" s="168">
@@ -10808,7 +11060,7 @@
         <v>1046908.832110286</v>
       </c>
       <c r="D22" s="183">
-        <f>IF($C$14&lt;B22,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B22,0,Valuation_Model!$C$13)</f>
         <v>-3.7999999999999999E-2</v>
       </c>
       <c r="E22" s="168">
@@ -10830,7 +11082,7 @@
         <v>1007126.2964900951</v>
       </c>
       <c r="D23" s="183">
-        <f>IF($C$14&lt;B23,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B23,0,Valuation_Model!$C$13)</f>
         <v>-3.7999999999999999E-2</v>
       </c>
       <c r="E23" s="168">
@@ -10852,7 +11104,7 @@
         <v>968855.49722347141</v>
       </c>
       <c r="D24" s="183">
-        <f>IF($C$14&lt;B24,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B24,0,Valuation_Model!$C$13)</f>
         <v>-3.7999999999999999E-2</v>
       </c>
       <c r="E24" s="168">
@@ -10874,7 +11126,7 @@
         <v>932038.98832897947</v>
       </c>
       <c r="D25" s="183">
-        <f>IF($C$14&lt;B25,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B25,0,Valuation_Model!$C$13)</f>
         <v>-3.7999999999999999E-2</v>
       </c>
       <c r="E25" s="168">
@@ -10896,7 +11148,7 @@
         <v>896621.50677247834</v>
       </c>
       <c r="D26" s="183">
-        <f>IF($C$14&lt;B26,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B26,0,Valuation_Model!$C$13)</f>
         <v>-3.7999999999999999E-2</v>
       </c>
       <c r="E26" s="168">
@@ -10918,7 +11170,7 @@
         <v>862549.88951512414</v>
       </c>
       <c r="D27" s="183">
-        <f>IF($C$14&lt;B27,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B27,0,Valuation_Model!$C$13)</f>
         <v>-3.7999999999999999E-2</v>
       </c>
       <c r="E27" s="168">
@@ -10940,7 +11192,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="183">
-        <f>IF($C$14&lt;B28,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B28,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E28" s="168">
@@ -10962,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="183">
-        <f>IF($C$14&lt;B29,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B29,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E29" s="168">
@@ -10984,7 +11236,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="183">
-        <f>IF($C$14&lt;B30,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B30,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E30" s="168">
@@ -11006,7 +11258,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="183">
-        <f>IF($C$14&lt;B31,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B31,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E31" s="168">
@@ -11028,7 +11280,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="183">
-        <f>IF($C$14&lt;B32,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B32,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E32" s="168">
@@ -11050,7 +11302,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="183">
-        <f>IF($C$14&lt;B33,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B33,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E33" s="168">
@@ -11072,7 +11324,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="183">
-        <f>IF($C$14&lt;B34,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B34,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E34" s="168">
@@ -11094,7 +11346,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="183">
-        <f>IF($C$14&lt;B35,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B35,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E35" s="168">
@@ -11116,7 +11368,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="183">
-        <f>IF($C$14&lt;B36,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B36,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E36" s="168">
@@ -11138,7 +11390,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="183">
-        <f>IF($C$14&lt;B37,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B37,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E37" s="168">
@@ -11160,7 +11412,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="183">
-        <f>IF($C$14&lt;B38,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B38,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E38" s="168">
@@ -11182,7 +11434,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="183">
-        <f>IF($C$14&lt;B39,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B39,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E39" s="168">
@@ -11204,7 +11456,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="183">
-        <f>IF($C$14&lt;B40,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B40,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E40" s="168">
@@ -11226,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="183">
-        <f>IF($C$14&lt;B41,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B41,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E41" s="168">
@@ -11248,7 +11500,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="183">
-        <f>IF($C$14&lt;B42,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B42,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E42" s="168">
@@ -11270,7 +11522,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="183">
-        <f>IF($C$14&lt;B43,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B43,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E43" s="168">
@@ -11292,7 +11544,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="183">
-        <f>IF($C$14&lt;B44,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B44,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E44" s="168">
@@ -11314,7 +11566,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="183">
-        <f>IF($C$14&lt;B45,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B45,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E45" s="168">
@@ -11336,7 +11588,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="183">
-        <f>IF($C$14&lt;B46,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B46,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E46" s="168">
@@ -11358,7 +11610,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="183">
-        <f>IF($C$14&lt;B47,0,Model!$C$13)</f>
+        <f>IF($C$14&lt;B47,0,Valuation_Model!$C$13)</f>
         <v>0</v>
       </c>
       <c r="E47" s="168">
@@ -11373,7 +11625,7 @@
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B48" s="170" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C48" s="167">
         <f>C$18*(1+Terminal_Growth)^$C$14/Equity_Cost</f>
@@ -11396,7 +11648,7 @@
     <row r="49" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C49" s="158"/>
       <c r="E49" s="171" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F49" s="182">
         <f>SUM(F18:F48)</f>
@@ -11410,7 +11662,7 @@
     </row>
     <row r="51" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B51" s="163" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="181"/>
@@ -11442,7 +11694,7 @@
       <c r="H52" s="164"/>
     </row>
     <row r="53" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B53" s="189">
+      <c r="B53" s="188">
         <v>5</v>
       </c>
       <c r="C53" s="167">
@@ -11461,7 +11713,7 @@
       <c r="H53" s="164"/>
     </row>
     <row r="54" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B54" s="189">
+      <c r="B54" s="188">
         <v>10</v>
       </c>
       <c r="C54" s="167">
@@ -11479,7 +11731,7 @@
       <c r="H54" s="164"/>
     </row>
     <row r="55" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B55" s="189">
+      <c r="B55" s="188">
         <v>15</v>
       </c>
       <c r="C55" s="167">
@@ -11497,7 +11749,7 @@
       <c r="H55" s="164"/>
     </row>
     <row r="56" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B56" s="190">
+      <c r="B56" s="189">
         <v>20</v>
       </c>
       <c r="C56" s="167">
@@ -11515,7 +11767,7 @@
       <c r="H56" s="164"/>
     </row>
     <row r="57" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B57" s="190">
+      <c r="B57" s="189">
         <v>25</v>
       </c>
       <c r="C57" s="167">
@@ -11533,7 +11785,7 @@
       <c r="H57" s="164"/>
     </row>
     <row r="58" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B58" s="190">
+      <c r="B58" s="189">
         <v>30</v>
       </c>
       <c r="C58" s="167">
@@ -11559,7 +11811,7 @@
     </row>
     <row r="60" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B60" s="163" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C60" s="158"/>
       <c r="D60" s="158"/>
@@ -11587,7 +11839,7 @@
       <c r="H61" s="164"/>
     </row>
     <row r="62" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B62" s="189">
+      <c r="B62" s="188">
         <f t="shared" ref="B62:B67" si="3">B53</f>
         <v>5</v>
       </c>
@@ -11610,7 +11862,7 @@
       <c r="H62" s="164"/>
     </row>
     <row r="63" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B63" s="189">
+      <c r="B63" s="188">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -11633,7 +11885,7 @@
       <c r="H63" s="164"/>
     </row>
     <row r="64" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B64" s="189">
+      <c r="B64" s="188">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
@@ -11656,7 +11908,7 @@
       <c r="H64" s="164"/>
     </row>
     <row r="65" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B65" s="190">
+      <c r="B65" s="189">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -11679,7 +11931,7 @@
       <c r="H65" s="164"/>
     </row>
     <row r="66" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B66" s="190">
+      <c r="B66" s="189">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
@@ -11701,7 +11953,7 @@
       </c>
     </row>
     <row r="67" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B67" s="190">
+      <c r="B67" s="189">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
@@ -11724,29 +11976,31 @@
     </row>
     <row r="69" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B69" s="172" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C69" s="172" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D69" s="172" t="s">
+        <v>250</v>
+      </c>
+      <c r="E69" s="173" t="s">
         <v>251</v>
       </c>
-      <c r="E69" s="173" t="s">
-        <v>252</v>
-      </c>
       <c r="F69" s="173" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B70" s="171" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C70" s="187">
+        <f>Scenarios!C40</f>
         <v>0.02</v>
       </c>
-      <c r="D70" s="191">
+      <c r="D70" s="190">
+        <f>Scenarios!C39</f>
         <v>10</v>
       </c>
       <c r="E70" s="180">
@@ -11754,20 +12008,23 @@
         <v>19.671034792004711</v>
       </c>
       <c r="F70" s="187">
+        <f>Scenarios!C42</f>
         <v>0.15</v>
       </c>
       <c r="H70" s="164" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B71" s="171" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C71" s="187">
+        <f>Scenarios!C28</f>
         <v>0.01</v>
       </c>
-      <c r="D71" s="191">
+      <c r="D71" s="190">
+        <f>Scenarios!C27</f>
         <v>5</v>
       </c>
       <c r="E71" s="180">
@@ -11775,20 +12032,21 @@
         <v>18.544754566520961</v>
       </c>
       <c r="F71" s="187">
+        <f>Scenarios!C30</f>
         <v>0.5</v>
       </c>
       <c r="H71" s="164" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B72" s="171" t="s">
-        <v>253</v>
-      </c>
-      <c r="C72" s="188">
-        <v>0</v>
-      </c>
-      <c r="D72" s="192">
+        <v>252</v>
+      </c>
+      <c r="C72" s="187">
+        <v>0</v>
+      </c>
+      <c r="D72" s="190">
         <v>0</v>
       </c>
       <c r="E72" s="180">
@@ -11796,20 +12054,23 @@
         <v>18.176897600606146</v>
       </c>
       <c r="F72" s="187">
+        <f>Scenarios!C18</f>
         <v>0.2</v>
       </c>
       <c r="H72" s="164" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B73" s="171" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C73" s="187">
+        <f>Scenarios!C34</f>
         <v>-0.15</v>
       </c>
-      <c r="D73" s="191">
+      <c r="D73" s="190">
+        <f>Scenarios!C33</f>
         <v>5</v>
       </c>
       <c r="E73" s="180">
@@ -11817,134 +12078,31 @@
         <v>13.288003893211801</v>
       </c>
       <c r="F73" s="187">
+        <f>Scenarios!C36</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B74" s="208" t="str">
+      <c r="B74" s="203" t="str">
         <f>IF(VLOOKUP("No Growth",B70:E73,4,FALSE)&gt;VLOOKUP("Base",B70:E73,4,FALSE),"Note: the No Growth value being higher than the Base or Optimistic values is unusual.","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C74" s="208"/>
-      <c r="D74" s="208"/>
-      <c r="E74" s="208"/>
-      <c r="F74" s="209" t="str">
+      <c r="C74" s="203"/>
+      <c r="D74" s="203"/>
+      <c r="E74" s="203"/>
+      <c r="F74" s="204" t="str">
         <f>IF(SUM(F70:F73)=1,"100% - OK",SUM(F70:F73)*100&amp;"% Error")</f>
         <v>100% - OK</v>
       </c>
     </row>
-    <row r="76" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B76" s="138" t="s">
-        <v>261</v>
-      </c>
-      <c r="C76" s="207">
-        <f>E70*F70+E71*F71+E72*F72+E73*F73</f>
-        <v>17.851612606164188</v>
-      </c>
-      <c r="D76" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="78" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B78" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="C78" s="40"/>
-      <c r="D78" s="40"/>
-      <c r="E78" s="40"/>
-      <c r="F78" s="40"/>
-    </row>
-    <row r="79" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B79" s="151" t="s">
-        <v>272</v>
-      </c>
-      <c r="E79" s="151" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B80" s="138" t="s">
-        <v>290</v>
-      </c>
-      <c r="C80" s="178">
-        <f>Thesis!C37</f>
-        <v>0.2</v>
-      </c>
-      <c r="E80" s="138" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B81" s="138" t="s">
-        <v>250</v>
-      </c>
-      <c r="C81">
-        <f>FCF!C87</f>
-        <v>1.3599999999999999</v>
-      </c>
-      <c r="D81" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E81" s="138" t="s">
-        <v>271</v>
-      </c>
-      <c r="F81" s="199">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B83" s="151" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B84" s="138" t="s">
-        <v>262</v>
-      </c>
-      <c r="C84" s="160">
-        <f>PV(C80, F81, -C81, 0)</f>
-        <v>2.8648148148148143</v>
-      </c>
-      <c r="D84" s="138"/>
-    </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B85" s="138" t="s">
-        <v>264</v>
-      </c>
-      <c r="C85" s="160">
-        <f>C76/(1+C80)^F81</f>
-        <v>10.330794332270942</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B86" s="153" t="s">
-        <v>238</v>
-      </c>
-      <c r="C86" s="154">
-        <f>C84+C85</f>
-        <v>13.195609147085756</v>
-      </c>
-      <c r="D86" s="193" t="s">
-        <v>276</v>
-      </c>
-      <c r="E86" s="194">
-        <f>-(C86/C76-1)</f>
-        <v>0.2608169671725179</v>
-      </c>
-      <c r="H86" s="164" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C87" s="159"/>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C88" s="159"/>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C89" s="159"/>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C90" s="159"/>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C91" s="159"/>
     </row>
   </sheetData>
   <autoFilter ref="B69:F69" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
@@ -11976,4 +12134,498 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
+  <dimension ref="B2:I60"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.59765625" customWidth="1"/>
+    <col min="3" max="4" width="10.59765625" customWidth="1"/>
+    <col min="5" max="5" width="83.06640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B2" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B3" s="209" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B4" s="198" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4" s="164">
+        <v>4</v>
+      </c>
+      <c r="D4" s="164"/>
+      <c r="E4" s="138" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B6" s="209" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="162" t="s">
+        <v>303</v>
+      </c>
+      <c r="C7" s="208">
+        <f>AVERAGE(Normalized_FCF!G42:INDEX(Normalized_FCF!G42:Q42, $C$4))</f>
+        <v>0.10334930065770259</v>
+      </c>
+      <c r="D7" s="208"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B8" s="193" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="138" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B11" s="209" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B12" s="138" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B13" s="193" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B15" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+    </row>
+    <row r="16" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B16" s="209" t="s">
+        <v>310</v>
+      </c>
+      <c r="E16" s="209" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="138" t="s">
+        <v>251</v>
+      </c>
+      <c r="C17" s="210">
+        <f>Valuation_Model!E72</f>
+        <v>18.176897600606146</v>
+      </c>
+      <c r="D17" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E17" s="220" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B18" s="138" t="s">
+        <v>313</v>
+      </c>
+      <c r="C18" s="215">
+        <v>0.2</v>
+      </c>
+      <c r="D18" s="215"/>
+      <c r="E18" s="221"/>
+    </row>
+    <row r="20" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B20" s="209" t="s">
+        <v>309</v>
+      </c>
+      <c r="E20" s="209" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B21" s="198" t="s">
+        <v>282</v>
+      </c>
+      <c r="C21" s="196">
+        <v>10</v>
+      </c>
+      <c r="D21" s="196"/>
+      <c r="E21" s="222"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B22" s="162" t="s">
+        <v>283</v>
+      </c>
+      <c r="C22" s="197">
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="D22" s="197"/>
+      <c r="E22" s="223"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B23" s="138" t="s">
+        <v>251</v>
+      </c>
+      <c r="C23" s="210">
+        <f>Valuation_Model!C15</f>
+        <v>15.699957264324397</v>
+      </c>
+      <c r="D23" s="210"/>
+      <c r="E23" s="224"/>
+    </row>
+    <row r="25" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B25" s="39" t="s">
+        <v>312</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+    </row>
+    <row r="26" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B26" s="209" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="209" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B27" s="198" t="s">
+        <v>282</v>
+      </c>
+      <c r="C27" s="213">
+        <v>5</v>
+      </c>
+      <c r="D27" s="213"/>
+      <c r="E27" s="221"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B28" s="162" t="s">
+        <v>283</v>
+      </c>
+      <c r="C28" s="214">
+        <v>0.01</v>
+      </c>
+      <c r="D28" s="214"/>
+      <c r="E28" s="221"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B29" s="138" t="s">
+        <v>251</v>
+      </c>
+      <c r="C29" s="210">
+        <f>Valuation_Model!E71</f>
+        <v>18.544754566520961</v>
+      </c>
+      <c r="D29" s="210"/>
+      <c r="E29" s="221"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="138" t="s">
+        <v>313</v>
+      </c>
+      <c r="C30" s="215">
+        <v>0.5</v>
+      </c>
+      <c r="D30" s="215"/>
+      <c r="E30" s="221"/>
+    </row>
+    <row r="32" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B32" s="209" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="209" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B33" s="198" t="s">
+        <v>282</v>
+      </c>
+      <c r="C33" s="213">
+        <v>5</v>
+      </c>
+      <c r="D33" s="213"/>
+      <c r="E33" s="221"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B34" s="162" t="s">
+        <v>283</v>
+      </c>
+      <c r="C34" s="214">
+        <v>-0.15</v>
+      </c>
+      <c r="D34" s="214"/>
+      <c r="E34" s="221"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B35" s="138" t="s">
+        <v>251</v>
+      </c>
+      <c r="C35" s="210">
+        <f>Valuation_Model!E73</f>
+        <v>13.288003893211801</v>
+      </c>
+      <c r="D35" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E35" s="221"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B36" s="138" t="s">
+        <v>313</v>
+      </c>
+      <c r="C36" s="215">
+        <v>0.15</v>
+      </c>
+      <c r="D36" s="215"/>
+      <c r="E36" s="221"/>
+    </row>
+    <row r="38" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B38" s="209" t="s">
+        <v>308</v>
+      </c>
+      <c r="E38" s="209" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B39" s="198" t="s">
+        <v>282</v>
+      </c>
+      <c r="C39" s="213">
+        <v>10</v>
+      </c>
+      <c r="D39" s="213"/>
+      <c r="E39" s="221"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B40" s="162" t="s">
+        <v>283</v>
+      </c>
+      <c r="C40" s="214">
+        <v>0.02</v>
+      </c>
+      <c r="D40" s="214"/>
+      <c r="E40" s="221"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B41" s="138" t="s">
+        <v>251</v>
+      </c>
+      <c r="C41" s="210">
+        <f>Valuation_Model!E70</f>
+        <v>19.671034792004711</v>
+      </c>
+      <c r="D41" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E41" s="221"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B42" s="138" t="s">
+        <v>313</v>
+      </c>
+      <c r="C42" s="215">
+        <v>0.15</v>
+      </c>
+      <c r="D42" s="215"/>
+      <c r="E42" s="221"/>
+    </row>
+    <row r="44" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B44" s="138" t="s">
+        <v>260</v>
+      </c>
+      <c r="C44" s="202">
+        <f>C18*C17+C30*C29+C36*C35+C42*C41</f>
+        <v>17.851612606164188</v>
+      </c>
+      <c r="D44" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B46" s="39" t="s">
+        <v>276</v>
+      </c>
+      <c r="C46" s="40"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+    </row>
+    <row r="47" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B47" s="151" t="s">
+        <v>271</v>
+      </c>
+      <c r="E47" s="151" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B48" s="138" t="s">
+        <v>289</v>
+      </c>
+      <c r="C48" s="218">
+        <f>Thesis!C68</f>
+        <v>0.2</v>
+      </c>
+      <c r="D48" s="178"/>
+      <c r="E48" s="138" t="s">
+        <v>272</v>
+      </c>
+      <c r="F48" s="216">
+        <f>Thesis!C67</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B49" s="138" t="s">
+        <v>249</v>
+      </c>
+      <c r="C49">
+        <f>Normalized_FCF!C91</f>
+        <v>1.3599999999999999</v>
+      </c>
+      <c r="D49" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E49" s="138" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B51" s="151" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B52" s="138" t="s">
+        <v>261</v>
+      </c>
+      <c r="C52" s="160">
+        <f>PV(C48, F48, -C49, 0)</f>
+        <v>2.8648148148148143</v>
+      </c>
+      <c r="D52" s="160"/>
+      <c r="E52" s="138"/>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B53" s="138" t="s">
+        <v>263</v>
+      </c>
+      <c r="C53" s="160">
+        <f>C44/(1+C48)^F48</f>
+        <v>10.330794332270942</v>
+      </c>
+      <c r="D53" s="160"/>
+    </row>
+    <row r="54" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B54" s="153" t="s">
+        <v>237</v>
+      </c>
+      <c r="C54" s="154">
+        <f>C52+C53</f>
+        <v>13.195609147085756</v>
+      </c>
+      <c r="D54" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E54" s="219" t="s">
+        <v>275</v>
+      </c>
+      <c r="F54" s="225">
+        <f>(C54/C44-1)</f>
+        <v>-0.2608169671725179</v>
+      </c>
+      <c r="I54" s="164" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D57" s="191"/>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B58" s="124" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="125" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="125" t="s">
+        <v>57</v>
+      </c>
+      <c r="E58" s="119" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B59" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59" s="14">
+        <f>Normalized_FCF!L8</f>
+        <v>1617067</v>
+      </c>
+      <c r="D59" s="14">
+        <f>Normalized_FCF!G8</f>
+        <v>1876773</v>
+      </c>
+      <c r="E59" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B60" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C60" s="8">
+        <f>(D59/C59)^(1/E59)-1</f>
+        <v>2.5133963029188244E-2</v>
+      </c>
+      <c r="D60" s="43"/>
+      <c r="E60" s="43"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="E27:E30"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="E39:E42"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E17:E18"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>